--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1508</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>104</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>645</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -62796,10 +62796,10 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>5000</v>
+        <v>33</v>
       </c>
       <c r="C2715" t="n">
         <v>2.70000004768372</v>
@@ -62819,10 +62819,10 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C2716" t="n">
         <v>2.70000004768372</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.64000010490417</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.64000010490417</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.64000010490417</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.64000010490417</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>291</v>
+        <v>10</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.66000008583069</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="D2718" t="n">
         <v>2.64000010490417</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.66000008583069</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.66000008583069</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,10 +62888,10 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1508</v>
+        <v>291</v>
       </c>
       <c r="C2719" t="n">
         <v>2.66000008583069</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>104</v>
+        <v>1508</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.77999997138977</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.77999997138977</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.77999997138977</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.77999997138977</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>645</v>
+        <v>104</v>
       </c>
       <c r="C2721" t="n">
         <v>2.77999997138977</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.66000008583069</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="E2721" t="n">
         <v>2.77999997138977</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.66000008583069</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,10 +62957,10 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>11</v>
+        <v>645</v>
       </c>
       <c r="C2722" t="n">
         <v>2.77999997138977</v>
@@ -62972,9 +62972,32 @@
         <v>2.77999997138977</v>
       </c>
       <c r="F2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>710</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2723" t="n">
         <v>2.6800000667572</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -447,7 +447,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544632434845</v>
+        <v>1.24544656276703</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327352523804</v>
+        <v>1.21327376365662</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683908462524</v>
+        <v>1.20683920383453</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G13" t="n">
-        <v>1.20040440559387</v>
+        <v>1.20040452480316</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468486309052</v>
+        <v>1.19468474388123</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688564777374</v>
+        <v>1.25688576698303</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475048065186</v>
+        <v>1.26475036144257</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542798519135</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>1.20040440559387</v>
+        <v>1.20040452480316</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G28" t="n">
-        <v>1.21041393280029</v>
+        <v>1.210413813591</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113811969757</v>
+        <v>1.22113823890686</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19397008419037</v>
+        <v>1.19396996498108</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469450950623</v>
+        <v>1.20469427108765</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.26546514034271</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903069972992</v>
+        <v>1.25903058052063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903998851776</v>
+        <v>1.26903986930847</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21684861183167</v>
+        <v>1.21684849262238</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542798519135</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.26546514034271</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.26546514034271</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>1.2676100730896</v>
+        <v>1.26760995388031</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>1.2676100730896</v>
+        <v>1.26760995388031</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545573234558</v>
+        <v>1.25545585155487</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.2626051902771</v>
+        <v>1.26260542869568</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24902129173279</v>
+        <v>1.2490211725235</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472213745117</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472213745117</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225377082825</v>
+        <v>1.25225353240967</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835489273071</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835489273071</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860152721405</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860152721405</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27421009540558</v>
+        <v>1.27420997619629</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445637226105</v>
+        <v>1.28445649147034</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.28079688549042</v>
+        <v>1.28079700469971</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811585903168</v>
+        <v>1.28811597824097</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>1.28738415241241</v>
+        <v>1.28738403320312</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663772106171</v>
+        <v>1.22663760185242</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.17833352088928</v>
+        <v>1.17833340167999</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784773349762</v>
+        <v>1.18784785270691</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955065727234</v>
+        <v>1.16955077648163</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>1.22151458263397</v>
+        <v>1.22151446342468</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G138" t="n">
-        <v>1.22151458263397</v>
+        <v>1.22151446342468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G144" t="n">
-        <v>1.2390798330307</v>
+        <v>1.23907959461212</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834764957428</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G147" t="n">
-        <v>1.23542010784149</v>
+        <v>1.23542034626007</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834764957428</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736230373383</v>
+        <v>1.19736218452454</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.21712303161621</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.21712303161621</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249268531799</v>
+        <v>1.23249292373657</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883343696594</v>
+        <v>1.22883331775665</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324624061584</v>
+        <v>1.32324647903442</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763755321503</v>
+        <v>1.32763767242432</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>1.30348551273346</v>
+        <v>1.30348539352417</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31592762470245</v>
+        <v>1.31592738628387</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982602596283</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884792327881</v>
+        <v>1.28884780406952</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543471336365</v>
+        <v>1.29543495178223</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.29323899745941</v>
+        <v>1.2932391166687</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250717163086</v>
+        <v>1.29250729084015</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27274632453918</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762306690216</v>
+        <v>1.26762330532074</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518107414246</v>
+        <v>1.25518119335175</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.26542747020721</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006517887115</v>
+        <v>1.28006505966187</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005781650543</v>
+        <v>1.25005805492401</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639868736267</v>
+        <v>1.24639856815338</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005781650543</v>
+        <v>1.25005805492401</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26542747020721</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126806735992</v>
+        <v>1.21126794815063</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.21858692169189</v>
+        <v>1.21858704090118</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492743492126</v>
+        <v>1.21492767333984</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004344940186</v>
+        <v>1.19004356861115</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>1.18199276924133</v>
+        <v>1.18199265003204</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.214195728302</v>
+        <v>1.21419560909271</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>1.19297087192535</v>
+        <v>1.19297099113464</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663035869598</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.22005069255829</v>
+        <v>1.220050573349</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957250595093</v>
+        <v>1.25957226753235</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592038154602</v>
+        <v>1.28592014312744</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="n">
-        <v>1.29689848423004</v>
+        <v>1.29689836502075</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>1.29689848423004</v>
+        <v>1.29689836502075</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.29323899745941</v>
+        <v>1.2932391166687</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G253" t="n">
-        <v>1.28738415241241</v>
+        <v>1.28738403320312</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.3100723028183</v>
+        <v>1.31007242202759</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544195652008</v>
+        <v>1.32544207572937</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081137180328</v>
+        <v>1.34081161022186</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.33349275588989</v>
+        <v>1.3334926366806</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>1.33202886581421</v>
+        <v>1.33202910423279</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3386162519455</v>
+        <v>1.33861577510834</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32105076313019</v>
+        <v>1.3210506439209</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130452156067</v>
+        <v>1.36130428314209</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057233810425</v>
+        <v>1.36057245731354</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="n">
-        <v>1.33276069164276</v>
+        <v>1.33276081085205</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959411621094</v>
+        <v>1.34959435462952</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>1.34520280361176</v>
+        <v>1.34520292282104</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.36789131164551</v>
+        <v>1.3678914308548</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667393684387</v>
+        <v>1.37667381763458</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789855480194</v>
+        <v>1.39789843559265</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253626346588</v>
+        <v>1.41253614425659</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668106079102</v>
+        <v>1.40668118000031</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.40814471244812</v>
+        <v>1.4081449508667</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302169322968</v>
+        <v>1.40302181243896</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.36935496330261</v>
+        <v>1.3693550825119</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.3788697719574</v>
+        <v>1.37886953353882</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911592960358</v>
+        <v>1.38911581039429</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155804157257</v>
+        <v>1.40155780315399</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157965183258</v>
+        <v>1.49157953262329</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50328981876373</v>
+        <v>1.50329005718231</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864474773407</v>
+        <v>1.45864498615265</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="n">
-        <v>1.49084794521332</v>
+        <v>1.49084770679474</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792052268982</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963757514954</v>
+        <v>1.52963745594025</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="n">
-        <v>1.53183364868164</v>
+        <v>1.53183341026306</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817392349243</v>
+        <v>1.52817380428314</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.48572444915771</v>
+        <v>1.485724568367</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792052268982</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108697891235</v>
+        <v>1.47108674049377</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376812458038</v>
+        <v>1.46376824378967</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498549938202</v>
+        <v>1.45498526096344</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499286174774</v>
+        <v>1.48499274253845</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085506916046</v>
+        <v>1.52085494995117</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768837451935</v>
+        <v>1.53768825531006</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126373291016</v>
+        <v>1.63126361370087</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427472114563</v>
+        <v>1.63427460193634</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857769012451</v>
+        <v>1.64857757091522</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288018226624</v>
+        <v>1.6628805398941</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.66137456893921</v>
+        <v>1.6613746881485</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902139186859</v>
+        <v>1.76902151107788</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816578865051</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429919719696</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485397338867</v>
+        <v>1.99485421180725</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345139503479</v>
+        <v>1.95345163345337</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>1.98205721378326</v>
+        <v>1.9820568561554</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.9301153421402</v>
+        <v>1.93011522293091</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429919719696</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376026153564</v>
+        <v>1.83376038074493</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.90301561355591</v>
+        <v>1.9030157327652</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452122688293</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.91204869747162</v>
+        <v>1.91204881668091</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.92258787155151</v>
+        <v>1.9225879907608</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>1.91581284999847</v>
+        <v>1.9158126115799</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92860984802246</v>
+        <v>1.92861008644104</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.92183482646942</v>
+        <v>1.92183494567871</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559862136841</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>1.94065451622009</v>
+        <v>1.94065427780151</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376853942871</v>
+        <v>1.90376842021942</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957652568817</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559862136841</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237352371216</v>
+        <v>1.93237376213074</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.92258787155151</v>
+        <v>1.9225879907608</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054320335388</v>
+        <v>1.91054308414459</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753209590912</v>
+        <v>1.9075323343277</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473521709442</v>
+        <v>1.89473509788513</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.7705272436142</v>
+        <v>1.77052700519562</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826870441437</v>
+        <v>1.76826882362366</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.79461586475372</v>
+        <v>1.79461598396301</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741310119629</v>
+        <v>1.80741286277771</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074903488159</v>
+        <v>1.83074915409088</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816578865051</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.82623243331909</v>
+        <v>1.82623279094696</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.8360184431076</v>
+        <v>1.83601868152618</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>1.83902978897095</v>
+        <v>1.83902966976166</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429919719696</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429919719696</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.84655725955963</v>
+        <v>1.8465576171875</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752417564392</v>
+        <v>1.83752405643463</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280162334442</v>
+        <v>1.91280174255371</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086802959442</v>
+        <v>1.93086814880371</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613767623901</v>
+        <v>1.93613755702972</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237352371216</v>
+        <v>1.93237376213074</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957652568817</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796007633209</v>
+        <v>1.88795983791351</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720703125</v>
+        <v>1.88720726966858</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452122688293</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="n">
-        <v>1.86914074420929</v>
+        <v>1.869140625</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860180854797</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>1.85709619522095</v>
+        <v>1.85709631443024</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182690620422</v>
+        <v>1.85182678699493</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494896888733</v>
+        <v>1.88494908809662</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860180854797</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193774223328</v>
+        <v>1.88193798065186</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365734577179</v>
+        <v>1.87365710735321</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8653769493103</v>
+        <v>1.86537683010101</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204065799713</v>
+        <v>1.84204077720642</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279346466064</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397425174713</v>
+        <v>1.82397413253784</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849097251892</v>
+        <v>1.82849085330963</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569361686707</v>
+        <v>1.81569385528564</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021009922028</v>
+        <v>1.82021045684814</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644654273987</v>
+        <v>1.81644630432129</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.81418812274933</v>
+        <v>1.81418800354004</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.8322548866272</v>
+        <v>1.83225464820862</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246851921082</v>
+        <v>1.82246875762939</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.8503212928772</v>
+        <v>1.85032153129578</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849877357483</v>
+        <v>1.89849889278412</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689036369324</v>
+        <v>1.93689024448395</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.9173184633255</v>
+        <v>1.91731834411621</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979879379272</v>
+        <v>1.97979867458344</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248483657837</v>
+        <v>1.96248459815979</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>2.04378414154053</v>
+        <v>2.04378437995911</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937057495117</v>
+        <v>1.99937081336975</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582053184509</v>
+        <v>1.98582065105438</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624863147736</v>
+        <v>1.96624851226807</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549570560455</v>
+        <v>1.96549594402313</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98280966281891</v>
+        <v>1.9828097820282</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540106773376</v>
+        <v>2.07540130615234</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765936851501</v>
+        <v>2.07765960693359</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="n">
-        <v>2.07013154029846</v>
+        <v>2.07013177871704</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034588813782</v>
+        <v>2.06034564971924</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>2.05884027481079</v>
+        <v>2.05883979797363</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540106773376</v>
+        <v>2.07540130615234</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615375518799</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="n">
-        <v>2.08368134498596</v>
+        <v>2.08368158340454</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.16799211502075</v>
+        <v>2.16799235343933</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="n">
-        <v>2.22068667411804</v>
+        <v>2.22068691253662</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="n">
-        <v>2.33360314369202</v>
+        <v>2.33360290527344</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="n">
-        <v>2.37124156951904</v>
+        <v>2.37124180793762</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>2.28843641281128</v>
+        <v>2.2884361743927</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>2.2658531665802</v>
+        <v>2.26585340499878</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>2.28090834617615</v>
+        <v>2.28090858459473</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.28843641281128</v>
+        <v>2.2884361743927</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810342788696</v>
+        <v>2.19810366630554</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="n">
-        <v>2.37124156951904</v>
+        <v>2.37124180793762</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190777778625</v>
+        <v>2.55190753936768</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>2.46157479286194</v>
+        <v>2.46157455444336</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.46157479286194</v>
+        <v>2.46157455444336</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888071060181</v>
+        <v>2.40888047218323</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G573" t="n">
-        <v>2.41640830039978</v>
+        <v>2.4164080619812</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363509178162</v>
+        <v>2.58363485336304</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56035923957825</v>
+        <v>2.56035900115967</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604820251465</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363509178162</v>
+        <v>2.58363485336304</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>32.5</v>
       </c>
       <c r="G599" t="n">
-        <v>2.52156591415405</v>
+        <v>2.52156567573547</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484152793884</v>
+        <v>2.54484176635742</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604820251465</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208205223083</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.2189781665802</v>
+        <v>2.21897792816162</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.2189781665802</v>
+        <v>2.21897792816162</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>2.08708047866821</v>
+        <v>2.08708071708679</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>2.08708047866821</v>
+        <v>2.08708071708679</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.1646671295166</v>
+        <v>2.16466736793518</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.96294176578522</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966603279114</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>1.88535535335541</v>
+        <v>1.8853554725647</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432064533234</v>
+        <v>1.85432052612305</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225122928619</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104479312897</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207926273346</v>
+        <v>1.86207938194275</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.00173497200012</v>
+        <v>2.0017352104187</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845911979675</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>2.00173497200012</v>
+        <v>2.0017352104187</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>2.00173497200012</v>
+        <v>2.0017352104187</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.96294176578522</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845911979675</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104479312897</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207926273346</v>
+        <v>1.86207938194275</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225122928619</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776858329773</v>
+        <v>1.80776882171631</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.75345826148987</v>
+        <v>1.75345814228058</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569940567017</v>
+        <v>1.74569928646088</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311397075653</v>
+        <v>1.89311408996582</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.88535535335541</v>
+        <v>1.8853554725647</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966603279114</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>2.08708047866821</v>
+        <v>2.08708071708679</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.1646671295166</v>
+        <v>2.16466736793518</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>2.08708047866821</v>
+        <v>2.08708071708679</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>2.1569082736969</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26552987098694</v>
+        <v>2.26553010940552</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>2.24225401878357</v>
+        <v>2.24225378036499</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>2.24225401878357</v>
+        <v>2.24225378036499</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087537765503</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.3353579044342</v>
+        <v>2.33535766601562</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208205223083</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41294479370117</v>
+        <v>2.41294455528259</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="n">
-        <v>2.3663923740387</v>
+        <v>2.36639261245728</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311676025391</v>
+        <v>2.34311628341675</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087537765503</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.3741512298584</v>
+        <v>2.37415146827698</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.55260062217712</v>
+        <v>2.5526008605957</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.51195383071899</v>
+        <v>2.51195406913757</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.51195383071899</v>
+        <v>2.51195406913757</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.51195383071899</v>
+        <v>2.51195406913757</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.18678188323975</v>
+        <v>2.18678212165833</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.048583984375</v>
+        <v>2.04858374595642</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412701129913</v>
+        <v>1.89412713050842</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51205015182495</v>
+        <v>1.51204991340637</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366617679596</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.55676114559174</v>
+        <v>1.55676102638245</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.56082606315613</v>
+        <v>1.56082582473755</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.58927810192108</v>
+        <v>1.58927834033966</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.87786865234375</v>
+        <v>1.87786841392517</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.81283390522003</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.81283390522003</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.6827654838562</v>
+        <v>1.68276536464691</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.6827654838562</v>
+        <v>1.68276536464691</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366617679596</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.60960137844086</v>
+        <v>1.60960161685944</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366617679596</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262780666351</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.40636909008026</v>
+        <v>1.40636897087097</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482148647308</v>
+        <v>1.43482160568237</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262780666351</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.41449844837189</v>
+        <v>1.4144983291626</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.3332052230835</v>
+        <v>1.33320546150208</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.35759329795837</v>
+        <v>1.35759341716766</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.3332052230835</v>
+        <v>1.33320546150208</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255878925323</v>
+        <v>1.29255890846252</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946405887604</v>
+        <v>1.34946393966675</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.35352861881256</v>
+        <v>1.35352849960327</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.41449844837189</v>
+        <v>1.4144983291626</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262780666351</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.56082606315613</v>
+        <v>1.56082582473755</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51205015182495</v>
+        <v>1.51204991340637</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973929405212</v>
+        <v>1.86973917484283</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994539260864</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994539260864</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.17865252494812</v>
+        <v>2.1786527633667</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>2.70000004768372</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -473,7 +473,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2218531370163</v>
+        <v>1.22185289859772</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327376365662</v>
+        <v>1.21327352523804</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683920383453</v>
+        <v>1.20683908462524</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.16680181026459</v>
+        <v>1.1668016910553</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468474388123</v>
+        <v>1.19468486309052</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687647819519</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687647819519</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2354371547699</v>
+        <v>1.23543727397919</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542798519135</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685778141022</v>
+        <v>1.2268580198288</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25831568241119</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903058052063</v>
+        <v>1.25903069972992</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903986930847</v>
+        <v>1.26903998851776</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542798519135</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404451370239</v>
+        <v>1.27404463291168</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>1.27189981937408</v>
+        <v>1.27189993858337</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25831568241119</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25831568241119</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25831568241119</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>1.26760995388031</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26760995388031</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545585155487</v>
+        <v>1.25545561313629</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.25831568241119</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830627441406</v>
+        <v>1.24830615520477</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.2490211725235</v>
+        <v>1.24902129173279</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685778141022</v>
+        <v>1.2268580198288</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472237586975</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472237586975</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400723934174</v>
+        <v>1.23400735855103</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.2354371547699</v>
+        <v>1.23543727397919</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225353240967</v>
+        <v>1.25225365161896</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835513114929</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835513114929</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323175430298</v>
+        <v>1.26323199272156</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323175430298</v>
+        <v>1.26323199272156</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.28079700469971</v>
+        <v>1.280797123909</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347826957703</v>
+        <v>1.27347815036774</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811597824097</v>
+        <v>1.28811573982239</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299272060394</v>
+        <v>1.28299283981323</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G112" t="n">
-        <v>1.26396381855011</v>
+        <v>1.2639639377594</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127542972565</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663760185242</v>
+        <v>1.22663772106171</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18565213680267</v>
+        <v>1.18565225601196</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955077648163</v>
+        <v>1.16955065727234</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834764957428</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G147" t="n">
-        <v>1.23542034626007</v>
+        <v>1.23542022705078</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834764957428</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.2061448097229</v>
+        <v>1.20614492893219</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736218452454</v>
+        <v>1.19736242294312</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.21712327003479</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.21712327003479</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249292373657</v>
+        <v>1.23249268531799</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518807888031</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884056091309</v>
+        <v>1.25884068012238</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884056091309</v>
+        <v>1.25884068012238</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518807888031</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30714499950409</v>
+        <v>1.3071448802948</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G169" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31592738628387</v>
+        <v>1.31592750549316</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>1.31812310218811</v>
+        <v>1.3181232213974</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982614517212</v>
+        <v>1.29982602596283</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884780406952</v>
+        <v>1.28884768486023</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836213588715</v>
+        <v>1.29836237430573</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250729084015</v>
+        <v>1.29250717163086</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G190" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G191" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G192" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568099021912</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884056091309</v>
+        <v>1.25884068012238</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786221981049</v>
+        <v>1.24786198139191</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006505966187</v>
+        <v>1.28006517887115</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810873508453</v>
+        <v>1.25810861587524</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054336547852</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639856815338</v>
+        <v>1.24639868736267</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054336547852</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2420072555542</v>
+        <v>1.24200713634491</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054336547852</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127542972565</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127542972565</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.20980441570282</v>
+        <v>1.20980429649353</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004356861115</v>
+        <v>1.19004344940186</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663035869598</v>
+        <v>1.19663047790527</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639132499695</v>
+        <v>1.21639144420624</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957226753235</v>
+        <v>1.25957238674164</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592014312744</v>
+        <v>1.28592026233673</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568099021912</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G256" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544207572937</v>
+        <v>1.32544183731079</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3334926366806</v>
+        <v>1.33349275588989</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422446250916</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861577510834</v>
+        <v>1.33861613273621</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422446250916</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G266" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227526187897</v>
+        <v>1.34227550029755</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>1.32690572738647</v>
+        <v>1.32690584659576</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130428314209</v>
+        <v>1.36130440235138</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057245731354</v>
+        <v>1.36057233810425</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="n">
-        <v>1.32690572738647</v>
+        <v>1.32690584659576</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>1.33788406848907</v>
+        <v>1.33788394927979</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34373915195465</v>
+        <v>1.34373903274536</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>1.34520292282104</v>
+        <v>1.34520280361176</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.32910132408142</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349999904633</v>
+        <v>1.36349987983704</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.3678914308548</v>
+        <v>1.36789131164551</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667381763458</v>
+        <v>1.37667393684387</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252890110016</v>
+        <v>1.38252878189087</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253614425659</v>
+        <v>1.4125360250473</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668118000031</v>
+        <v>1.40668106079102</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.3693550825119</v>
+        <v>1.36935496330261</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50329005718231</v>
+        <v>1.50328981876373</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.47913765907288</v>
+        <v>1.4791374206543</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="n">
-        <v>1.49084770679474</v>
+        <v>1.49084782600403</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792028427124</v>
+        <v>1.48792004585266</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963745594025</v>
+        <v>1.52963757514954</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51499998569489</v>
+        <v>1.51500022411346</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.498166680336</v>
+        <v>1.49816656112671</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792028427124</v>
+        <v>1.48792004585266</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108674049377</v>
+        <v>1.47108697891235</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="n">
-        <v>1.4842609167099</v>
+        <v>1.48426079750061</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376824378967</v>
+        <v>1.46376812458038</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498526096344</v>
+        <v>1.45498549938202</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499274253845</v>
+        <v>1.48499286174774</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427460193634</v>
+        <v>1.63427484035492</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.6628805398941</v>
+        <v>1.66288018226624</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6613746881485</v>
+        <v>1.66137444972992</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="n">
-        <v>1.9165655374527</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011522293091</v>
+        <v>1.93011546134949</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376038074493</v>
+        <v>1.83376049995422</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.9030157327652</v>
+        <v>1.90301549434662</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538475036621</v>
+        <v>1.93538498878479</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.9225879907608</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>1.9158126115799</v>
+        <v>1.91581284999847</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92861008644104</v>
+        <v>1.92860996723175</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.92635130882263</v>
+        <v>1.92635154724121</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>1.9165655374527</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882395744324</v>
+        <v>1.91882383823395</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.9225879907608</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699339866638</v>
+        <v>1.89699363708496</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826882362366</v>
+        <v>1.76826858520508</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741286277771</v>
+        <v>1.807412981987</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074915409088</v>
+        <v>1.83074903488159</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.83601868152618</v>
+        <v>1.83601856231689</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>1.82171595096588</v>
+        <v>1.82171583175659</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.8465576171875</v>
+        <v>1.84655737876892</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752405643463</v>
+        <v>1.83752417564392</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774596691132</v>
+        <v>1.8977462053299</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280174255371</v>
+        <v>1.91280150413513</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613755702972</v>
+        <v>1.93613767623901</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88795983791351</v>
+        <v>1.88796007633209</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494908809662</v>
+        <v>1.88494896888733</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.87064611911774</v>
+        <v>1.87064635753632</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365710735321</v>
+        <v>1.87365734577179</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.86537683010101</v>
+        <v>1.8653769493103</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795191764832</v>
+        <v>1.8179520368576</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021045684814</v>
+        <v>1.82021009922028</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117677688599</v>
+        <v>1.81117689609528</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644630432129</v>
+        <v>1.81644642353058</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246875762939</v>
+        <v>1.82246851921082</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.85032153129578</v>
+        <v>1.8503212928772</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689024448395</v>
+        <v>1.93689036369324</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979867458344</v>
+        <v>1.97979855537415</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474301815033</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248459815979</v>
+        <v>1.96248483657837</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732626438141</v>
+        <v>1.98732650279999</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937081336975</v>
+        <v>1.99937057495117</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582065105438</v>
+        <v>1.98582077026367</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861812591553</v>
+        <v>1.99861788749695</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549594402313</v>
+        <v>1.96549570560455</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474301815033</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="n">
-        <v>1.97603487968445</v>
+        <v>1.97603499889374</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.9828097820282</v>
+        <v>1.98280966281891</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540130615234</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.08142352104187</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="n">
-        <v>2.08593988418579</v>
+        <v>2.08593964576721</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>2.08142352104187</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765960693359</v>
+        <v>2.07765936851501</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.11153411865234</v>
+        <v>2.11153435707092</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959296226501</v>
+        <v>2.05959272384644</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540130615234</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185930252075</v>
+        <v>2.13185906410217</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17552018165588</v>
+        <v>2.17552042007446</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.17552018165588</v>
+        <v>2.17552042007446</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="n">
-        <v>2.22068691253662</v>
+        <v>2.22068667411804</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="n">
-        <v>2.33360290527344</v>
+        <v>2.33360314369202</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>2.2884361743927</v>
+        <v>2.28843665122986</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>2.26585340499878</v>
+        <v>2.2658531665802</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.2884361743927</v>
+        <v>2.28843665122986</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810366630554</v>
+        <v>2.19810342788696</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190753936768</v>
+        <v>2.55190777778625</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>2.46157455444336</v>
+        <v>2.46157479286194</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.46157455444336</v>
+        <v>2.46157479286194</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="n">
-        <v>2.48415780067444</v>
+        <v>2.48415803909302</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651889801025</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="n">
-        <v>2.48415780067444</v>
+        <v>2.48415803909302</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.5067412853241</v>
+        <v>2.50674152374268</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363485336304</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56035900115967</v>
+        <v>2.56035923957825</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604820251465</v>
+        <v>2.50604867935181</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363485336304</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484176635742</v>
+        <v>2.54484152793884</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604820251465</v>
+        <v>2.50604867935181</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846202850342</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208205223083</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>2.00949382781982</v>
+        <v>2.0094940662384</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.96294188499451</v>
+        <v>1.9629420042038</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966591358185</v>
+        <v>1.93966579437256</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432052612305</v>
+        <v>1.85432076454163</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983799934387</v>
+        <v>1.86983823776245</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>1.83880352973938</v>
+        <v>1.8388032913208</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.00949382781982</v>
+        <v>2.0094940662384</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>2.00949382781982</v>
+        <v>2.0094940662384</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845947742462</v>
+        <v>1.97845923900604</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>2.00949382781982</v>
+        <v>2.0094940662384</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397647380829</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.96294188499451</v>
+        <v>1.9629420042038</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845947742462</v>
+        <v>1.97845923900604</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397647380829</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>1.83880352973938</v>
+        <v>1.8388032913208</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776882171631</v>
+        <v>1.80776870250702</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.75345814228058</v>
+        <v>1.753457903862</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673399448395</v>
+        <v>1.77673423290253</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569928646088</v>
+        <v>1.74569952487946</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966591358185</v>
+        <v>1.93966579437256</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91639029979706</v>
+        <v>1.91639006137848</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397647380829</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26553010940552</v>
+        <v>2.26552987098694</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087513923645</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.33535766601562</v>
+        <v>2.3353579044342</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208205223083</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846202850342</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311628341675</v>
+        <v>2.34311652183533</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087513923645</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.37415146827698</v>
+        <v>2.3741512298584</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5526008605957</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.28433346748352</v>
+        <v>2.2843337059021</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="n">
-        <v>2.60137629508972</v>
+        <v>2.6013765335083</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="n">
-        <v>2.60137629508972</v>
+        <v>2.6013765335083</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>2.54447102546692</v>
+        <v>2.5444712638855</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.28433346748352</v>
+        <v>2.2843337059021</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.12987685203552</v>
+        <v>2.1298770904541</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548877716064</v>
+        <v>2.10548901557922</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412713050842</v>
+        <v>1.89412701129913</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.65837728977203</v>
+        <v>1.65837752819061</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205003261566</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.54863166809082</v>
+        <v>1.5486319065094</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.49579131603241</v>
+        <v>1.4957914352417</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.60147249698639</v>
+        <v>1.60147225856781</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.60147249698639</v>
+        <v>1.60147225856781</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.65837728977203</v>
+        <v>1.65837752819061</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60147249698639</v>
+        <v>1.60147225856781</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.75592911243439</v>
+        <v>1.75592887401581</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096362113953</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.82909274101257</v>
+        <v>1.82909286022186</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096362113953</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.72341191768646</v>
+        <v>1.72341179847717</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.75592911243439</v>
+        <v>1.75592887401581</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.72341191768646</v>
+        <v>1.72341179847717</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.75592911243439</v>
+        <v>1.75592887401581</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.72341191768646</v>
+        <v>1.72341179847717</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.60147249698639</v>
+        <v>1.60147225856781</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.64211893081665</v>
+        <v>1.64211869239807</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.49579131603241</v>
+        <v>1.4957914352417</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482160568237</v>
+        <v>1.43482172489166</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.33320546150208</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.33320546150208</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255890846252</v>
+        <v>1.29255878925323</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.33727014064789</v>
+        <v>1.3372700214386</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946393966675</v>
+        <v>1.34946405887604</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.37385189533234</v>
+        <v>1.37385177612305</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.35352849960327</v>
+        <v>1.35352873802185</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823997020721</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.38604581356049</v>
+        <v>1.3860456943512</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823997020721</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205003261566</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.50798523426056</v>
+        <v>1.50798535346985</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.47953283786774</v>
+        <v>1.47953271865845</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973917484283</v>
+        <v>1.86973929405212</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.0729718208313</v>
+        <v>2.07297158241272</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.2599458694458</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.2599458694458</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.1786527633667</v>
+        <v>2.17865252494812</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.12987685203552</v>
+        <v>2.1298770904541</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.0729718208313</v>
+        <v>2.07297158241272</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671286582947</v>
+        <v>2.05671310424805</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.17804360389709</v>
+        <v>2.17804384231567</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>30</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>30</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>30</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835478782654</v>
+        <v>2.12835454940796</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835478782654</v>
+        <v>2.12835454940796</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.1035099029541</v>
+        <v>2.10351014137268</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.14491748809814</v>
+        <v>2.14491772651672</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102353096008</v>
+        <v>2.50102376937866</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>30</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930523872375</v>
+        <v>2.50930500030518</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.71634364128113</v>
+        <v>2.71634340286255</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978046417236</v>
+        <v>2.69978022575378</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>34</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.81572222709656</v>
+        <v>2.81572198867798</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>37</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>37</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994498252869</v>
+        <v>2.93994474411011</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>36.5</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>37</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>36.5</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>37</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526509284973</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>37</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>37</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.00619721412659</v>
+        <v>3.00619745254517</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>36.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>36.5</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>37</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>37</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>37</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>36.5</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>36.5</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.00619721412659</v>
+        <v>3.00619745254517</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.00619721412659</v>
+        <v>3.00619745254517</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>37</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>37</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>37</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>36.5</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>36.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>37</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>36.5</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>36.5</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.02276039123535</v>
+        <v>3.02276015281677</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>37</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>37</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>37</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>37</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>37</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>37</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073139190674</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557556152344</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.16354656219482</v>
+        <v>3.1635468006134</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526509284973</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>39.5</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>39.5</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585006713867</v>
+        <v>5.01585054397583</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.58285999298096</v>
+        <v>5.5828595161438</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669895172119</v>
+        <v>5.14669847488403</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212244033813</v>
+        <v>5.21212291717529</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669895172119</v>
+        <v>5.14669847488403</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924322128296</v>
+        <v>5.53924369812012</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495845794678</v>
+        <v>6.93495798110962</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.782301902771</v>
+        <v>6.78230237960815</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868608474731</v>
+        <v>6.73868560791016</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433271408081</v>
+        <v>6.32433319091797</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964582443237</v>
+        <v>6.62964534759521</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049375534058</v>
+        <v>6.76049423217773</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.782301902771</v>
+        <v>6.78230237960815</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.0221905708313</v>
+        <v>7.02219104766846</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.06580686569214</v>
+        <v>7.0658073425293</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399824142456</v>
+        <v>7.04399871826172</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.06580686569214</v>
+        <v>7.0658073425293</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835161209106</v>
+        <v>7.45835208892822</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377557754517</v>
+        <v>7.52377510070801</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377557754517</v>
+        <v>7.52377510070801</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259269714355</v>
+        <v>8.11259365081787</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>2.6800000667572</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>1120</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -447,7 +447,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544656276703</v>
+        <v>1.24544668197632</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22185289859772</v>
+        <v>1.22185301780701</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327352523804</v>
+        <v>1.21327364444733</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683908462524</v>
+        <v>1.20683884620667</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G13" t="n">
-        <v>1.20040452480316</v>
+        <v>1.20040464401245</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468486309052</v>
+        <v>1.19468474388123</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>1.20040452480316</v>
+        <v>1.20040464401245</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396996498108</v>
+        <v>1.19397008419037</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.2268580198288</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469427108765</v>
+        <v>1.20469415187836</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903069972992</v>
+        <v>1.25903058052063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828757762909</v>
+        <v>1.22828769683838</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689493656158</v>
+        <v>1.26689505577087</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545561313629</v>
+        <v>1.25545573234558</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.26260542869568</v>
+        <v>1.26260530948639</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830615520477</v>
+        <v>1.24830627441406</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686695098877</v>
+        <v>1.23686707019806</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.2268580198288</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400735855103</v>
+        <v>1.23400723934174</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27420997619629</v>
+        <v>1.27421021461487</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323199272156</v>
+        <v>1.26323187351227</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323199272156</v>
+        <v>1.26323187351227</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G87" t="n">
-        <v>1.26689124107361</v>
+        <v>1.26689112186432</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445649147034</v>
+        <v>1.28445637226105</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.27933311462402</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.27933311462402</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.27933311462402</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811573982239</v>
+        <v>1.28811597824097</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.27933311462402</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27933311462402</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299283981323</v>
+        <v>1.28299272060394</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G112" t="n">
-        <v>1.2639639377594</v>
+        <v>1.26396369934082</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663772106171</v>
+        <v>1.226637840271</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.17833340167999</v>
+        <v>1.1783332824707</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784785270691</v>
+        <v>1.18784773349762</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G142" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G143" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G144" t="n">
-        <v>1.23907959461212</v>
+        <v>1.23907971382141</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.2310289144516</v>
+        <v>1.23102903366089</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.2310289144516</v>
+        <v>1.23102903366089</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736242294312</v>
+        <v>1.19736230373383</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249268531799</v>
+        <v>1.23249280452728</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518807888031</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518807888031</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.3071448802948</v>
+        <v>1.30714499950409</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324647903442</v>
+        <v>1.32324635982513</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>1.30348539352417</v>
+        <v>1.30348551273346</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982602596283</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884768486023</v>
+        <v>1.28884780406952</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543495178223</v>
+        <v>1.29543471336365</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836237430573</v>
+        <v>1.29836225509644</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.29323923587799</v>
+        <v>1.29323899745941</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.30568099021912</v>
+        <v>1.30568110942841</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762330532074</v>
+        <v>1.26762318611145</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786198139191</v>
+        <v>1.24786233901978</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518119335175</v>
+        <v>1.25518107414246</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810861587524</v>
+        <v>1.25810873508453</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>1.24054336547852</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639868736267</v>
+        <v>1.24639856815338</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>1.24054336547852</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420297145844</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420297145844</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.24200713634491</v>
+        <v>1.2420072555542</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>1.24054336547852</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126794815063</v>
+        <v>1.21126806735992</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.21858704090118</v>
+        <v>1.2185868024826</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492767333984</v>
+        <v>1.21492755413055</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004344940186</v>
+        <v>1.19004356861115</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.220050573349</v>
+        <v>1.22005069255829</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639144420624</v>
+        <v>1.21639120578766</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957238674164</v>
+        <v>1.25957262516022</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786946296692</v>
+        <v>1.27786934375763</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592026233673</v>
+        <v>1.28592038154602</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="n">
-        <v>1.29689836502075</v>
+        <v>1.29689848423004</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>1.29689836502075</v>
+        <v>1.29689848423004</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.29323923587799</v>
+        <v>1.29323899745941</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.30568099021912</v>
+        <v>1.30568110942841</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007242202759</v>
+        <v>1.31007254123688</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544183731079</v>
+        <v>1.32544207572937</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081161022186</v>
+        <v>1.34081149101257</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422446250916</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861613273621</v>
+        <v>1.33861601352692</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422446250916</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227550029755</v>
+        <v>1.34227538108826</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>1.32690584659576</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="n">
-        <v>1.3459347486496</v>
+        <v>1.34593462944031</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130440235138</v>
+        <v>1.3613041639328</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057233810425</v>
+        <v>1.36057245731354</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="n">
-        <v>1.32690584659576</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959435462952</v>
+        <v>1.34959423542023</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>1.33788394927979</v>
+        <v>1.33788418769836</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34373903274536</v>
+        <v>1.34373915195465</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910132408142</v>
+        <v>1.32910144329071</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667393684387</v>
+        <v>1.37667381763458</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252878189087</v>
+        <v>1.38252890110016</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668106079102</v>
+        <v>1.40668118000031</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.4081449508667</v>
+        <v>1.40814483165741</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887689590454</v>
+        <v>1.40887677669525</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.36935496330261</v>
+        <v>1.3693550825119</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911581039429</v>
+        <v>1.38911592960358</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155780315399</v>
+        <v>1.40155792236328</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304330348969</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304330348969</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621011734009</v>
+        <v>1.47621023654938</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206496238708</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157953262329</v>
+        <v>1.49157965183258</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864498615265</v>
+        <v>1.45864486694336</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.4791374206543</v>
+        <v>1.47913777828217</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="n">
-        <v>1.49084782600403</v>
+        <v>1.49084794521332</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792004585266</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206496238708</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987672805786</v>
+        <v>1.50987684726715</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963757514954</v>
+        <v>1.52963769435883</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51500022411346</v>
+        <v>1.51499998569489</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="n">
-        <v>1.49963045120239</v>
+        <v>1.49963057041168</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.485724568367</v>
+        <v>1.48572444915771</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206496238708</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792004585266</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206496238708</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376812458038</v>
+        <v>1.46376800537109</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498549938202</v>
+        <v>1.45498526096344</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499286174774</v>
+        <v>1.48499274253845</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085494995117</v>
+        <v>1.52085506916046</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768825531006</v>
+        <v>1.53768837451935</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="n">
-        <v>1.58233344554901</v>
+        <v>1.58233332633972</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427484035492</v>
+        <v>1.63427460193634</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857757091522</v>
+        <v>1.64857733249664</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6666442155838</v>
+        <v>1.66664397716522</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288018226624</v>
+        <v>1.66288030147552</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.66137444972992</v>
+        <v>1.6613746881485</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902151107788</v>
+        <v>1.76902174949646</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816614627838</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485421180725</v>
+        <v>1.99485397338867</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345163345337</v>
+        <v>1.95345139503479</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376049995422</v>
+        <v>1.83376038074493</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.90301549434662</v>
+        <v>1.9030157327652</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452122688293</v>
+        <v>1.90452098846436</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538498878479</v>
+        <v>1.93538475036621</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>1.91581284999847</v>
+        <v>1.9158126115799</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118505477905</v>
+        <v>1.88118481636047</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.92559862136841</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.92635154724121</v>
+        <v>1.9263516664505</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376842021942</v>
+        <v>1.90376830101013</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.92559862136841</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882383823395</v>
+        <v>1.91882395744324</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>1.94366538524628</v>
+        <v>1.94366526603699</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699363708496</v>
+        <v>1.89699327945709</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052700519562</v>
+        <v>1.77052688598633</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826858520508</v>
+        <v>1.76826882362366</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074903488159</v>
+        <v>1.83074915409088</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>1.81042420864105</v>
+        <v>1.81042397022247</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816614627838</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.82623279094696</v>
+        <v>1.82623255252838</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>1.81042420864105</v>
+        <v>1.81042397022247</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257983207703</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257983207703</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806275367737</v>
+        <v>1.84806287288666</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.84655737876892</v>
+        <v>1.8465576171875</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752417564392</v>
+        <v>1.83752405643463</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.8977462053299</v>
+        <v>1.89774596691132</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280150413513</v>
+        <v>1.91280174255371</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086814880371</v>
+        <v>1.93086838722229</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613767623901</v>
+        <v>1.93613755702972</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>1.9210821390152</v>
+        <v>1.92108201980591</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720726966858</v>
+        <v>1.88720750808716</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>1.89548778533936</v>
+        <v>1.89548802375793</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452122688293</v>
+        <v>1.90452098846436</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>1.85709631443024</v>
+        <v>1.85709607601166</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182678699493</v>
+        <v>1.85182690620422</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494896888733</v>
+        <v>1.88494908809662</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161291599274</v>
+        <v>1.86161279678345</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193798065186</v>
+        <v>1.88193774223328</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763501167297</v>
+        <v>1.86763525009155</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8653769493103</v>
+        <v>1.86537683010101</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257983207703</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204077720642</v>
+        <v>1.84204065799713</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731018543243</v>
+        <v>1.84731030464172</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279358386993</v>
+        <v>1.84279334545135</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.8179520368576</v>
+        <v>1.81795167922974</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397401332855</v>
+        <v>1.82397413253784</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849085330963</v>
+        <v>1.82849097251892</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569385528564</v>
+        <v>1.81569373607635</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021009922028</v>
+        <v>1.82021045684814</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117689609528</v>
+        <v>1.81117677688599</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644642353058</v>
+        <v>1.81644630432129</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526575565338</v>
+        <v>1.83526563644409</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526575565338</v>
+        <v>1.83526563644409</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689036369324</v>
+        <v>1.93689024448395</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731834411621</v>
+        <v>1.91731810569763</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474301815033</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>1.94366538524628</v>
+        <v>1.94366526603699</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775412559509</v>
+        <v>1.9677540063858</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732650279999</v>
+        <v>1.98732626438141</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582077026367</v>
+        <v>1.98582065105438</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624851226807</v>
+        <v>1.96624863147736</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549570560455</v>
+        <v>1.96549606323242</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474301815033</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="n">
-        <v>1.97603499889374</v>
+        <v>1.97603487968445</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.0249650478363</v>
+        <v>2.02496528625488</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>2.09045672416687</v>
+        <v>2.09045648574829</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.11153435707092</v>
+        <v>2.11153411865234</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024261474609</v>
+        <v>2.10024285316467</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959272384644</v>
+        <v>2.05959296226501</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185906410217</v>
+        <v>2.13185930252075</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057583808899</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17552042007446</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.17552042007446</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="n">
-        <v>2.33360314369202</v>
+        <v>2.33360266685486</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>2.28843665122986</v>
+        <v>2.28843641281128</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30349183082581</v>
+        <v>2.30349206924438</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.28843665122986</v>
+        <v>2.28843641281128</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057583808899</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810342788696</v>
+        <v>2.19810366630554</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057583808899</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="n">
-        <v>2.18304800987244</v>
+        <v>2.18304777145386</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057583808899</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>2.61965751647949</v>
+        <v>2.61965727806091</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>2.40135264396667</v>
+        <v>2.40135288238525</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="n">
-        <v>2.48415803909302</v>
+        <v>2.48415780067444</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.44651889801025</v>
+        <v>2.44651913642883</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="n">
-        <v>2.48415803909302</v>
+        <v>2.48415780067444</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50674152374268</v>
+        <v>2.50674104690552</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.5836353302002</v>
+        <v>2.58363485336304</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56035923957825</v>
+        <v>2.56035900115967</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604820251465</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.5836353302002</v>
+        <v>2.58363485336304</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484152793884</v>
+        <v>2.54484176635742</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="n">
-        <v>2.48277258872986</v>
+        <v>2.48277235031128</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604820251465</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="n">
-        <v>2.48277258872986</v>
+        <v>2.48277235031128</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846202850342</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208205223083</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156348228455</v>
+        <v>2.07156324386597</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>2.03277015686035</v>
+        <v>2.03276991844177</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966579437256</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432076454163</v>
+        <v>1.85432052612305</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983823776245</v>
+        <v>1.86983799934387</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>1.8388032913208</v>
+        <v>1.83880352973938</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104467391968</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03277015686035</v>
+        <v>2.03276991844177</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03277015686035</v>
+        <v>2.03276991844177</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397683143616</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725244522095</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397683143616</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>1.8388032913208</v>
+        <v>1.83880352973938</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104467391968</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776870250702</v>
+        <v>1.80776882171631</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.753457903862</v>
+        <v>1.75345814228058</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673423290253</v>
+        <v>1.77673399448395</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569952487946</v>
+        <v>1.74569928646088</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966579437256</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91639006137848</v>
+        <v>1.91639029979706</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156348228455</v>
+        <v>2.07156324386597</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397683143616</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>2.03277015686035</v>
+        <v>2.03276991844177</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26552987098694</v>
+        <v>2.26553010940552</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087537765503</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.3353579044342</v>
+        <v>2.33535766601562</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208205223083</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846202850342</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311652183533</v>
+        <v>2.34311628341675</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087537765503</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.3741512298584</v>
+        <v>2.37415146827698</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966822624207</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.55260062217712</v>
+        <v>2.5526008605957</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="n">
-        <v>2.6013765335083</v>
+        <v>2.60137629508972</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="n">
-        <v>2.6013765335083</v>
+        <v>2.60137629508972</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>2.57698845863342</v>
+        <v>2.576988697052</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.1298770904541</v>
+        <v>2.12987685203552</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.08110094070435</v>
+        <v>2.08110117912292</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548901557922</v>
+        <v>2.10548877716064</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412701129913</v>
+        <v>1.89412713050842</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.65837752819061</v>
+        <v>1.65837728977203</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51205003261566</v>
+        <v>1.51204991340637</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.5486319065094</v>
+        <v>1.54863166809082</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237330913544</v>
+        <v>1.53237318992615</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.60147225856781</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.60147225856781</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.65837752819061</v>
+        <v>1.65837728977203</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60147225856781</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096362113953</v>
+        <v>1.82096338272095</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.82909286022186</v>
+        <v>1.82909274101257</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096362113953</v>
+        <v>1.82096338272095</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089484214783</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.60147225856781</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.64211869239807</v>
+        <v>1.64211893081665</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.60553693771362</v>
+        <v>1.60553705692291</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.48766195774078</v>
+        <v>1.48766207695007</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482172489166</v>
+        <v>1.43482160568237</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.33320534229279</v>
+        <v>1.33320546150208</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.33320534229279</v>
+        <v>1.33320546150208</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255878925323</v>
+        <v>1.29255890846252</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.3372700214386</v>
+        <v>1.33727014064789</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946405887604</v>
+        <v>1.34946393966675</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.37385177612305</v>
+        <v>1.37385189533234</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.35352873802185</v>
+        <v>1.35352849960327</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.39823997020721</v>
+        <v>1.39823985099792</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.3860456943512</v>
+        <v>1.38604581356049</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39823997020721</v>
+        <v>1.39823985099792</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.48766195774078</v>
+        <v>1.48766207695007</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237330913544</v>
+        <v>1.53237318992615</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51205003261566</v>
+        <v>1.51204991340637</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.50798535346985</v>
+        <v>1.50798523426056</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643798828125</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.47953271865845</v>
+        <v>1.47953283786774</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.54456722736359</v>
+        <v>1.5445671081543</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973929405212</v>
+        <v>1.86973917484283</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.17865252494812</v>
+        <v>2.1786527633667</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.1298770904541</v>
+        <v>2.12987685203552</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.08110094070435</v>
+        <v>2.08110117912292</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671310424805</v>
+        <v>2.05671286582947</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.08110094070435</v>
+        <v>2.08110117912292</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.08110094070435</v>
+        <v>2.08110117912292</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.17804384231567</v>
+        <v>2.17804360389709</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>30</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>30</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>30</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.10351014137268</v>
+        <v>2.1035099029541</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.14491772651672</v>
+        <v>2.14491748809814</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102376937866</v>
+        <v>2.50102353096008</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>30</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930500030518</v>
+        <v>2.50930523872375</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.71634340286255</v>
+        <v>2.71634364128113</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978022575378</v>
+        <v>2.69978046417236</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>34</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.81572198867798</v>
+        <v>2.81572222709656</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>37</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>37</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464367866516</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994474411011</v>
+        <v>2.93994498252869</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>36.5</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>37</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>36.5</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>37</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526509284973</v>
+        <v>3.15526461601257</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>37</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>37</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>36.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>36.5</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>37</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>37</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>37</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>36.5</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>36.5</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>37</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>37</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>37</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>36.5</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>36.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>37</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>36.5</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>36.5</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>37</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>37</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>37</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>37</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>37</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>37</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.10557556152344</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526509284973</v>
+        <v>3.15526461601257</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>39.5</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.27120637893677</v>
+        <v>3.27120661735535</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464367866516</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>39.5</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.27120637893677</v>
+        <v>3.27120661735535</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585054397583</v>
+        <v>5.01585006713867</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.5828595161438</v>
+        <v>5.58285999298096</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212291717529</v>
+        <v>5.21212244033813</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924369812012</v>
+        <v>5.53924322128296</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495798110962</v>
+        <v>6.93495845794678</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868560791016</v>
+        <v>6.73868608474731</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433319091797</v>
+        <v>6.32433271408081</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964534759521</v>
+        <v>6.62964582443237</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049423217773</v>
+        <v>6.76049375534058</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.02219104766846</v>
+        <v>7.0221905708313</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399871826172</v>
+        <v>7.04399824142456</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835208892822</v>
+        <v>7.45835161209106</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259365081787</v>
+        <v>8.11259269714355</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>2.66000008583069</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>123</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544668197632</v>
+        <v>1.24544656276703</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541857719421</v>
+        <v>1.2154186964035</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22185301780701</v>
+        <v>1.2218531370163</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470355987549</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683884620667</v>
+        <v>1.20683896541595</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1668016910553</v>
+        <v>1.16680181026459</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468474388123</v>
+        <v>1.19468486309052</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688576698303</v>
+        <v>1.25688564777374</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045132637024</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687659740448</v>
+        <v>1.24687647819519</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687659740448</v>
+        <v>1.24687647819519</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470355987549</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541857719421</v>
+        <v>1.2154186964035</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19397008419037</v>
+        <v>1.19396996498108</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685778141022</v>
+        <v>1.22685790061951</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469415187836</v>
+        <v>1.20469439029694</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903058052063</v>
+        <v>1.25903069972992</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903998851776</v>
+        <v>1.26903986930847</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>17.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>1.27189993858337</v>
+        <v>1.27189970016479</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.26260530948639</v>
+        <v>1.26260542869568</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830627441406</v>
+        <v>1.24830615520477</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>17.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24902129173279</v>
+        <v>1.2490211725235</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045132637024</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686707019806</v>
+        <v>1.23686695098877</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685778141022</v>
+        <v>1.22685790061951</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400723934174</v>
+        <v>1.23400735855103</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176798343658</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27421021461487</v>
+        <v>1.27421009540558</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347815036774</v>
+        <v>1.27347826957703</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27933323383331</v>
+        <v>1.27933311462402</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299272060394</v>
+        <v>1.28299260139465</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176798343658</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G112" t="n">
-        <v>1.26396369934082</v>
+        <v>1.26396381855011</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.226637840271</v>
+        <v>1.22663760185242</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.1783332824707</v>
+        <v>1.17833340167999</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784773349762</v>
+        <v>1.18784785270691</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224628925323</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224628925323</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834788799286</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834788799286</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.20614492893219</v>
+        <v>1.2061448097229</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736230373383</v>
+        <v>1.19736218452454</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297823429108</v>
+        <v>1.22297811508179</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883331775665</v>
+        <v>1.22883343696594</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30714499950409</v>
+        <v>1.3071448802948</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324635982513</v>
+        <v>1.32324624061584</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763767242432</v>
+        <v>1.32763755321503</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>1.30348551273346</v>
+        <v>1.30348539352417</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982614517212</v>
+        <v>1.29982602596283</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884780406952</v>
+        <v>1.28884792327881</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543471336365</v>
+        <v>1.29543483257294</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836225509644</v>
+        <v>1.29836213588715</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.29323899745941</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250717163086</v>
+        <v>1.29250729084015</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274644374847</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762318611145</v>
+        <v>1.26762306690216</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786233901978</v>
+        <v>1.24786221981049</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518107414246</v>
+        <v>1.25518119335175</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542747020721</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005805492401</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639856815338</v>
+        <v>1.24639844894409</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2420072555542</v>
+        <v>1.24200713634491</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005805492401</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542747020721</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297823429108</v>
+        <v>1.22297811508179</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.23176085948944</v>
+        <v>1.23176097869873</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.20980429649353</v>
+        <v>1.20980441570282</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.2185868024826</v>
+        <v>1.21858692169189</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.22005069255829</v>
+        <v>1.220050573349</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639120578766</v>
+        <v>1.21639132499695</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957262516022</v>
+        <v>1.25957250595093</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786934375763</v>
+        <v>1.27786946296692</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592038154602</v>
+        <v>1.28592026233673</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.29323899745941</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007254123688</v>
+        <v>1.31007242202759</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081149101257</v>
+        <v>1.34081161022186</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>1.33202910423279</v>
+        <v>1.3320289850235</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227538108826</v>
+        <v>1.34227526187897</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="n">
-        <v>1.34593462944031</v>
+        <v>1.3459347486496</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.3613041639328</v>
+        <v>1.36130428314209</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934772014618</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.32910132408142</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252890110016</v>
+        <v>1.38252902030945</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789843559265</v>
+        <v>1.39789867401123</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.4125360250473</v>
+        <v>1.41253614425659</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668118000031</v>
+        <v>1.40668129920959</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887677669525</v>
+        <v>1.40887665748596</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.3693550825119</v>
+        <v>1.36935496330261</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.37886953353882</v>
+        <v>1.37886965274811</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911592960358</v>
+        <v>1.38911581039429</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155792236328</v>
+        <v>1.40155780315399</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304330348969</v>
+        <v>1.49304342269897</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304330348969</v>
+        <v>1.49304342269897</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621023654938</v>
+        <v>1.4762099981308</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206496238708</v>
+        <v>1.48206508159637</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157965183258</v>
+        <v>1.49157953262329</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864486694336</v>
+        <v>1.45864498615265</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.47913777828217</v>
+        <v>1.47913753986359</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="n">
-        <v>1.49084794521332</v>
+        <v>1.49084782600403</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206496238708</v>
+        <v>1.48206508159637</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744209766388</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744209766388</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>1.53256523609161</v>
+        <v>1.53256547451019</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963769435883</v>
+        <v>1.52963757514954</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="n">
-        <v>1.49963057041168</v>
+        <v>1.49963045120239</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.49816656112671</v>
+        <v>1.49816644191742</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.48572444915771</v>
+        <v>1.485724568367</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206496238708</v>
+        <v>1.48206508159637</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206496238708</v>
+        <v>1.48206508159637</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498526096344</v>
+        <v>1.45498549938202</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085506916046</v>
+        <v>1.52085518836975</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768837451935</v>
+        <v>1.53768849372864</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126361370087</v>
+        <v>1.63126385211945</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427460193634</v>
+        <v>1.63427484035492</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857733249664</v>
+        <v>1.64857757091522</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="n">
-        <v>1.63578033447266</v>
+        <v>1.63578045368195</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902174949646</v>
+        <v>1.76902151107788</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816614627838</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345139503479</v>
+        <v>1.95345163345337</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011546134949</v>
+        <v>1.93011558055878</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118481636047</v>
+        <v>1.88118505477905</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9263516664505</v>
+        <v>1.92635154724121</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882395744324</v>
+        <v>1.91882383823395</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237376213074</v>
+        <v>1.93237364292145</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.9075323343277</v>
+        <v>1.90753221511841</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742114067078</v>
+        <v>1.87742137908936</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762709140778</v>
+        <v>1.79762721061707</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.79461598396301</v>
+        <v>1.7946161031723</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.807412981987</v>
+        <v>1.80741322040558</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>1.81042397022247</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816614627838</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>1.81042397022247</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806287288666</v>
+        <v>1.84806311130524</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.8465576171875</v>
+        <v>1.84655737876892</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280174255371</v>
+        <v>1.91280150413513</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237376213074</v>
+        <v>1.93237364292145</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>1.92108201980591</v>
+        <v>1.9210821390152</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720750808716</v>
+        <v>1.88720726966858</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="n">
-        <v>1.869140625</v>
+        <v>1.86914050579071</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161279678345</v>
+        <v>1.86161291599274</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763525009155</v>
+        <v>1.86763501167297</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731030464172</v>
+        <v>1.84731018543243</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279334545135</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795167922974</v>
+        <v>1.81795191764832</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849097251892</v>
+        <v>1.82849085330963</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117677688599</v>
+        <v>1.81117689609528</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644630432129</v>
+        <v>1.81644666194916</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83225464820862</v>
+        <v>1.8322548866272</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.8503212928772</v>
+        <v>1.85032117366791</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689024448395</v>
+        <v>1.93689036369324</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979855537415</v>
+        <v>1.97979831695557</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.9677540063858</v>
+        <v>1.96775412559509</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937057495117</v>
+        <v>1.99937081336975</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624863147736</v>
+        <v>1.96624886989594</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861788749695</v>
+        <v>1.99861764907837</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549606323242</v>
+        <v>1.96549594402313</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="n">
-        <v>1.97603487968445</v>
+        <v>1.97603464126587</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98280966281891</v>
+        <v>1.98280942440033</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034564971924</v>
+        <v>2.06034588813782</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959296226501</v>
+        <v>2.05959272384644</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>2.05883979797363</v>
+        <v>2.05884003639221</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="n">
-        <v>2.37124180793762</v>
+        <v>2.37124156951904</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810366630554</v>
+        <v>2.19810342788696</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="n">
-        <v>2.18304777145386</v>
+        <v>2.18304800987244</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="n">
-        <v>2.37124180793762</v>
+        <v>2.37124156951904</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>2.61965727806091</v>
+        <v>2.61965751647949</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>2.46157479286194</v>
+        <v>2.46157503128052</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.46157479286194</v>
+        <v>2.46157503128052</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888047218323</v>
+        <v>2.40888023376465</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432343482971</v>
+        <v>2.30432319641113</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>1.84656190872192</v>
+        <v>1.8465621471405</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>1.84656190872192</v>
+        <v>1.8465621471405</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673399448395</v>
+        <v>1.77673375606537</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569928646088</v>
+        <v>1.74569952487946</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91639029979706</v>
+        <v>1.91639006137848</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="n">
-        <v>2.05604600906372</v>
+        <v>2.05604577064514</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="n">
-        <v>2.05604600906372</v>
+        <v>2.05604577064514</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26553010940552</v>
+        <v>2.26552987098694</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087513923645</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.33535766601562</v>
+        <v>2.3353579044342</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432343482971</v>
+        <v>2.30432319641113</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>2.39742708206177</v>
+        <v>2.39742732048035</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>2.39742708206177</v>
+        <v>2.39742732048035</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>2.39742708206177</v>
+        <v>2.39742732048035</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518569946289</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311628341675</v>
+        <v>2.34311652183533</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087513923645</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.39742708206177</v>
+        <v>2.39742732048035</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>2.6800000667572</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63216,15 +63216,17 @@
         <v>1</v>
       </c>
       <c r="C2733" t="n">
-        <v>2.75999999046326</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="D2733" t="n">
-        <v>2.64000010490417</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="E2733" t="n">
-        <v>2.64000010490417</v>
-      </c>
-      <c r="F2733"/>
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>2.77999997138977</v>
+      </c>
       <c r="G2733" t="s">
         <v>7</v>
       </c>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63231,6 +63231,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2734" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>84</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2735"/>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.66000008583069</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.75999999046326</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63293,7 +63293,9 @@
       <c r="E2736" t="n">
         <v>2.70000004768372</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.66000008583069</v>
+      </c>
       <c r="G2736" t="s">
         <v>7</v>
       </c>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63300,6 +63300,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2737" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>342</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.70000004768372</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.6800000667572</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1387</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>405</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616134166718</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544644355774</v>
+        <v>1.24544668197632</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256827354431</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541833877563</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2361524105072</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327376365662</v>
+        <v>1.21327364444733</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683920383453</v>
+        <v>1.20683908462524</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1946849822998</v>
+        <v>1.19468486309052</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688576698303</v>
+        <v>1.25688588619232</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045096874237</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2361524105072</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.25116622447968</v>
+        <v>1.2511659860611</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475024223328</v>
+        <v>1.26475036144257</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541833877563</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542762756348</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G28" t="n">
-        <v>1.21041393280029</v>
+        <v>1.210413813591</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396984577179</v>
+        <v>1.19396996498108</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256827354431</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469427108765</v>
+        <v>1.20469439029694</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256827354431</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25116622447968</v>
+        <v>1.2511659860611</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25831580162048</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903069972992</v>
+        <v>1.25903046131134</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828781604767</v>
+        <v>1.22828757762909</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542762756348</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616134166718</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>17.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.25116622447968</v>
+        <v>1.2511659860611</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404463291168</v>
+        <v>1.27404451370239</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689505577087</v>
+        <v>1.26689493656158</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25831580162048</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G52" t="n">
-        <v>1.2790492773056</v>
+        <v>1.27904915809631</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25831580162048</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25831580162048</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546537876129</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>1.2676100730896</v>
+        <v>1.26760983467102</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>1.2676100730896</v>
+        <v>1.26760983467102</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545573234558</v>
+        <v>1.25545585155487</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.26260530948639</v>
+        <v>1.26260554790497</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.25831580162048</v>
+        <v>1.2583155632019</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>17.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25116622447968</v>
+        <v>1.2511659860611</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.2490211725235</v>
+        <v>1.24902129173279</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045096874237</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472213745117</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472213745117</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400747776031</v>
+        <v>1.23400723934174</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.2361524105072</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.2361524105072</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225353240967</v>
+        <v>1.25225377082825</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27640569210052</v>
+        <v>1.2764059305191</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323199272156</v>
+        <v>1.26323175430298</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323199272156</v>
+        <v>1.26323175430298</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445637226105</v>
+        <v>1.28445649147034</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.280797123909</v>
+        <v>1.28079688549042</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811609745026</v>
+        <v>1.28811585903168</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G112" t="n">
-        <v>1.26396381855011</v>
+        <v>1.26396369934082</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663760185242</v>
+        <v>1.22663772106171</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.17833316326141</v>
+        <v>1.17833340167999</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.1878479719162</v>
+        <v>1.18784773349762</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955077648163</v>
+        <v>1.16955053806305</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>16.25</v>
       </c>
       <c r="G131" t="n">
-        <v>1.1893116235733</v>
+        <v>1.18931138515472</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151434421539</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G138" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151434421539</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G144" t="n">
-        <v>1.2390798330307</v>
+        <v>1.23907959461212</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G147" t="n">
-        <v>1.23542046546936</v>
+        <v>1.23542022705078</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.20614469051361</v>
+        <v>1.2061448097229</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736230373383</v>
+        <v>1.19736218452454</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249268531799</v>
+        <v>1.23249292373657</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324635982513</v>
+        <v>1.32324624061584</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G169" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>1.30348539352417</v>
+        <v>1.30348551273346</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>1.3181232213974</v>
+        <v>1.31812310218811</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982602596283</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884792327881</v>
+        <v>1.28884768486023</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543483257294</v>
+        <v>1.29543495178223</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055785179138</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055785179138</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836213588715</v>
+        <v>1.29836225509644</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250729084015</v>
+        <v>1.29250741004944</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G190" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G191" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G192" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.2727462053299</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.26542770862579</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006505966187</v>
+        <v>1.28006517887115</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810873508453</v>
+        <v>1.25810861587524</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>1.24054360389709</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>1.24054360389709</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420273303986</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688411712646</v>
+        <v>1.23688387870789</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420273303986</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2420072555542</v>
+        <v>1.24200713634491</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26542770862579</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>1.24054360389709</v>
+        <v>1.24054348468781</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127542972565</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2098046541214</v>
+        <v>1.20980441570282</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126806735992</v>
+        <v>1.21126794815063</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.21858692169189</v>
+        <v>1.21858704090118</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322474956512</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492743492126</v>
+        <v>1.21492755413055</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004356861115</v>
+        <v>1.19004344940186</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>1.18199288845062</v>
+        <v>1.18199253082275</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21419560909271</v>
+        <v>1.214195728302</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>1.19297087192535</v>
+        <v>1.19297111034393</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663035869598</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639132499695</v>
+        <v>1.21639144420624</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957250595093</v>
+        <v>1.25957226753235</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="n">
-        <v>1.2947028875351</v>
+        <v>1.29470300674438</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="n">
-        <v>1.29689848423004</v>
+        <v>1.29689836502075</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>1.29689848423004</v>
+        <v>1.29689836502075</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="n">
-        <v>1.2947028875351</v>
+        <v>1.29470300674438</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G256" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081161022186</v>
+        <v>1.34081137180328</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3334926366806</v>
+        <v>1.33349275588989</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>1.3320289850235</v>
+        <v>1.33202922344208</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861601352692</v>
+        <v>1.33861589431763</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G266" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.34666669368744</v>
+        <v>1.34666681289673</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227526187897</v>
+        <v>1.34227538108826</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>1.32690572738647</v>
+        <v>1.32690584659576</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="n">
-        <v>1.34593462944031</v>
+        <v>1.3459347486496</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130428314209</v>
+        <v>1.36130440235138</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="n">
-        <v>1.32690572738647</v>
+        <v>1.32690584659576</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="n">
-        <v>1.33276069164276</v>
+        <v>1.33276081085205</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959411621094</v>
+        <v>1.34959423542023</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34373915195465</v>
+        <v>1.34373903274536</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>1.34520280361176</v>
+        <v>1.34520292282104</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.3291015625</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349987983704</v>
+        <v>1.36349999904633</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.36789119243622</v>
+        <v>1.3678914308548</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667381763458</v>
+        <v>1.37667393684387</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252902030945</v>
+        <v>1.38252890110016</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668118000031</v>
+        <v>1.40668106079102</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.4081449508667</v>
+        <v>1.40814483165741</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="n">
-        <v>1.39277541637421</v>
+        <v>1.39277529716492</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.36935496330261</v>
+        <v>1.3693550825119</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.37886953353882</v>
+        <v>1.37886965274811</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911592960358</v>
+        <v>1.38911604881287</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621035575867</v>
+        <v>1.47620987892151</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206543922424</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157953262329</v>
+        <v>1.49157965183258</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742749214172</v>
+        <v>1.46742761135101</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206543922424</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987660884857</v>
+        <v>1.50987648963928</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>1.53256511688232</v>
+        <v>1.53256523609161</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963769435883</v>
+        <v>1.52963745594025</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817392349243</v>
+        <v>1.52817380428314</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51499998569489</v>
+        <v>1.51500010490417</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.498166680336</v>
+        <v>1.49816679954529</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.48572444915771</v>
+        <v>1.485724568367</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206543922424</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108697891235</v>
+        <v>1.47108685970306</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="n">
-        <v>1.48426079750061</v>
+        <v>1.4842609167099</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206543922424</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376800537109</v>
+        <v>1.46376812458038</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498538017273</v>
+        <v>1.45498526096344</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499274253845</v>
+        <v>1.48499286174774</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="n">
-        <v>1.58233320713043</v>
+        <v>1.58233344554901</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126361370087</v>
+        <v>1.63126373291016</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427484035492</v>
+        <v>1.63427472114563</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857745170593</v>
+        <v>1.64857757091522</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66664397716522</v>
+        <v>1.66664409637451</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288030147552</v>
+        <v>1.66288042068481</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.66137480735779</v>
+        <v>1.66137456893921</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902151107788</v>
+        <v>1.76902163028717</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816578865051</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="n">
-        <v>1.91656541824341</v>
+        <v>1.9165655374527</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345139503479</v>
+        <v>1.95345163345337</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>1.98205709457397</v>
+        <v>1.98205697536469</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011546134949</v>
+        <v>1.9301153421402</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376014232635</v>
+        <v>1.83376026153564</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.90301585197449</v>
+        <v>1.9030157327652</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538475036621</v>
+        <v>1.93538463115692</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.92258751392365</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118493556976</v>
+        <v>1.88118517398834</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.921835064888</v>
+        <v>1.92183494567871</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.92559885978699</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>1.94065427780151</v>
+        <v>1.9406543970108</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.92635178565979</v>
+        <v>1.92635130882263</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>1.91656541824341</v>
+        <v>1.9165655374527</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376842021942</v>
+        <v>1.90376853942871</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.92559885978699</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237388134003</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.92258751392365</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054320335388</v>
+        <v>1.91054308414459</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753221511841</v>
+        <v>1.90753209590912</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699339866638</v>
+        <v>1.89699351787567</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473509788513</v>
+        <v>1.89473497867584</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762673377991</v>
+        <v>1.7976268529892</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826882362366</v>
+        <v>1.76826870441437</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.79461562633514</v>
+        <v>1.79461598396301</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741310119629</v>
+        <v>1.807412981987</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074903488159</v>
+        <v>1.83074915409088</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816578865051</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.82623255252838</v>
+        <v>1.82623267173767</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.8360184431076</v>
+        <v>1.83601856231689</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>1.82171607017517</v>
+        <v>1.82171595096588</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806287288666</v>
+        <v>1.84806275367737</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752393722534</v>
+        <v>1.83752417564392</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.8977462053299</v>
+        <v>1.89774608612061</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.912801861763</v>
+        <v>1.91280162334442</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.97377645969391</v>
+        <v>1.97377634048462</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.97377645969391</v>
+        <v>1.97377634048462</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>1.97151827812195</v>
+        <v>1.97151815891266</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.930868268013</v>
+        <v>1.93086814880371</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.9361377954483</v>
+        <v>1.93613767623901</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237388134003</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796019554138</v>
+        <v>1.8879599571228</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720726966858</v>
+        <v>1.88720715045929</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>1.89548766613007</v>
+        <v>1.89548778533936</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182678699493</v>
+        <v>1.85182690620422</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494884967804</v>
+        <v>1.88494896888733</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215173244476</v>
+        <v>1.87215185165405</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161291599274</v>
+        <v>1.86161303520203</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193774223328</v>
+        <v>1.88193798065186</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763501167297</v>
+        <v>1.86763513088226</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365734577179</v>
+        <v>1.8736572265625</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="n">
-        <v>1.84505200386047</v>
+        <v>1.84505188465118</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204065799713</v>
+        <v>1.84204077720642</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731030464172</v>
+        <v>1.84731018543243</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279334545135</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795191764832</v>
+        <v>1.81795179843903</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849085330963</v>
+        <v>1.82849073410034</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117689609528</v>
+        <v>1.81117701530457</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644654273987</v>
+        <v>1.81644630432129</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83225464820862</v>
+        <v>1.83225476741791</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246840000153</v>
+        <v>1.8224686384201</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689036369324</v>
+        <v>1.93689012527466</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731822490692</v>
+        <v>1.9173184633255</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979843616486</v>
+        <v>1.97979867458344</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474313735962</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="n">
-        <v>1.94667661190033</v>
+        <v>1.94667649269104</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="n">
-        <v>1.97076535224915</v>
+        <v>1.97076523303986</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775424480438</v>
+        <v>1.96775436401367</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248459815979</v>
+        <v>1.96248483657837</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="n">
-        <v>2.10325407981873</v>
+        <v>2.10325360298157</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>2.04378437995911</v>
+        <v>2.04378461837769</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G476" t="n">
-        <v>2.02421259880066</v>
+        <v>2.02421236038208</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732650279999</v>
+        <v>1.98732614517212</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937057495117</v>
+        <v>1.99937093257904</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="n">
-        <v>1.99033737182617</v>
+        <v>1.99033749103546</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861776828766</v>
+        <v>1.99861800670624</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549582481384</v>
+        <v>1.96549570560455</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474313735962</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="n">
-        <v>1.97603487968445</v>
+        <v>1.97603464126587</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98281002044678</v>
+        <v>1.98280966281891</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.97377645969391</v>
+        <v>1.97377634048462</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.02496528625488</v>
+        <v>2.0249650478363</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540059089661</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.08142304420471</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="n">
-        <v>2.08217597007751</v>
+        <v>2.08217620849609</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="n">
-        <v>2.08593988418579</v>
+        <v>2.08594012260437</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>2.08142304420471</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>2.09045648574829</v>
+        <v>2.09045672416687</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024261474609</v>
+        <v>2.10024237632751</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="n">
-        <v>2.07013154029846</v>
+        <v>2.07013130187988</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034564971924</v>
+        <v>2.06034588813782</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959296226501</v>
+        <v>2.05959272384644</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540059089661</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.10400676727295</v>
+        <v>2.10400605201721</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185906410217</v>
+        <v>2.13185930252075</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>2.21315860748291</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.16799235343933</v>
+        <v>2.16799259185791</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="n">
-        <v>2.33360314369202</v>
+        <v>2.33360290527344</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>2.28843665122986</v>
+        <v>2.28843641281128</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596424102783</v>
+        <v>2.29596447944641</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.28843665122986</v>
+        <v>2.28843641281128</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810366630554</v>
+        <v>2.19810342788696</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>2.21315860748291</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="n">
-        <v>2.18304800987244</v>
+        <v>2.18304777145386</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.21315860748291</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>2.43899154663086</v>
+        <v>2.43899130821228</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>2.38629722595215</v>
+        <v>2.38629698753357</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>2.43899154663086</v>
+        <v>2.43899130821228</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888023376465</v>
+        <v>2.40888047218323</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146347999573</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.5067412853241</v>
+        <v>2.50674152374268</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56035900115967</v>
+        <v>2.56035923957825</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>2.51380729675293</v>
+        <v>2.51380753517151</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>2.49829006195068</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>2.49829006195068</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432367324829</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208157539368</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="n">
-        <v>2.25001263618469</v>
+        <v>2.25001239776611</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>1.97070074081421</v>
+        <v>1.97070062160492</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966603279114</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>1.88535523414612</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432064533234</v>
+        <v>1.85432076454163</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983788013458</v>
+        <v>1.86983799934387</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207950115204</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207950115204</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776858329773</v>
+        <v>1.80776870250702</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.75345802307129</v>
+        <v>1.75345814228058</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673411369324</v>
+        <v>1.77673399448395</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569940567017</v>
+        <v>1.74569952487946</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311385154724</v>
+        <v>1.89311408996582</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.88535523414612</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966603279114</v>
+        <v>1.93966591358185</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932186126709</v>
+        <v>2.07932209968567</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>2.24225378036499</v>
+        <v>2.24225354194641</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>2.24225378036499</v>
+        <v>2.24225354194641</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432367324829</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208157539368</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>2.3819100856781</v>
+        <v>2.38190960884094</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>2.42070341110229</v>
+        <v>2.42070317268372</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="n">
-        <v>2.3663923740387</v>
+        <v>2.36639261245728</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>2.45173811912537</v>
+        <v>2.45173788070679</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.45173811912537</v>
+        <v>2.45173788070679</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>2.45173811912537</v>
+        <v>2.45173788070679</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>2.49829006195068</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5526008605957</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>2.2274284362793</v>
+        <v>2.22742867469788</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>2.25181651115417</v>
+        <v>2.2518162727356</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>2.25181651115417</v>
+        <v>2.2518162727356</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="n">
-        <v>2.25181651115417</v>
+        <v>2.2518162727356</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>2.46317791938782</v>
+        <v>2.4631781578064</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="n">
-        <v>2.60950541496277</v>
+        <v>2.60950565338135</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>2.5688591003418</v>
+        <v>2.56885933876038</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>2.5688591003418</v>
+        <v>2.56885933876038</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>29.5</v>
       </c>
       <c r="G922" t="n">
-        <v>2.39814400672913</v>
+        <v>2.39814376831055</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>2.46317791938782</v>
+        <v>2.4631781578064</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>29.5</v>
       </c>
       <c r="G937" t="n">
-        <v>2.39814400672913</v>
+        <v>2.39814376831055</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="n">
-        <v>2.39814400672913</v>
+        <v>2.39814376831055</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>2.46317791938782</v>
+        <v>2.4631781578064</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>2.46317791938782</v>
+        <v>2.4631781578064</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>2.44691967964172</v>
+        <v>2.44691944122314</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>2.5688591003418</v>
+        <v>2.56885933876038</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>2.5688591003418</v>
+        <v>2.56885933876038</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.52008366584778</v>
+        <v>2.52008318901062</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361861228943</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.1298770904541</v>
+        <v>2.12987685203552</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548877716064</v>
+        <v>2.10548901557922</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.04858374595642</v>
+        <v>2.048583984375</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412689208984</v>
+        <v>1.89412713050842</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.55676114559174</v>
+        <v>1.55676102638245</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.57301986217499</v>
+        <v>1.5730197429657</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114898204803</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.56895518302917</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.56895518302917</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114898204803</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63398945331573</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114898204803</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.63398945331573</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.58927822113037</v>
+        <v>1.58927834033966</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.63398945331573</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.674635887146</v>
+        <v>1.67463600635529</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.7640585899353</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.7315411567688</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.71528255939484</v>
+        <v>1.71528267860413</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.71528255939484</v>
+        <v>1.71528267860413</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.674635887146</v>
+        <v>1.67463600635529</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.674635887146</v>
+        <v>1.67463600635529</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.674635887146</v>
+        <v>1.67463600635529</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.674635887146</v>
+        <v>1.67463600635529</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.7559289932251</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.87786853313446</v>
+        <v>1.87786841392517</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.8128342628479</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.8128342628479</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470478534698</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.7640585899353</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.7640585899353</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.7315411567688</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.7315411567688</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.71528255939484</v>
+        <v>1.71528267860413</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.71528255939484</v>
+        <v>1.71528267860413</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.7315411567688</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.7640585899353</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.7559289932251</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.7315411567688</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.7559289932251</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.71528255939484</v>
+        <v>1.71528267860413</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.68276536464691</v>
+        <v>1.68276524543762</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.68276536464691</v>
+        <v>1.68276524543762</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.63398945331573</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.60960149765015</v>
+        <v>1.60960161685944</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.64211893081665</v>
+        <v>1.64211881160736</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114898204803</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.43075692653656</v>
+        <v>1.43075704574585</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482160568237</v>
+        <v>1.43482172489166</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.36572253704071</v>
+        <v>1.36572241783142</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.35759317874908</v>
+        <v>1.35759329795837</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.30475270748138</v>
+        <v>1.30475282669067</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946393966675</v>
+        <v>1.34946405887604</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.37385177612305</v>
+        <v>1.37385189533234</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823973178864</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.3860456943512</v>
+        <v>1.38604581356049</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823973178864</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.46733868122101</v>
+        <v>1.4673388004303</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.49172675609589</v>
+        <v>1.49172687530518</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.54050266742706</v>
+        <v>1.54050254821777</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.56895518302917</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.56895518302917</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.54050266742706</v>
+        <v>1.54050254821777</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973929405212</v>
+        <v>1.86973917484283</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.95103216171265</v>
+        <v>1.95103228092194</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.33310961723328</v>
+        <v>2.3331093788147</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807498931885</v>
+        <v>2.26807522773743</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.27620410919189</v>
+        <v>2.27620434761047</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.24368691444397</v>
+        <v>2.24368715286255</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.1298770904541</v>
+        <v>2.12987685203552</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361861228943</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671286582947</v>
+        <v>2.05671310424805</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361861228943</v>
+        <v>2.11361813545227</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.24368691444397</v>
+        <v>2.24368715286255</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.21116971969604</v>
+        <v>2.2111701965332</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.21116971969604</v>
+        <v>2.2111701965332</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.21116971969604</v>
+        <v>2.2111701965332</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.17804360389709</v>
+        <v>2.17804384231567</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711172103882</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>28</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>28</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711172103882</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>28</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.29398536682129</v>
+        <v>2.29398512840271</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>28</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>2.29398536682129</v>
+        <v>2.29398512840271</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>28</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711172103882</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>28</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>28</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>28</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>26</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>26</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>26</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.08694672584534</v>
+        <v>2.08694696426392</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.10351014137268</v>
+        <v>2.1035099029541</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>26</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>26</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>26</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>26</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>26</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>28</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>28</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>28</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.31882977485657</v>
+        <v>2.31883001327515</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.26085925102234</v>
+        <v>2.26085901260376</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.29398536682129</v>
+        <v>2.29398512840271</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.25257754325867</v>
+        <v>2.25257778167725</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.40992665290833</v>
+        <v>2.4099268913269</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.46789741516113</v>
+        <v>2.46789765357971</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102353096008</v>
+        <v>2.50102376937866</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>30.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>30.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930500030518</v>
+        <v>2.50930523872375</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978022575378</v>
+        <v>2.69978046417236</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.84884834289551</v>
+        <v>2.84884810447693</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.01447892189026</v>
+        <v>3.01447916030884</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.24636197090149</v>
+        <v>3.24636220932007</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.23808002471924</v>
+        <v>3.23808026313782</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>39</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.22979879379272</v>
+        <v>3.22979855537415</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.23808002471924</v>
+        <v>3.23808026313782</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.3043327331543</v>
+        <v>3.30433297157288</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464344024658</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994522094727</v>
+        <v>2.93994498252869</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.01447892189026</v>
+        <v>3.01447916030884</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.08073115348816</v>
+        <v>3.08073091506958</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.20495438575745</v>
+        <v>3.20495414733887</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464344024658</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585054397583</v>
+        <v>5.01585006713867</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.5828595161438</v>
+        <v>5.58285999298096</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212291717529</v>
+        <v>5.21212244033813</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924369812012</v>
+        <v>5.53924322128296</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495798110962</v>
+        <v>6.93495845794678</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868560791016</v>
+        <v>6.73868608474731</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433319091797</v>
+        <v>6.32433271408081</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964534759521</v>
+        <v>6.62964582443237</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049423217773</v>
+        <v>6.76049375534058</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.02219104766846</v>
+        <v>7.0221905708313</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399871826172</v>
+        <v>7.04399824142456</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835208892822</v>
+        <v>7.45835161209106</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259365081787</v>
+        <v>8.11259269714355</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>2.64000010490417</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>331</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H2" t="n">
         <v>328</v>
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544656276703</v>
+        <v>1.24544644355774</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -485,7 +485,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330151081085</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H4" t="n">
         <v>158</v>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541845798492</v>
+        <v>1.2154186964035</v>
       </c>
       <c r="H6" t="n">
         <v>466</v>
@@ -572,7 +572,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22185337543488</v>
+        <v>1.2218531370163</v>
       </c>
       <c r="H7" t="n">
         <v>1052</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -630,7 +630,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H9" t="n">
         <v>8746</v>
@@ -659,7 +659,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327352523804</v>
+        <v>1.21327364444733</v>
       </c>
       <c r="H10" t="n">
         <v>4107</v>
@@ -688,7 +688,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683896541595</v>
+        <v>1.20683920383453</v>
       </c>
       <c r="H11" t="n">
         <v>9368</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.20111954212189</v>
+        <v>1.20111930370331</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -746,7 +746,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G13" t="n">
-        <v>1.20040452480316</v>
+        <v>1.20040464401245</v>
       </c>
       <c r="H13" t="n">
         <v>1439</v>
@@ -775,7 +775,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1668016910553</v>
+        <v>1.16680192947388</v>
       </c>
       <c r="H14" t="n">
         <v>2159</v>
@@ -804,7 +804,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468486309052</v>
+        <v>1.1946849822998</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688564777374</v>
+        <v>1.25688600540161</v>
       </c>
       <c r="H16" t="n">
         <v>6127</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -891,7 +891,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H18" t="n">
         <v>605</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687659740448</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687659740448</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -978,7 +978,7 @@
         <v>17.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.25116634368896</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H21" t="n">
         <v>1559</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1065,7 +1065,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541845798492</v>
+        <v>1.2154186964035</v>
       </c>
       <c r="H24" t="n">
         <v>132</v>
@@ -1094,7 +1094,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.23543727397919</v>
+        <v>1.23543751239777</v>
       </c>
       <c r="H25" t="n">
         <v>505</v>
@@ -1123,7 +1123,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542762756348</v>
       </c>
       <c r="H26" t="n">
         <v>2636</v>
@@ -1152,7 +1152,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>1.20040452480316</v>
+        <v>1.20040464401245</v>
       </c>
       <c r="H27" t="n">
         <v>4499</v>
@@ -1210,7 +1210,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113823890686</v>
+        <v>1.22113800048828</v>
       </c>
       <c r="H29" t="n">
         <v>111</v>
@@ -1239,7 +1239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396996498108</v>
+        <v>1.19397008419037</v>
       </c>
       <c r="H30" t="n">
         <v>419</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.2268580198288</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1326,7 +1326,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469439029694</v>
+        <v>1.20469415187836</v>
       </c>
       <c r="H33" t="n">
         <v>276</v>
@@ -1384,7 +1384,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25116634368896</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H35" t="n">
         <v>2452</v>
@@ -1413,7 +1413,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25831568241119</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H36" t="n">
         <v>1696</v>
@@ -1529,7 +1529,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21684849262238</v>
+        <v>1.21684861183167</v>
       </c>
       <c r="H40" t="n">
         <v>6016</v>
@@ -1558,7 +1558,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828781604767</v>
+        <v>1.22828757762909</v>
       </c>
       <c r="H41" t="n">
         <v>573</v>
@@ -1587,7 +1587,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542762756348</v>
       </c>
       <c r="H42" t="n">
         <v>340</v>
@@ -1616,7 +1616,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H43" t="n">
         <v>1037</v>
@@ -1645,7 +1645,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330151081085</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H44" t="n">
         <v>139</v>
@@ -1674,7 +1674,7 @@
         <v>17.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.25116634368896</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H45" t="n">
         <v>26</v>
@@ -1703,7 +1703,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404451370239</v>
+        <v>1.27404463291168</v>
       </c>
       <c r="H46" t="n">
         <v>3010</v>
@@ -1732,7 +1732,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689481735229</v>
+        <v>1.26689493656158</v>
       </c>
       <c r="H47" t="n">
         <v>7764</v>
@@ -1848,7 +1848,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25831568241119</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H51" t="n">
         <v>1451</v>
@@ -1877,7 +1877,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G52" t="n">
-        <v>1.2790492773056</v>
+        <v>1.27904915809631</v>
       </c>
       <c r="H52" t="n">
         <v>663</v>
@@ -1906,7 +1906,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25831568241119</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H53" t="n">
         <v>4204</v>
@@ -1935,7 +1935,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25831568241119</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H54" t="n">
         <v>60</v>
@@ -2109,7 +2109,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.26260530948639</v>
+        <v>1.26260542869568</v>
       </c>
       <c r="H60" t="n">
         <v>703</v>
@@ -2138,7 +2138,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.25831568241119</v>
+        <v>1.25831580162048</v>
       </c>
       <c r="H61" t="n">
         <v>3448</v>
@@ -2167,7 +2167,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830627441406</v>
+        <v>1.24830603599548</v>
       </c>
       <c r="H62" t="n">
         <v>745</v>
@@ -2196,7 +2196,7 @@
         <v>17.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25116634368896</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H63" t="n">
         <v>556</v>
@@ -2225,7 +2225,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24902105331421</v>
+        <v>1.2490211725235</v>
       </c>
       <c r="H64" t="n">
         <v>523</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258673191071</v>
+        <v>1.24258661270142</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2312,7 +2312,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686707019806</v>
+        <v>1.23686718940735</v>
       </c>
       <c r="H67" t="n">
         <v>70</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.2268580198288</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2370,7 +2370,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472213745117</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H69" t="n">
         <v>538</v>
@@ -2399,7 +2399,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472213745117</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.23543727397919</v>
+        <v>1.23543751239777</v>
       </c>
       <c r="H72" t="n">
         <v>795</v>
@@ -2486,7 +2486,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H73" t="n">
         <v>1010</v>
@@ -2515,7 +2515,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H74" t="n">
         <v>1039</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225353240967</v>
+        <v>1.25225365161896</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2573,7 +2573,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H76" t="n">
         <v>2231</v>
@@ -2660,7 +2660,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H79" t="n">
         <v>1551</v>
@@ -2689,7 +2689,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27421009540558</v>
+        <v>1.27420997619629</v>
       </c>
       <c r="H82" t="n">
         <v>323</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2892,7 +2892,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G87" t="n">
-        <v>1.2668913602829</v>
+        <v>1.26689124107361</v>
       </c>
       <c r="H87" t="n">
         <v>1058</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -2950,7 +2950,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445649147034</v>
+        <v>1.28445661067963</v>
       </c>
       <c r="H89" t="n">
         <v>1506</v>
@@ -3095,7 +3095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347815036774</v>
+        <v>1.27347803115845</v>
       </c>
       <c r="H94" t="n">
         <v>370</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3153,7 +3153,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H96" t="n">
         <v>81</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811609745026</v>
+        <v>1.28811597824097</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299272060394</v>
+        <v>1.28299283981323</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H104" t="n">
         <v>741</v>
@@ -3414,7 +3414,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H106" t="n">
         <v>93</v>
@@ -3472,7 +3472,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H111" t="n">
         <v>594</v>
@@ -3617,7 +3617,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G112" t="n">
-        <v>1.26396369934082</v>
+        <v>1.26396381855011</v>
       </c>
       <c r="H112" t="n">
         <v>1613</v>
@@ -3704,7 +3704,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H115" t="n">
         <v>1050</v>
@@ -3733,7 +3733,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468828201294</v>
       </c>
       <c r="H116" t="n">
         <v>761</v>
@@ -3791,7 +3791,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -3878,7 +3878,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18565225601196</v>
+        <v>1.18565213680267</v>
       </c>
       <c r="H121" t="n">
         <v>6050</v>
@@ -3907,7 +3907,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.1783332824707</v>
+        <v>1.17833340167999</v>
       </c>
       <c r="H122" t="n">
         <v>4621</v>
@@ -3965,7 +3965,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955065727234</v>
+        <v>1.16955077648163</v>
       </c>
       <c r="H124" t="n">
         <v>4411</v>
@@ -3994,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101430892944</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H125" t="n">
         <v>673</v>
@@ -4110,7 +4110,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101430892944</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H129" t="n">
         <v>1649</v>
@@ -4197,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101430892944</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H132" t="n">
         <v>171</v>
@@ -4226,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101430892944</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H133" t="n">
         <v>101</v>
@@ -4255,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101430892944</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H134" t="n">
         <v>245</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4313,7 +4313,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224652767181</v>
       </c>
       <c r="H136" t="n">
         <v>10</v>
@@ -4342,7 +4342,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>1.22151434421539</v>
+        <v>1.22151458263397</v>
       </c>
       <c r="H137" t="n">
         <v>610</v>
@@ -4371,7 +4371,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G138" t="n">
-        <v>1.22151434421539</v>
+        <v>1.22151458263397</v>
       </c>
       <c r="H138" t="n">
         <v>215</v>
@@ -4400,7 +4400,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224652767181</v>
       </c>
       <c r="H139" t="n">
         <v>451</v>
@@ -4487,7 +4487,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G142" t="n">
-        <v>1.23981165885925</v>
+        <v>1.23981153964996</v>
       </c>
       <c r="H142" t="n">
         <v>152</v>
@@ -4516,7 +4516,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G143" t="n">
-        <v>1.23981165885925</v>
+        <v>1.23981153964996</v>
       </c>
       <c r="H143" t="n">
         <v>116</v>
@@ -4574,7 +4574,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834764957428</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H145" t="n">
         <v>265</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4661,7 +4661,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834764957428</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H148" t="n">
         <v>20</v>
@@ -4690,7 +4690,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23981165885925</v>
+        <v>1.23981153964996</v>
       </c>
       <c r="H149" t="n">
         <v>1154</v>
@@ -4719,7 +4719,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.20614492893219</v>
+        <v>1.20614469051361</v>
       </c>
       <c r="H150" t="n">
         <v>2847</v>
@@ -4748,7 +4748,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H151" t="n">
         <v>1211</v>
@@ -4777,7 +4777,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H152" t="n">
         <v>20</v>
@@ -4806,7 +4806,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736230373383</v>
+        <v>1.19736242294312</v>
       </c>
       <c r="H153" t="n">
         <v>1720</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.21712303161621</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.21712303161621</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -4893,7 +4893,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H156" t="n">
         <v>410</v>
@@ -4922,7 +4922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H157" t="n">
         <v>390</v>
@@ -4951,7 +4951,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249268531799</v>
+        <v>1.2324925661087</v>
       </c>
       <c r="H158" t="n">
         <v>2050</v>
@@ -4980,7 +4980,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883343696594</v>
+        <v>1.22883331775665</v>
       </c>
       <c r="H159" t="n">
         <v>486</v>
@@ -5009,7 +5009,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468828201294</v>
       </c>
       <c r="H160" t="n">
         <v>366</v>
@@ -5038,7 +5038,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518855571747</v>
       </c>
       <c r="H161" t="n">
         <v>10275</v>
@@ -5067,7 +5067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="n">
         <v>4104</v>
@@ -5096,7 +5096,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="n">
         <v>2568</v>
@@ -5154,7 +5154,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518855571747</v>
       </c>
       <c r="H165" t="n">
         <v>430</v>
@@ -5241,7 +5241,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324635982513</v>
+        <v>1.32324647903442</v>
       </c>
       <c r="H168" t="n">
         <v>18315</v>
@@ -5299,7 +5299,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763755321503</v>
+        <v>1.32763779163361</v>
       </c>
       <c r="H170" t="n">
         <v>14161</v>
@@ -5357,7 +5357,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G172" t="n">
-        <v>1.31592738628387</v>
+        <v>1.31592750549316</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5531,7 +5531,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543495178223</v>
+        <v>1.29543483257294</v>
       </c>
       <c r="H178" t="n">
         <v>703</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5763,7 +5763,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836213588715</v>
+        <v>1.29836225509644</v>
       </c>
       <c r="H186" t="n">
         <v>4389</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.2976301908493</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250717163086</v>
+        <v>1.29250729084015</v>
       </c>
       <c r="H189" t="n">
         <v>625</v>
@@ -5966,7 +5966,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568134784698</v>
       </c>
       <c r="H193" t="n">
         <v>4252</v>
@@ -5995,7 +5995,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>1.26908683776855</v>
+        <v>1.26908695697784</v>
       </c>
       <c r="H194" t="n">
         <v>6154</v>
@@ -6024,7 +6024,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27274632453918</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H195" t="n">
         <v>5744</v>
@@ -6053,7 +6053,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762306690216</v>
+        <v>1.26762318611145</v>
       </c>
       <c r="H196" t="n">
         <v>4114</v>
@@ -6082,7 +6082,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="n">
         <v>5843</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786233901978</v>
+        <v>1.24786221981049</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6140,7 +6140,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518119335175</v>
+        <v>1.25518107414246</v>
       </c>
       <c r="H199" t="n">
         <v>1811</v>
@@ -6198,7 +6198,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006517887115</v>
+        <v>1.28006529808044</v>
       </c>
       <c r="H201" t="n">
         <v>19504</v>
@@ -6256,7 +6256,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810873508453</v>
+        <v>1.25810861587524</v>
       </c>
       <c r="H203" t="n">
         <v>11122</v>
@@ -6285,7 +6285,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005781650543</v>
       </c>
       <c r="H204" t="n">
         <v>3493</v>
@@ -6314,7 +6314,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H205" t="n">
         <v>7291</v>
@@ -6343,7 +6343,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639856815338</v>
+        <v>1.24639868736267</v>
       </c>
       <c r="H206" t="n">
         <v>7757</v>
@@ -6372,7 +6372,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H207" t="n">
         <v>6005</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420297145844</v>
+        <v>1.24420309066772</v>
       </c>
       <c r="H208" t="n">
         <v>6264</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688399791718</v>
+        <v>1.23688387870789</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6488,7 +6488,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420297145844</v>
+        <v>1.24420309066772</v>
       </c>
       <c r="H211" t="n">
         <v>1424</v>
@@ -6517,7 +6517,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.24200737476349</v>
+        <v>1.2420072555542</v>
       </c>
       <c r="H212" t="n">
         <v>21105</v>
@@ -6546,7 +6546,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23981165885925</v>
+        <v>1.23981153964996</v>
       </c>
       <c r="H213" t="n">
         <v>5199</v>
@@ -6575,7 +6575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005781650543</v>
       </c>
       <c r="H214" t="n">
         <v>3399</v>
@@ -6633,7 +6633,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H216" t="n">
         <v>6370</v>
@@ -6662,7 +6662,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H217" t="n">
         <v>3330</v>
@@ -6691,7 +6691,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H218" t="n">
         <v>9836</v>
@@ -6720,7 +6720,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H219" t="n">
         <v>20</v>
@@ -6749,7 +6749,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.23176085948944</v>
+        <v>1.23176074028015</v>
       </c>
       <c r="H220" t="n">
         <v>8086</v>
@@ -6778,7 +6778,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H221" t="n">
         <v>2500</v>
@@ -6865,7 +6865,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H224" t="n">
         <v>2881</v>
@@ -6894,7 +6894,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H225" t="n">
         <v>13996</v>
@@ -6923,7 +6923,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H226" t="n">
         <v>2165</v>
@@ -6952,7 +6952,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H227" t="n">
         <v>1452</v>
@@ -6981,7 +6981,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.20980441570282</v>
+        <v>1.20980429649353</v>
       </c>
       <c r="H228" t="n">
         <v>5599</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126782894135</v>
+        <v>1.21126806735992</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7039,7 +7039,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.2185868024826</v>
+        <v>1.21858692169189</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H231" t="n">
         <v>434</v>
@@ -7213,7 +7213,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>1.19297099113464</v>
+        <v>1.19297111034393</v>
       </c>
       <c r="H236" t="n">
         <v>8622</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663035869598</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7358,7 +7358,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639144420624</v>
+        <v>1.21639132499695</v>
       </c>
       <c r="H241" t="n">
         <v>6606</v>
@@ -7387,7 +7387,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956538200378</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H242" t="n">
         <v>6732</v>
@@ -7503,7 +7503,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786946296692</v>
+        <v>1.27786934375763</v>
       </c>
       <c r="H246" t="n">
         <v>2816</v>
@@ -7532,7 +7532,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592026233673</v>
+        <v>1.28592038154602</v>
       </c>
       <c r="H247" t="n">
         <v>4452</v>
@@ -7764,7 +7764,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568134784698</v>
       </c>
       <c r="H255" t="n">
         <v>2306</v>
@@ -7822,7 +7822,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.3100723028183</v>
+        <v>1.31007242202759</v>
       </c>
       <c r="H257" t="n">
         <v>7253</v>
@@ -7851,7 +7851,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544219493866</v>
+        <v>1.32544207572937</v>
       </c>
       <c r="H258" t="n">
         <v>4943</v>
@@ -7880,7 +7880,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081161022186</v>
+        <v>1.34081149101257</v>
       </c>
       <c r="H259" t="n">
         <v>24867</v>
@@ -7938,7 +7938,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422458171844</v>
       </c>
       <c r="H261" t="n">
         <v>6768</v>
@@ -7996,7 +7996,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861589431763</v>
+        <v>1.33861601352692</v>
       </c>
       <c r="H263" t="n">
         <v>3514</v>
@@ -8054,7 +8054,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422458171844</v>
       </c>
       <c r="H265" t="n">
         <v>1429</v>
@@ -8112,7 +8112,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.34666681289673</v>
+        <v>1.34666669368744</v>
       </c>
       <c r="H267" t="n">
         <v>4055</v>
@@ -8141,7 +8141,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227550029755</v>
+        <v>1.34227526187897</v>
       </c>
       <c r="H268" t="n">
         <v>2370</v>
@@ -8170,7 +8170,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34007978439331</v>
+        <v>1.34007954597473</v>
       </c>
       <c r="H269" t="n">
         <v>383</v>
@@ -8199,7 +8199,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>1.32690584659576</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H270" t="n">
         <v>1643</v>
@@ -8257,7 +8257,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="n">
-        <v>1.34593486785889</v>
+        <v>1.3459347486496</v>
       </c>
       <c r="H272" t="n">
         <v>12265</v>
@@ -8286,7 +8286,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130428314209</v>
+        <v>1.36130440235138</v>
       </c>
       <c r="H273" t="n">
         <v>6282</v>
@@ -8315,7 +8315,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057245731354</v>
+        <v>1.36057233810425</v>
       </c>
       <c r="H274" t="n">
         <v>7391</v>
@@ -8344,7 +8344,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="n">
-        <v>1.32690584659576</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H275" t="n">
         <v>14713</v>
@@ -8402,7 +8402,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959411621094</v>
+        <v>1.34959399700165</v>
       </c>
       <c r="H277" t="n">
         <v>1064</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.32910132408142</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8605,7 +8605,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349999904633</v>
+        <v>1.36349987983704</v>
       </c>
       <c r="H284" t="n">
         <v>4639</v>
@@ -8634,7 +8634,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.36789119243622</v>
+        <v>1.36789131164551</v>
       </c>
       <c r="H285" t="n">
         <v>3430</v>
@@ -8663,7 +8663,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667369842529</v>
+        <v>1.37667393684387</v>
       </c>
       <c r="H286" t="n">
         <v>5575</v>
@@ -8692,7 +8692,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252890110016</v>
+        <v>1.38252902030945</v>
       </c>
       <c r="H287" t="n">
         <v>4266</v>
@@ -8721,7 +8721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789855480194</v>
+        <v>1.39789867401123</v>
       </c>
       <c r="H288" t="n">
         <v>6393</v>
@@ -8750,7 +8750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253614425659</v>
+        <v>1.4125360250473</v>
       </c>
       <c r="H289" t="n">
         <v>1447</v>
@@ -8779,7 +8779,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668106079102</v>
+        <v>1.40668118000031</v>
       </c>
       <c r="H290" t="n">
         <v>14299</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302169322968</v>
+        <v>1.40302181243896</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -8953,7 +8953,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.37886953353882</v>
+        <v>1.37886965274811</v>
       </c>
       <c r="H296" t="n">
         <v>1185</v>
@@ -8982,7 +8982,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911581039429</v>
+        <v>1.389115691185</v>
       </c>
       <c r="H297" t="n">
         <v>1150</v>
@@ -9011,7 +9011,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155780315399</v>
+        <v>1.40155792236328</v>
       </c>
       <c r="H298" t="n">
         <v>640</v>
@@ -9040,7 +9040,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H299" t="n">
         <v>23394</v>
@@ -9069,7 +9069,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H300" t="n">
         <v>14396</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621023654938</v>
+        <v>1.4762099981308</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9127,7 +9127,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H302" t="n">
         <v>4239</v>
@@ -9156,7 +9156,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157953262329</v>
+        <v>1.49157965183258</v>
       </c>
       <c r="H303" t="n">
         <v>5662</v>
@@ -9185,7 +9185,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50328981876373</v>
+        <v>1.50328993797302</v>
       </c>
       <c r="H304" t="n">
         <v>18505</v>
@@ -9243,7 +9243,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864498615265</v>
+        <v>1.45864486694336</v>
       </c>
       <c r="H306" t="n">
         <v>3108</v>
@@ -9272,7 +9272,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.4791374206543</v>
+        <v>1.47913753986359</v>
       </c>
       <c r="H307" t="n">
         <v>4196</v>
@@ -9301,7 +9301,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H308" t="n">
         <v>1440</v>
@@ -9359,7 +9359,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792016506195</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H310" t="n">
         <v>3021</v>
@@ -9388,7 +9388,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H311" t="n">
         <v>124</v>
@@ -9417,7 +9417,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H312" t="n">
         <v>332</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744209766388</v>
+        <v>1.5274418592453</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744209766388</v>
+        <v>1.5274418592453</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9562,7 +9562,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963769435883</v>
+        <v>1.52963757514954</v>
       </c>
       <c r="H317" t="n">
         <v>1725</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817368507385</v>
+        <v>1.52817380428314</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9649,7 +9649,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51500010490417</v>
+        <v>1.51499998569489</v>
       </c>
       <c r="H320" t="n">
         <v>2425</v>
@@ -9678,7 +9678,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="n">
-        <v>1.49963057041168</v>
+        <v>1.4996303319931</v>
       </c>
       <c r="H321" t="n">
         <v>5351</v>
@@ -9707,7 +9707,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.49816656112671</v>
+        <v>1.498166680336</v>
       </c>
       <c r="H322" t="n">
         <v>1750</v>
@@ -9765,7 +9765,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H324" t="n">
         <v>6036</v>
@@ -9794,7 +9794,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H325" t="n">
         <v>4358</v>
@@ -9823,7 +9823,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792016506195</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H326" t="n">
         <v>7683</v>
@@ -9852,7 +9852,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108697891235</v>
+        <v>1.47108685970306</v>
       </c>
       <c r="H327" t="n">
         <v>10631</v>
@@ -9910,7 +9910,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H329" t="n">
         <v>3153</v>
@@ -9939,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376812458038</v>
+        <v>1.46376824378967</v>
       </c>
       <c r="H330" t="n">
         <v>9218</v>
@@ -9968,7 +9968,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498549938202</v>
+        <v>1.45498538017273</v>
       </c>
       <c r="H331" t="n">
         <v>6285</v>
@@ -10026,7 +10026,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085530757904</v>
+        <v>1.52085518836975</v>
       </c>
       <c r="H333" t="n">
         <v>14974</v>
@@ -10055,7 +10055,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768837451935</v>
+        <v>1.53768849372864</v>
       </c>
       <c r="H334" t="n">
         <v>12975</v>
@@ -10113,7 +10113,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126361370087</v>
+        <v>1.63126373291016</v>
       </c>
       <c r="H336" t="n">
         <v>30984</v>
@@ -10142,7 +10142,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427484035492</v>
+        <v>1.63427472114563</v>
       </c>
       <c r="H337" t="n">
         <v>3259</v>
@@ -10200,7 +10200,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="n">
-        <v>1.63578021526337</v>
+        <v>1.63578033447266</v>
       </c>
       <c r="H339" t="n">
         <v>8432</v>
@@ -10229,7 +10229,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66664409637451</v>
+        <v>1.6666442155838</v>
       </c>
       <c r="H340" t="n">
         <v>4864</v>
@@ -10258,7 +10258,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288030147552</v>
+        <v>1.66288018226624</v>
       </c>
       <c r="H341" t="n">
         <v>8452</v>
@@ -10287,7 +10287,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6613746881485</v>
+        <v>1.66137480735779</v>
       </c>
       <c r="H342" t="n">
         <v>1480</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429895877838</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10403,7 +10403,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="n">
-        <v>1.91656529903412</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H346" t="n">
         <v>37449</v>
@@ -10461,7 +10461,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="n">
-        <v>2.01367354393005</v>
+        <v>2.01367330551147</v>
       </c>
       <c r="H348" t="n">
         <v>26110</v>
@@ -10490,7 +10490,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345175266266</v>
+        <v>1.95345139503479</v>
       </c>
       <c r="H349" t="n">
         <v>31940</v>
@@ -10519,7 +10519,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>1.9820568561554</v>
+        <v>1.98205697536469</v>
       </c>
       <c r="H350" t="n">
         <v>15329</v>
@@ -10548,7 +10548,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011558055878</v>
+        <v>1.93011546134949</v>
       </c>
       <c r="H351" t="n">
         <v>6514</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429895877838</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376002311707</v>
+        <v>1.83376038074493</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10635,7 +10635,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.90301537513733</v>
+        <v>1.90301549434662</v>
       </c>
       <c r="H354" t="n">
         <v>11029</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452122688293</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10693,7 +10693,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.91204905509949</v>
+        <v>1.9120489358902</v>
       </c>
       <c r="H356" t="n">
         <v>4977</v>
@@ -10780,7 +10780,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>1.91581249237061</v>
+        <v>1.91581273078918</v>
       </c>
       <c r="H359" t="n">
         <v>3397</v>
@@ -10838,7 +10838,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92860984802246</v>
+        <v>1.92860996723175</v>
       </c>
       <c r="H361" t="n">
         <v>5572</v>
@@ -10867,7 +10867,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.921835064888</v>
+        <v>1.92183482646942</v>
       </c>
       <c r="H362" t="n">
         <v>4932</v>
@@ -10896,7 +10896,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559897899628</v>
       </c>
       <c r="H363" t="n">
         <v>5423</v>
@@ -10954,7 +10954,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9263516664505</v>
+        <v>1.92635154724121</v>
       </c>
       <c r="H365" t="n">
         <v>10408</v>
@@ -10983,7 +10983,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>1.91656529903412</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H366" t="n">
         <v>5653</v>
@@ -11012,7 +11012,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376830101013</v>
+        <v>1.90376853942871</v>
       </c>
       <c r="H367" t="n">
         <v>5873</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11070,7 +11070,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559897899628</v>
       </c>
       <c r="H369" t="n">
         <v>1846</v>
@@ -11215,7 +11215,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054332256317</v>
+        <v>1.91054320335388</v>
       </c>
       <c r="H374" t="n">
         <v>414</v>
@@ -11273,7 +11273,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753221511841</v>
+        <v>1.90753209590912</v>
       </c>
       <c r="H376" t="n">
         <v>4843</v>
@@ -11302,7 +11302,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699339866638</v>
+        <v>1.89699327945709</v>
       </c>
       <c r="H377" t="n">
         <v>2654</v>
@@ -11360,7 +11360,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742114067078</v>
+        <v>1.87742125988007</v>
       </c>
       <c r="H379" t="n">
         <v>4228</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86010718345642</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052700519562</v>
+        <v>1.7705272436142</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11476,7 +11476,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826870441437</v>
+        <v>1.76826882362366</v>
       </c>
       <c r="H383" t="n">
         <v>2862</v>
@@ -11505,7 +11505,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.7946161031723</v>
+        <v>1.79461574554443</v>
       </c>
       <c r="H384" t="n">
         <v>2507</v>
@@ -11534,7 +11534,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741333961487</v>
+        <v>1.80741310119629</v>
       </c>
       <c r="H385" t="n">
         <v>3798</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11650,7 +11650,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>1.81042432785034</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H389" t="n">
         <v>98</v>
@@ -11737,7 +11737,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>1.81042432785034</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H392" t="n">
         <v>1413</v>
@@ -11795,7 +11795,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>1.83902966976166</v>
+        <v>1.83902955055237</v>
       </c>
       <c r="H394" t="n">
         <v>3433</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429895877838</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429895877838</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11940,7 +11940,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>1.8217157125473</v>
+        <v>1.82171607017517</v>
       </c>
       <c r="H399" t="n">
         <v>788</v>
@@ -11969,7 +11969,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806311130524</v>
+        <v>1.84806299209595</v>
       </c>
       <c r="H400" t="n">
         <v>1454</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.84655737876892</v>
+        <v>1.8465576171875</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752405643463</v>
+        <v>1.83752393722534</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774596691132</v>
+        <v>1.89774608612061</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12085,7 +12085,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280162334442</v>
+        <v>1.912801861763</v>
       </c>
       <c r="H404" t="n">
         <v>21296</v>
@@ -12172,7 +12172,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>1.97151827812195</v>
+        <v>1.97151815891266</v>
       </c>
       <c r="H407" t="n">
         <v>2092</v>
@@ -12201,7 +12201,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086838722229</v>
+        <v>1.930868268013</v>
       </c>
       <c r="H408" t="n">
         <v>4037</v>
@@ -12288,7 +12288,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>1.9210821390152</v>
+        <v>1.92108237743378</v>
       </c>
       <c r="H411" t="n">
         <v>931</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12346,7 +12346,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.8879599571228</v>
+        <v>1.88796007633209</v>
       </c>
       <c r="H413" t="n">
         <v>1727</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452122688293</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12491,7 +12491,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>1.89322948455811</v>
+        <v>1.89322936534882</v>
       </c>
       <c r="H418" t="n">
         <v>346</v>
@@ -12520,7 +12520,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="n">
-        <v>1.869140625</v>
+        <v>1.86914074420929</v>
       </c>
       <c r="H419" t="n">
         <v>2296</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.86010718345642</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12578,7 +12578,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860168933868</v>
       </c>
       <c r="H421" t="n">
         <v>1458</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.85634338855743</v>
+        <v>1.85634362697601</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12665,7 +12665,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>1.85709619522095</v>
+        <v>1.85709631443024</v>
       </c>
       <c r="H424" t="n">
         <v>891</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H426" t="n">
         <v>1972</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.85634338855743</v>
+        <v>1.85634362697601</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12781,7 +12781,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494908809662</v>
+        <v>1.88494896888733</v>
       </c>
       <c r="H428" t="n">
         <v>2953</v>
@@ -12810,7 +12810,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215173244476</v>
+        <v>1.87215161323547</v>
       </c>
       <c r="H429" t="n">
         <v>140</v>
@@ -12839,7 +12839,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860168933868</v>
       </c>
       <c r="H430" t="n">
         <v>1130</v>
@@ -12868,7 +12868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H431" t="n">
         <v>1257</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.86010718345642</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12926,7 +12926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H433" t="n">
         <v>2572</v>
@@ -13071,7 +13071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H438" t="n">
         <v>969</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365734577179</v>
+        <v>1.8736572265625</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.86537683010101</v>
+        <v>1.86537659168243</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.86010718345642</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13245,7 +13245,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204053878784</v>
+        <v>1.84204077720642</v>
       </c>
       <c r="H444" t="n">
         <v>1977</v>
@@ -13274,7 +13274,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731018543243</v>
+        <v>1.84731030464172</v>
       </c>
       <c r="H445" t="n">
         <v>2208</v>
@@ -13303,7 +13303,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279370307922</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="n">
         <v>1136</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397425174713</v>
+        <v>1.82397389411926</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569373607635</v>
+        <v>1.81569349765778</v>
       </c>
       <c r="H451" t="n">
         <v>4388</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117713451385</v>
+        <v>1.81117701530457</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13564,7 +13564,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.81418800354004</v>
+        <v>1.81418812274933</v>
       </c>
       <c r="H455" t="n">
         <v>1684</v>
@@ -13593,7 +13593,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526575565338</v>
+        <v>1.83526587486267</v>
       </c>
       <c r="H456" t="n">
         <v>3211</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13651,7 +13651,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83225464820862</v>
+        <v>1.83225476741791</v>
       </c>
       <c r="H458" t="n">
         <v>1829</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8224686384201</v>
+        <v>1.82246851921082</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13767,7 +13767,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526575565338</v>
+        <v>1.83526587486267</v>
       </c>
       <c r="H462" t="n">
         <v>3800</v>
@@ -13854,7 +13854,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689024448395</v>
+        <v>1.93689012527466</v>
       </c>
       <c r="H465" t="n">
         <v>5512</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731822490692</v>
+        <v>1.91731810569763</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13912,7 +13912,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979855537415</v>
+        <v>1.97979843616486</v>
       </c>
       <c r="H467" t="n">
         <v>24938</v>
@@ -13999,7 +13999,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="n">
-        <v>1.94667661190033</v>
+        <v>1.94667673110962</v>
       </c>
       <c r="H470" t="n">
         <v>11729</v>
@@ -14028,7 +14028,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="n">
-        <v>1.97076535224915</v>
+        <v>1.97076523303986</v>
       </c>
       <c r="H471" t="n">
         <v>6065</v>
@@ -14057,7 +14057,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.9677540063858</v>
+        <v>1.96775424480438</v>
       </c>
       <c r="H472" t="n">
         <v>6595</v>
@@ -14115,7 +14115,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="n">
-        <v>2.10325384140015</v>
+        <v>2.10325360298157</v>
       </c>
       <c r="H474" t="n">
         <v>27423</v>
@@ -14202,7 +14202,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732650279999</v>
+        <v>1.98732614517212</v>
       </c>
       <c r="H477" t="n">
         <v>8901</v>
@@ -14231,7 +14231,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937069416046</v>
+        <v>1.99937057495117</v>
       </c>
       <c r="H478" t="n">
         <v>3901</v>
@@ -14289,7 +14289,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="n">
-        <v>1.99033761024475</v>
+        <v>1.99033749103546</v>
       </c>
       <c r="H480" t="n">
         <v>2850</v>
@@ -14347,7 +14347,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861776828766</v>
+        <v>1.99861800670624</v>
       </c>
       <c r="H482" t="n">
         <v>7953</v>
@@ -14376,7 +14376,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549606323242</v>
+        <v>1.96549594402313</v>
       </c>
       <c r="H483" t="n">
         <v>212</v>
@@ -14695,7 +14695,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="n">
-        <v>2.08217620849609</v>
+        <v>2.08217597007751</v>
       </c>
       <c r="H494" t="n">
         <v>11805</v>
@@ -14811,7 +14811,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G498" t="n">
-        <v>2.09572601318359</v>
+        <v>2.09572625160217</v>
       </c>
       <c r="H498" t="n">
         <v>366</v>
@@ -14840,7 +14840,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>2.09045672416687</v>
+        <v>2.09045648574829</v>
       </c>
       <c r="H499" t="n">
         <v>6270</v>
@@ -14869,7 +14869,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.11153411865234</v>
+        <v>2.11153435707092</v>
       </c>
       <c r="H500" t="n">
         <v>1908</v>
@@ -14927,7 +14927,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>2.08669281005859</v>
+        <v>2.08669257164001</v>
       </c>
       <c r="H502" t="n">
         <v>2825</v>
@@ -14956,7 +14956,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="n">
-        <v>2.07013201713562</v>
+        <v>2.07013130187988</v>
       </c>
       <c r="H503" t="n">
         <v>1243</v>
@@ -15043,7 +15043,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>2.05883979797363</v>
+        <v>2.05884003639221</v>
       </c>
       <c r="H506" t="n">
         <v>1639</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615399360657</v>
+        <v>2.07615375518799</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15130,7 +15130,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="n">
-        <v>2.08368134498596</v>
+        <v>2.08368158340454</v>
       </c>
       <c r="H509" t="n">
         <v>2098</v>
@@ -15159,7 +15159,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.10400652885437</v>
+        <v>2.10400676727295</v>
       </c>
       <c r="H510" t="n">
         <v>2425</v>
@@ -15188,7 +15188,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08518743515015</v>
+        <v>2.08518719673157</v>
       </c>
       <c r="H511" t="n">
         <v>1601</v>
@@ -15217,7 +15217,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185930252075</v>
+        <v>2.13185954093933</v>
       </c>
       <c r="H512" t="n">
         <v>18197</v>
@@ -15246,7 +15246,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H513" t="n">
         <v>13248</v>
@@ -15333,7 +15333,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.16799235343933</v>
+        <v>2.16799259185791</v>
       </c>
       <c r="H516" t="n">
         <v>4995</v>
@@ -15449,7 +15449,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H520" t="n">
         <v>13063</v>
@@ -15652,7 +15652,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G527" t="n">
-        <v>2.32607531547546</v>
+        <v>2.32607507705688</v>
       </c>
       <c r="H527" t="n">
         <v>3389</v>
@@ -15681,7 +15681,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H528" t="n">
         <v>6112</v>
@@ -15739,7 +15739,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>2.2658531665802</v>
+        <v>2.26585340499878</v>
       </c>
       <c r="H530" t="n">
         <v>7075</v>
@@ -15768,7 +15768,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>2.28090858459473</v>
+        <v>2.28090882301331</v>
       </c>
       <c r="H531" t="n">
         <v>1414</v>
@@ -15797,7 +15797,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30349206924438</v>
+        <v>2.30349183082581</v>
       </c>
       <c r="H532" t="n">
         <v>3569</v>
@@ -15942,7 +15942,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H537" t="n">
         <v>6576</v>
@@ -15971,7 +15971,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810342788696</v>
+        <v>2.19810318946838</v>
       </c>
       <c r="H538" t="n">
         <v>2100</v>
@@ -16029,7 +16029,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H540" t="n">
         <v>5940</v>
@@ -16116,7 +16116,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057583808899</v>
       </c>
       <c r="H543" t="n">
         <v>161</v>
@@ -16203,7 +16203,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>2.43899154663086</v>
+        <v>2.43899130821228</v>
       </c>
       <c r="H546" t="n">
         <v>30842</v>
@@ -16290,7 +16290,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190777778625</v>
+        <v>2.55190801620483</v>
       </c>
       <c r="H549" t="n">
         <v>41764</v>
@@ -16319,7 +16319,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>2.5443799495697</v>
+        <v>2.54437971115112</v>
       </c>
       <c r="H550" t="n">
         <v>7288</v>
@@ -16348,7 +16348,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>2.61965751647949</v>
+        <v>2.61965727806091</v>
       </c>
       <c r="H551" t="n">
         <v>11195</v>
@@ -16406,7 +16406,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="n">
-        <v>2.49168539047241</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H553" t="n">
         <v>5398</v>
@@ -16435,7 +16435,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H554" t="n">
         <v>6023</v>
@@ -16522,7 +16522,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>2.43899154663086</v>
+        <v>2.43899130821228</v>
       </c>
       <c r="H557" t="n">
         <v>6923</v>
@@ -16580,7 +16580,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H559" t="n">
         <v>4701</v>
@@ -16609,7 +16609,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H560" t="n">
         <v>3851</v>
@@ -16696,7 +16696,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888023376465</v>
+        <v>2.40888047218323</v>
       </c>
       <c r="H563" t="n">
         <v>3721</v>
@@ -16812,7 +16812,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H567" t="n">
         <v>3892</v>
@@ -16841,7 +16841,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H568" t="n">
         <v>2129</v>
@@ -17131,7 +17131,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H578" t="n">
         <v>1479</v>
@@ -17189,7 +17189,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>2.49168539047241</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H580" t="n">
         <v>7145</v>
@@ -17247,7 +17247,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H582" t="n">
         <v>1436</v>
@@ -17276,7 +17276,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>2.49168539047241</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H583" t="n">
         <v>1838</v>
@@ -17334,7 +17334,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H585" t="n">
         <v>521</v>
@@ -17363,7 +17363,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910262107849</v>
       </c>
       <c r="H586" t="n">
         <v>3037</v>
@@ -17392,7 +17392,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50674104690552</v>
+        <v>2.5067412853241</v>
       </c>
       <c r="H587" t="n">
         <v>11895</v>
@@ -17421,7 +17421,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>2.52932476997375</v>
+        <v>2.5293242931366</v>
       </c>
       <c r="H588" t="n">
         <v>10382</v>
@@ -17479,7 +17479,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H590" t="n">
         <v>1457</v>
@@ -17508,7 +17508,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H591" t="n">
         <v>1072</v>
@@ -17537,7 +17537,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363485336304</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H592" t="n">
         <v>1427</v>
@@ -17624,7 +17624,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>2.51380729675293</v>
+        <v>2.51380753517151</v>
       </c>
       <c r="H595" t="n">
         <v>4077</v>
@@ -17653,7 +17653,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G596" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H596" t="n">
         <v>14950</v>
@@ -17682,7 +17682,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363485336304</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H597" t="n">
         <v>5094</v>
@@ -17769,7 +17769,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484152793884</v>
+        <v>2.544842004776</v>
       </c>
       <c r="H600" t="n">
         <v>1367</v>
@@ -17856,7 +17856,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>2.4982898235321</v>
+        <v>2.49829006195068</v>
       </c>
       <c r="H603" t="n">
         <v>729</v>
@@ -17885,7 +17885,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>2.4982898235321</v>
+        <v>2.49829006195068</v>
       </c>
       <c r="H604" t="n">
         <v>238</v>
@@ -18030,7 +18030,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H609" t="n">
         <v>3124</v>
@@ -18059,7 +18059,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>2.28104710578918</v>
+        <v>2.28104734420776</v>
       </c>
       <c r="H610" t="n">
         <v>2910</v>
@@ -18088,7 +18088,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="n">
-        <v>2.28104710578918</v>
+        <v>2.28104734420776</v>
       </c>
       <c r="H611" t="n">
         <v>3246</v>
@@ -18117,7 +18117,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H612" t="n">
         <v>1071</v>
@@ -18146,7 +18146,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H613" t="n">
         <v>5750</v>
@@ -18175,7 +18175,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H614" t="n">
         <v>7400</v>
@@ -18233,7 +18233,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H616" t="n">
         <v>2444</v>
@@ -18262,7 +18262,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H617" t="n">
         <v>4378</v>
@@ -18320,7 +18320,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H619" t="n">
         <v>2215</v>
@@ -18349,7 +18349,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H620" t="n">
         <v>2933</v>
@@ -18378,7 +18378,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H621" t="n">
         <v>1043</v>
@@ -18407,7 +18407,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>2.11811494827271</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H622" t="n">
         <v>1065</v>
@@ -18436,7 +18436,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H623" t="n">
         <v>4311</v>
@@ -18465,7 +18465,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H624" t="n">
         <v>215</v>
@@ -18494,7 +18494,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H625" t="n">
         <v>1193</v>
@@ -18523,7 +18523,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>2.28104710578918</v>
+        <v>2.28104734420776</v>
       </c>
       <c r="H626" t="n">
         <v>5404</v>
@@ -18552,7 +18552,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="n">
-        <v>2.25001239776611</v>
+        <v>2.25001263618469</v>
       </c>
       <c r="H627" t="n">
         <v>1402</v>
@@ -18581,7 +18581,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H628" t="n">
         <v>125</v>
@@ -18610,7 +18610,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H629" t="n">
         <v>1246</v>
@@ -18639,7 +18639,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H630" t="n">
         <v>1237</v>
@@ -18697,7 +18697,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H632" t="n">
         <v>2259</v>
@@ -18726,7 +18726,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H633" t="n">
         <v>3975</v>
@@ -18784,7 +18784,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.13363289833069</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H635" t="n">
         <v>2701</v>
@@ -18813,7 +18813,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H636" t="n">
         <v>1273</v>
@@ -18871,7 +18871,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H638" t="n">
         <v>413</v>
@@ -18900,7 +18900,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.11811494827271</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H639" t="n">
         <v>152</v>
@@ -18929,7 +18929,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.11811494827271</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H642" t="n">
         <v>1013</v>
@@ -19045,7 +19045,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H644" t="n">
         <v>1452</v>
@@ -19219,7 +19219,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.16466736793518</v>
+        <v>2.16466689109802</v>
       </c>
       <c r="H650" t="n">
         <v>2832</v>
@@ -19335,7 +19335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656481742859</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H654" t="n">
         <v>4303</v>
@@ -19364,7 +19364,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H655" t="n">
         <v>3734</v>
@@ -19393,7 +19393,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H656" t="n">
         <v>2106</v>
@@ -19451,7 +19451,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H658" t="n">
         <v>1560</v>
@@ -19480,7 +19480,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23449516296387</v>
+        <v>2.23449492454529</v>
       </c>
       <c r="H659" t="n">
         <v>4624</v>
@@ -19509,7 +19509,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H660" t="n">
         <v>1057</v>
@@ -19596,7 +19596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H663" t="n">
         <v>44</v>
@@ -19625,7 +19625,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="n">
-        <v>2.13363289833069</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H664" t="n">
         <v>190</v>
@@ -19770,7 +19770,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H669" t="n">
         <v>1070</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H671" t="n">
         <v>3968</v>
@@ -19857,7 +19857,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H672" t="n">
         <v>8845</v>
@@ -19915,7 +19915,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H674" t="n">
         <v>3748</v>
@@ -19944,7 +19944,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>1.9707008600235</v>
+        <v>1.97070062160492</v>
       </c>
       <c r="H675" t="n">
         <v>420</v>
@@ -20031,7 +20031,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>1.88535523414612</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H678" t="n">
         <v>5198</v>
@@ -20060,7 +20060,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H679" t="n">
         <v>3984</v>
@@ -20089,7 +20089,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432052612305</v>
+        <v>1.85432088375092</v>
       </c>
       <c r="H680" t="n">
         <v>1873</v>
@@ -20118,7 +20118,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983799934387</v>
+        <v>1.86983788013458</v>
       </c>
       <c r="H681" t="n">
         <v>254</v>
@@ -20147,7 +20147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225122928619</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H682" t="n">
         <v>1859</v>
@@ -20176,7 +20176,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880364894867</v>
       </c>
       <c r="H683" t="n">
         <v>3849</v>
@@ -20205,7 +20205,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H684" t="n">
         <v>5886</v>
@@ -20263,7 +20263,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H686" t="n">
         <v>8550</v>
@@ -20292,7 +20292,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H687" t="n">
         <v>17503</v>
@@ -20321,7 +20321,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H688" t="n">
         <v>6201</v>
@@ -20437,7 +20437,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H692" t="n">
         <v>1912</v>
@@ -20466,7 +20466,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H693" t="n">
         <v>2480</v>
@@ -20495,7 +20495,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H694" t="n">
         <v>80</v>
@@ -20524,7 +20524,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H695" t="n">
         <v>2142</v>
@@ -20553,7 +20553,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H696" t="n">
         <v>2090</v>
@@ -20582,7 +20582,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H697" t="n">
         <v>2474</v>
@@ -20611,7 +20611,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H698" t="n">
         <v>1482</v>
@@ -20640,7 +20640,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H699" t="n">
         <v>4797</v>
@@ -20669,7 +20669,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H700" t="n">
         <v>2148</v>
@@ -20698,7 +20698,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H701" t="n">
         <v>7483</v>
@@ -20727,7 +20727,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>2.0094940662384</v>
+        <v>2.00949382781982</v>
       </c>
       <c r="H702" t="n">
         <v>581</v>
@@ -20756,7 +20756,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H703" t="n">
         <v>3410</v>
@@ -20785,7 +20785,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H704" t="n">
         <v>1</v>
@@ -20814,7 +20814,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H705" t="n">
         <v>2758</v>
@@ -20843,7 +20843,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H706" t="n">
         <v>1168</v>
@@ -20901,7 +20901,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H708" t="n">
         <v>6007</v>
@@ -20930,7 +20930,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H709" t="n">
         <v>2556</v>
@@ -21017,7 +21017,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880364894867</v>
       </c>
       <c r="H712" t="n">
         <v>2116</v>
@@ -21046,7 +21046,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>1.8465621471405</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H713" t="n">
         <v>609</v>
@@ -21075,7 +21075,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H714" t="n">
         <v>2033</v>
@@ -21133,7 +21133,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>1.8465621471405</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H716" t="n">
         <v>48</v>
@@ -21162,7 +21162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225122928619</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H717" t="n">
         <v>747</v>
@@ -21191,7 +21191,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776870250702</v>
+        <v>1.80776858329773</v>
       </c>
       <c r="H718" t="n">
         <v>821</v>
@@ -21220,7 +21220,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.753457903862</v>
+        <v>1.75345814228058</v>
       </c>
       <c r="H719" t="n">
         <v>3685</v>
@@ -21278,7 +21278,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569952487946</v>
+        <v>1.74569928646088</v>
       </c>
       <c r="H721" t="n">
         <v>2119</v>
@@ -21307,7 +21307,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328617572784</v>
       </c>
       <c r="H722" t="n">
         <v>1535</v>
@@ -21336,7 +21336,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328617572784</v>
       </c>
       <c r="H723" t="n">
         <v>8398</v>
@@ -21365,7 +21365,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H724" t="n">
         <v>2115</v>
@@ -21394,7 +21394,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311385154724</v>
+        <v>1.89311397075653</v>
       </c>
       <c r="H726" t="n">
         <v>6832</v>
@@ -21452,7 +21452,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.88535523414612</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H727" t="n">
         <v>1177</v>
@@ -21481,7 +21481,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H728" t="n">
         <v>961</v>
@@ -21539,7 +21539,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91638994216919</v>
+        <v>1.91639006137848</v>
       </c>
       <c r="H730" t="n">
         <v>2333</v>
@@ -21568,7 +21568,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H731" t="n">
         <v>15291</v>
@@ -21626,7 +21626,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="n">
-        <v>2.13363289833069</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H733" t="n">
         <v>5119</v>
@@ -21684,7 +21684,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H735" t="n">
         <v>3881</v>
@@ -21742,7 +21742,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H737" t="n">
         <v>2727</v>
@@ -21800,7 +21800,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H739" t="n">
         <v>2280</v>
@@ -21829,7 +21829,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H740" t="n">
         <v>526</v>
@@ -21858,7 +21858,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H741" t="n">
         <v>1711</v>
@@ -21916,7 +21916,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.16466736793518</v>
+        <v>2.16466689109802</v>
       </c>
       <c r="H743" t="n">
         <v>2565</v>
@@ -21945,7 +21945,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H744" t="n">
         <v>6975</v>
@@ -21974,7 +21974,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13363289833069</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H745" t="n">
         <v>2434</v>
@@ -22032,7 +22032,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>2.11811494827271</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H747" t="n">
         <v>149</v>
@@ -22061,7 +22061,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="n">
-        <v>2.13363289833069</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H748" t="n">
         <v>1576</v>
@@ -22177,7 +22177,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397647380829</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H752" t="n">
         <v>6924</v>
@@ -22322,7 +22322,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="n">
-        <v>2.05604577064514</v>
+        <v>2.05604600906372</v>
       </c>
       <c r="H757" t="n">
         <v>2911</v>
@@ -22351,7 +22351,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H758" t="n">
         <v>645</v>
@@ -22409,7 +22409,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H760" t="n">
         <v>1417</v>
@@ -22438,7 +22438,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H761" t="n">
         <v>5897</v>
@@ -22496,7 +22496,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H763" t="n">
         <v>154</v>
@@ -22554,7 +22554,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="n">
-        <v>2.05604577064514</v>
+        <v>2.05604600906372</v>
       </c>
       <c r="H765" t="n">
         <v>1593</v>
@@ -22583,7 +22583,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>2.08708071708679</v>
+        <v>2.08708095550537</v>
       </c>
       <c r="H766" t="n">
         <v>55</v>
@@ -22641,7 +22641,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H768" t="n">
         <v>3478</v>
@@ -22757,7 +22757,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H772" t="n">
         <v>443</v>
@@ -22786,7 +22786,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H773" t="n">
         <v>702</v>
@@ -22844,7 +22844,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="n">
-        <v>2.1724259853363</v>
+        <v>2.17242574691772</v>
       </c>
       <c r="H775" t="n">
         <v>703</v>
@@ -22902,7 +22902,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H777" t="n">
         <v>329</v>
@@ -22931,7 +22931,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H778" t="n">
         <v>160</v>
@@ -22960,7 +22960,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690898895264</v>
       </c>
       <c r="H779" t="n">
         <v>3252</v>
@@ -23018,7 +23018,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H781" t="n">
         <v>1441</v>
@@ -23047,7 +23047,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H782" t="n">
         <v>15901</v>
@@ -23105,7 +23105,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>2.28104710578918</v>
+        <v>2.28104734420776</v>
       </c>
       <c r="H784" t="n">
         <v>793</v>
@@ -23134,7 +23134,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26552987098694</v>
+        <v>2.26553010940552</v>
       </c>
       <c r="H785" t="n">
         <v>674</v>
@@ -23163,7 +23163,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H786" t="n">
         <v>7919</v>
@@ -23308,7 +23308,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656481742859</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H791" t="n">
         <v>238</v>
@@ -23366,7 +23366,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656481742859</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H793" t="n">
         <v>206</v>
@@ -23453,7 +23453,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.3353579044342</v>
+        <v>2.33535814285278</v>
       </c>
       <c r="H796" t="n">
         <v>1137</v>
@@ -23511,7 +23511,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H798" t="n">
         <v>381</v>
@@ -23540,7 +23540,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H799" t="n">
         <v>553</v>
@@ -23598,7 +23598,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H801" t="n">
         <v>693</v>
@@ -23714,7 +23714,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>2.3819100856781</v>
+        <v>2.38190984725952</v>
       </c>
       <c r="H805" t="n">
         <v>1473</v>
@@ -23743,7 +23743,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H806" t="n">
         <v>3492</v>
@@ -23772,7 +23772,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>2.39742732048035</v>
+        <v>2.39742708206177</v>
       </c>
       <c r="H807" t="n">
         <v>339</v>
@@ -23917,7 +23917,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41294455528259</v>
+        <v>2.41294431686401</v>
       </c>
       <c r="H812" t="n">
         <v>1173</v>
@@ -23946,7 +23946,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H813" t="n">
         <v>222</v>
@@ -23975,7 +23975,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>2.39742732048035</v>
+        <v>2.39742708206177</v>
       </c>
       <c r="H814" t="n">
         <v>625</v>
@@ -24033,7 +24033,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H816" t="n">
         <v>378</v>
@@ -24091,7 +24091,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>2.39742732048035</v>
+        <v>2.39742708206177</v>
       </c>
       <c r="H818" t="n">
         <v>182</v>
@@ -24149,7 +24149,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H820" t="n">
         <v>2462</v>
@@ -24294,7 +24294,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H825" t="n">
         <v>186</v>
@@ -24323,7 +24323,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H826" t="n">
         <v>1041</v>
@@ -24352,7 +24352,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966822624207</v>
       </c>
       <c r="H827" t="n">
         <v>622</v>
@@ -24381,7 +24381,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.39742732048035</v>
+        <v>2.39742708206177</v>
       </c>
       <c r="H828" t="n">
         <v>2565</v>
@@ -24410,7 +24410,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H829" t="n">
         <v>12604</v>
@@ -24439,7 +24439,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H830" t="n">
         <v>1806</v>
@@ -24468,7 +24468,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H831" t="n">
         <v>6065</v>
@@ -24497,7 +24497,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H832" t="n">
         <v>6312</v>
@@ -24526,7 +24526,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H833" t="n">
         <v>10097</v>
@@ -24555,7 +24555,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H834" t="n">
         <v>2763</v>
@@ -24584,7 +24584,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>2.4982898235321</v>
+        <v>2.49829006195068</v>
       </c>
       <c r="H835" t="n">
         <v>9123</v>
@@ -24613,7 +24613,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5526008605957</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H836" t="n">
         <v>21589</v>
@@ -24642,7 +24642,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H837" t="n">
         <v>17949</v>
@@ -24729,7 +24729,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H840" t="n">
         <v>2792</v>
@@ -24816,7 +24816,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H843" t="n">
         <v>3263</v>
@@ -24845,7 +24845,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H844" t="n">
         <v>715</v>
@@ -24874,7 +24874,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H845" t="n">
         <v>800</v>
@@ -24903,7 +24903,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H846" t="n">
         <v>241</v>
@@ -24961,7 +24961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H848" t="n">
         <v>2347</v>
@@ -25048,7 +25048,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H851" t="n">
         <v>2444</v>
@@ -25106,7 +25106,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H853" t="n">
         <v>3476</v>
@@ -25135,7 +25135,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>2.2274284362793</v>
+        <v>2.22742867469788</v>
       </c>
       <c r="H854" t="n">
         <v>3272</v>
@@ -25164,7 +25164,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H855" t="n">
         <v>1424</v>
@@ -25367,7 +25367,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H862" t="n">
         <v>669</v>
@@ -25483,7 +25483,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H866" t="n">
         <v>6419</v>
@@ -25715,7 +25715,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H874" t="n">
         <v>1167</v>
@@ -25744,7 +25744,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H875" t="n">
         <v>3142</v>
@@ -25802,7 +25802,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H877" t="n">
         <v>834</v>
@@ -25831,7 +25831,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H878" t="n">
         <v>1616</v>
@@ -25860,7 +25860,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H879" t="n">
         <v>4136</v>
@@ -25889,7 +25889,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H880" t="n">
         <v>3525</v>
@@ -25918,7 +25918,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H881" t="n">
         <v>2373</v>
@@ -25947,7 +25947,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H882" t="n">
         <v>5668</v>
@@ -25976,7 +25976,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H883" t="n">
         <v>3351</v>
@@ -26005,7 +26005,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H884" t="n">
         <v>1520</v>
@@ -26034,7 +26034,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H885" t="n">
         <v>538</v>
@@ -26063,7 +26063,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H886" t="n">
         <v>7315</v>
@@ -26092,7 +26092,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H887" t="n">
         <v>800</v>
@@ -26150,7 +26150,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H889" t="n">
         <v>1830</v>
@@ -26179,7 +26179,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H890" t="n">
         <v>1360</v>
@@ -26266,7 +26266,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H893" t="n">
         <v>110</v>
@@ -26324,7 +26324,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H895" t="n">
         <v>1271</v>
@@ -26498,7 +26498,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H901" t="n">
         <v>609</v>
@@ -26556,7 +26556,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H903" t="n">
         <v>350</v>
@@ -26585,7 +26585,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H904" t="n">
         <v>217</v>
@@ -26614,7 +26614,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H905" t="n">
         <v>1973</v>
@@ -26701,7 +26701,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H908" t="n">
         <v>2849</v>
@@ -26759,7 +26759,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H910" t="n">
         <v>1929</v>
@@ -26817,7 +26817,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H912" t="n">
         <v>600</v>
@@ -26933,7 +26933,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H916" t="n">
         <v>326</v>
@@ -27078,7 +27078,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H921" t="n">
         <v>26</v>
@@ -27165,7 +27165,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H924" t="n">
         <v>715</v>
@@ -27368,7 +27368,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H931" t="n">
         <v>382</v>
@@ -27600,7 +27600,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H939" t="n">
         <v>2176</v>
@@ -27629,7 +27629,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H940" t="n">
         <v>650</v>
@@ -27832,7 +27832,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H947" t="n">
         <v>252</v>
@@ -27861,7 +27861,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H948" t="n">
         <v>60</v>
@@ -28006,7 +28006,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H953" t="n">
         <v>2198</v>
@@ -28789,7 +28789,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H980" t="n">
         <v>239</v>
@@ -28818,7 +28818,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H981" t="n">
         <v>487</v>
@@ -28847,7 +28847,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H982" t="n">
         <v>1427</v>
@@ -28905,7 +28905,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H984" t="n">
         <v>3320</v>
@@ -28934,7 +28934,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H985" t="n">
         <v>1181</v>
@@ -28992,7 +28992,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H987" t="n">
         <v>13081</v>
@@ -29050,7 +29050,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H989" t="n">
         <v>3240</v>
@@ -29108,7 +29108,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H991" t="n">
         <v>1405</v>
@@ -29137,7 +29137,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H992" t="n">
         <v>1412</v>
@@ -29166,7 +29166,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H993" t="n">
         <v>1096</v>
@@ -29195,7 +29195,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072950363159</v>
       </c>
       <c r="H994" t="n">
         <v>3106</v>
@@ -29224,7 +29224,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H995" t="n">
         <v>1008</v>
@@ -29282,7 +29282,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H997" t="n">
         <v>2043</v>
@@ -29311,7 +29311,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H998" t="n">
         <v>2368</v>
@@ -29340,7 +29340,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H999" t="n">
         <v>2190</v>
@@ -29369,7 +29369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1000" t="n">
         <v>2768</v>
@@ -29398,7 +29398,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1001" t="n">
         <v>6864</v>
@@ -29427,7 +29427,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1002" t="n">
         <v>900</v>
@@ -29456,7 +29456,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1003" t="n">
         <v>101</v>
@@ -29485,7 +29485,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1004" t="n">
         <v>50</v>
@@ -29514,7 +29514,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1005" t="n">
         <v>605</v>
@@ -29572,7 +29572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382494926453</v>
       </c>
       <c r="H1007" t="n">
         <v>1267</v>
@@ -29659,7 +29659,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1010" t="n">
         <v>24</v>
@@ -29688,7 +29688,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1011" t="n">
         <v>1121</v>
@@ -29717,7 +29717,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1012" t="n">
         <v>21303</v>
@@ -29746,7 +29746,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1013" t="n">
         <v>1283</v>
@@ -29775,7 +29775,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1014" t="n">
         <v>2374</v>
@@ -29833,7 +29833,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1016" t="n">
         <v>257</v>
@@ -29891,7 +29891,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H1018" t="n">
         <v>5441</v>
@@ -29949,7 +29949,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1020" t="n">
         <v>2880</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1021" t="n">
         <v>1241</v>
@@ -30007,7 +30007,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1022" t="n">
         <v>825</v>
@@ -30036,7 +30036,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1023" t="n">
         <v>1133</v>
@@ -30152,7 +30152,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066072463989</v>
       </c>
       <c r="H1027" t="n">
         <v>4984</v>
@@ -30384,7 +30384,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H1035" t="n">
         <v>4055</v>
@@ -30442,7 +30442,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936761856079</v>
       </c>
       <c r="H1037" t="n">
         <v>281</v>
@@ -30558,7 +30558,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1041" t="n">
         <v>2270</v>
@@ -30587,7 +30587,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.30872130393982</v>
+        <v>2.30872178077698</v>
       </c>
       <c r="H1042" t="n">
         <v>304</v>
@@ -30703,7 +30703,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1046" t="n">
         <v>202</v>
@@ -30790,7 +30790,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1049" t="n">
         <v>199</v>
@@ -30877,7 +30877,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1052" t="n">
         <v>1908</v>
@@ -31138,7 +31138,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.04858374595642</v>
+        <v>2.048583984375</v>
       </c>
       <c r="H1061" t="n">
         <v>1381</v>
@@ -31167,7 +31167,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412713050842</v>
+        <v>1.89412701129913</v>
       </c>
       <c r="H1062" t="n">
         <v>1691</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1064" t="n">
         <v>931</v>
@@ -31254,7 +31254,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1065" t="n">
         <v>2252</v>
@@ -31283,7 +31283,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.4714035987854</v>
+        <v>1.47140347957611</v>
       </c>
       <c r="H1066" t="n">
         <v>4041</v>
@@ -31312,7 +31312,7 @@
         <v>18.5</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1067" t="n">
         <v>1768</v>
@@ -31370,7 +31370,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1069" t="n">
         <v>3426</v>
@@ -31428,7 +31428,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.5486319065094</v>
+        <v>1.54863178730011</v>
       </c>
       <c r="H1071" t="n">
         <v>1513</v>
@@ -31457,7 +31457,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1072" t="n">
         <v>3746</v>
@@ -31515,7 +31515,7 @@
         <v>19.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.58521366119385</v>
+        <v>1.58521378040314</v>
       </c>
       <c r="H1074" t="n">
         <v>4651</v>
@@ -31544,7 +31544,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.60147225856781</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1075" t="n">
         <v>5340</v>
@@ -31573,7 +31573,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1076" t="n">
         <v>10</v>
@@ -31602,7 +31602,7 @@
         <v>19.5</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.58521366119385</v>
+        <v>1.58521378040314</v>
       </c>
       <c r="H1077" t="n">
         <v>744</v>
@@ -31631,7 +31631,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.5730197429657</v>
+        <v>1.57301986217499</v>
       </c>
       <c r="H1078" t="n">
         <v>1319</v>
@@ -31718,7 +31718,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1081" t="n">
         <v>3195</v>
@@ -31747,7 +31747,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1082" t="n">
         <v>830</v>
@@ -31776,7 +31776,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.60147225856781</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1083" t="n">
         <v>2497</v>
@@ -31834,7 +31834,7 @@
         <v>19.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.58521366119385</v>
+        <v>1.58521378040314</v>
       </c>
       <c r="H1085" t="n">
         <v>5919</v>
@@ -31863,7 +31863,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.6339898109436</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1086" t="n">
         <v>6045</v>
@@ -32008,7 +32008,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.62179565429688</v>
+        <v>1.62179553508759</v>
       </c>
       <c r="H1091" t="n">
         <v>4180</v>
@@ -32037,7 +32037,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.6339898109436</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1092" t="n">
         <v>531</v>
@@ -32066,7 +32066,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.58927834033966</v>
+        <v>1.58927822113037</v>
       </c>
       <c r="H1093" t="n">
         <v>1175</v>
@@ -32124,7 +32124,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60147225856781</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1095" t="n">
         <v>2072</v>
@@ -32153,7 +32153,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.6339898109436</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1096" t="n">
         <v>1044</v>
@@ -32182,7 +32182,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1097" t="n">
         <v>2013</v>
@@ -32240,7 +32240,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1099" t="n">
         <v>3686</v>
@@ -32269,7 +32269,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1100" t="n">
         <v>668</v>
@@ -32298,7 +32298,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1101" t="n">
         <v>390</v>
@@ -32385,7 +32385,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1104" t="n">
         <v>934</v>
@@ -32414,7 +32414,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1105" t="n">
         <v>1244</v>
@@ -32443,7 +32443,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1106" t="n">
         <v>660</v>
@@ -32472,7 +32472,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1107" t="n">
         <v>749</v>
@@ -32501,7 +32501,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1108" t="n">
         <v>2147</v>
@@ -32530,7 +32530,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1109" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1110" t="n">
         <v>1215</v>
@@ -32617,7 +32617,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1112" t="n">
         <v>194</v>
@@ -32646,7 +32646,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1113" t="n">
         <v>865</v>
@@ -32704,7 +32704,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1115" t="n">
         <v>2809</v>
@@ -32733,7 +32733,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1116" t="n">
         <v>2022</v>
@@ -32791,7 +32791,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1118" t="n">
         <v>546</v>
@@ -32849,7 +32849,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1120" t="n">
         <v>2501</v>
@@ -32878,7 +32878,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1121" t="n">
         <v>1115</v>
@@ -32965,7 +32965,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1124" t="n">
         <v>4336</v>
@@ -32994,7 +32994,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096326351166</v>
       </c>
       <c r="H1125" t="n">
         <v>10904</v>
@@ -33081,7 +33081,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1128" t="n">
         <v>2449</v>
@@ -33110,7 +33110,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1129" t="n">
         <v>1066</v>
@@ -33139,7 +33139,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1130" t="n">
         <v>474</v>
@@ -33226,7 +33226,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1133" t="n">
         <v>100</v>
@@ -33255,7 +33255,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096326351166</v>
       </c>
       <c r="H1134" t="n">
         <v>1491</v>
@@ -33284,7 +33284,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1135" t="n">
         <v>289</v>
@@ -33342,7 +33342,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.79657530784607</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1137" t="n">
         <v>525</v>
@@ -33371,7 +33371,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1138" t="n">
         <v>536</v>
@@ -33400,7 +33400,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1139" t="n">
         <v>2191</v>
@@ -33429,7 +33429,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1140" t="n">
         <v>87</v>
@@ -33458,7 +33458,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1141" t="n">
         <v>161</v>
@@ -33487,7 +33487,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1142" t="n">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1143" t="n">
         <v>1762</v>
@@ -33545,7 +33545,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1144" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1146" t="n">
         <v>30</v>
@@ -33632,7 +33632,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.79657530784607</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1147" t="n">
         <v>103</v>
@@ -33661,7 +33661,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1148" t="n">
         <v>1910</v>
@@ -33690,7 +33690,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1149" t="n">
         <v>143</v>
@@ -33748,7 +33748,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1151" t="n">
         <v>3317</v>
@@ -33777,7 +33777,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1152" t="n">
         <v>7260</v>
@@ -33806,7 +33806,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1153" t="n">
         <v>4915</v>
@@ -33835,7 +33835,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1154" t="n">
         <v>50</v>
@@ -33893,7 +33893,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1156" t="n">
         <v>1638</v>
@@ -33922,7 +33922,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1157" t="n">
         <v>452</v>
@@ -33951,7 +33951,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1158" t="n">
         <v>1478</v>
@@ -34009,7 +34009,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1160" t="n">
         <v>405</v>
@@ -34038,7 +34038,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1161" t="n">
         <v>200</v>
@@ -34067,7 +34067,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1162" t="n">
         <v>185</v>
@@ -34096,7 +34096,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1163" t="n">
         <v>392</v>
@@ -34125,7 +34125,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1164" t="n">
         <v>12</v>
@@ -34183,7 +34183,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1166" t="n">
         <v>1391</v>
@@ -34241,7 +34241,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1168" t="n">
         <v>182</v>
@@ -34270,7 +34270,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1169" t="n">
         <v>540</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1171" t="n">
         <v>330</v>
@@ -34386,7 +34386,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1173" t="n">
         <v>886</v>
@@ -34415,7 +34415,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1174" t="n">
         <v>16</v>
@@ -34444,7 +34444,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1175" t="n">
         <v>176</v>
@@ -34473,7 +34473,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1176" t="n">
         <v>992</v>
@@ -34502,7 +34502,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1177" t="n">
         <v>402</v>
@@ -34531,7 +34531,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1178" t="n">
         <v>250</v>
@@ -34560,7 +34560,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.78031694889069</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1179" t="n">
         <v>520</v>
@@ -34618,7 +34618,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1181" t="n">
         <v>15</v>
@@ -34676,7 +34676,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1183" t="n">
         <v>139</v>
@@ -34821,7 +34821,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1188" t="n">
         <v>3060</v>
@@ -34908,7 +34908,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1191" t="n">
         <v>1130</v>
@@ -34937,7 +34937,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1192" t="n">
         <v>3300</v>
@@ -34995,7 +34995,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.6339898109436</v>
+        <v>1.63398957252502</v>
       </c>
       <c r="H1194" t="n">
         <v>630</v>
@@ -35024,7 +35024,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.60147225856781</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1195" t="n">
         <v>486</v>
@@ -35082,7 +35082,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1197" t="n">
         <v>6595</v>
@@ -35169,7 +35169,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1200" t="n">
         <v>1704</v>
@@ -35343,7 +35343,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1206" t="n">
         <v>183</v>
@@ -35401,7 +35401,7 @@
         <v>18.5</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1208" t="n">
         <v>3005</v>
@@ -35459,7 +35459,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1210" t="n">
         <v>1502</v>
@@ -35517,7 +35517,7 @@
         <v>18.5</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1212" t="n">
         <v>7885</v>
@@ -35546,7 +35546,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1213" t="n">
         <v>1613</v>
@@ -35575,7 +35575,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1214" t="n">
         <v>540</v>
@@ -35604,7 +35604,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359727859497</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1215" t="n">
         <v>1216</v>
@@ -35662,7 +35662,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262756824493</v>
       </c>
       <c r="H1217" t="n">
         <v>5136</v>
@@ -35778,7 +35778,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262756824493</v>
       </c>
       <c r="H1221" t="n">
         <v>283</v>
@@ -35836,7 +35836,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.36572241783142</v>
+        <v>1.36572253704071</v>
       </c>
       <c r="H1223" t="n">
         <v>2886</v>
@@ -35923,7 +35923,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.35759341716766</v>
+        <v>1.35759317874908</v>
       </c>
       <c r="H1226" t="n">
         <v>100</v>
@@ -36010,7 +36010,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255878925323</v>
+        <v>1.29255890846252</v>
       </c>
       <c r="H1229" t="n">
         <v>989</v>
@@ -36068,7 +36068,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.3372700214386</v>
+        <v>1.33727014064789</v>
       </c>
       <c r="H1231" t="n">
         <v>1538</v>
@@ -36126,7 +36126,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946405887604</v>
+        <v>1.34946393966675</v>
       </c>
       <c r="H1233" t="n">
         <v>466</v>
@@ -36300,7 +36300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.38604581356049</v>
+        <v>1.3860456943512</v>
       </c>
       <c r="H1239" t="n">
         <v>2206</v>
@@ -36358,7 +36358,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39011061191559</v>
+        <v>1.3901104927063</v>
       </c>
       <c r="H1241" t="n">
         <v>2655</v>
@@ -36474,7 +36474,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.42262768745422</v>
+        <v>1.42262756824493</v>
       </c>
       <c r="H1245" t="n">
         <v>4463</v>
@@ -36561,7 +36561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1248" t="n">
         <v>2886</v>
@@ -36590,7 +36590,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1249" t="n">
         <v>996</v>
@@ -36619,7 +36619,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1250" t="n">
         <v>4696</v>
@@ -36677,7 +36677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1252" t="n">
         <v>3478</v>
@@ -36735,7 +36735,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1254" t="n">
         <v>12588</v>
@@ -36793,7 +36793,7 @@
         <v>18.5</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1256" t="n">
         <v>3388</v>
@@ -36822,7 +36822,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.4714035987854</v>
+        <v>1.47140347957611</v>
       </c>
       <c r="H1257" t="n">
         <v>8111</v>
@@ -36851,7 +36851,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359727859497</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1258" t="n">
         <v>2500</v>
@@ -36880,7 +36880,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1259" t="n">
         <v>4474</v>
@@ -36909,7 +36909,7 @@
         <v>18.5</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1260" t="n">
         <v>4292</v>
@@ -36938,7 +36938,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1261" t="n">
         <v>4222</v>
@@ -36996,7 +36996,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1263" t="n">
         <v>3075</v>
@@ -37025,7 +37025,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1264" t="n">
         <v>5320</v>
@@ -37054,7 +37054,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.52424383163452</v>
+        <v>1.52424395084381</v>
       </c>
       <c r="H1265" t="n">
         <v>1723</v>
@@ -37083,7 +37083,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1266" t="n">
         <v>600</v>
@@ -37112,7 +37112,7 @@
         <v>18.5</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1267" t="n">
         <v>225</v>
@@ -37199,7 +37199,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1270" t="n">
         <v>19327</v>
@@ -37257,7 +37257,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1272" t="n">
         <v>822</v>
@@ -37286,7 +37286,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1273" t="n">
         <v>2790</v>
@@ -37315,7 +37315,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1274" t="n">
         <v>23428</v>
@@ -37344,7 +37344,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1275" t="n">
         <v>5078</v>
@@ -37373,7 +37373,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1276" t="n">
         <v>3233</v>
@@ -37402,7 +37402,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.5526967048645</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1277" t="n">
         <v>639</v>
@@ -37431,7 +37431,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1278" t="n">
         <v>607</v>
@@ -37460,7 +37460,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1279" t="n">
         <v>753</v>
@@ -37518,7 +37518,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643798828125</v>
       </c>
       <c r="H1281" t="n">
         <v>355</v>
@@ -37547,7 +37547,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1282" t="n">
         <v>945</v>
@@ -37576,7 +37576,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.52830851078033</v>
+        <v>1.52830862998962</v>
       </c>
       <c r="H1283" t="n">
         <v>21</v>
@@ -37605,7 +37605,7 @@
         <v>18.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1284" t="n">
         <v>2717</v>
@@ -37634,7 +37634,7 @@
         <v>18.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.50392079353333</v>
+        <v>1.50392067432404</v>
       </c>
       <c r="H1285" t="n">
         <v>2979</v>
@@ -37692,7 +37692,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.4714035987854</v>
+        <v>1.47140347957611</v>
       </c>
       <c r="H1287" t="n">
         <v>320</v>
@@ -37721,7 +37721,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.4714035987854</v>
+        <v>1.47140347957611</v>
       </c>
       <c r="H1288" t="n">
         <v>1744</v>
@@ -37779,7 +37779,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359727859497</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1290" t="n">
         <v>593</v>
@@ -37808,7 +37808,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1291" t="n">
         <v>5905</v>
@@ -37837,7 +37837,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1292" t="n">
         <v>4865</v>
@@ -37895,7 +37895,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.95103216171265</v>
+        <v>1.95103228092194</v>
       </c>
       <c r="H1294" t="n">
         <v>24305</v>
@@ -37953,7 +37953,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1296" t="n">
         <v>31317</v>
@@ -38127,7 +38127,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1302" t="n">
         <v>4831</v>
@@ -38185,7 +38185,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1304" t="n">
         <v>3101</v>
@@ -38214,7 +38214,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1305" t="n">
         <v>1089</v>
@@ -38272,7 +38272,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.30872130393982</v>
+        <v>2.30872178077698</v>
       </c>
       <c r="H1307" t="n">
         <v>2734</v>
@@ -38301,7 +38301,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.30872130393982</v>
+        <v>2.30872178077698</v>
       </c>
       <c r="H1308" t="n">
         <v>12016</v>
@@ -38330,7 +38330,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1309" t="n">
         <v>5914</v>
@@ -38475,7 +38475,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1314" t="n">
         <v>802</v>
@@ -38504,7 +38504,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1315" t="n">
         <v>2691</v>
@@ -38533,7 +38533,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1316" t="n">
         <v>902</v>
@@ -38562,7 +38562,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1317" t="n">
         <v>1038</v>
@@ -38591,7 +38591,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994563102722</v>
+        <v>2.2599458694458</v>
       </c>
       <c r="H1318" t="n">
         <v>245</v>
@@ -38997,7 +38997,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1332" t="n">
         <v>261</v>
@@ -39026,7 +39026,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1333" t="n">
         <v>364</v>
@@ -39316,7 +39316,7 @@
         <v>27</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1343" t="n">
         <v>1560</v>
@@ -39577,7 +39577,7 @@
         <v>27</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1352" t="n">
         <v>626</v>
@@ -39664,7 +39664,7 @@
         <v>27</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1355" t="n">
         <v>15</v>
@@ -40128,7 +40128,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.17804384231567</v>
+        <v>2.17804360389709</v>
       </c>
       <c r="H1371" t="n">
         <v>1402</v>
@@ -40360,7 +40360,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1379" t="n">
         <v>4492</v>
@@ -40389,7 +40389,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1380" t="n">
         <v>3109</v>
@@ -40418,7 +40418,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1381" t="n">
         <v>14062</v>
@@ -40447,7 +40447,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1382" t="n">
         <v>4336</v>
@@ -40563,7 +40563,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1386" t="n">
         <v>12870</v>
@@ -40708,7 +40708,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1391" t="n">
         <v>1103</v>
@@ -40737,7 +40737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1392" t="n">
         <v>2136</v>
@@ -40766,7 +40766,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1393" t="n">
         <v>3074</v>
@@ -40824,7 +40824,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1395" t="n">
         <v>3834</v>
@@ -40911,7 +40911,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1398" t="n">
         <v>1418</v>
@@ -40940,7 +40940,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1399" t="n">
         <v>110</v>
@@ -41027,7 +41027,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1402" t="n">
         <v>1523</v>
@@ -41259,7 +41259,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1410" t="n">
         <v>603</v>
@@ -41578,7 +41578,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1421" t="n">
         <v>2630</v>
@@ -41665,7 +41665,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1424" t="n">
         <v>784</v>
@@ -41694,7 +41694,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1425" t="n">
         <v>1447</v>
@@ -41926,7 +41926,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1433" t="n">
         <v>2277</v>
@@ -42245,7 +42245,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1444" t="n">
         <v>1866</v>
@@ -42274,7 +42274,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1445" t="n">
         <v>1333</v>
@@ -42303,7 +42303,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1446" t="n">
         <v>2352</v>
@@ -42564,7 +42564,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1455" t="n">
         <v>1776</v>
@@ -42941,7 +42941,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1468" t="n">
         <v>141</v>
@@ -43144,7 +43144,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1475" t="n">
         <v>691</v>
@@ -43173,7 +43173,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1476" t="n">
         <v>1400</v>
@@ -43202,7 +43202,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1477" t="n">
         <v>169</v>
@@ -43231,7 +43231,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1478" t="n">
         <v>890</v>
@@ -43579,7 +43579,7 @@
         <v>27.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1490" t="n">
         <v>3333</v>
@@ -43753,7 +43753,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1496" t="n">
         <v>5031</v>
@@ -43869,7 +43869,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1500" t="n">
         <v>252</v>
@@ -43898,7 +43898,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -43927,7 +43927,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1502" t="n">
         <v>3129</v>
@@ -43985,7 +43985,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.10351014137268</v>
+        <v>2.1035099029541</v>
       </c>
       <c r="H1504" t="n">
         <v>610</v>
@@ -44246,7 +44246,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.14491772651672</v>
+        <v>2.14491748809814</v>
       </c>
       <c r="H1513" t="n">
         <v>1555</v>
@@ -44739,7 +44739,7 @@
         <v>27.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1530" t="n">
         <v>242</v>
@@ -44826,7 +44826,7 @@
         <v>27.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1533" t="n">
         <v>200</v>
@@ -44855,7 +44855,7 @@
         <v>27.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1534" t="n">
         <v>0</v>
@@ -44884,7 +44884,7 @@
         <v>27.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1535" t="n">
         <v>300</v>
@@ -44913,7 +44913,7 @@
         <v>27.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1536" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>27</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1540" t="n">
         <v>140</v>
@@ -45087,7 +45087,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1542" t="n">
         <v>511</v>
@@ -45116,7 +45116,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.26085901260376</v>
+        <v>2.26085925102234</v>
       </c>
       <c r="H1543" t="n">
         <v>516</v>
@@ -45145,7 +45145,7 @@
         <v>27</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1544" t="n">
         <v>135</v>
@@ -45464,7 +45464,7 @@
         <v>27.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1555" t="n">
         <v>107</v>
@@ -45493,7 +45493,7 @@
         <v>27.5</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1556" t="n">
         <v>639</v>
@@ -45551,7 +45551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1558" t="n">
         <v>1582</v>
@@ -45638,7 +45638,7 @@
         <v>27</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1561" t="n">
         <v>1549</v>
@@ -45667,7 +45667,7 @@
         <v>27</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1562" t="n">
         <v>1015</v>
@@ -45754,7 +45754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1565" t="n">
         <v>2831</v>
@@ -45899,7 +45899,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1570" t="n">
         <v>3995</v>
@@ -45986,7 +45986,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.46789741516113</v>
+        <v>2.46789717674255</v>
       </c>
       <c r="H1573" t="n">
         <v>685</v>
@@ -46073,7 +46073,7 @@
         <v>30.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1576" t="n">
         <v>2316</v>
@@ -46102,7 +46102,7 @@
         <v>30.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1577" t="n">
         <v>2195</v>
@@ -46131,7 +46131,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930500030518</v>
+        <v>2.50930523872375</v>
       </c>
       <c r="H1578" t="n">
         <v>2055</v>
@@ -46218,7 +46218,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978022575378</v>
+        <v>2.69978046417236</v>
       </c>
       <c r="H1581" t="n">
         <v>4224</v>
@@ -46392,7 +46392,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.24636220932007</v>
+        <v>3.24636197090149</v>
       </c>
       <c r="H1587" t="n">
         <v>14504</v>
@@ -46421,7 +46421,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1588" t="n">
         <v>15352</v>
@@ -46479,7 +46479,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1590" t="n">
         <v>7873</v>
@@ -46537,7 +46537,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1592" t="n">
         <v>19325</v>
@@ -46566,7 +46566,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1593" t="n">
         <v>22959</v>
@@ -46595,7 +46595,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1594" t="n">
         <v>22091</v>
@@ -46624,7 +46624,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1595" t="n">
         <v>58723</v>
@@ -46653,7 +46653,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.21323561668396</v>
+        <v>3.21323585510254</v>
       </c>
       <c r="H1596" t="n">
         <v>2947</v>
@@ -46885,7 +46885,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1604" t="n">
         <v>3473</v>
@@ -46914,7 +46914,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1605" t="n">
         <v>2307</v>
@@ -46943,7 +46943,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1606" t="n">
         <v>701</v>
@@ -46972,7 +46972,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1607" t="n">
         <v>5882</v>
@@ -47001,7 +47001,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1608" t="n">
         <v>869</v>
@@ -47030,7 +47030,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1609" t="n">
         <v>201</v>
@@ -47117,7 +47117,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1612" t="n">
         <v>150</v>
@@ -47146,7 +47146,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1613" t="n">
         <v>1275</v>
@@ -47233,7 +47233,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1616" t="n">
         <v>221</v>
@@ -47291,7 +47291,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1618" t="n">
         <v>2357</v>
@@ -47407,7 +47407,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994474411011</v>
+        <v>2.93994498252869</v>
       </c>
       <c r="H1622" t="n">
         <v>2912</v>
@@ -47436,7 +47436,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1623" t="n">
         <v>4769</v>
@@ -47465,7 +47465,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1624" t="n">
         <v>1292</v>
@@ -47494,7 +47494,7 @@
         <v>36.5</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1625" t="n">
         <v>521</v>
@@ -47523,7 +47523,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1626" t="n">
         <v>396</v>
@@ -47581,7 +47581,7 @@
         <v>36.5</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1628" t="n">
         <v>3363</v>
@@ -47639,7 +47639,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1630" t="n">
         <v>625</v>
@@ -47668,7 +47668,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1631" t="n">
         <v>40</v>
@@ -47784,7 +47784,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1635" t="n">
         <v>1882</v>
@@ -47813,7 +47813,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1636" t="n">
         <v>365</v>
@@ -47842,7 +47842,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1637" t="n">
         <v>2785</v>
@@ -47871,7 +47871,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1638" t="n">
         <v>2270</v>
@@ -47900,7 +47900,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1639" t="n">
         <v>2725</v>
@@ -47929,7 +47929,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1640" t="n">
         <v>1150</v>
@@ -47987,7 +47987,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1642" t="n">
         <v>925</v>
@@ -48045,7 +48045,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1644" t="n">
         <v>4061</v>
@@ -48074,7 +48074,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1645" t="n">
         <v>8289</v>
@@ -48103,7 +48103,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1646" t="n">
         <v>569</v>
@@ -48161,7 +48161,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1648" t="n">
         <v>13</v>
@@ -48190,7 +48190,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1649" t="n">
         <v>642</v>
@@ -48335,7 +48335,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526509284973</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1654" t="n">
         <v>513</v>
@@ -48422,7 +48422,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1657" t="n">
         <v>692</v>
@@ -48451,7 +48451,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1658" t="n">
         <v>1340</v>
@@ -48480,7 +48480,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1659" t="n">
         <v>408</v>
@@ -48509,7 +48509,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1660" t="n">
         <v>866</v>
@@ -48538,7 +48538,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1661" t="n">
         <v>277</v>
@@ -48596,7 +48596,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1663" t="n">
         <v>3180</v>
@@ -48683,7 +48683,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1666" t="n">
         <v>1566</v>
@@ -48770,7 +48770,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1669" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1669" t="n">
         <v>390</v>
@@ -48799,7 +48799,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1670" t="n">
         <v>184</v>
@@ -48828,7 +48828,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1671" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1671" t="n">
         <v>607</v>
@@ -48857,7 +48857,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1672" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1672" t="n">
         <v>161</v>
@@ -48886,7 +48886,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1673" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1673" t="n">
         <v>13388</v>
@@ -49060,7 +49060,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1679" t="n">
         <v>653</v>
@@ -49147,7 +49147,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1682" t="n">
         <v>1000</v>
@@ -49263,7 +49263,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1686" t="n">
         <v>1797</v>
@@ -49292,7 +49292,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1687" t="n">
         <v>76</v>
@@ -49321,7 +49321,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1688" t="n">
         <v>0</v>
@@ -49379,7 +49379,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1690" t="n">
         <v>92</v>
@@ -49408,7 +49408,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1691" t="n">
         <v>198</v>
@@ -49437,7 +49437,7 @@
         <v>36.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1692" t="n">
         <v>140</v>
@@ -49466,7 +49466,7 @@
         <v>36.5</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1693" t="n">
         <v>20</v>
@@ -49611,7 +49611,7 @@
         <v>36.5</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1698" t="n">
         <v>250</v>
@@ -49640,7 +49640,7 @@
         <v>36.5</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1699" t="n">
         <v>0</v>
@@ -49669,7 +49669,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1700" t="n">
         <v>2260</v>
@@ -49698,7 +49698,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.00619745254517</v>
+        <v>3.00619721412659</v>
       </c>
       <c r="H1701" t="n">
         <v>0</v>
@@ -49727,7 +49727,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1702" t="n">
         <v>142</v>
@@ -49756,7 +49756,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1703" t="n">
         <v>0</v>
@@ -49785,7 +49785,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1704" t="n">
         <v>395</v>
@@ -50017,7 +50017,7 @@
         <v>36.5</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1712" t="n">
         <v>4099</v>
@@ -50075,7 +50075,7 @@
         <v>36.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1714" t="n">
         <v>23</v>
@@ -50278,7 +50278,7 @@
         <v>36.5</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1721" t="n">
         <v>665</v>
@@ -50307,7 +50307,7 @@
         <v>36.5</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.02276015281677</v>
+        <v>3.02276039123535</v>
       </c>
       <c r="H1722" t="n">
         <v>2325</v>
@@ -50568,7 +50568,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1731" t="n">
         <v>10</v>
@@ -50597,7 +50597,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1732" t="n">
         <v>150</v>
@@ -50684,7 +50684,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1735" t="n">
         <v>1334</v>
@@ -50713,7 +50713,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1736" t="n">
         <v>6368</v>
@@ -50771,7 +50771,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1738" t="n">
         <v>492</v>
@@ -50829,7 +50829,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1740" t="n">
         <v>4</v>
@@ -50858,7 +50858,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.08073139190674</v>
+        <v>3.08073115348816</v>
       </c>
       <c r="H1741" t="n">
         <v>1376</v>
@@ -50887,7 +50887,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1742" t="n">
         <v>1413</v>
@@ -50916,7 +50916,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1743" t="n">
         <v>71451</v>
@@ -50974,7 +50974,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1745" t="n">
         <v>4978</v>
@@ -51003,7 +51003,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1746" t="n">
         <v>21294</v>
@@ -51032,7 +51032,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1747" t="n">
         <v>14353</v>
@@ -51090,7 +51090,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1749" t="n">
         <v>20045</v>
@@ -51119,7 +51119,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1750" t="n">
         <v>29641</v>
@@ -51148,7 +51148,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1751" t="n">
         <v>15953</v>
@@ -51177,7 +51177,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1752" t="n">
         <v>4145</v>
@@ -51264,7 +51264,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.10557556152344</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1755" t="n">
         <v>2128</v>
@@ -51322,7 +51322,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.1635468006134</v>
+        <v>3.16354656219482</v>
       </c>
       <c r="H1757" t="n">
         <v>13342</v>
@@ -51409,7 +51409,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1760" t="n">
         <v>8943</v>
@@ -51467,7 +51467,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1762" t="n">
         <v>17040</v>
@@ -51496,7 +51496,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1763" t="n">
         <v>11932</v>
@@ -51525,7 +51525,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526509284973</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1764" t="n">
         <v>6338</v>
@@ -51554,7 +51554,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1765" t="n">
         <v>11888</v>
@@ -51583,7 +51583,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1766" t="n">
         <v>9167</v>
@@ -51612,7 +51612,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.20495414733887</v>
+        <v>3.20495438575745</v>
       </c>
       <c r="H1767" t="n">
         <v>15127</v>
@@ -52047,7 +52047,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585054397583</v>
+        <v>5.01585006713867</v>
       </c>
       <c r="H1782" t="n">
         <v>29263</v>
@@ -52076,7 +52076,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.5828595161438</v>
+        <v>5.58285999298096</v>
       </c>
       <c r="H1783" t="n">
         <v>88580</v>
@@ -52105,7 +52105,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1784" t="n">
         <v>63372</v>
@@ -52250,7 +52250,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1789" t="n">
         <v>19527</v>
@@ -52366,7 +52366,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212291717529</v>
+        <v>5.21212244033813</v>
       </c>
       <c r="H1793" t="n">
         <v>17331</v>
@@ -52395,7 +52395,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1794" t="n">
         <v>14779</v>
@@ -52540,7 +52540,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924369812012</v>
+        <v>5.53924322128296</v>
       </c>
       <c r="H1799" t="n">
         <v>13906</v>
@@ -52598,7 +52598,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1801" t="n">
         <v>9611</v>
@@ -52656,7 +52656,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1803" t="n">
         <v>17158</v>
@@ -52685,7 +52685,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1804" t="n">
         <v>13501</v>
@@ -52714,7 +52714,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1805" t="n">
         <v>6792</v>
@@ -52743,7 +52743,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1806" t="n">
         <v>7235</v>
@@ -52830,7 +52830,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1809" t="n">
         <v>6507</v>
@@ -52859,7 +52859,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1810" t="n">
         <v>8854</v>
@@ -52917,7 +52917,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1812" t="n">
         <v>9617</v>
@@ -52975,7 +52975,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1814" t="n">
         <v>872</v>
@@ -53004,7 +53004,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1815" t="n">
         <v>5517</v>
@@ -53033,7 +53033,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1816" t="n">
         <v>8058</v>
@@ -53062,7 +53062,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1817" t="n">
         <v>10014</v>
@@ -53091,7 +53091,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1818" t="n">
         <v>6825</v>
@@ -53236,7 +53236,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1823" t="n">
         <v>239358</v>
@@ -53294,7 +53294,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495798110962</v>
+        <v>6.93495845794678</v>
       </c>
       <c r="H1825" t="n">
         <v>187542</v>
@@ -53323,7 +53323,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1826" t="n">
         <v>81830</v>
@@ -53352,7 +53352,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868560791016</v>
+        <v>6.73868608474731</v>
       </c>
       <c r="H1827" t="n">
         <v>53720</v>
@@ -53497,7 +53497,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433319091797</v>
+        <v>6.32433271408081</v>
       </c>
       <c r="H1832" t="n">
         <v>51065</v>
@@ -53671,7 +53671,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964534759521</v>
+        <v>6.62964582443237</v>
       </c>
       <c r="H1838" t="n">
         <v>62153</v>
@@ -53700,7 +53700,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049423217773</v>
+        <v>6.76049375534058</v>
       </c>
       <c r="H1839" t="n">
         <v>45114</v>
@@ -53729,7 +53729,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1840" t="n">
         <v>29296</v>
@@ -53758,7 +53758,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1841" t="n">
         <v>16687</v>
@@ -53787,7 +53787,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1842" t="n">
         <v>31740</v>
@@ -53816,7 +53816,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.02219104766846</v>
+        <v>7.0221905708313</v>
       </c>
       <c r="H1843" t="n">
         <v>31076</v>
@@ -53845,7 +53845,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1844" t="n">
         <v>50948</v>
@@ -53874,7 +53874,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399871826172</v>
+        <v>7.04399824142456</v>
       </c>
       <c r="H1845" t="n">
         <v>21268</v>
@@ -53932,7 +53932,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1847" t="n">
         <v>32316</v>
@@ -53961,7 +53961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835208892822</v>
+        <v>7.45835161209106</v>
       </c>
       <c r="H1848" t="n">
         <v>130442</v>
@@ -53990,7 +53990,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1849" t="n">
         <v>125182</v>
@@ -54019,7 +54019,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1850" t="n">
         <v>51748</v>
@@ -54135,7 +54135,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259365081787</v>
+        <v>8.11259269714355</v>
       </c>
       <c r="H1854" t="n">
         <v>76643</v>
@@ -79980,6 +79980,35 @@
         <v>3684</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>213</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616146087646</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H2" t="n">
         <v>328</v>
@@ -485,7 +485,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330151081085</v>
       </c>
       <c r="H4" t="n">
         <v>158</v>
@@ -514,7 +514,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H5" t="n">
         <v>1168</v>
@@ -572,7 +572,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2218531370163</v>
+        <v>1.22185301780701</v>
       </c>
       <c r="H7" t="n">
         <v>1052</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -630,7 +630,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H9" t="n">
         <v>8746</v>
@@ -659,7 +659,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327364444733</v>
+        <v>1.21327352523804</v>
       </c>
       <c r="H10" t="n">
         <v>4107</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.20111930370331</v>
+        <v>1.2011194229126</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -833,7 +833,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688576698303</v>
+        <v>1.25688588619232</v>
       </c>
       <c r="H16" t="n">
         <v>6127</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -891,7 +891,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H18" t="n">
         <v>605</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687647819519</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687647819519</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -978,7 +978,7 @@
         <v>17.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H21" t="n">
         <v>1559</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1094,7 +1094,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H25" t="n">
         <v>505</v>
@@ -1210,7 +1210,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113823890686</v>
+        <v>1.22113811969757</v>
       </c>
       <c r="H29" t="n">
         <v>111</v>
@@ -1239,7 +1239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396984577179</v>
+        <v>1.19397008419037</v>
       </c>
       <c r="H30" t="n">
         <v>419</v>
@@ -1268,7 +1268,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H31" t="n">
         <v>39</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1326,7 +1326,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469427108765</v>
+        <v>1.20469439029694</v>
       </c>
       <c r="H33" t="n">
         <v>276</v>
@@ -1355,7 +1355,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256791591644</v>
       </c>
       <c r="H34" t="n">
         <v>772</v>
@@ -1384,7 +1384,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H35" t="n">
         <v>2452</v>
@@ -1413,7 +1413,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H36" t="n">
         <v>1696</v>
@@ -1442,7 +1442,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.26546514034271</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H37" t="n">
         <v>11933</v>
@@ -1471,7 +1471,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903069972992</v>
+        <v>1.25903058052063</v>
       </c>
       <c r="H38" t="n">
         <v>6392</v>
@@ -1500,7 +1500,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903986930847</v>
+        <v>1.26903998851776</v>
       </c>
       <c r="H39" t="n">
         <v>3180</v>
@@ -1529,7 +1529,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21684837341309</v>
+        <v>1.21684849262238</v>
       </c>
       <c r="H40" t="n">
         <v>6016</v>
@@ -1558,7 +1558,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828757762909</v>
+        <v>1.22828769683838</v>
       </c>
       <c r="H41" t="n">
         <v>573</v>
@@ -1616,7 +1616,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616146087646</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H43" t="n">
         <v>1037</v>
@@ -1645,7 +1645,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330151081085</v>
       </c>
       <c r="H44" t="n">
         <v>139</v>
@@ -1674,7 +1674,7 @@
         <v>17.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H45" t="n">
         <v>26</v>
@@ -1703,7 +1703,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404451370239</v>
+        <v>1.27404463291168</v>
       </c>
       <c r="H46" t="n">
         <v>3010</v>
@@ -1732,7 +1732,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689493656158</v>
+        <v>1.26689505577087</v>
       </c>
       <c r="H47" t="n">
         <v>7764</v>
@@ -1790,7 +1790,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>1.27189981937408</v>
+        <v>1.27189970016479</v>
       </c>
       <c r="H49" t="n">
         <v>500</v>
@@ -1819,7 +1819,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.26546514034271</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H50" t="n">
         <v>3624</v>
@@ -1848,7 +1848,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H51" t="n">
         <v>1451</v>
@@ -1877,7 +1877,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G52" t="n">
-        <v>1.2790492773056</v>
+        <v>1.27904903888702</v>
       </c>
       <c r="H52" t="n">
         <v>663</v>
@@ -1906,7 +1906,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H53" t="n">
         <v>4204</v>
@@ -1935,7 +1935,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H54" t="n">
         <v>60</v>
@@ -1964,7 +1964,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.26546514034271</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H55" t="n">
         <v>584</v>
@@ -1993,7 +1993,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>1.26760995388031</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H56" t="n">
         <v>23</v>
@@ -2051,7 +2051,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26760995388031</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H58" t="n">
         <v>1444</v>
@@ -2080,7 +2080,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545573234558</v>
+        <v>1.25545597076416</v>
       </c>
       <c r="H59" t="n">
         <v>2269</v>
@@ -2109,7 +2109,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>1.2626051902771</v>
+        <v>1.26260530948639</v>
       </c>
       <c r="H60" t="n">
         <v>703</v>
@@ -2138,7 +2138,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.25831580162048</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H61" t="n">
         <v>3448</v>
@@ -2167,7 +2167,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830627441406</v>
+        <v>1.24830615520477</v>
       </c>
       <c r="H62" t="n">
         <v>745</v>
@@ -2196,7 +2196,7 @@
         <v>17.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25116610527039</v>
+        <v>1.25116622447968</v>
       </c>
       <c r="H63" t="n">
         <v>556</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258661270142</v>
+        <v>1.24258637428284</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2457,7 +2457,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.23543727397919</v>
+        <v>1.2354371547699</v>
       </c>
       <c r="H72" t="n">
         <v>795</v>
@@ -2486,7 +2486,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H73" t="n">
         <v>1010</v>
@@ -2515,7 +2515,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H74" t="n">
         <v>1039</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225353240967</v>
+        <v>1.25225365161896</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2573,7 +2573,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H76" t="n">
         <v>2231</v>
@@ -2718,7 +2718,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27640581130981</v>
+        <v>1.2764059305191</v>
       </c>
       <c r="H81" t="n">
         <v>410</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2834,7 +2834,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128255367279</v>
+        <v>1.2712824344635</v>
       </c>
       <c r="H85" t="n">
         <v>149</v>
@@ -2892,7 +2892,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G87" t="n">
-        <v>1.26689124107361</v>
+        <v>1.26689112186432</v>
       </c>
       <c r="H87" t="n">
         <v>1058</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -3008,7 +3008,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.27933323383331</v>
+        <v>1.2793333530426</v>
       </c>
       <c r="H91" t="n">
         <v>100</v>
@@ -3037,7 +3037,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.27933323383331</v>
+        <v>1.2793333530426</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.27933323383331</v>
+        <v>1.2793333530426</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3153,7 +3153,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H96" t="n">
         <v>81</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811597824097</v>
+        <v>1.28811609745026</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
@@ -3269,7 +3269,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>1.28738403320312</v>
+        <v>1.28738415241241</v>
       </c>
       <c r="H100" t="n">
         <v>70</v>
@@ -3298,7 +3298,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.27933323383331</v>
+        <v>1.2793333530426</v>
       </c>
       <c r="H101" t="n">
         <v>361</v>
@@ -3327,7 +3327,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27933323383331</v>
+        <v>1.2793333530426</v>
       </c>
       <c r="H102" t="n">
         <v>20</v>
@@ -3356,7 +3356,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299272060394</v>
+        <v>1.28299295902252</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H104" t="n">
         <v>741</v>
@@ -3414,7 +3414,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H106" t="n">
         <v>93</v>
@@ -3472,7 +3472,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128255367279</v>
+        <v>1.2712824344635</v>
       </c>
       <c r="H108" t="n">
         <v>3785</v>
@@ -3530,7 +3530,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128255367279</v>
+        <v>1.2712824344635</v>
       </c>
       <c r="H109" t="n">
         <v>12</v>
@@ -3559,7 +3559,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128255367279</v>
+        <v>1.2712824344635</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H111" t="n">
         <v>594</v>
@@ -3646,7 +3646,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H113" t="n">
         <v>1458</v>
@@ -3675,7 +3675,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H114" t="n">
         <v>1307</v>
@@ -3704,7 +3704,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H115" t="n">
         <v>1050</v>
@@ -3791,7 +3791,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687663555145</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18565213680267</v>
+        <v>1.18565225601196</v>
       </c>
       <c r="H121" t="n">
         <v>6050</v>
@@ -3936,7 +3936,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784785270691</v>
+        <v>1.18784773349762</v>
       </c>
       <c r="H123" t="n">
         <v>1361</v>
@@ -3965,7 +3965,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955089569092</v>
+        <v>1.16955077648163</v>
       </c>
       <c r="H124" t="n">
         <v>4411</v>
@@ -3994,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H125" t="n">
         <v>673</v>
@@ -4110,7 +4110,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H129" t="n">
         <v>1649</v>
@@ -4197,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H132" t="n">
         <v>171</v>
@@ -4226,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H133" t="n">
         <v>101</v>
@@ -4255,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H134" t="n">
         <v>245</v>
@@ -4342,7 +4342,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151434421539</v>
       </c>
       <c r="H137" t="n">
         <v>610</v>
@@ -4371,7 +4371,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G138" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151434421539</v>
       </c>
       <c r="H138" t="n">
         <v>215</v>
@@ -4429,7 +4429,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H140" t="n">
         <v>730</v>
@@ -4458,7 +4458,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G142" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H142" t="n">
         <v>152</v>
@@ -4516,7 +4516,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G143" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H143" t="n">
         <v>116</v>
@@ -4574,7 +4574,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H145" t="n">
         <v>265</v>
@@ -4632,7 +4632,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G147" t="n">
-        <v>1.23542022705078</v>
+        <v>1.23542010784149</v>
       </c>
       <c r="H147" t="n">
         <v>2025</v>
@@ -4661,7 +4661,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834776878357</v>
+        <v>1.23834788799286</v>
       </c>
       <c r="H148" t="n">
         <v>20</v>
@@ -4690,7 +4690,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H149" t="n">
         <v>1154</v>
@@ -4719,7 +4719,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.20614492893219</v>
+        <v>1.2061448097229</v>
       </c>
       <c r="H150" t="n">
         <v>2847</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="n">
         <v>4104</v>
@@ -5096,7 +5096,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="n">
         <v>2568</v>
@@ -5212,7 +5212,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H167" t="n">
         <v>1738</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5473,7 +5473,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982626438141</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="n">
         <v>1808</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5705,7 +5705,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250717163086</v>
+        <v>1.29250729084015</v>
       </c>
       <c r="H189" t="n">
         <v>625</v>
@@ -6024,7 +6024,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27274644374847</v>
+        <v>1.2727462053299</v>
       </c>
       <c r="H195" t="n">
         <v>5744</v>
@@ -6082,7 +6082,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="n">
         <v>5843</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786221981049</v>
+        <v>1.24786233901978</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6140,7 +6140,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518119335175</v>
+        <v>1.25518107414246</v>
       </c>
       <c r="H199" t="n">
         <v>1811</v>
@@ -6198,7 +6198,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006517887115</v>
+        <v>1.28006529808044</v>
       </c>
       <c r="H201" t="n">
         <v>19504</v>
@@ -6256,7 +6256,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810885429382</v>
+        <v>1.25810861587524</v>
       </c>
       <c r="H203" t="n">
         <v>11122</v>
@@ -6285,7 +6285,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H204" t="n">
         <v>3493</v>
@@ -6343,7 +6343,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639856815338</v>
+        <v>1.24639868736267</v>
       </c>
       <c r="H206" t="n">
         <v>7757</v>
@@ -6430,7 +6430,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615193367004</v>
       </c>
       <c r="H209" t="n">
         <v>5810</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688399791718</v>
+        <v>1.23688387870789</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6517,7 +6517,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2420072555542</v>
+        <v>1.24200713634491</v>
       </c>
       <c r="H212" t="n">
         <v>21105</v>
@@ -6546,7 +6546,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H213" t="n">
         <v>5199</v>
@@ -6575,7 +6575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H214" t="n">
         <v>3399</v>
@@ -6662,7 +6662,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H217" t="n">
         <v>3330</v>
@@ -6749,7 +6749,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.23176085948944</v>
+        <v>1.23176074028015</v>
       </c>
       <c r="H220" t="n">
         <v>8086</v>
@@ -6778,7 +6778,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H221" t="n">
         <v>2500</v>
@@ -6807,7 +6807,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H222" t="n">
         <v>2781</v>
@@ -6836,7 +6836,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H223" t="n">
         <v>275</v>
@@ -6894,7 +6894,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H225" t="n">
         <v>13996</v>
@@ -6923,7 +6923,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H226" t="n">
         <v>2165</v>
@@ -6952,7 +6952,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H227" t="n">
         <v>1452</v>
@@ -6981,7 +6981,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.20980453491211</v>
+        <v>1.20980441570282</v>
       </c>
       <c r="H228" t="n">
         <v>5599</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126794815063</v>
+        <v>1.21126806735992</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7039,7 +7039,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.21858692169189</v>
+        <v>1.2185868024826</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7126,7 +7126,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004356861115</v>
+        <v>1.19004344940186</v>
       </c>
       <c r="H233" t="n">
         <v>13873</v>
@@ -7184,7 +7184,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21419560909271</v>
+        <v>1.214195728302</v>
       </c>
       <c r="H235" t="n">
         <v>750</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663023948669</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7329,7 +7329,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.220050573349</v>
+        <v>1.22005069255829</v>
       </c>
       <c r="H240" t="n">
         <v>740</v>
@@ -7387,7 +7387,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956526279449</v>
       </c>
       <c r="H242" t="n">
         <v>6732</v>
@@ -7416,7 +7416,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="n">
-        <v>1.25957250595093</v>
+        <v>1.25957238674164</v>
       </c>
       <c r="H243" t="n">
         <v>12078</v>
@@ -7445,7 +7445,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128255367279</v>
+        <v>1.2712824344635</v>
       </c>
       <c r="H244" t="n">
         <v>6714</v>
@@ -7532,7 +7532,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592014312744</v>
+        <v>1.28592038154602</v>
       </c>
       <c r="H247" t="n">
         <v>4452</v>
@@ -7590,7 +7590,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H249" t="n">
         <v>2175</v>
@@ -7706,7 +7706,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G253" t="n">
-        <v>1.28738403320312</v>
+        <v>1.28738415241241</v>
       </c>
       <c r="H253" t="n">
         <v>1178</v>
@@ -7822,7 +7822,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007242202759</v>
+        <v>1.3100723028183</v>
       </c>
       <c r="H257" t="n">
         <v>7253</v>
@@ -7909,7 +7909,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3334926366806</v>
+        <v>1.33349275588989</v>
       </c>
       <c r="H260" t="n">
         <v>1372</v>
@@ -7967,7 +7967,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>1.33202910423279</v>
+        <v>1.3320289850235</v>
       </c>
       <c r="H262" t="n">
         <v>1416</v>
@@ -8141,7 +8141,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227526187897</v>
+        <v>1.34227538108826</v>
       </c>
       <c r="H268" t="n">
         <v>2370</v>
@@ -8170,7 +8170,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34007978439331</v>
+        <v>1.34007966518402</v>
       </c>
       <c r="H269" t="n">
         <v>383</v>
@@ -8228,7 +8228,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>1.3210506439209</v>
+        <v>1.32105088233948</v>
       </c>
       <c r="H271" t="n">
         <v>1933</v>
@@ -8286,7 +8286,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.3613041639328</v>
+        <v>1.36130464076996</v>
       </c>
       <c r="H273" t="n">
         <v>6282</v>
@@ -8373,7 +8373,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="n">
-        <v>1.33276081085205</v>
+        <v>1.33276069164276</v>
       </c>
       <c r="H276" t="n">
         <v>684</v>
@@ -8402,7 +8402,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959423542023</v>
+        <v>1.34959411621094</v>
       </c>
       <c r="H277" t="n">
         <v>1064</v>
@@ -8605,7 +8605,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349987983704</v>
+        <v>1.36349999904633</v>
       </c>
       <c r="H284" t="n">
         <v>4639</v>
@@ -8692,7 +8692,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252890110016</v>
+        <v>1.38252913951874</v>
       </c>
       <c r="H287" t="n">
         <v>4266</v>
@@ -8721,7 +8721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789843559265</v>
+        <v>1.39789867401123</v>
       </c>
       <c r="H288" t="n">
         <v>6393</v>
@@ -8750,7 +8750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253614425659</v>
+        <v>1.4125360250473</v>
       </c>
       <c r="H289" t="n">
         <v>1447</v>
@@ -8837,7 +8837,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887677669525</v>
+        <v>1.40887689590454</v>
       </c>
       <c r="H292" t="n">
         <v>5253</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302193164825</v>
+        <v>1.40302181243896</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -9011,7 +9011,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155780315399</v>
+        <v>1.40155792236328</v>
       </c>
       <c r="H298" t="n">
         <v>640</v>
@@ -9040,7 +9040,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H299" t="n">
         <v>23394</v>
@@ -9069,7 +9069,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H300" t="n">
         <v>14396</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621023654938</v>
+        <v>1.4762099981308</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9127,7 +9127,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206508159637</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H302" t="n">
         <v>4239</v>
@@ -9156,7 +9156,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157953262329</v>
+        <v>1.49157965183258</v>
       </c>
       <c r="H303" t="n">
         <v>5662</v>
@@ -9185,7 +9185,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50328981876373</v>
+        <v>1.50328993797302</v>
       </c>
       <c r="H304" t="n">
         <v>18505</v>
@@ -9214,7 +9214,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742725372314</v>
+        <v>1.46742749214172</v>
       </c>
       <c r="H305" t="n">
         <v>2232</v>
@@ -9272,7 +9272,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.47913765907288</v>
+        <v>1.47913753986359</v>
       </c>
       <c r="H307" t="n">
         <v>4196</v>
@@ -9330,7 +9330,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="n">
-        <v>1.49084782600403</v>
+        <v>1.49084794521332</v>
       </c>
       <c r="H309" t="n">
         <v>4684</v>
@@ -9359,7 +9359,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792040348053</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H310" t="n">
         <v>3021</v>
@@ -9388,7 +9388,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206508159637</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H311" t="n">
         <v>124</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987672805786</v>
+        <v>1.50987660884857</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -9562,7 +9562,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963757514954</v>
+        <v>1.52963769435883</v>
       </c>
       <c r="H317" t="n">
         <v>1725</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817380428314</v>
+        <v>1.52817392349243</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9649,7 +9649,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51499998569489</v>
+        <v>1.51500010490417</v>
       </c>
       <c r="H320" t="n">
         <v>2425</v>
@@ -9678,7 +9678,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="n">
-        <v>1.49963068962097</v>
+        <v>1.49963045120239</v>
       </c>
       <c r="H321" t="n">
         <v>5351</v>
@@ -9736,7 +9736,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.485724568367</v>
+        <v>1.48572468757629</v>
       </c>
       <c r="H323" t="n">
         <v>2881</v>
@@ -9765,7 +9765,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206508159637</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H324" t="n">
         <v>6036</v>
@@ -9823,7 +9823,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792040348053</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H326" t="n">
         <v>7683</v>
@@ -9881,7 +9881,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="n">
-        <v>1.48426079750061</v>
+        <v>1.48426103591919</v>
       </c>
       <c r="H328" t="n">
         <v>6549</v>
@@ -9910,7 +9910,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206508159637</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H329" t="n">
         <v>3153</v>
@@ -9939,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376824378967</v>
+        <v>1.46376812458038</v>
       </c>
       <c r="H330" t="n">
         <v>9218</v>
@@ -9968,7 +9968,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498526096344</v>
+        <v>1.45498549938202</v>
       </c>
       <c r="H331" t="n">
         <v>6285</v>
@@ -9997,7 +9997,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499274253845</v>
+        <v>1.48499286174774</v>
       </c>
       <c r="H332" t="n">
         <v>9406</v>
@@ -10026,7 +10026,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085494995117</v>
+        <v>1.52085518836975</v>
       </c>
       <c r="H333" t="n">
         <v>14974</v>
@@ -10055,7 +10055,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768825531006</v>
+        <v>1.53768849372864</v>
       </c>
       <c r="H334" t="n">
         <v>12975</v>
@@ -10142,7 +10142,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427460193634</v>
+        <v>1.63427472114563</v>
       </c>
       <c r="H337" t="n">
         <v>3259</v>
@@ -10258,7 +10258,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.6628805398941</v>
+        <v>1.66288042068481</v>
       </c>
       <c r="H341" t="n">
         <v>8452</v>
@@ -10287,7 +10287,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6613746881485</v>
+        <v>1.66137480735779</v>
       </c>
       <c r="H342" t="n">
         <v>1480</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816614627838</v>
+        <v>1.80816602706909</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10403,7 +10403,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="n">
-        <v>1.91656541824341</v>
+        <v>1.9165655374527</v>
       </c>
       <c r="H346" t="n">
         <v>37449</v>
@@ -10432,7 +10432,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485397338867</v>
+        <v>1.99485385417938</v>
       </c>
       <c r="H347" t="n">
         <v>48029</v>
@@ -10490,7 +10490,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345163345337</v>
+        <v>1.95345139503479</v>
       </c>
       <c r="H349" t="n">
         <v>31940</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376038074493</v>
+        <v>1.83376049995422</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10635,7 +10635,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.9030157327652</v>
+        <v>1.90301549434662</v>
       </c>
       <c r="H354" t="n">
         <v>11029</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452086925507</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10693,7 +10693,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.91204857826233</v>
+        <v>1.91204881668091</v>
       </c>
       <c r="H356" t="n">
         <v>4977</v>
@@ -10722,7 +10722,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538498878479</v>
+        <v>1.93538475036621</v>
       </c>
       <c r="H357" t="n">
         <v>14132</v>
@@ -10751,7 +10751,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.9225879907608</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H358" t="n">
         <v>3542</v>
@@ -10780,7 +10780,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>1.9158126115799</v>
+        <v>1.91581284999847</v>
       </c>
       <c r="H359" t="n">
         <v>3397</v>
@@ -10809,7 +10809,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118481636047</v>
+        <v>1.88118517398834</v>
       </c>
       <c r="H360" t="n">
         <v>6883</v>
@@ -10838,7 +10838,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92861008644104</v>
+        <v>1.92860996723175</v>
       </c>
       <c r="H361" t="n">
         <v>5572</v>
@@ -10896,7 +10896,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559885978699</v>
       </c>
       <c r="H363" t="n">
         <v>5423</v>
@@ -10954,7 +10954,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.92635154724121</v>
+        <v>1.92635142803192</v>
       </c>
       <c r="H365" t="n">
         <v>10408</v>
@@ -10983,7 +10983,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>1.91656541824341</v>
+        <v>1.9165655374527</v>
       </c>
       <c r="H366" t="n">
         <v>5653</v>
@@ -11012,7 +11012,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376830101013</v>
+        <v>1.90376842021942</v>
       </c>
       <c r="H367" t="n">
         <v>5873</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11070,7 +11070,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559885978699</v>
       </c>
       <c r="H369" t="n">
         <v>1846</v>
@@ -11128,7 +11128,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237388134003</v>
       </c>
       <c r="H371" t="n">
         <v>2941</v>
@@ -11157,7 +11157,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>1.94366526603699</v>
+        <v>1.94366538524628</v>
       </c>
       <c r="H372" t="n">
         <v>2905</v>
@@ -11186,7 +11186,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.9225879907608</v>
+        <v>1.92258787155151</v>
       </c>
       <c r="H373" t="n">
         <v>1590</v>
@@ -11244,7 +11244,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>1.89021861553192</v>
+        <v>1.89021849632263</v>
       </c>
       <c r="H375" t="n">
         <v>1836</v>
@@ -11273,7 +11273,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.9075323343277</v>
+        <v>1.90753221511841</v>
       </c>
       <c r="H376" t="n">
         <v>4843</v>
@@ -11360,7 +11360,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742102146149</v>
+        <v>1.87742114067078</v>
       </c>
       <c r="H379" t="n">
         <v>4228</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052700519562</v>
+        <v>1.7705272436142</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762721061707</v>
+        <v>1.79762697219849</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11476,7 +11476,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826882362366</v>
+        <v>1.76826894283295</v>
       </c>
       <c r="H383" t="n">
         <v>2862</v>
@@ -11505,7 +11505,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.79461574554443</v>
+        <v>1.79461586475372</v>
       </c>
       <c r="H384" t="n">
         <v>2507</v>
@@ -11534,7 +11534,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741286277771</v>
+        <v>1.80741310119629</v>
       </c>
       <c r="H385" t="n">
         <v>3798</v>
@@ -11563,7 +11563,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074915409088</v>
+        <v>1.83074939250946</v>
       </c>
       <c r="H386" t="n">
         <v>3583</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816614627838</v>
+        <v>1.80816602706909</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11708,7 +11708,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.82623255252838</v>
+        <v>1.82623243331909</v>
       </c>
       <c r="H391" t="n">
         <v>2650</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.83601868152618</v>
+        <v>1.83601856231689</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11882,7 +11882,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H397" t="n">
         <v>2269</v>
@@ -11911,7 +11911,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H398" t="n">
         <v>776</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.8465576171875</v>
+        <v>1.84655749797821</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752405643463</v>
+        <v>1.83752417564392</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774596691132</v>
+        <v>1.89774584770203</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12114,7 +12114,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H405" t="n">
         <v>8569</v>
@@ -12143,7 +12143,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H406" t="n">
         <v>3339</v>
@@ -12172,7 +12172,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>1.97151803970337</v>
+        <v>1.97151815891266</v>
       </c>
       <c r="H407" t="n">
         <v>2092</v>
@@ -12201,7 +12201,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086838722229</v>
+        <v>1.93086802959442</v>
       </c>
       <c r="H408" t="n">
         <v>4037</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613755702972</v>
+        <v>1.93613743782043</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12259,7 +12259,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237388134003</v>
       </c>
       <c r="H410" t="n">
         <v>3461</v>
@@ -12288,7 +12288,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>1.9210821390152</v>
+        <v>1.92108237743378</v>
       </c>
       <c r="H411" t="n">
         <v>931</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12346,7 +12346,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796007633209</v>
+        <v>1.88796019554138</v>
       </c>
       <c r="H413" t="n">
         <v>1727</v>
@@ -12375,7 +12375,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="n">
-        <v>1.89021861553192</v>
+        <v>1.89021849632263</v>
       </c>
       <c r="H414" t="n">
         <v>818</v>
@@ -12404,7 +12404,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720726966858</v>
+        <v>1.88720738887787</v>
       </c>
       <c r="H415" t="n">
         <v>1165</v>
@@ -12433,7 +12433,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>1.89548802375793</v>
+        <v>1.89548778533936</v>
       </c>
       <c r="H416" t="n">
         <v>873</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452086925507</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.85634362697601</v>
+        <v>1.85634338855743</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12665,7 +12665,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>1.85709607601166</v>
+        <v>1.85709619522095</v>
       </c>
       <c r="H424" t="n">
         <v>891</v>
@@ -12694,7 +12694,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182678699493</v>
+        <v>1.85182690620422</v>
       </c>
       <c r="H425" t="n">
         <v>2952</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.85634362697601</v>
+        <v>1.85634338855743</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12781,7 +12781,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494896888733</v>
+        <v>1.88494908809662</v>
       </c>
       <c r="H428" t="n">
         <v>2953</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12955,7 +12955,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.87064635753632</v>
+        <v>1.87064611911774</v>
       </c>
       <c r="H434" t="n">
         <v>4633</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365710735321</v>
+        <v>1.8736572265625</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.86537683010101</v>
+        <v>1.8653769493103</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13187,7 +13187,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="n">
-        <v>1.84505200386047</v>
+        <v>1.84505188465118</v>
       </c>
       <c r="H442" t="n">
         <v>4195</v>
@@ -13216,7 +13216,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257983207703</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H443" t="n">
         <v>1174</v>
@@ -13361,7 +13361,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795191764832</v>
+        <v>1.81795179843903</v>
       </c>
       <c r="H448" t="n">
         <v>5592</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13419,7 +13419,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849097251892</v>
+        <v>1.82849109172821</v>
       </c>
       <c r="H450" t="n">
         <v>3382</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569385528564</v>
+        <v>1.81569361686707</v>
       </c>
       <c r="H451" t="n">
         <v>4388</v>
@@ -13477,7 +13477,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021045684814</v>
+        <v>1.82021033763885</v>
       </c>
       <c r="H452" t="n">
         <v>6137</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117677688599</v>
+        <v>1.81117713451385</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13535,7 +13535,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644630432129</v>
+        <v>1.816446185112</v>
       </c>
       <c r="H454" t="n">
         <v>4767</v>
@@ -13564,7 +13564,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.81418800354004</v>
+        <v>1.81418812274933</v>
       </c>
       <c r="H455" t="n">
         <v>1684</v>
@@ -13593,7 +13593,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H456" t="n">
         <v>3211</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246875762939</v>
+        <v>1.82246840000153</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13738,7 +13738,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.85032153129578</v>
+        <v>1.8503212928772</v>
       </c>
       <c r="H461" t="n">
         <v>11043</v>
@@ -13767,7 +13767,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H462" t="n">
         <v>3800</v>
@@ -13825,7 +13825,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849889278412</v>
+        <v>1.89849865436554</v>
       </c>
       <c r="H464" t="n">
         <v>4953</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731810569763</v>
+        <v>1.9173184633255</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13912,7 +13912,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979855537415</v>
+        <v>1.97979831695557</v>
       </c>
       <c r="H467" t="n">
         <v>24938</v>
@@ -13941,7 +13941,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474313735962</v>
       </c>
       <c r="H468" t="n">
         <v>14648</v>
@@ -13970,7 +13970,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>1.94366526603699</v>
+        <v>1.94366538524628</v>
       </c>
       <c r="H469" t="n">
         <v>12171</v>
@@ -13999,7 +13999,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="n">
-        <v>1.94667673110962</v>
+        <v>1.94667649269104</v>
       </c>
       <c r="H470" t="n">
         <v>11729</v>
@@ -14028,7 +14028,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="n">
-        <v>1.97076547145844</v>
+        <v>1.97076559066772</v>
       </c>
       <c r="H471" t="n">
         <v>6065</v>
@@ -14057,7 +14057,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775412559509</v>
+        <v>1.96775424480438</v>
       </c>
       <c r="H472" t="n">
         <v>6595</v>
@@ -14086,7 +14086,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248459815979</v>
+        <v>1.96248483657837</v>
       </c>
       <c r="H473" t="n">
         <v>11988</v>
@@ -14202,7 +14202,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732626438141</v>
+        <v>1.9873263835907</v>
       </c>
       <c r="H477" t="n">
         <v>8901</v>
@@ -14231,7 +14231,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937057495117</v>
+        <v>1.99937069416046</v>
       </c>
       <c r="H478" t="n">
         <v>3901</v>
@@ -14260,7 +14260,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582077026367</v>
+        <v>1.98582053184509</v>
       </c>
       <c r="H479" t="n">
         <v>3201</v>
@@ -14289,7 +14289,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="n">
-        <v>1.99033737182617</v>
+        <v>1.99033749103546</v>
       </c>
       <c r="H480" t="n">
         <v>2850</v>
@@ -14318,7 +14318,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624863147736</v>
+        <v>1.96624886989594</v>
       </c>
       <c r="H481" t="n">
         <v>7605</v>
@@ -14376,7 +14376,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549606323242</v>
+        <v>1.96549594402313</v>
       </c>
       <c r="H483" t="n">
         <v>212</v>
@@ -14405,7 +14405,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474313735962</v>
       </c>
       <c r="H484" t="n">
         <v>3107</v>
@@ -14463,7 +14463,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.9828097820282</v>
+        <v>1.98280966281891</v>
       </c>
       <c r="H486" t="n">
         <v>699</v>
@@ -14492,7 +14492,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H487" t="n">
         <v>871</v>
@@ -14521,7 +14521,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>2.0249650478363</v>
+        <v>2.02496528625488</v>
       </c>
       <c r="H488" t="n">
         <v>2714</v>
@@ -14550,7 +14550,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H489" t="n">
         <v>11786</v>
@@ -14579,7 +14579,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H490" t="n">
         <v>4910</v>
@@ -14608,7 +14608,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540130615234</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H491" t="n">
         <v>2166</v>
@@ -14637,7 +14637,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.08142304420471</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H492" t="n">
         <v>5737</v>
@@ -14666,7 +14666,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H493" t="n">
         <v>9201</v>
@@ -14724,7 +14724,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="n">
-        <v>2.08593988418579</v>
+        <v>2.08594012260437</v>
       </c>
       <c r="H495" t="n">
         <v>1780</v>
@@ -14753,7 +14753,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>2.08142304420471</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H496" t="n">
         <v>1344</v>
@@ -14782,7 +14782,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765960693359</v>
+        <v>2.07765936851501</v>
       </c>
       <c r="H497" t="n">
         <v>3216</v>
@@ -14811,7 +14811,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G498" t="n">
-        <v>2.09572601318359</v>
+        <v>2.09572577476501</v>
       </c>
       <c r="H498" t="n">
         <v>366</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024285316467</v>
+        <v>2.10024261474609</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -14927,7 +14927,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>2.08669257164001</v>
+        <v>2.08669281005859</v>
       </c>
       <c r="H502" t="n">
         <v>2825</v>
@@ -14956,7 +14956,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="n">
-        <v>2.07013177871704</v>
+        <v>2.07013154029846</v>
       </c>
       <c r="H503" t="n">
         <v>1243</v>
@@ -14985,7 +14985,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034564971924</v>
+        <v>2.06034541130066</v>
       </c>
       <c r="H504" t="n">
         <v>2924</v>
@@ -15014,7 +15014,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959296226501</v>
+        <v>2.05959272384644</v>
       </c>
       <c r="H505" t="n">
         <v>2166</v>
@@ -15043,7 +15043,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>2.05883979797363</v>
+        <v>2.05884027481079</v>
       </c>
       <c r="H506" t="n">
         <v>1639</v>
@@ -15072,7 +15072,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540130615234</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H507" t="n">
         <v>1590</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615399360657</v>
+        <v>2.07615351676941</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15130,7 +15130,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="n">
-        <v>2.08368182182312</v>
+        <v>2.08368158340454</v>
       </c>
       <c r="H509" t="n">
         <v>2098</v>
@@ -15275,7 +15275,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H514" t="n">
         <v>7527</v>
@@ -15333,7 +15333,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.16799235343933</v>
+        <v>2.16799259185791</v>
       </c>
       <c r="H516" t="n">
         <v>4995</v>
@@ -15391,7 +15391,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H518" t="n">
         <v>3359</v>
@@ -15449,7 +15449,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H520" t="n">
         <v>13063</v>
@@ -15507,7 +15507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31854748725891</v>
+        <v>2.31854724884033</v>
       </c>
       <c r="H522" t="n">
         <v>6269</v>
@@ -15536,7 +15536,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>2.31854748725891</v>
+        <v>2.31854724884033</v>
       </c>
       <c r="H523" t="n">
         <v>1601</v>
@@ -15594,7 +15594,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="n">
-        <v>2.37124180793762</v>
+        <v>2.37124156951904</v>
       </c>
       <c r="H525" t="n">
         <v>3481</v>
@@ -15681,7 +15681,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H528" t="n">
         <v>6112</v>
@@ -15768,7 +15768,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>2.28090882301331</v>
+        <v>2.28090858459473</v>
       </c>
       <c r="H531" t="n">
         <v>1414</v>
@@ -15826,7 +15826,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596424102783</v>
+        <v>2.29596447944641</v>
       </c>
       <c r="H533" t="n">
         <v>4435</v>
@@ -15971,7 +15971,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810366630554</v>
+        <v>2.19810318946838</v>
       </c>
       <c r="H538" t="n">
         <v>2100</v>
@@ -16000,7 +16000,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H539" t="n">
         <v>1456</v>
@@ -16058,7 +16058,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="n">
-        <v>2.18304800987244</v>
+        <v>2.18304777145386</v>
       </c>
       <c r="H541" t="n">
         <v>2730</v>
@@ -16087,7 +16087,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H542" t="n">
         <v>3615</v>
@@ -16145,7 +16145,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H544" t="n">
         <v>815</v>
@@ -16261,7 +16261,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="n">
-        <v>2.37124180793762</v>
+        <v>2.37124156951904</v>
       </c>
       <c r="H548" t="n">
         <v>2154</v>
@@ -16290,7 +16290,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190753936768</v>
+        <v>2.55190777778625</v>
       </c>
       <c r="H549" t="n">
         <v>41764</v>
@@ -16435,7 +16435,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H554" t="n">
         <v>6023</v>
@@ -16551,7 +16551,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H558" t="n">
         <v>4749</v>
@@ -16580,7 +16580,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H559" t="n">
         <v>4701</v>
@@ -16696,7 +16696,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888047218323</v>
+        <v>2.40888071060181</v>
       </c>
       <c r="H563" t="n">
         <v>3721</v>
@@ -16725,7 +16725,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H564" t="n">
         <v>2298</v>
@@ -16841,7 +16841,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H568" t="n">
         <v>2129</v>
@@ -16928,7 +16928,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H571" t="n">
         <v>3605</v>
@@ -16986,7 +16986,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G573" t="n">
-        <v>2.4164080619812</v>
+        <v>2.41640782356262</v>
       </c>
       <c r="H573" t="n">
         <v>747</v>
@@ -17044,7 +17044,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146347999573</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H575" t="n">
         <v>4786</v>
@@ -17131,7 +17131,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H578" t="n">
         <v>1479</v>
@@ -17363,7 +17363,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910262107849</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H586" t="n">
         <v>3037</v>
@@ -17421,7 +17421,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>2.5293242931366</v>
+        <v>2.52932453155518</v>
       </c>
       <c r="H588" t="n">
         <v>10382</v>
@@ -17537,7 +17537,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363485336304</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H592" t="n">
         <v>1427</v>
@@ -17595,7 +17595,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604820251465</v>
+        <v>2.50604844093323</v>
       </c>
       <c r="H594" t="n">
         <v>2722</v>
@@ -17682,7 +17682,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363485336304</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H597" t="n">
         <v>5094</v>
@@ -17798,7 +17798,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>2.5293242931366</v>
+        <v>2.52932453155518</v>
       </c>
       <c r="H601" t="n">
         <v>2010</v>
@@ -17827,7 +17827,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H602" t="n">
         <v>16769</v>
@@ -17914,7 +17914,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604820251465</v>
+        <v>2.50604844093323</v>
       </c>
       <c r="H605" t="n">
         <v>1385</v>
@@ -17943,7 +17943,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H606" t="n">
         <v>109</v>
@@ -17972,7 +17972,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846202850342</v>
       </c>
       <c r="H607" t="n">
         <v>6484</v>
@@ -18001,7 +18001,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H608" t="n">
         <v>12294</v>
@@ -18117,7 +18117,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H612" t="n">
         <v>1071</v>
@@ -18146,7 +18146,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H613" t="n">
         <v>5750</v>
@@ -18175,7 +18175,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H614" t="n">
         <v>7400</v>
@@ -18204,7 +18204,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H615" t="n">
         <v>6196</v>
@@ -18407,7 +18407,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H622" t="n">
         <v>1065</v>
@@ -18436,7 +18436,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H623" t="n">
         <v>4311</v>
@@ -18465,7 +18465,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H624" t="n">
         <v>215</v>
@@ -18494,7 +18494,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H625" t="n">
         <v>1193</v>
@@ -18552,7 +18552,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="n">
-        <v>2.25001239776611</v>
+        <v>2.25001263618469</v>
       </c>
       <c r="H627" t="n">
         <v>1402</v>
@@ -18581,7 +18581,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H628" t="n">
         <v>125</v>
@@ -18668,7 +18668,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H631" t="n">
         <v>1652</v>
@@ -18697,7 +18697,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H632" t="n">
         <v>2259</v>
@@ -18726,7 +18726,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H633" t="n">
         <v>3975</v>
@@ -18755,7 +18755,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259771347046</v>
       </c>
       <c r="H634" t="n">
         <v>786</v>
@@ -18842,7 +18842,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259771347046</v>
       </c>
       <c r="H637" t="n">
         <v>1582</v>
@@ -18871,7 +18871,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H638" t="n">
         <v>413</v>
@@ -18900,7 +18900,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H639" t="n">
         <v>152</v>
@@ -18929,7 +18929,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259771347046</v>
       </c>
       <c r="H641" t="n">
         <v>2464</v>
@@ -19016,7 +19016,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H643" t="n">
         <v>2317</v>
@@ -19074,7 +19074,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H645" t="n">
         <v>4007</v>
@@ -19103,7 +19103,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H646" t="n">
         <v>7254</v>
@@ -19161,7 +19161,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H648" t="n">
         <v>3807</v>
@@ -19219,7 +19219,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.16466736793518</v>
+        <v>2.1646671295166</v>
       </c>
       <c r="H650" t="n">
         <v>2832</v>
@@ -19335,7 +19335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H654" t="n">
         <v>4303</v>
@@ -19364,7 +19364,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H655" t="n">
         <v>3734</v>
@@ -19393,7 +19393,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H656" t="n">
         <v>2106</v>
@@ -19422,7 +19422,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H657" t="n">
         <v>790</v>
@@ -19451,7 +19451,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H658" t="n">
         <v>1560</v>
@@ -19509,7 +19509,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H660" t="n">
         <v>1057</v>
@@ -19596,7 +19596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H663" t="n">
         <v>44</v>
@@ -19741,7 +19741,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259771347046</v>
       </c>
       <c r="H668" t="n">
         <v>25</v>
@@ -19799,7 +19799,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H670" t="n">
         <v>10470</v>
@@ -19857,7 +19857,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H672" t="n">
         <v>8845</v>
@@ -19973,7 +19973,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.96294188499451</v>
+        <v>1.96294176578522</v>
       </c>
       <c r="H676" t="n">
         <v>3545</v>
@@ -20002,7 +20002,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966591358185</v>
+        <v>1.93966603279114</v>
       </c>
       <c r="H677" t="n">
         <v>2534</v>
@@ -20031,7 +20031,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>1.8853554725647</v>
+        <v>1.88535559177399</v>
       </c>
       <c r="H678" t="n">
         <v>5198</v>
@@ -20060,7 +20060,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H679" t="n">
         <v>3984</v>
@@ -20089,7 +20089,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432052612305</v>
+        <v>1.85432076454163</v>
       </c>
       <c r="H680" t="n">
         <v>1873</v>
@@ -20118,7 +20118,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983799934387</v>
+        <v>1.86983788013458</v>
       </c>
       <c r="H681" t="n">
         <v>254</v>
@@ -20147,7 +20147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225122928619</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H682" t="n">
         <v>1859</v>
@@ -20176,7 +20176,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880341053009</v>
       </c>
       <c r="H683" t="n">
         <v>3849</v>
@@ -20205,7 +20205,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H684" t="n">
         <v>5886</v>
@@ -20234,7 +20234,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207950115204</v>
       </c>
       <c r="H685" t="n">
         <v>1968</v>
@@ -20321,7 +20321,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H688" t="n">
         <v>6201</v>
@@ -20379,7 +20379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H690" t="n">
         <v>725</v>
@@ -20408,7 +20408,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H693" t="n">
         <v>2480</v>
@@ -20495,7 +20495,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H694" t="n">
         <v>80</v>
@@ -20524,7 +20524,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H695" t="n">
         <v>2142</v>
@@ -20553,7 +20553,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H696" t="n">
         <v>2090</v>
@@ -20611,7 +20611,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H698" t="n">
         <v>1482</v>
@@ -20669,7 +20669,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H700" t="n">
         <v>2148</v>
@@ -20785,7 +20785,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H704" t="n">
         <v>1</v>
@@ -20814,7 +20814,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725244522095</v>
+        <v>2.01725268363953</v>
       </c>
       <c r="H705" t="n">
         <v>2758</v>
@@ -20872,7 +20872,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.96294188499451</v>
+        <v>1.96294176578522</v>
       </c>
       <c r="H707" t="n">
         <v>4382</v>
@@ -20930,7 +20930,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H709" t="n">
         <v>2556</v>
@@ -21017,7 +21017,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880341053009</v>
       </c>
       <c r="H712" t="n">
         <v>2116</v>
@@ -21046,7 +21046,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>1.84656190872192</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H713" t="n">
         <v>609</v>
@@ -21075,7 +21075,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H714" t="n">
         <v>2033</v>
@@ -21104,7 +21104,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207950115204</v>
       </c>
       <c r="H715" t="n">
         <v>1620</v>
@@ -21133,7 +21133,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>1.84656190872192</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H716" t="n">
         <v>48</v>
@@ -21162,7 +21162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225122928619</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H717" t="n">
         <v>747</v>
@@ -21191,7 +21191,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776882171631</v>
+        <v>1.80776858329773</v>
       </c>
       <c r="H718" t="n">
         <v>821</v>
@@ -21278,7 +21278,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569928646088</v>
+        <v>1.74569940567017</v>
       </c>
       <c r="H721" t="n">
         <v>2119</v>
@@ -21307,7 +21307,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328593730927</v>
       </c>
       <c r="H722" t="n">
         <v>1535</v>
@@ -21336,7 +21336,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328593730927</v>
       </c>
       <c r="H723" t="n">
         <v>8398</v>
@@ -21365,7 +21365,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H724" t="n">
         <v>2115</v>
@@ -21394,7 +21394,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311408996582</v>
+        <v>1.89311385154724</v>
       </c>
       <c r="H726" t="n">
         <v>6832</v>
@@ -21452,7 +21452,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.8853554725647</v>
+        <v>1.88535559177399</v>
       </c>
       <c r="H727" t="n">
         <v>1177</v>
@@ -21481,7 +21481,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759673595428</v>
       </c>
       <c r="H728" t="n">
         <v>961</v>
@@ -21510,7 +21510,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966591358185</v>
+        <v>1.93966603279114</v>
       </c>
       <c r="H729" t="n">
         <v>4613</v>
@@ -21539,7 +21539,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91639029979706</v>
+        <v>1.91638994216919</v>
       </c>
       <c r="H730" t="n">
         <v>2333</v>
@@ -21597,7 +21597,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H732" t="n">
         <v>19299</v>
@@ -21655,7 +21655,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>2.19570183753967</v>
+        <v>2.19570207595825</v>
       </c>
       <c r="H734" t="n">
         <v>12578</v>
@@ -21684,7 +21684,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H735" t="n">
         <v>3881</v>
@@ -21800,7 +21800,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H739" t="n">
         <v>2280</v>
@@ -21916,7 +21916,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.16466736793518</v>
+        <v>2.1646671295166</v>
       </c>
       <c r="H743" t="n">
         <v>2565</v>
@@ -21945,7 +21945,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H744" t="n">
         <v>6975</v>
@@ -22003,7 +22003,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H746" t="n">
         <v>1264</v>
@@ -22032,7 +22032,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H747" t="n">
         <v>149</v>
@@ -22090,7 +22090,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H749" t="n">
         <v>391</v>
@@ -22119,7 +22119,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H750" t="n">
         <v>1498</v>
@@ -22177,7 +22177,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H752" t="n">
         <v>6924</v>
@@ -22235,7 +22235,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H754" t="n">
         <v>2611</v>
@@ -22264,7 +22264,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H755" t="n">
         <v>1058</v>
@@ -22293,7 +22293,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H756" t="n">
         <v>1439</v>
@@ -22322,7 +22322,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="n">
-        <v>2.05604600906372</v>
+        <v>2.05604577064514</v>
       </c>
       <c r="H757" t="n">
         <v>2911</v>
@@ -22351,7 +22351,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H758" t="n">
         <v>645</v>
@@ -22409,7 +22409,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H760" t="n">
         <v>1417</v>
@@ -22554,7 +22554,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="n">
-        <v>2.05604600906372</v>
+        <v>2.05604577064514</v>
       </c>
       <c r="H765" t="n">
         <v>1593</v>
@@ -22641,7 +22641,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H768" t="n">
         <v>3478</v>
@@ -22699,7 +22699,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H770" t="n">
         <v>1195</v>
@@ -22989,7 +22989,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H780" t="n">
         <v>7946</v>
@@ -23018,7 +23018,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H781" t="n">
         <v>1441</v>
@@ -23047,7 +23047,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H782" t="n">
         <v>15901</v>
@@ -23134,7 +23134,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26553010940552</v>
+        <v>2.26552987098694</v>
       </c>
       <c r="H785" t="n">
         <v>674</v>
@@ -23163,7 +23163,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H786" t="n">
         <v>7919</v>
@@ -23192,7 +23192,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>2.24225378036499</v>
+        <v>2.24225401878357</v>
       </c>
       <c r="H787" t="n">
         <v>101</v>
@@ -23221,7 +23221,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>2.24225378036499</v>
+        <v>2.24225401878357</v>
       </c>
       <c r="H788" t="n">
         <v>2392</v>
@@ -23250,7 +23250,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087490081787</v>
       </c>
       <c r="H789" t="n">
         <v>9758</v>
@@ -23279,7 +23279,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H790" t="n">
         <v>6067</v>
@@ -23308,7 +23308,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H791" t="n">
         <v>238</v>
@@ -23337,7 +23337,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H792" t="n">
         <v>323</v>
@@ -23366,7 +23366,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656481742859</v>
       </c>
       <c r="H793" t="n">
         <v>206</v>
@@ -23395,7 +23395,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H794" t="n">
         <v>836</v>
@@ -23424,7 +23424,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H795" t="n">
         <v>1453</v>
@@ -23453,7 +23453,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.33535766601562</v>
+        <v>2.33535814285278</v>
       </c>
       <c r="H796" t="n">
         <v>1137</v>
@@ -23482,7 +23482,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H797" t="n">
         <v>1948</v>
@@ -23511,7 +23511,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H798" t="n">
         <v>381</v>
@@ -23569,7 +23569,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H800" t="n">
         <v>673</v>
@@ -23598,7 +23598,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H801" t="n">
         <v>693</v>
@@ -23627,7 +23627,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H802" t="n">
         <v>276</v>
@@ -23656,7 +23656,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846202850342</v>
       </c>
       <c r="H803" t="n">
         <v>8524</v>
@@ -23917,7 +23917,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41294455528259</v>
+        <v>2.41294431686401</v>
       </c>
       <c r="H812" t="n">
         <v>1173</v>
@@ -24207,7 +24207,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311628341675</v>
+        <v>2.34311652183533</v>
       </c>
       <c r="H822" t="n">
         <v>940</v>
@@ -24236,7 +24236,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087537765503</v>
+        <v>2.35087490081787</v>
       </c>
       <c r="H823" t="n">
         <v>367</v>
@@ -24265,7 +24265,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.37415146827698</v>
+        <v>2.3741512298584</v>
       </c>
       <c r="H824" t="n">
         <v>915</v>
@@ -24294,7 +24294,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H825" t="n">
         <v>186</v>
@@ -24323,7 +24323,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863399505615</v>
+        <v>2.35863375663757</v>
       </c>
       <c r="H826" t="n">
         <v>1041</v>
@@ -24410,7 +24410,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H829" t="n">
         <v>12604</v>
@@ -24439,7 +24439,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H830" t="n">
         <v>1806</v>
@@ -24468,7 +24468,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H831" t="n">
         <v>6065</v>
@@ -24497,7 +24497,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H832" t="n">
         <v>6312</v>
@@ -24526,7 +24526,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H833" t="n">
         <v>10097</v>
@@ -24555,7 +24555,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H834" t="n">
         <v>2763</v>
@@ -24613,7 +24613,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5526008605957</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H836" t="n">
         <v>21589</v>
@@ -24671,7 +24671,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H838" t="n">
         <v>12949</v>
@@ -24700,7 +24700,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H839" t="n">
         <v>9697</v>
@@ -24787,7 +24787,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H842" t="n">
         <v>1676</v>
@@ -25048,7 +25048,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H851" t="n">
         <v>2444</v>
@@ -25251,7 +25251,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H858" t="n">
         <v>6283</v>
@@ -25425,7 +25425,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H864" t="n">
         <v>462</v>
@@ -25483,7 +25483,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H866" t="n">
         <v>6419</v>
@@ -25657,7 +25657,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H872" t="n">
         <v>854</v>
@@ -25773,7 +25773,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.51195406913757</v>
+        <v>2.51195383071899</v>
       </c>
       <c r="H876" t="n">
         <v>900</v>
@@ -25860,7 +25860,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H879" t="n">
         <v>4136</v>
@@ -26353,7 +26353,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H896" t="n">
         <v>727</v>
@@ -26411,7 +26411,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H898" t="n">
         <v>2539</v>
@@ -26440,7 +26440,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H899" t="n">
         <v>483</v>
@@ -26469,7 +26469,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -26498,7 +26498,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H901" t="n">
         <v>609</v>
@@ -26527,7 +26527,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H902" t="n">
         <v>587</v>
@@ -26585,7 +26585,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H904" t="n">
         <v>217</v>
@@ -26643,7 +26643,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H906" t="n">
         <v>2576</v>
@@ -26672,7 +26672,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H907" t="n">
         <v>1983</v>
@@ -26730,7 +26730,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H909" t="n">
         <v>1732</v>
@@ -26788,7 +26788,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H911" t="n">
         <v>241</v>
@@ -26846,7 +26846,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H913" t="n">
         <v>1085</v>
@@ -26962,7 +26962,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="n">
-        <v>2.4144024848938</v>
+        <v>2.41440272331238</v>
       </c>
       <c r="H917" t="n">
         <v>2353</v>
@@ -27165,7 +27165,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H924" t="n">
         <v>715</v>
@@ -27223,7 +27223,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H926" t="n">
         <v>550</v>
@@ -27310,7 +27310,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H929" t="n">
         <v>12745</v>
@@ -27339,7 +27339,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H930" t="n">
         <v>855</v>
@@ -27426,7 +27426,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H933" t="n">
         <v>570</v>
@@ -27455,7 +27455,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H934" t="n">
         <v>259</v>
@@ -27484,7 +27484,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H935" t="n">
         <v>2163</v>
@@ -27600,7 +27600,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H939" t="n">
         <v>2176</v>
@@ -27658,7 +27658,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H941" t="n">
         <v>2257</v>
@@ -27687,7 +27687,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H942" t="n">
         <v>1218</v>
@@ -27774,7 +27774,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H945" t="n">
         <v>1348</v>
@@ -27919,7 +27919,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H950" t="n">
         <v>1523</v>
@@ -27977,7 +27977,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H952" t="n">
         <v>822</v>
@@ -28035,7 +28035,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H954" t="n">
         <v>2250</v>
@@ -28412,7 +28412,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H967" t="n">
         <v>563</v>
@@ -28499,7 +28499,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H970" t="n">
         <v>60</v>
@@ -28528,7 +28528,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H971" t="n">
         <v>600</v>
@@ -28586,7 +28586,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H973" t="n">
         <v>1750</v>
@@ -28615,7 +28615,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H974" t="n">
         <v>2339</v>
@@ -28673,7 +28673,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>2.44691944122314</v>
+        <v>2.44691967964172</v>
       </c>
       <c r="H976" t="n">
         <v>1209</v>
@@ -28702,7 +28702,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H977" t="n">
         <v>2732</v>
@@ -28731,7 +28731,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H978" t="n">
         <v>1913</v>
@@ -28760,7 +28760,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H979" t="n">
         <v>295</v>
@@ -28789,7 +28789,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H980" t="n">
         <v>239</v>
@@ -28876,7 +28876,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H983" t="n">
         <v>562</v>
@@ -28963,7 +28963,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H986" t="n">
         <v>1030</v>
@@ -29079,7 +29079,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>2.576988697052</v>
+        <v>2.57698845863342</v>
       </c>
       <c r="H990" t="n">
         <v>48</v>
@@ -29543,7 +29543,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.52008318901062</v>
+        <v>2.5200834274292</v>
       </c>
       <c r="H1006" t="n">
         <v>585</v>
@@ -29601,7 +29601,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.51195406913757</v>
+        <v>2.51195383071899</v>
       </c>
       <c r="H1008" t="n">
         <v>440</v>
@@ -29630,7 +29630,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.51195406913757</v>
+        <v>2.51195383071899</v>
       </c>
       <c r="H1009" t="n">
         <v>102</v>
@@ -29804,7 +29804,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1015" t="n">
         <v>284</v>
@@ -29862,7 +29862,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1017" t="n">
         <v>2120</v>
@@ -30065,7 +30065,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1024" t="n">
         <v>15330</v>
@@ -30094,7 +30094,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1025" t="n">
         <v>1646</v>
@@ -30123,7 +30123,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1026" t="n">
         <v>3715</v>
@@ -30181,7 +30181,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1028" t="n">
         <v>637</v>
@@ -30210,7 +30210,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30297,7 +30297,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504879951477</v>
+        <v>2.45504903793335</v>
       </c>
       <c r="H1032" t="n">
         <v>515</v>
@@ -30500,7 +30500,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1039" t="n">
         <v>2151</v>
@@ -30587,7 +30587,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1042" t="n">
         <v>304</v>
@@ -30703,7 +30703,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1046" t="n">
         <v>202</v>
@@ -30761,7 +30761,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1048" t="n">
         <v>5485</v>
@@ -30790,7 +30790,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1049" t="n">
         <v>199</v>
@@ -30848,7 +30848,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1051" t="n">
         <v>425</v>
@@ -30906,7 +30906,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1053" t="n">
         <v>6320</v>
@@ -31022,7 +31022,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1057" t="n">
         <v>6151</v>
@@ -31051,7 +31051,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548877716064</v>
+        <v>2.10548901557922</v>
       </c>
       <c r="H1058" t="n">
         <v>1769</v>
@@ -31138,7 +31138,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.04858374595642</v>
+        <v>2.048583984375</v>
       </c>
       <c r="H1061" t="n">
         <v>1381</v>
@@ -31167,7 +31167,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412713050842</v>
+        <v>1.89412724971771</v>
       </c>
       <c r="H1062" t="n">
         <v>1691</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1064" t="n">
         <v>931</v>
@@ -31254,7 +31254,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1065" t="n">
         <v>2252</v>
@@ -31341,7 +31341,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205015182495</v>
       </c>
       <c r="H1068" t="n">
         <v>7444</v>
@@ -31370,7 +31370,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1069" t="n">
         <v>3426</v>
@@ -31428,7 +31428,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.54863166809082</v>
+        <v>1.54863178730011</v>
       </c>
       <c r="H1071" t="n">
         <v>1513</v>
@@ -31457,7 +31457,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1072" t="n">
         <v>3746</v>
@@ -31544,7 +31544,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1075" t="n">
         <v>5340</v>
@@ -31573,7 +31573,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1076" t="n">
         <v>10</v>
@@ -31631,7 +31631,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.5730197429657</v>
+        <v>1.57301986217499</v>
       </c>
       <c r="H1078" t="n">
         <v>1319</v>
@@ -31689,7 +31689,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1080" t="n">
         <v>1096</v>
@@ -31776,7 +31776,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1083" t="n">
         <v>2497</v>
@@ -31805,7 +31805,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1084" t="n">
         <v>8072</v>
@@ -31892,7 +31892,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1087" t="n">
         <v>6324</v>
@@ -31950,7 +31950,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1089" t="n">
         <v>2736</v>
@@ -31979,7 +31979,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1090" t="n">
         <v>2958</v>
@@ -32124,7 +32124,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1095" t="n">
         <v>2072</v>
@@ -32182,7 +32182,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1097" t="n">
         <v>2013</v>
@@ -32298,7 +32298,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1101" t="n">
         <v>390</v>
@@ -32356,7 +32356,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1103" t="n">
         <v>1415</v>
@@ -32385,7 +32385,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1104" t="n">
         <v>934</v>
@@ -32414,7 +32414,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1105" t="n">
         <v>1244</v>
@@ -32443,7 +32443,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1106" t="n">
         <v>660</v>
@@ -32472,7 +32472,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1107" t="n">
         <v>749</v>
@@ -32501,7 +32501,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1108" t="n">
         <v>2147</v>
@@ -32530,7 +32530,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1109" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1110" t="n">
         <v>1215</v>
@@ -32588,7 +32588,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1111" t="n">
         <v>125</v>
@@ -32617,7 +32617,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1112" t="n">
         <v>194</v>
@@ -32646,7 +32646,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1113" t="n">
         <v>865</v>
@@ -32675,7 +32675,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.6502480506897</v>
+        <v>1.65024816989899</v>
       </c>
       <c r="H1114" t="n">
         <v>253</v>
@@ -32704,7 +32704,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1115" t="n">
         <v>2809</v>
@@ -32733,7 +32733,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1116" t="n">
         <v>2022</v>
@@ -32791,7 +32791,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1118" t="n">
         <v>546</v>
@@ -32849,7 +32849,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1120" t="n">
         <v>2501</v>
@@ -32878,7 +32878,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1121" t="n">
         <v>1115</v>
@@ -32936,7 +32936,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1123" t="n">
         <v>1674</v>
@@ -32965,7 +32965,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1124" t="n">
         <v>4336</v>
@@ -32994,7 +32994,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096350193024</v>
       </c>
       <c r="H1125" t="n">
         <v>10904</v>
@@ -33023,7 +33023,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1126" t="n">
         <v>735</v>
@@ -33052,7 +33052,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.87786841392517</v>
+        <v>1.87786865234375</v>
       </c>
       <c r="H1127" t="n">
         <v>3120</v>
@@ -33081,7 +33081,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1128" t="n">
         <v>2449</v>
@@ -33110,7 +33110,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1129" t="n">
         <v>1066</v>
@@ -33139,7 +33139,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1130" t="n">
         <v>474</v>
@@ -33168,7 +33168,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1131" t="n">
         <v>1560</v>
@@ -33226,7 +33226,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1133" t="n">
         <v>100</v>
@@ -33255,7 +33255,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096350193024</v>
       </c>
       <c r="H1134" t="n">
         <v>1491</v>
@@ -33284,7 +33284,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1135" t="n">
         <v>289</v>
@@ -33342,7 +33342,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1137" t="n">
         <v>525</v>
@@ -33371,7 +33371,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1138" t="n">
         <v>536</v>
@@ -33400,7 +33400,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1139" t="n">
         <v>2191</v>
@@ -33429,7 +33429,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.78031694889069</v>
+        <v>1.78031671047211</v>
       </c>
       <c r="H1140" t="n">
         <v>87</v>
@@ -33458,7 +33458,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1141" t="n">
         <v>161</v>
@@ -33487,7 +33487,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1142" t="n">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1143" t="n">
         <v>1762</v>
@@ -33545,7 +33545,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1144" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1146" t="n">
         <v>30</v>
@@ -33632,7 +33632,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1147" t="n">
         <v>103</v>
@@ -33661,7 +33661,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1148" t="n">
         <v>1910</v>
@@ -33748,7 +33748,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1151" t="n">
         <v>3317</v>
@@ -33777,7 +33777,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.78031694889069</v>
+        <v>1.78031671047211</v>
       </c>
       <c r="H1152" t="n">
         <v>7260</v>
@@ -33806,7 +33806,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.78031694889069</v>
+        <v>1.78031671047211</v>
       </c>
       <c r="H1153" t="n">
         <v>4915</v>
@@ -33864,7 +33864,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1155" t="n">
         <v>151</v>
@@ -33951,7 +33951,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1158" t="n">
         <v>1478</v>
@@ -33980,7 +33980,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1159" t="n">
         <v>1358</v>
@@ -34009,7 +34009,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1160" t="n">
         <v>405</v>
@@ -34038,7 +34038,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1161" t="n">
         <v>200</v>
@@ -34067,7 +34067,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1162" t="n">
         <v>185</v>
@@ -34096,7 +34096,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1163" t="n">
         <v>392</v>
@@ -34125,7 +34125,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1164" t="n">
         <v>12</v>
@@ -34183,7 +34183,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1166" t="n">
         <v>1391</v>
@@ -34212,7 +34212,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089484214783</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1167" t="n">
         <v>1114</v>
@@ -34241,7 +34241,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1168" t="n">
         <v>182</v>
@@ -34270,7 +34270,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1169" t="n">
         <v>540</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1171" t="n">
         <v>330</v>
@@ -34357,7 +34357,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1172" t="n">
         <v>950</v>
@@ -34386,7 +34386,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1173" t="n">
         <v>886</v>
@@ -34444,7 +34444,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1175" t="n">
         <v>176</v>
@@ -34502,7 +34502,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1177" t="n">
         <v>402</v>
@@ -34531,7 +34531,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1178" t="n">
         <v>250</v>
@@ -34560,7 +34560,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.78031694889069</v>
+        <v>1.78031671047211</v>
       </c>
       <c r="H1179" t="n">
         <v>520</v>
@@ -34618,7 +34618,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1181" t="n">
         <v>15</v>
@@ -34821,7 +34821,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1188" t="n">
         <v>3060</v>
@@ -34850,7 +34850,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.68276536464691</v>
+        <v>1.6827654838562</v>
       </c>
       <c r="H1189" t="n">
         <v>2798</v>
@@ -34879,7 +34879,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.68276536464691</v>
+        <v>1.6827654838562</v>
       </c>
       <c r="H1190" t="n">
         <v>545</v>
@@ -34908,7 +34908,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1191" t="n">
         <v>1130</v>
@@ -34937,7 +34937,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1192" t="n">
         <v>3300</v>
@@ -35024,7 +35024,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1195" t="n">
         <v>486</v>
@@ -35053,7 +35053,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.6502480506897</v>
+        <v>1.65024816989899</v>
       </c>
       <c r="H1196" t="n">
         <v>335</v>
@@ -35082,7 +35082,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1197" t="n">
         <v>6595</v>
@@ -35111,7 +35111,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.60960161685944</v>
+        <v>1.60960149765015</v>
       </c>
       <c r="H1198" t="n">
         <v>201</v>
@@ -35140,7 +35140,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.64211893081665</v>
+        <v>1.64211881160736</v>
       </c>
       <c r="H1199" t="n">
         <v>1905</v>
@@ -35169,7 +35169,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1200" t="n">
         <v>1704</v>
@@ -35198,7 +35198,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1201" t="n">
         <v>718</v>
@@ -35227,7 +35227,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114910125732</v>
+        <v>1.58114922046661</v>
       </c>
       <c r="H1202" t="n">
         <v>782</v>
@@ -35256,7 +35256,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1203" t="n">
         <v>1145</v>
@@ -35285,7 +35285,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.60553705692291</v>
+        <v>1.60553693771362</v>
       </c>
       <c r="H1204" t="n">
         <v>874</v>
@@ -35314,7 +35314,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1205" t="n">
         <v>2215</v>
@@ -35372,7 +35372,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1207" t="n">
         <v>299</v>
@@ -35488,7 +35488,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1211" t="n">
         <v>302</v>
@@ -35546,7 +35546,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1213" t="n">
         <v>1613</v>
@@ -35662,7 +35662,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.42262780666351</v>
+        <v>1.42262768745422</v>
       </c>
       <c r="H1217" t="n">
         <v>5136</v>
@@ -35691,7 +35691,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.41043376922607</v>
+        <v>1.41043388843536</v>
       </c>
       <c r="H1218" t="n">
         <v>1274</v>
@@ -35720,7 +35720,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.40636897087097</v>
+        <v>1.40636909008026</v>
       </c>
       <c r="H1219" t="n">
         <v>2254</v>
@@ -35778,7 +35778,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.42262780666351</v>
+        <v>1.42262768745422</v>
       </c>
       <c r="H1221" t="n">
         <v>283</v>
@@ -35807,7 +35807,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.4144983291626</v>
+        <v>1.41449844837189</v>
       </c>
       <c r="H1222" t="n">
         <v>2154</v>
@@ -35865,7 +35865,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.33320546150208</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1224" t="n">
         <v>2739</v>
@@ -35894,7 +35894,7 @@
         <v>17</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.38198125362396</v>
+        <v>1.38198113441467</v>
       </c>
       <c r="H1225" t="n">
         <v>2336</v>
@@ -35923,7 +35923,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.35759341716766</v>
+        <v>1.35759329795837</v>
       </c>
       <c r="H1226" t="n">
         <v>100</v>
@@ -35952,7 +35952,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.33320546150208</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1227" t="n">
         <v>4118</v>
@@ -36126,7 +36126,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946393966675</v>
+        <v>1.34946405887604</v>
       </c>
       <c r="H1233" t="n">
         <v>466</v>
@@ -36184,7 +36184,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.35352849960327</v>
+        <v>1.35352861881256</v>
       </c>
       <c r="H1235" t="n">
         <v>9650</v>
@@ -36213,7 +36213,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823973178864</v>
       </c>
       <c r="H1236" t="n">
         <v>5735</v>
@@ -36271,7 +36271,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.4144983291626</v>
+        <v>1.41449844837189</v>
       </c>
       <c r="H1238" t="n">
         <v>1249</v>
@@ -36300,7 +36300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.38604581356049</v>
+        <v>1.3860456943512</v>
       </c>
       <c r="H1239" t="n">
         <v>2206</v>
@@ -36329,7 +36329,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39823985099792</v>
+        <v>1.39823973178864</v>
       </c>
       <c r="H1240" t="n">
         <v>3452</v>
@@ -36358,7 +36358,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.3901104927063</v>
+        <v>1.39011061191559</v>
       </c>
       <c r="H1241" t="n">
         <v>2655</v>
@@ -36474,7 +36474,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.42262780666351</v>
+        <v>1.42262768745422</v>
       </c>
       <c r="H1245" t="n">
         <v>4463</v>
@@ -36503,7 +36503,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.4673388004303</v>
+        <v>1.46733868122101</v>
       </c>
       <c r="H1246" t="n">
         <v>4901</v>
@@ -36590,7 +36590,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1249" t="n">
         <v>996</v>
@@ -36677,7 +36677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1252" t="n">
         <v>3478</v>
@@ -36735,7 +36735,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1254" t="n">
         <v>12588</v>
@@ -36764,7 +36764,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.49172675609589</v>
+        <v>1.49172687530518</v>
       </c>
       <c r="H1255" t="n">
         <v>3603</v>
@@ -36880,7 +36880,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1259" t="n">
         <v>4474</v>
@@ -36938,7 +36938,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1261" t="n">
         <v>4222</v>
@@ -36967,7 +36967,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205015182495</v>
       </c>
       <c r="H1262" t="n">
         <v>2986</v>
@@ -37054,7 +37054,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.5242440700531</v>
+        <v>1.52424395084381</v>
       </c>
       <c r="H1265" t="n">
         <v>1723</v>
@@ -37199,7 +37199,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1270" t="n">
         <v>19327</v>
@@ -37228,7 +37228,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.54050266742706</v>
+        <v>1.54050254821777</v>
       </c>
       <c r="H1271" t="n">
         <v>7329</v>
@@ -37315,7 +37315,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1274" t="n">
         <v>23428</v>
@@ -37402,7 +37402,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.55269658565521</v>
+        <v>1.5526967048645</v>
       </c>
       <c r="H1277" t="n">
         <v>639</v>
@@ -37431,7 +37431,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1278" t="n">
         <v>607</v>
@@ -37663,7 +37663,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.47953283786774</v>
+        <v>1.47953295707703</v>
       </c>
       <c r="H1286" t="n">
         <v>5166</v>
@@ -37750,7 +37750,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.54050266742706</v>
+        <v>1.54050254821777</v>
       </c>
       <c r="H1289" t="n">
         <v>1527</v>
@@ -37808,7 +37808,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.49985611438751</v>
+        <v>1.49985599517822</v>
       </c>
       <c r="H1291" t="n">
         <v>5905</v>
@@ -37837,7 +37837,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.5445671081543</v>
+        <v>1.54456722736359</v>
       </c>
       <c r="H1292" t="n">
         <v>4865</v>
@@ -37866,7 +37866,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973917484283</v>
+        <v>1.86973929405212</v>
       </c>
       <c r="H1293" t="n">
         <v>71320</v>
@@ -37953,7 +37953,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1296" t="n">
         <v>31317</v>
@@ -37982,7 +37982,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1297" t="n">
         <v>34162</v>
@@ -38040,7 +38040,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1299" t="n">
         <v>11185</v>
@@ -38098,7 +38098,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1301" t="n">
         <v>6160</v>
@@ -38127,7 +38127,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1302" t="n">
         <v>4831</v>
@@ -38185,7 +38185,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1304" t="n">
         <v>3101</v>
@@ -38214,7 +38214,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1305" t="n">
         <v>1089</v>
@@ -38272,7 +38272,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1307" t="n">
         <v>2734</v>
@@ -38301,7 +38301,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1308" t="n">
         <v>12016</v>
@@ -38359,7 +38359,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1310" t="n">
         <v>2703</v>
@@ -38388,7 +38388,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1311" t="n">
         <v>801</v>
@@ -38562,7 +38562,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.2599458694458</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1317" t="n">
         <v>1038</v>
@@ -38591,7 +38591,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.2599458694458</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1318" t="n">
         <v>245</v>
@@ -38736,7 +38736,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1323" t="n">
         <v>547</v>
@@ -38765,7 +38765,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1324" t="n">
         <v>1989</v>
@@ -38823,7 +38823,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671286582947</v>
+        <v>2.05671310424805</v>
       </c>
       <c r="H1326" t="n">
         <v>2194</v>
@@ -38852,7 +38852,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1327" t="n">
         <v>825</v>
@@ -38881,7 +38881,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.08110117912292</v>
+        <v>2.08110094070435</v>
       </c>
       <c r="H1328" t="n">
         <v>985</v>
@@ -38910,7 +38910,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361813545227</v>
+        <v>2.11361837387085</v>
       </c>
       <c r="H1329" t="n">
         <v>574</v>
@@ -38997,7 +38997,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1332" t="n">
         <v>261</v>
@@ -39026,7 +39026,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1333" t="n">
         <v>364</v>
@@ -39316,7 +39316,7 @@
         <v>27</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1343" t="n">
         <v>1560</v>
@@ -39577,7 +39577,7 @@
         <v>27</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1352" t="n">
         <v>626</v>
@@ -39664,7 +39664,7 @@
         <v>27</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1355" t="n">
         <v>15</v>
@@ -40360,7 +40360,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1379" t="n">
         <v>4492</v>
@@ -40389,7 +40389,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1380" t="n">
         <v>3109</v>
@@ -40418,7 +40418,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1381" t="n">
         <v>14062</v>
@@ -40447,7 +40447,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1382" t="n">
         <v>4336</v>
@@ -40563,7 +40563,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1386" t="n">
         <v>12870</v>
@@ -40592,7 +40592,7 @@
         <v>30</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1387" t="n">
         <v>3844</v>
@@ -40621,7 +40621,7 @@
         <v>30</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1388" t="n">
         <v>3485</v>
@@ -40650,7 +40650,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1389" t="n">
         <v>1513</v>
@@ -40679,7 +40679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1390" t="n">
         <v>11</v>
@@ -40708,7 +40708,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1391" t="n">
         <v>1103</v>
@@ -40737,7 +40737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1392" t="n">
         <v>2136</v>
@@ -40766,7 +40766,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1393" t="n">
         <v>3074</v>
@@ -40824,7 +40824,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1395" t="n">
         <v>3834</v>
@@ -40911,7 +40911,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1398" t="n">
         <v>1418</v>
@@ -40940,7 +40940,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1399" t="n">
         <v>110</v>
@@ -41027,7 +41027,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1402" t="n">
         <v>1523</v>
@@ -41085,7 +41085,7 @@
         <v>30</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1404" t="n">
         <v>1557</v>
@@ -41259,7 +41259,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1410" t="n">
         <v>603</v>
@@ -41578,7 +41578,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1421" t="n">
         <v>2630</v>
@@ -41665,7 +41665,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1424" t="n">
         <v>784</v>
@@ -41694,7 +41694,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1425" t="n">
         <v>1447</v>
@@ -41926,7 +41926,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1433" t="n">
         <v>2277</v>
@@ -42071,7 +42071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1438" t="n">
         <v>325</v>
@@ -42129,7 +42129,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1440" t="n">
         <v>160</v>
@@ -42245,7 +42245,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1444" t="n">
         <v>1866</v>
@@ -42274,7 +42274,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1445" t="n">
         <v>1333</v>
@@ -42303,7 +42303,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1446" t="n">
         <v>2352</v>
@@ -42564,7 +42564,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1455" t="n">
         <v>1776</v>
@@ -42941,7 +42941,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1468" t="n">
         <v>141</v>
@@ -43144,7 +43144,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1475" t="n">
         <v>691</v>
@@ -43173,7 +43173,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1476" t="n">
         <v>1400</v>
@@ -43202,7 +43202,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1477" t="n">
         <v>169</v>
@@ -43231,7 +43231,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1478" t="n">
         <v>890</v>
@@ -43521,7 +43521,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1488" t="n">
         <v>110</v>
@@ -43579,7 +43579,7 @@
         <v>27.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1490" t="n">
         <v>3333</v>
@@ -43869,7 +43869,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1500" t="n">
         <v>252</v>
@@ -43898,7 +43898,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -44565,7 +44565,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1524" t="n">
         <v>420</v>
@@ -44623,7 +44623,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1526" t="n">
         <v>311</v>
@@ -44652,7 +44652,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1527" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1528" t="n">
         <v>137</v>
@@ -44739,7 +44739,7 @@
         <v>27.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1530" t="n">
         <v>242</v>
@@ -44826,7 +44826,7 @@
         <v>27.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1533" t="n">
         <v>200</v>
@@ -44855,7 +44855,7 @@
         <v>27.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1534" t="n">
         <v>0</v>
@@ -44884,7 +44884,7 @@
         <v>27.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1535" t="n">
         <v>300</v>
@@ -44913,7 +44913,7 @@
         <v>27.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1536" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>27</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1540" t="n">
         <v>140</v>
@@ -45087,7 +45087,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1542" t="n">
         <v>511</v>
@@ -45116,7 +45116,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.26085901260376</v>
+        <v>2.26085925102234</v>
       </c>
       <c r="H1543" t="n">
         <v>516</v>
@@ -45145,7 +45145,7 @@
         <v>27</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1544" t="n">
         <v>135</v>
@@ -45464,7 +45464,7 @@
         <v>27.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1555" t="n">
         <v>107</v>
@@ -45493,7 +45493,7 @@
         <v>27.5</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1556" t="n">
         <v>639</v>
@@ -45551,7 +45551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1558" t="n">
         <v>1582</v>
@@ -45638,7 +45638,7 @@
         <v>27</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1561" t="n">
         <v>1549</v>
@@ -45667,7 +45667,7 @@
         <v>27</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1562" t="n">
         <v>1015</v>
@@ -45754,7 +45754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1565" t="n">
         <v>2831</v>
@@ -45899,7 +45899,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1570" t="n">
         <v>3995</v>
@@ -45986,7 +45986,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.46789741516113</v>
+        <v>2.46789717674255</v>
       </c>
       <c r="H1573" t="n">
         <v>685</v>
@@ -46015,7 +46015,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102353096008</v>
+        <v>2.50102376937866</v>
       </c>
       <c r="H1574" t="n">
         <v>6269</v>
@@ -46044,7 +46044,7 @@
         <v>30</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1575" t="n">
         <v>632</v>
@@ -46073,7 +46073,7 @@
         <v>30.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1576" t="n">
         <v>2316</v>
@@ -46102,7 +46102,7 @@
         <v>30.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1577" t="n">
         <v>2195</v>
@@ -46189,7 +46189,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.71634364128113</v>
+        <v>2.71634340286255</v>
       </c>
       <c r="H1580" t="n">
         <v>8590</v>
@@ -46247,7 +46247,7 @@
         <v>34</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.81572222709656</v>
+        <v>2.81572198867798</v>
       </c>
       <c r="H1582" t="n">
         <v>5135</v>
@@ -46392,7 +46392,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.24636220932007</v>
+        <v>3.24636197090149</v>
       </c>
       <c r="H1587" t="n">
         <v>14504</v>
@@ -46421,7 +46421,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1588" t="n">
         <v>15352</v>
@@ -46479,7 +46479,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1590" t="n">
         <v>7873</v>
@@ -46537,7 +46537,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1592" t="n">
         <v>19325</v>
@@ -46595,7 +46595,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1594" t="n">
         <v>22091</v>
@@ -46624,7 +46624,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1595" t="n">
         <v>58723</v>
@@ -46653,7 +46653,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.21323561668396</v>
+        <v>3.21323585510254</v>
       </c>
       <c r="H1596" t="n">
         <v>2947</v>
@@ -46885,7 +46885,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1604" t="n">
         <v>3473</v>
@@ -46943,7 +46943,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1606" t="n">
         <v>701</v>
@@ -46972,7 +46972,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1607" t="n">
         <v>5882</v>
@@ -47001,7 +47001,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1608" t="n">
         <v>869</v>
@@ -47030,7 +47030,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1609" t="n">
         <v>201</v>
@@ -47088,7 +47088,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1611" t="n">
         <v>2250</v>
@@ -47117,7 +47117,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1612" t="n">
         <v>150</v>
@@ -47175,7 +47175,7 @@
         <v>37</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1614" t="n">
         <v>1853</v>
@@ -47204,7 +47204,7 @@
         <v>37</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1615" t="n">
         <v>1740</v>
@@ -47233,7 +47233,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1616" t="n">
         <v>221</v>
@@ -47262,7 +47262,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1617" t="n">
         <v>1595</v>
@@ -47291,7 +47291,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1618" t="n">
         <v>2357</v>
@@ -47436,7 +47436,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1623" t="n">
         <v>4769</v>
@@ -47552,7 +47552,7 @@
         <v>37</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1627" t="n">
         <v>500</v>
@@ -47726,7 +47726,7 @@
         <v>37</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1633" t="n">
         <v>593</v>
@@ -47784,7 +47784,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1635" t="n">
         <v>1882</v>
@@ -47813,7 +47813,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1636" t="n">
         <v>365</v>
@@ -47842,7 +47842,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1637" t="n">
         <v>2785</v>
@@ -47871,7 +47871,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1638" t="n">
         <v>2270</v>
@@ -47900,7 +47900,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1639" t="n">
         <v>2725</v>
@@ -48045,7 +48045,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1644" t="n">
         <v>4061</v>
@@ -48074,7 +48074,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1645" t="n">
         <v>8289</v>
@@ -48103,7 +48103,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1646" t="n">
         <v>569</v>
@@ -48161,7 +48161,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1648" t="n">
         <v>13</v>
@@ -48190,7 +48190,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1649" t="n">
         <v>642</v>
@@ -48335,7 +48335,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1654" t="n">
         <v>513</v>
@@ -48422,7 +48422,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1657" t="n">
         <v>692</v>
@@ -48451,7 +48451,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1658" t="n">
         <v>1340</v>
@@ -48480,7 +48480,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1659" t="n">
         <v>408</v>
@@ -48538,7 +48538,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1661" t="n">
         <v>277</v>
@@ -48596,7 +48596,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1663" t="n">
         <v>3180</v>
@@ -48799,7 +48799,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1670" t="n">
         <v>184</v>
@@ -49060,7 +49060,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1679" t="n">
         <v>653</v>
@@ -49089,7 +49089,7 @@
         <v>37</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1680" t="n">
         <v>61</v>
@@ -49118,7 +49118,7 @@
         <v>37</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1681" t="n">
         <v>25</v>
@@ -49292,7 +49292,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1687" t="n">
         <v>76</v>
@@ -49321,7 +49321,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1688" t="n">
         <v>0</v>
@@ -49408,7 +49408,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1691" t="n">
         <v>198</v>
@@ -49495,7 +49495,7 @@
         <v>37</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1694" t="n">
         <v>3210</v>
@@ -49524,7 +49524,7 @@
         <v>37</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1695" t="n">
         <v>46</v>
@@ -49553,7 +49553,7 @@
         <v>37</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1696" t="n">
         <v>3</v>
@@ -49727,7 +49727,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1702" t="n">
         <v>142</v>
@@ -49756,7 +49756,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1703" t="n">
         <v>0</v>
@@ -49785,7 +49785,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1704" t="n">
         <v>395</v>
@@ -49843,7 +49843,7 @@
         <v>37</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1706" t="n">
         <v>63</v>
@@ -49901,7 +49901,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1708" t="n">
         <v>796</v>
@@ -49959,7 +49959,7 @@
         <v>37</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1710" t="n">
         <v>2446</v>
@@ -49988,7 +49988,7 @@
         <v>37</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50249,7 +50249,7 @@
         <v>37</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1720" t="n">
         <v>1410</v>
@@ -50336,7 +50336,7 @@
         <v>37</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1723" t="n">
         <v>2800</v>
@@ -50510,7 +50510,7 @@
         <v>37</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1729" t="n">
         <v>7186</v>
@@ -50568,7 +50568,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1731" t="n">
         <v>10</v>
@@ -50597,7 +50597,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1732" t="n">
         <v>150</v>
@@ -50626,7 +50626,7 @@
         <v>37</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1733" t="n">
         <v>3284</v>
@@ -50655,7 +50655,7 @@
         <v>37</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1734" t="n">
         <v>886</v>
@@ -50684,7 +50684,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1735" t="n">
         <v>1334</v>
@@ -50713,7 +50713,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1736" t="n">
         <v>6368</v>
@@ -50742,7 +50742,7 @@
         <v>37</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1737" t="n">
         <v>860</v>
@@ -50771,7 +50771,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1738" t="n">
         <v>492</v>
@@ -50800,7 +50800,7 @@
         <v>37</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1739" t="n">
         <v>958</v>
@@ -50829,7 +50829,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1740" t="n">
         <v>4</v>
@@ -50887,7 +50887,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1742" t="n">
         <v>1413</v>
@@ -50916,7 +50916,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1743" t="n">
         <v>71451</v>
@@ -50945,7 +50945,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1744" t="n">
         <v>53786</v>
@@ -50974,7 +50974,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1745" t="n">
         <v>4978</v>
@@ -51003,7 +51003,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1746" t="n">
         <v>21294</v>
@@ -51032,7 +51032,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1747" t="n">
         <v>14353</v>
@@ -51061,7 +51061,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1748" t="n">
         <v>4653</v>
@@ -51090,7 +51090,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1749" t="n">
         <v>20045</v>
@@ -51119,7 +51119,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1750" t="n">
         <v>29641</v>
@@ -51148,7 +51148,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1751" t="n">
         <v>15953</v>
@@ -51177,7 +51177,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1752" t="n">
         <v>4145</v>
@@ -51264,7 +51264,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1755" t="n">
         <v>2128</v>
@@ -51409,7 +51409,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1760" t="n">
         <v>8943</v>
@@ -51467,7 +51467,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1762" t="n">
         <v>17040</v>
@@ -51496,7 +51496,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1763" t="n">
         <v>11932</v>
@@ -51525,7 +51525,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1764" t="n">
         <v>6338</v>
@@ -51554,7 +51554,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1765" t="n">
         <v>11888</v>
@@ -51583,7 +51583,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1766" t="n">
         <v>9167</v>
@@ -51612,7 +51612,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.20495414733887</v>
+        <v>3.20495438575745</v>
       </c>
       <c r="H1767" t="n">
         <v>15127</v>
@@ -51670,7 +51670,7 @@
         <v>39.5</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1769" t="n">
         <v>2890</v>
@@ -51699,7 +51699,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1770" t="n">
         <v>4370</v>
@@ -51786,7 +51786,7 @@
         <v>39.5</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1773" t="n">
         <v>44802</v>
@@ -80026,7 +80026,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="E2747" t="n">
-        <v>2.6800000667572</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="F2747" t="n">
         <v>2.66000008583069</v>
@@ -80038,6 +80038,35 @@
         <v>200</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>566</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H2" t="n">
         <v>328</v>
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544644355774</v>
+        <v>1.24544656276703</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -514,7 +514,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H5" t="n">
         <v>1168</v>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541845798492</v>
       </c>
       <c r="H6" t="n">
         <v>466</v>
@@ -630,7 +630,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H9" t="n">
         <v>8746</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2011194229126</v>
+        <v>1.20111954212189</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -775,7 +775,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.16680181026459</v>
+        <v>1.16680192947388</v>
       </c>
       <c r="H14" t="n">
         <v>2159</v>
@@ -804,7 +804,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468486309052</v>
+        <v>1.19468474388123</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045144557953</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -891,7 +891,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H18" t="n">
         <v>605</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687623977661</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687623977661</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -978,7 +978,7 @@
         <v>17.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.25116622447968</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H21" t="n">
         <v>1559</v>
@@ -1007,7 +1007,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475024223328</v>
+        <v>1.26475036144257</v>
       </c>
       <c r="H22" t="n">
         <v>1772</v>
@@ -1065,7 +1065,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541845798492</v>
       </c>
       <c r="H24" t="n">
         <v>132</v>
@@ -1123,7 +1123,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H26" t="n">
         <v>2636</v>
@@ -1181,7 +1181,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G28" t="n">
-        <v>1.210413813591</v>
+        <v>1.21041393280029</v>
       </c>
       <c r="H28" t="n">
         <v>118</v>
@@ -1268,7 +1268,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H31" t="n">
         <v>39</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1326,7 +1326,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>1.20469439029694</v>
+        <v>1.20469427108765</v>
       </c>
       <c r="H33" t="n">
         <v>276</v>
@@ -1355,7 +1355,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256791591644</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H34" t="n">
         <v>772</v>
@@ -1384,7 +1384,7 @@
         <v>17.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25116622447968</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H35" t="n">
         <v>2452</v>
@@ -1442,7 +1442,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H37" t="n">
         <v>11933</v>
@@ -1471,7 +1471,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903058052063</v>
+        <v>1.25903081893921</v>
       </c>
       <c r="H38" t="n">
         <v>6392</v>
@@ -1500,7 +1500,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903986930847</v>
+        <v>1.26903998851776</v>
       </c>
       <c r="H39" t="n">
         <v>3180</v>
@@ -1587,7 +1587,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H42" t="n">
         <v>340</v>
@@ -1616,7 +1616,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616158008575</v>
+        <v>1.24616146087646</v>
       </c>
       <c r="H43" t="n">
         <v>1037</v>
@@ -1674,7 +1674,7 @@
         <v>17.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.25116622447968</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H45" t="n">
         <v>26</v>
@@ -1732,7 +1732,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689493656158</v>
+        <v>1.26689505577087</v>
       </c>
       <c r="H47" t="n">
         <v>7764</v>
@@ -1761,7 +1761,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H48" t="n">
         <v>1421</v>
@@ -1790,7 +1790,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>1.27189970016479</v>
+        <v>1.27189993858337</v>
       </c>
       <c r="H49" t="n">
         <v>500</v>
@@ -1819,7 +1819,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H50" t="n">
         <v>3624</v>
@@ -1964,7 +1964,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.26546537876129</v>
+        <v>1.265465259552</v>
       </c>
       <c r="H55" t="n">
         <v>584</v>
@@ -2022,7 +2022,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H57" t="n">
         <v>62</v>
@@ -2196,7 +2196,7 @@
         <v>17.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25116622447968</v>
+        <v>1.25116610527039</v>
       </c>
       <c r="H63" t="n">
         <v>556</v>
@@ -2225,7 +2225,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.2490211725235</v>
+        <v>1.24902129173279</v>
       </c>
       <c r="H64" t="n">
         <v>523</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045144557953</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258673191071</v>
+        <v>1.24258649349213</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2312,7 +2312,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686683177948</v>
+        <v>1.23686695098877</v>
       </c>
       <c r="H67" t="n">
         <v>70</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2370,7 +2370,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H69" t="n">
         <v>538</v>
@@ -2399,7 +2399,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400723934174</v>
+        <v>1.23400712013245</v>
       </c>
       <c r="H71" t="n">
         <v>6242</v>
@@ -2486,7 +2486,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H73" t="n">
         <v>1010</v>
@@ -2515,7 +2515,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615229129791</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H74" t="n">
         <v>1039</v>
@@ -2573,7 +2573,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H76" t="n">
         <v>2231</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2805,7 +2805,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323187351227</v>
+        <v>1.26323175430298</v>
       </c>
       <c r="H84" t="n">
         <v>220</v>
@@ -2834,7 +2834,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H85" t="n">
         <v>149</v>
@@ -2863,7 +2863,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323187351227</v>
+        <v>1.26323175430298</v>
       </c>
       <c r="H86" t="n">
         <v>105</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -2950,7 +2950,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445637226105</v>
+        <v>1.28445661067963</v>
       </c>
       <c r="H89" t="n">
         <v>1506</v>
@@ -3095,7 +3095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347826957703</v>
+        <v>1.27347815036774</v>
       </c>
       <c r="H94" t="n">
         <v>370</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494204044342</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3182,7 +3182,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H97" t="n">
         <v>1320</v>
@@ -3211,7 +3211,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>1.28226089477539</v>
+        <v>1.28226101398468</v>
       </c>
       <c r="H98" t="n">
         <v>573</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811585903168</v>
+        <v>1.28811597824097</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H108" t="n">
         <v>3785</v>
@@ -3530,7 +3530,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H109" t="n">
         <v>12</v>
@@ -3559,7 +3559,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176810264587</v>
+        <v>1.26176822185516</v>
       </c>
       <c r="H111" t="n">
         <v>594</v>
@@ -3733,7 +3733,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H116" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663772106171</v>
+        <v>1.226637840271</v>
       </c>
       <c r="H117" t="n">
         <v>120</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -3936,7 +3936,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784785270691</v>
+        <v>1.18784773349762</v>
       </c>
       <c r="H123" t="n">
         <v>1361</v>
@@ -3994,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H125" t="n">
         <v>673</v>
@@ -4023,7 +4023,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>1.17028272151947</v>
+        <v>1.17028260231018</v>
       </c>
       <c r="H126" t="n">
         <v>237</v>
@@ -4052,7 +4052,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G127" t="n">
-        <v>1.17028272151947</v>
+        <v>1.17028260231018</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G128" t="n">
-        <v>1.17028272151947</v>
+        <v>1.17028260231018</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H129" t="n">
         <v>1649</v>
@@ -4139,7 +4139,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>1.17028272151947</v>
+        <v>1.17028260231018</v>
       </c>
       <c r="H130" t="n">
         <v>350</v>
@@ -4197,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H132" t="n">
         <v>171</v>
@@ -4226,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H133" t="n">
         <v>101</v>
@@ -4255,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H134" t="n">
         <v>245</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4806,7 +4806,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736242294312</v>
+        <v>1.19736230373383</v>
       </c>
       <c r="H153" t="n">
         <v>1720</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712303161621</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322474956512</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H157" t="n">
         <v>390</v>
@@ -4951,7 +4951,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249268531799</v>
+        <v>1.23249280452728</v>
       </c>
       <c r="H158" t="n">
         <v>2050</v>
@@ -4980,7 +4980,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883355617523</v>
+        <v>1.22883343696594</v>
       </c>
       <c r="H159" t="n">
         <v>486</v>
@@ -5009,7 +5009,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H160" t="n">
         <v>366</v>
@@ -5038,7 +5038,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H161" t="n">
         <v>10275</v>
@@ -5125,7 +5125,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G164" t="n">
-        <v>1.28226089477539</v>
+        <v>1.28226101398468</v>
       </c>
       <c r="H164" t="n">
         <v>5537</v>
@@ -5154,7 +5154,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H165" t="n">
         <v>430</v>
@@ -5183,7 +5183,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.3071448802948</v>
+        <v>1.30714499950409</v>
       </c>
       <c r="H166" t="n">
         <v>3048</v>
@@ -5299,7 +5299,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763767242432</v>
+        <v>1.32763755321503</v>
       </c>
       <c r="H170" t="n">
         <v>14161</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763054847717</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5473,7 +5473,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982602596283</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="n">
         <v>1808</v>
@@ -5531,7 +5531,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543483257294</v>
+        <v>1.29543495178223</v>
       </c>
       <c r="H178" t="n">
         <v>703</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763054847717</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5705,7 +5705,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055809020996</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055809020996</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836237430573</v>
+        <v>1.29836225509644</v>
       </c>
       <c r="H186" t="n">
         <v>4389</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763054847717</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250729084015</v>
+        <v>1.29250717163086</v>
       </c>
       <c r="H189" t="n">
         <v>625</v>
@@ -5879,7 +5879,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G190" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H190" t="n">
         <v>135</v>
@@ -5908,7 +5908,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G191" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H191" t="n">
         <v>80</v>
@@ -5937,7 +5937,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G192" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H192" t="n">
         <v>81</v>
@@ -5995,7 +5995,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>1.26908695697784</v>
+        <v>1.26908683776855</v>
       </c>
       <c r="H194" t="n">
         <v>6154</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786221981049</v>
+        <v>1.2478621006012</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6140,7 +6140,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G199" t="n">
-        <v>1.25518095493317</v>
+        <v>1.25518107414246</v>
       </c>
       <c r="H199" t="n">
         <v>1811</v>
@@ -6169,7 +6169,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542747020721</v>
       </c>
       <c r="H200" t="n">
         <v>14244</v>
@@ -6198,7 +6198,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006517887115</v>
+        <v>1.28006529808044</v>
       </c>
       <c r="H201" t="n">
         <v>19504</v>
@@ -6227,7 +6227,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H202" t="n">
         <v>22671</v>
@@ -6256,7 +6256,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810861587524</v>
+        <v>1.25810873508453</v>
       </c>
       <c r="H203" t="n">
         <v>11122</v>
@@ -6343,7 +6343,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639868736267</v>
+        <v>1.24639856815338</v>
       </c>
       <c r="H206" t="n">
         <v>7757</v>
@@ -6430,7 +6430,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H209" t="n">
         <v>5810</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688399791718</v>
+        <v>1.23688411712646</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6517,7 +6517,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2420072555542</v>
+        <v>1.24200713634491</v>
       </c>
       <c r="H212" t="n">
         <v>21105</v>
@@ -6604,7 +6604,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542747020721</v>
       </c>
       <c r="H215" t="n">
         <v>1220</v>
@@ -6633,7 +6633,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322474956512</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H216" t="n">
         <v>6370</v>
@@ -6749,7 +6749,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.23176097869873</v>
+        <v>1.23176085948944</v>
       </c>
       <c r="H220" t="n">
         <v>8086</v>
@@ -6865,7 +6865,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322474956512</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H224" t="n">
         <v>2881</v>
@@ -6981,7 +6981,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="n">
-        <v>1.20980429649353</v>
+        <v>1.20980441570282</v>
       </c>
       <c r="H228" t="n">
         <v>5599</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126818656921</v>
+        <v>1.21126806735992</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7039,7 +7039,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>1.21858704090118</v>
+        <v>1.21858692169189</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322474956512</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H231" t="n">
         <v>434</v>
@@ -7097,7 +7097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492755413055</v>
+        <v>1.21492743492126</v>
       </c>
       <c r="H232" t="n">
         <v>842</v>
@@ -7184,7 +7184,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.214195728302</v>
+        <v>1.21419560909271</v>
       </c>
       <c r="H235" t="n">
         <v>750</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7358,7 +7358,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639144420624</v>
+        <v>1.21639132499695</v>
       </c>
       <c r="H241" t="n">
         <v>6606</v>
@@ -7445,7 +7445,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H244" t="n">
         <v>6714</v>
@@ -7474,7 +7474,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H245" t="n">
         <v>4030</v>
@@ -7532,7 +7532,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592026233673</v>
+        <v>1.28592014312744</v>
       </c>
       <c r="H247" t="n">
         <v>4452</v>
@@ -7561,7 +7561,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="n">
-        <v>1.29470300674438</v>
+        <v>1.2947028875351</v>
       </c>
       <c r="H248" t="n">
         <v>6791</v>
@@ -7735,7 +7735,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="n">
-        <v>1.29470300674438</v>
+        <v>1.2947028875351</v>
       </c>
       <c r="H254" t="n">
         <v>310</v>
@@ -7793,7 +7793,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G256" t="n">
-        <v>1.30128979682922</v>
+        <v>1.30128991603851</v>
       </c>
       <c r="H256" t="n">
         <v>1826</v>
@@ -7822,7 +7822,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007254123688</v>
+        <v>1.31007242202759</v>
       </c>
       <c r="H257" t="n">
         <v>7253</v>
@@ -7851,7 +7851,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544219493866</v>
+        <v>1.32544207572937</v>
       </c>
       <c r="H258" t="n">
         <v>4943</v>
@@ -7880,7 +7880,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081161022186</v>
+        <v>1.34081172943115</v>
       </c>
       <c r="H259" t="n">
         <v>24867</v>
@@ -7909,7 +7909,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3334926366806</v>
+        <v>1.33349275588989</v>
       </c>
       <c r="H260" t="n">
         <v>1372</v>
@@ -7996,7 +7996,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861589431763</v>
+        <v>1.33861601352692</v>
       </c>
       <c r="H263" t="n">
         <v>3514</v>
@@ -8112,7 +8112,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.34666657447815</v>
+        <v>1.34666669368744</v>
       </c>
       <c r="H267" t="n">
         <v>4055</v>
@@ -8228,7 +8228,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32105076313019</v>
+        <v>1.3210506439209</v>
       </c>
       <c r="H271" t="n">
         <v>1933</v>
@@ -8315,7 +8315,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057245731354</v>
+        <v>1.36057257652283</v>
       </c>
       <c r="H274" t="n">
         <v>7391</v>
@@ -8373,7 +8373,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="n">
-        <v>1.33276081085205</v>
+        <v>1.33276069164276</v>
       </c>
       <c r="H276" t="n">
         <v>684</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910132408142</v>
+        <v>1.32910144329071</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8634,7 +8634,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.36789131164551</v>
+        <v>1.3678914308548</v>
       </c>
       <c r="H285" t="n">
         <v>3430</v>
@@ -8663,7 +8663,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667393684387</v>
+        <v>1.37667381763458</v>
       </c>
       <c r="H286" t="n">
         <v>5575</v>
@@ -8692,7 +8692,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252890110016</v>
+        <v>1.38252878189087</v>
       </c>
       <c r="H287" t="n">
         <v>4266</v>
@@ -8837,7 +8837,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887677669525</v>
+        <v>1.40887665748596</v>
       </c>
       <c r="H292" t="n">
         <v>5253</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302169322968</v>
+        <v>1.40302157402039</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -9185,7 +9185,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50328993797302</v>
+        <v>1.50329005718231</v>
       </c>
       <c r="H304" t="n">
         <v>18505</v>
@@ -9214,7 +9214,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742737293243</v>
+        <v>1.46742749214172</v>
       </c>
       <c r="H305" t="n">
         <v>2232</v>
@@ -9243,7 +9243,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864498615265</v>
+        <v>1.45864486694336</v>
       </c>
       <c r="H306" t="n">
         <v>3108</v>
@@ -9301,7 +9301,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H308" t="n">
         <v>1440</v>
@@ -9359,7 +9359,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792040348053</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H310" t="n">
         <v>3021</v>
@@ -9417,7 +9417,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H312" t="n">
         <v>332</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987660884857</v>
+        <v>1.50987672805786</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -9533,7 +9533,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>1.53256523609161</v>
+        <v>1.5325653553009</v>
       </c>
       <c r="H316" t="n">
         <v>3089</v>
@@ -9591,7 +9591,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="n">
-        <v>1.53183329105377</v>
+        <v>1.53183341026306</v>
       </c>
       <c r="H318" t="n">
         <v>1564</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817380428314</v>
+        <v>1.52817392349243</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9794,7 +9794,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523913860321</v>
+        <v>1.49523901939392</v>
       </c>
       <c r="H325" t="n">
         <v>4358</v>
@@ -9823,7 +9823,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792040348053</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H326" t="n">
         <v>7683</v>
@@ -9939,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376812458038</v>
+        <v>1.46376800537109</v>
       </c>
       <c r="H330" t="n">
         <v>9218</v>
@@ -10113,7 +10113,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126361370087</v>
+        <v>1.63126373291016</v>
       </c>
       <c r="H336" t="n">
         <v>30984</v>
@@ -10142,7 +10142,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427484035492</v>
+        <v>1.63427472114563</v>
       </c>
       <c r="H337" t="n">
         <v>3259</v>
@@ -10171,7 +10171,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857745170593</v>
+        <v>1.64857769012451</v>
       </c>
       <c r="H338" t="n">
         <v>10071</v>
@@ -10229,7 +10229,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66664397716522</v>
+        <v>1.66664409637451</v>
       </c>
       <c r="H340" t="n">
         <v>4864</v>
@@ -10258,7 +10258,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288042068481</v>
+        <v>1.66288030147552</v>
       </c>
       <c r="H341" t="n">
         <v>8452</v>
@@ -10316,7 +10316,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902174949646</v>
+        <v>1.76902163028717</v>
       </c>
       <c r="H343" t="n">
         <v>13422</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816578865051</v>
+        <v>1.80816566944122</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429895877838</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10461,7 +10461,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="n">
-        <v>2.01367354393005</v>
+        <v>2.01367330551147</v>
       </c>
       <c r="H348" t="n">
         <v>26110</v>
@@ -10490,7 +10490,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345139503479</v>
+        <v>1.95345163345337</v>
       </c>
       <c r="H349" t="n">
         <v>31940</v>
@@ -10519,7 +10519,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>1.98205721378326</v>
+        <v>1.98205697536469</v>
       </c>
       <c r="H350" t="n">
         <v>15329</v>
@@ -10548,7 +10548,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011558055878</v>
+        <v>1.9301153421402</v>
       </c>
       <c r="H351" t="n">
         <v>6514</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429895877838</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376026153564</v>
+        <v>1.83376038074493</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452110767365</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10693,7 +10693,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.9120489358902</v>
+        <v>1.91204917430878</v>
       </c>
       <c r="H356" t="n">
         <v>4977</v>
@@ -10809,7 +10809,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118493556976</v>
+        <v>1.88118481636047</v>
       </c>
       <c r="H360" t="n">
         <v>6883</v>
@@ -10838,7 +10838,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92861008644104</v>
+        <v>1.92860984802246</v>
       </c>
       <c r="H361" t="n">
         <v>5572</v>
@@ -10867,7 +10867,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.921835064888</v>
+        <v>1.92183482646942</v>
       </c>
       <c r="H362" t="n">
         <v>4932</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11157,7 +11157,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>1.9436651468277</v>
+        <v>1.94366562366486</v>
       </c>
       <c r="H372" t="n">
         <v>2905</v>
@@ -11244,7 +11244,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>1.89021837711334</v>
+        <v>1.89021849632263</v>
       </c>
       <c r="H375" t="n">
         <v>1836</v>
@@ -11273,7 +11273,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753197669983</v>
+        <v>1.90753221511841</v>
       </c>
       <c r="H376" t="n">
         <v>4843</v>
@@ -11302,7 +11302,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699327945709</v>
+        <v>1.89699339866638</v>
       </c>
       <c r="H377" t="n">
         <v>2654</v>
@@ -11331,7 +11331,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473497867584</v>
+        <v>1.89473509788513</v>
       </c>
       <c r="H378" t="n">
         <v>803</v>
@@ -11360,7 +11360,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742137908936</v>
+        <v>1.87742114067078</v>
       </c>
       <c r="H379" t="n">
         <v>4228</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86010730266571</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052700519562</v>
+        <v>1.77052712440491</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7976268529892</v>
+        <v>1.79762697219849</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11534,7 +11534,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741333961487</v>
+        <v>1.80741310119629</v>
       </c>
       <c r="H385" t="n">
         <v>3798</v>
@@ -11563,7 +11563,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074915409088</v>
+        <v>1.83074927330017</v>
       </c>
       <c r="H386" t="n">
         <v>3583</v>
@@ -11592,7 +11592,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H387" t="n">
         <v>1000</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816578865051</v>
+        <v>1.80816566944122</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11708,7 +11708,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.82623243331909</v>
+        <v>1.8262323141098</v>
       </c>
       <c r="H391" t="n">
         <v>2650</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.8360184431076</v>
+        <v>1.83601832389832</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429895877838</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429895877838</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11882,7 +11882,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257959365845</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H397" t="n">
         <v>2269</v>
@@ -11911,7 +11911,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257959365845</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H398" t="n">
         <v>776</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752405643463</v>
+        <v>1.83752393722534</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613767623901</v>
+        <v>1.93613743782043</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12346,7 +12346,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796007633209</v>
+        <v>1.88796019554138</v>
       </c>
       <c r="H413" t="n">
         <v>1727</v>
@@ -12375,7 +12375,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="n">
-        <v>1.89021837711334</v>
+        <v>1.89021849632263</v>
       </c>
       <c r="H414" t="n">
         <v>818</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452110767365</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.86010730266571</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12607,7 +12607,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H422" t="n">
         <v>5360</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.8563437461853</v>
+        <v>1.85634350776672</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12665,7 +12665,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>1.85709643363953</v>
+        <v>1.85709631443024</v>
       </c>
       <c r="H424" t="n">
         <v>891</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.8563437461853</v>
+        <v>1.85634350776672</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12781,7 +12781,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494884967804</v>
+        <v>1.88494908809662</v>
       </c>
       <c r="H428" t="n">
         <v>2953</v>
@@ -12810,7 +12810,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215197086334</v>
+        <v>1.87215173244476</v>
       </c>
       <c r="H429" t="n">
         <v>140</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.86010730266571</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12955,7 +12955,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.87064623832703</v>
+        <v>1.87064647674561</v>
       </c>
       <c r="H434" t="n">
         <v>4633</v>
@@ -12984,7 +12984,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161303520203</v>
+        <v>1.86161291599274</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193774223328</v>
+        <v>1.88193762302399</v>
       </c>
       <c r="H436" t="n">
         <v>2642</v>
@@ -13042,7 +13042,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763501167297</v>
+        <v>1.86763513088226</v>
       </c>
       <c r="H437" t="n">
         <v>1511</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365734577179</v>
+        <v>1.8736572265625</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8653769493103</v>
+        <v>1.86537706851959</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.86010730266571</v>
+        <v>1.86010718345642</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13216,7 +13216,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257959365845</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H443" t="n">
         <v>1174</v>
@@ -13332,7 +13332,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H447" t="n">
         <v>5011</v>
@@ -13361,7 +13361,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795191764832</v>
+        <v>1.81795179843903</v>
       </c>
       <c r="H448" t="n">
         <v>5592</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569385528564</v>
+        <v>1.81569397449493</v>
       </c>
       <c r="H451" t="n">
         <v>4388</v>
@@ -13477,7 +13477,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021021842957</v>
+        <v>1.82021033763885</v>
       </c>
       <c r="H452" t="n">
         <v>6137</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.8111766576767</v>
+        <v>1.81117677688599</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13535,7 +13535,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644642353058</v>
+        <v>1.81644630432129</v>
       </c>
       <c r="H454" t="n">
         <v>4767</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13651,7 +13651,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83225476741791</v>
+        <v>1.8322548866272</v>
       </c>
       <c r="H458" t="n">
         <v>1829</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246851921082</v>
+        <v>1.82246840000153</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547962665558</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13738,7 +13738,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.85032117366791</v>
+        <v>1.8503212928772</v>
       </c>
       <c r="H461" t="n">
         <v>11043</v>
@@ -13796,7 +13796,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H463" t="n">
         <v>34293</v>
@@ -13825,7 +13825,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849889278412</v>
+        <v>1.89849901199341</v>
       </c>
       <c r="H464" t="n">
         <v>4953</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731822490692</v>
+        <v>1.91731798648834</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13912,7 +13912,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979879379272</v>
+        <v>1.97979855537415</v>
       </c>
       <c r="H467" t="n">
         <v>24938</v>
@@ -13941,7 +13941,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474301815033</v>
       </c>
       <c r="H468" t="n">
         <v>14648</v>
@@ -13970,7 +13970,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>1.9436651468277</v>
+        <v>1.94366562366486</v>
       </c>
       <c r="H469" t="n">
         <v>12171</v>
@@ -14086,7 +14086,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248459815979</v>
+        <v>1.96248483657837</v>
       </c>
       <c r="H473" t="n">
         <v>11988</v>
@@ -14202,7 +14202,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732626438141</v>
+        <v>1.98732650279999</v>
       </c>
       <c r="H477" t="n">
         <v>8901</v>
@@ -14231,7 +14231,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937081336975</v>
+        <v>1.99937057495117</v>
       </c>
       <c r="H478" t="n">
         <v>3901</v>
@@ -14318,7 +14318,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624886989594</v>
+        <v>1.96624863147736</v>
       </c>
       <c r="H481" t="n">
         <v>7605</v>
@@ -14347,7 +14347,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861788749695</v>
+        <v>1.99861812591553</v>
       </c>
       <c r="H482" t="n">
         <v>7953</v>
@@ -14405,7 +14405,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474301815033</v>
       </c>
       <c r="H484" t="n">
         <v>3107</v>
@@ -14463,7 +14463,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98280966281891</v>
+        <v>1.98280990123749</v>
       </c>
       <c r="H486" t="n">
         <v>699</v>
@@ -14608,7 +14608,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540082931519</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H491" t="n">
         <v>2166</v>
@@ -14695,7 +14695,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="n">
-        <v>2.08217597007751</v>
+        <v>2.08217620849609</v>
       </c>
       <c r="H494" t="n">
         <v>11805</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024261474609</v>
+        <v>2.10024285316467</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -15043,7 +15043,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>2.05884027481079</v>
+        <v>2.05884003639221</v>
       </c>
       <c r="H506" t="n">
         <v>1639</v>
@@ -15072,7 +15072,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540082931519</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H507" t="n">
         <v>1590</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615399360657</v>
+        <v>2.07615375518799</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15188,7 +15188,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08518719673157</v>
+        <v>2.08518743515015</v>
       </c>
       <c r="H511" t="n">
         <v>1601</v>
@@ -15217,7 +15217,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185882568359</v>
+        <v>2.13185906410217</v>
       </c>
       <c r="H512" t="n">
         <v>18197</v>
@@ -15246,7 +15246,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H513" t="n">
         <v>13248</v>
@@ -15275,7 +15275,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H514" t="n">
         <v>7527</v>
@@ -15391,7 +15391,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H518" t="n">
         <v>3359</v>
@@ -15478,7 +15478,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H521" t="n">
         <v>10697</v>
@@ -15623,7 +15623,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H526" t="n">
         <v>2705</v>
@@ -15884,7 +15884,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H535" t="n">
         <v>3431</v>
@@ -15913,7 +15913,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H536" t="n">
         <v>5445</v>
@@ -15942,7 +15942,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H537" t="n">
         <v>6576</v>
@@ -16000,7 +16000,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H539" t="n">
         <v>1456</v>
@@ -16029,7 +16029,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H540" t="n">
         <v>5940</v>
@@ -16087,7 +16087,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563101768494</v>
+        <v>2.20563125610352</v>
       </c>
       <c r="H542" t="n">
         <v>3615</v>
@@ -16116,7 +16116,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H543" t="n">
         <v>161</v>
@@ -16145,7 +16145,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.21315908432007</v>
+        <v>2.21315884590149</v>
       </c>
       <c r="H544" t="n">
         <v>815</v>
@@ -16174,7 +16174,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H545" t="n">
         <v>2533</v>
@@ -16232,7 +16232,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>2.38629746437073</v>
+        <v>2.38629722595215</v>
       </c>
       <c r="H547" t="n">
         <v>6727</v>
@@ -16464,7 +16464,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>2.40135264396667</v>
+        <v>2.40135288238525</v>
       </c>
       <c r="H555" t="n">
         <v>12859</v>
@@ -16493,7 +16493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H556" t="n">
         <v>9076</v>
@@ -16551,7 +16551,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H558" t="n">
         <v>4749</v>
@@ -16609,7 +16609,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="n">
-        <v>2.47663044929504</v>
+        <v>2.47663068771362</v>
       </c>
       <c r="H560" t="n">
         <v>3851</v>
@@ -16696,7 +16696,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888071060181</v>
+        <v>2.40888047218323</v>
       </c>
       <c r="H563" t="n">
         <v>3721</v>
@@ -16725,7 +16725,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H564" t="n">
         <v>2298</v>
@@ -16812,7 +16812,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>2.47663044929504</v>
+        <v>2.47663068771362</v>
       </c>
       <c r="H567" t="n">
         <v>3892</v>
@@ -16928,7 +16928,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H571" t="n">
         <v>3605</v>
@@ -17044,7 +17044,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H575" t="n">
         <v>4786</v>
@@ -17247,7 +17247,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="n">
-        <v>2.47663044929504</v>
+        <v>2.47663068771362</v>
       </c>
       <c r="H582" t="n">
         <v>1436</v>
@@ -17334,7 +17334,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="n">
-        <v>2.47663044929504</v>
+        <v>2.47663068771362</v>
       </c>
       <c r="H585" t="n">
         <v>521</v>
@@ -17392,7 +17392,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.5067412853241</v>
+        <v>2.50674104690552</v>
       </c>
       <c r="H587" t="n">
         <v>11895</v>
@@ -17421,7 +17421,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>2.52932453155518</v>
+        <v>2.5293242931366</v>
       </c>
       <c r="H588" t="n">
         <v>10382</v>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G2" t="n">
-        <v>1.24616146087646</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H2" t="n">
         <v>328</v>
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544656276703</v>
+        <v>1.24544644355774</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -514,7 +514,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H5" t="n">
         <v>1168</v>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H6" t="n">
         <v>466</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -659,7 +659,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327352523804</v>
+        <v>1.21327364444733</v>
       </c>
       <c r="H10" t="n">
         <v>4107</v>
@@ -688,7 +688,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683908462524</v>
+        <v>1.20683896541595</v>
       </c>
       <c r="H11" t="n">
         <v>9368</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.20111954212189</v>
+        <v>1.20111930370331</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -775,7 +775,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.16680192947388</v>
+        <v>1.1668016910553</v>
       </c>
       <c r="H14" t="n">
         <v>2159</v>
@@ -804,7 +804,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468474388123</v>
+        <v>1.19468486309052</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688564777374</v>
+        <v>1.25688576698303</v>
       </c>
       <c r="H16" t="n">
         <v>6127</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -1007,7 +1007,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475036144257</v>
+        <v>1.26475024223328</v>
       </c>
       <c r="H22" t="n">
         <v>1772</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470367908478</v>
+        <v>1.2147034406662</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1065,7 +1065,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H24" t="n">
         <v>132</v>
@@ -1123,7 +1123,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H26" t="n">
         <v>2636</v>
@@ -1181,7 +1181,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G28" t="n">
-        <v>1.21041393280029</v>
+        <v>1.210413813591</v>
       </c>
       <c r="H28" t="n">
         <v>118</v>
@@ -1210,7 +1210,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113811969757</v>
+        <v>1.22113823890686</v>
       </c>
       <c r="H29" t="n">
         <v>111</v>
@@ -1239,7 +1239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19397008419037</v>
+        <v>1.19396996498108</v>
       </c>
       <c r="H30" t="n">
         <v>419</v>
@@ -1268,7 +1268,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H31" t="n">
         <v>39</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685778141022</v>
+        <v>1.22685790061951</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1355,7 +1355,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H34" t="n">
         <v>772</v>
@@ -1413,7 +1413,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H36" t="n">
         <v>1696</v>
@@ -1471,7 +1471,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903081893921</v>
+        <v>1.25903069972992</v>
       </c>
       <c r="H38" t="n">
         <v>6392</v>
@@ -1500,7 +1500,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903998851776</v>
+        <v>1.26903986930847</v>
       </c>
       <c r="H39" t="n">
         <v>3180</v>
@@ -1558,7 +1558,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828769683838</v>
+        <v>1.22828781604767</v>
       </c>
       <c r="H41" t="n">
         <v>573</v>
@@ -1587,7 +1587,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542774677277</v>
+        <v>1.22542786598206</v>
       </c>
       <c r="H42" t="n">
         <v>340</v>
@@ -1616,7 +1616,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G43" t="n">
-        <v>1.24616146087646</v>
+        <v>1.24616158008575</v>
       </c>
       <c r="H43" t="n">
         <v>1037</v>
@@ -1732,7 +1732,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689505577087</v>
+        <v>1.26689517498016</v>
       </c>
       <c r="H47" t="n">
         <v>7764</v>
@@ -1761,7 +1761,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H48" t="n">
         <v>1421</v>
@@ -1790,7 +1790,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G49" t="n">
-        <v>1.27189993858337</v>
+        <v>1.27189981937408</v>
       </c>
       <c r="H49" t="n">
         <v>500</v>
@@ -1848,7 +1848,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G51" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H51" t="n">
         <v>1451</v>
@@ -1906,7 +1906,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H53" t="n">
         <v>4204</v>
@@ -1935,7 +1935,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H54" t="n">
         <v>60</v>
@@ -1993,7 +1993,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G56" t="n">
-        <v>1.26761019229889</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H56" t="n">
         <v>23</v>
@@ -2022,7 +2022,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261459827423</v>
+        <v>1.27261471748352</v>
       </c>
       <c r="H57" t="n">
         <v>62</v>
@@ -2051,7 +2051,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26761019229889</v>
+        <v>1.2676100730896</v>
       </c>
       <c r="H58" t="n">
         <v>1444</v>
@@ -2080,7 +2080,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545573234558</v>
+        <v>1.25545585155487</v>
       </c>
       <c r="H59" t="n">
         <v>2269</v>
@@ -2138,7 +2138,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>1.2583155632019</v>
+        <v>1.25831568241119</v>
       </c>
       <c r="H61" t="n">
         <v>3448</v>
@@ -2225,7 +2225,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24902129173279</v>
+        <v>1.2490211725235</v>
       </c>
       <c r="H64" t="n">
         <v>523</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045108795166</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258649349213</v>
+        <v>1.24258673191071</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2312,7 +2312,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686695098877</v>
+        <v>1.23686707019806</v>
       </c>
       <c r="H67" t="n">
         <v>70</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685778141022</v>
+        <v>1.22685790061951</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2428,7 +2428,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400712013245</v>
+        <v>1.23400735855103</v>
       </c>
       <c r="H71" t="n">
         <v>6242</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225377082825</v>
+        <v>1.25225365161896</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2573,7 +2573,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176798343658</v>
       </c>
       <c r="H76" t="n">
         <v>2231</v>
@@ -2602,7 +2602,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835489273071</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H77" t="n">
         <v>1512</v>
@@ -2631,7 +2631,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835489273071</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H78" t="n">
         <v>2507</v>
@@ -2660,7 +2660,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H79" t="n">
         <v>1551</v>
@@ -2689,7 +2689,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860140800476</v>
+        <v>1.27860128879547</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27421009540558</v>
+        <v>1.27420997619629</v>
       </c>
       <c r="H82" t="n">
         <v>323</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2805,7 +2805,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323175430298</v>
+        <v>1.26323187351227</v>
       </c>
       <c r="H84" t="n">
         <v>220</v>
@@ -2834,7 +2834,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H85" t="n">
         <v>149</v>
@@ -2863,7 +2863,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323175430298</v>
+        <v>1.26323187351227</v>
       </c>
       <c r="H86" t="n">
         <v>105</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -2950,7 +2950,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445661067963</v>
+        <v>1.28445625305176</v>
       </c>
       <c r="H89" t="n">
         <v>1506</v>
@@ -2979,7 +2979,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.28079700469971</v>
+        <v>1.280797123909</v>
       </c>
       <c r="H90" t="n">
         <v>217</v>
@@ -3008,7 +3008,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H91" t="n">
         <v>100</v>
@@ -3037,7 +3037,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G92" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G93" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347815036774</v>
+        <v>1.27347826957703</v>
       </c>
       <c r="H94" t="n">
         <v>370</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3153,7 +3153,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G96" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H96" t="n">
         <v>81</v>
@@ -3182,7 +3182,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615941524506</v>
       </c>
       <c r="H97" t="n">
         <v>1320</v>
@@ -3211,7 +3211,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>1.28226101398468</v>
+        <v>1.28226089477539</v>
       </c>
       <c r="H98" t="n">
         <v>573</v>
@@ -3298,7 +3298,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H101" t="n">
         <v>361</v>
@@ -3327,7 +3327,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>1.2793333530426</v>
+        <v>1.27933323383331</v>
       </c>
       <c r="H102" t="n">
         <v>20</v>
@@ -3385,7 +3385,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G104" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H104" t="n">
         <v>741</v>
@@ -3414,7 +3414,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G106" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H106" t="n">
         <v>93</v>
@@ -3472,7 +3472,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G107" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H108" t="n">
         <v>3785</v>
@@ -3530,7 +3530,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H109" t="n">
         <v>12</v>
@@ -3559,7 +3559,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176822185516</v>
+        <v>1.26176798343658</v>
       </c>
       <c r="H111" t="n">
         <v>594</v>
@@ -3646,7 +3646,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H113" t="n">
         <v>1458</v>
@@ -3675,7 +3675,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H114" t="n">
         <v>1307</v>
@@ -3704,7 +3704,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H115" t="n">
         <v>1050</v>
@@ -3762,7 +3762,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.226637840271</v>
+        <v>1.22663772106171</v>
       </c>
       <c r="H117" t="n">
         <v>120</v>
@@ -3791,7 +3791,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760881900787</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -3936,7 +3936,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784773349762</v>
+        <v>1.18784785270691</v>
       </c>
       <c r="H123" t="n">
         <v>1361</v>
@@ -3965,7 +3965,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955065727234</v>
+        <v>1.16955077648163</v>
       </c>
       <c r="H124" t="n">
         <v>4411</v>
@@ -3994,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H125" t="n">
         <v>673</v>
@@ -4110,7 +4110,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H129" t="n">
         <v>1649</v>
@@ -4197,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H132" t="n">
         <v>171</v>
@@ -4226,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H133" t="n">
         <v>101</v>
@@ -4255,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101454734802</v>
+        <v>1.17101442813873</v>
       </c>
       <c r="H134" t="n">
         <v>245</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760881900787</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4342,7 +4342,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G137" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151458263397</v>
       </c>
       <c r="H137" t="n">
         <v>610</v>
@@ -4371,7 +4371,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G138" t="n">
-        <v>1.22151446342468</v>
+        <v>1.22151458263397</v>
       </c>
       <c r="H138" t="n">
         <v>215</v>
@@ -4429,7 +4429,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H140" t="n">
         <v>730</v>
@@ -4458,7 +4458,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.24347102642059</v>
+        <v>1.2434709072113</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760881900787</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4719,7 +4719,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.20614492893219</v>
+        <v>1.2061448097229</v>
       </c>
       <c r="H150" t="n">
         <v>2847</v>
@@ -4748,7 +4748,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.23102903366089</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H151" t="n">
         <v>1211</v>
@@ -4777,7 +4777,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.23102903366089</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H152" t="n">
         <v>20</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.21712303161621</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.21712303161621</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H157" t="n">
         <v>390</v>
@@ -5038,7 +5038,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H161" t="n">
         <v>10275</v>
@@ -5125,7 +5125,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G164" t="n">
-        <v>1.28226101398468</v>
+        <v>1.28226089477539</v>
       </c>
       <c r="H164" t="n">
         <v>5537</v>
@@ -5154,7 +5154,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518831729889</v>
+        <v>1.28518843650818</v>
       </c>
       <c r="H165" t="n">
         <v>430</v>
@@ -5183,7 +5183,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30714499950409</v>
+        <v>1.3071448802948</v>
       </c>
       <c r="H166" t="n">
         <v>3048</v>
@@ -5212,7 +5212,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H167" t="n">
         <v>1738</v>
@@ -5241,7 +5241,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324635982513</v>
+        <v>1.32324624061584</v>
       </c>
       <c r="H168" t="n">
         <v>18315</v>
@@ -5270,7 +5270,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G169" t="n">
-        <v>1.31665921211243</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H169" t="n">
         <v>3060</v>
@@ -5299,7 +5299,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763755321503</v>
+        <v>1.32763767242432</v>
       </c>
       <c r="H170" t="n">
         <v>14161</v>
@@ -5386,7 +5386,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>1.31812334060669</v>
+        <v>1.3181232213974</v>
       </c>
       <c r="H173" t="n">
         <v>2430</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763054847717</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5444,7 +5444,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30275368690491</v>
+        <v>1.30275356769562</v>
       </c>
       <c r="H175" t="n">
         <v>4841</v>
@@ -5473,7 +5473,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982614517212</v>
+        <v>1.29982602596283</v>
       </c>
       <c r="H176" t="n">
         <v>1808</v>
@@ -5502,7 +5502,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884780406952</v>
+        <v>1.28884792327881</v>
       </c>
       <c r="H177" t="n">
         <v>3982</v>
@@ -5531,7 +5531,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543495178223</v>
+        <v>1.29543483257294</v>
       </c>
       <c r="H178" t="n">
         <v>703</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763054847717</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5589,7 +5589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>1.30275368690491</v>
+        <v>1.30275356769562</v>
       </c>
       <c r="H180" t="n">
         <v>600</v>
@@ -5618,7 +5618,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>1.30275368690491</v>
+        <v>1.30275356769562</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>1.30275368690491</v>
+        <v>1.30275356769562</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>1.30275368690491</v>
+        <v>1.30275356769562</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836225509644</v>
+        <v>1.29836237430573</v>
       </c>
       <c r="H186" t="n">
         <v>4389</v>
@@ -5792,7 +5792,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H187" t="n">
         <v>4615</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763054847717</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568110942841</v>
       </c>
       <c r="H193" t="n">
         <v>4252</v>
@@ -5995,7 +5995,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>1.26908683776855</v>
+        <v>1.26908695697784</v>
       </c>
       <c r="H194" t="n">
         <v>6154</v>
@@ -6024,7 +6024,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G195" t="n">
-        <v>1.27274644374847</v>
+        <v>1.27274632453918</v>
       </c>
       <c r="H195" t="n">
         <v>5744</v>
@@ -6053,7 +6053,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762318611145</v>
+        <v>1.26762306690216</v>
       </c>
       <c r="H196" t="n">
         <v>4114</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.2478621006012</v>
+        <v>1.24786221981049</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6169,7 +6169,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.26542747020721</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H200" t="n">
         <v>14244</v>
@@ -6198,7 +6198,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006529808044</v>
+        <v>1.28006517887115</v>
       </c>
       <c r="H201" t="n">
         <v>19504</v>
@@ -6227,7 +6227,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615941524506</v>
       </c>
       <c r="H202" t="n">
         <v>22671</v>
@@ -6256,7 +6256,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810873508453</v>
+        <v>1.25810885429382</v>
       </c>
       <c r="H203" t="n">
         <v>11122</v>
@@ -6343,7 +6343,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639856815338</v>
+        <v>1.24639868736267</v>
       </c>
       <c r="H206" t="n">
         <v>7757</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420297145844</v>
+        <v>1.24420285224915</v>
       </c>
       <c r="H208" t="n">
         <v>6264</v>
@@ -6430,7 +6430,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615217208862</v>
       </c>
       <c r="H209" t="n">
         <v>5810</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688411712646</v>
+        <v>1.23688399791718</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6488,7 +6488,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420297145844</v>
+        <v>1.24420285224915</v>
       </c>
       <c r="H211" t="n">
         <v>1424</v>
@@ -6604,7 +6604,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.26542747020721</v>
+        <v>1.2654275894165</v>
       </c>
       <c r="H215" t="n">
         <v>1220</v>
@@ -6633,7 +6633,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H216" t="n">
         <v>6370</v>
@@ -6662,7 +6662,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H217" t="n">
         <v>3330</v>
@@ -6778,7 +6778,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H221" t="n">
         <v>2500</v>
@@ -6807,7 +6807,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H222" t="n">
         <v>2781</v>
@@ -6836,7 +6836,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H223" t="n">
         <v>275</v>
@@ -6865,7 +6865,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H224" t="n">
         <v>2881</v>
@@ -6894,7 +6894,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H225" t="n">
         <v>13996</v>
@@ -6923,7 +6923,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H226" t="n">
         <v>2165</v>
@@ -6952,7 +6952,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H227" t="n">
         <v>1452</v>
@@ -7068,7 +7068,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H231" t="n">
         <v>434</v>
@@ -7097,7 +7097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492743492126</v>
+        <v>1.21492755413055</v>
       </c>
       <c r="H232" t="n">
         <v>842</v>
@@ -7213,7 +7213,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>1.19297087192535</v>
+        <v>1.19297099113464</v>
       </c>
       <c r="H236" t="n">
         <v>8622</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663035869598</v>
+        <v>1.19663047790527</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760881900787</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760881900787</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7329,7 +7329,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.220050573349</v>
+        <v>1.22005069255829</v>
       </c>
       <c r="H240" t="n">
         <v>740</v>
@@ -7358,7 +7358,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639132499695</v>
+        <v>1.21639144420624</v>
       </c>
       <c r="H241" t="n">
         <v>6606</v>
@@ -7387,7 +7387,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H242" t="n">
         <v>6732</v>
@@ -7445,7 +7445,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128267288208</v>
+        <v>1.27128279209137</v>
       </c>
       <c r="H244" t="n">
         <v>6714</v>
@@ -7474,7 +7474,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615929603577</v>
+        <v>1.26615941524506</v>
       </c>
       <c r="H245" t="n">
         <v>4030</v>
@@ -7503,7 +7503,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786958217621</v>
+        <v>1.27786946296692</v>
       </c>
       <c r="H246" t="n">
         <v>2816</v>
@@ -7590,7 +7590,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909420013428</v>
+        <v>1.29909408092499</v>
       </c>
       <c r="H249" t="n">
         <v>2175</v>
@@ -7677,7 +7677,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.2932391166687</v>
+        <v>1.29323923587799</v>
       </c>
       <c r="H252" t="n">
         <v>321</v>
@@ -7764,7 +7764,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568110942841</v>
       </c>
       <c r="H255" t="n">
         <v>2306</v>
@@ -7851,7 +7851,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544207572937</v>
+        <v>1.32544195652008</v>
       </c>
       <c r="H258" t="n">
         <v>4943</v>
@@ -7880,7 +7880,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081172943115</v>
+        <v>1.34081161022186</v>
       </c>
       <c r="H259" t="n">
         <v>24867</v>
@@ -7909,7 +7909,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="n">
-        <v>1.33349275588989</v>
+        <v>1.3334926366806</v>
       </c>
       <c r="H260" t="n">
         <v>1372</v>
@@ -7938,7 +7938,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H261" t="n">
         <v>6768</v>
@@ -7996,7 +7996,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861601352692</v>
+        <v>1.33861589431763</v>
       </c>
       <c r="H263" t="n">
         <v>3514</v>
@@ -8025,7 +8025,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934760093689</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H264" t="n">
         <v>396</v>
@@ -8054,7 +8054,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422458171844</v>
+        <v>1.33422470092773</v>
       </c>
       <c r="H265" t="n">
         <v>1429</v>
@@ -8083,7 +8083,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G266" t="n">
-        <v>1.31665921211243</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H266" t="n">
         <v>3165</v>
@@ -8112,7 +8112,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.34666669368744</v>
+        <v>1.34666657447815</v>
       </c>
       <c r="H267" t="n">
         <v>4055</v>
@@ -8141,7 +8141,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227538108826</v>
+        <v>1.34227526187897</v>
       </c>
       <c r="H268" t="n">
         <v>2370</v>
@@ -8170,7 +8170,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34007966518402</v>
+        <v>1.34007978439331</v>
       </c>
       <c r="H269" t="n">
         <v>383</v>
@@ -8373,7 +8373,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="n">
-        <v>1.33276069164276</v>
+        <v>1.33276081085205</v>
       </c>
       <c r="H276" t="n">
         <v>684</v>
@@ -8431,7 +8431,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>1.33788418769836</v>
+        <v>1.33788406848907</v>
       </c>
       <c r="H278" t="n">
         <v>534</v>
@@ -8489,7 +8489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934760093689</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H280" t="n">
         <v>113</v>
@@ -8518,7 +8518,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934760093689</v>
+        <v>1.33934783935547</v>
       </c>
       <c r="H281" t="n">
         <v>3002</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.32910132408142</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8634,7 +8634,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.3678914308548</v>
+        <v>1.36789119243622</v>
       </c>
       <c r="H285" t="n">
         <v>3430</v>
@@ -8663,7 +8663,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667381763458</v>
+        <v>1.37667393684387</v>
       </c>
       <c r="H286" t="n">
         <v>5575</v>
@@ -8692,7 +8692,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252878189087</v>
+        <v>1.38252902030945</v>
       </c>
       <c r="H287" t="n">
         <v>4266</v>
@@ -8721,7 +8721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789843559265</v>
+        <v>1.39789867401123</v>
       </c>
       <c r="H288" t="n">
         <v>6393</v>
@@ -8750,7 +8750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253626346588</v>
+        <v>1.4125360250473</v>
       </c>
       <c r="H289" t="n">
         <v>1447</v>
@@ -8779,7 +8779,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668106079102</v>
+        <v>1.40668094158173</v>
       </c>
       <c r="H290" t="n">
         <v>14299</v>
@@ -8808,7 +8808,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.40814483165741</v>
+        <v>1.4081449508667</v>
       </c>
       <c r="H291" t="n">
         <v>7943</v>
@@ -8837,7 +8837,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887665748596</v>
+        <v>1.40887677669525</v>
       </c>
       <c r="H292" t="n">
         <v>5253</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302157402039</v>
+        <v>1.40302181243896</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -8895,7 +8895,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="n">
-        <v>1.39277541637421</v>
+        <v>1.39277529716492</v>
       </c>
       <c r="H294" t="n">
         <v>2571</v>
@@ -8924,7 +8924,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.3693550825119</v>
+        <v>1.36935484409332</v>
       </c>
       <c r="H295" t="n">
         <v>3982</v>
@@ -8953,7 +8953,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.37886953353882</v>
+        <v>1.37886965274811</v>
       </c>
       <c r="H296" t="n">
         <v>1185</v>
@@ -8982,7 +8982,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911592960358</v>
+        <v>1.38911581039429</v>
       </c>
       <c r="H297" t="n">
         <v>1150</v>
@@ -9040,7 +9040,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304330348969</v>
+        <v>1.49304342269897</v>
       </c>
       <c r="H299" t="n">
         <v>23394</v>
@@ -9069,7 +9069,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304330348969</v>
+        <v>1.49304342269897</v>
       </c>
       <c r="H300" t="n">
         <v>14396</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621011734009</v>
+        <v>1.4762099981308</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9156,7 +9156,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157965183258</v>
+        <v>1.49157953262329</v>
       </c>
       <c r="H303" t="n">
         <v>5662</v>
@@ -9185,7 +9185,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50329005718231</v>
+        <v>1.50328993797302</v>
       </c>
       <c r="H304" t="n">
         <v>18505</v>
@@ -9214,7 +9214,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742749214172</v>
+        <v>1.46742761135101</v>
       </c>
       <c r="H305" t="n">
         <v>2232</v>
@@ -9243,7 +9243,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864486694336</v>
+        <v>1.45864510536194</v>
       </c>
       <c r="H306" t="n">
         <v>3108</v>
@@ -9301,7 +9301,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H308" t="n">
         <v>1440</v>
@@ -9359,7 +9359,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792028427124</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H310" t="n">
         <v>3021</v>
@@ -9417,7 +9417,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H312" t="n">
         <v>332</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744209766388</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744209766388</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987672805786</v>
+        <v>1.50987684726715</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -9533,7 +9533,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>1.5325653553009</v>
+        <v>1.53256547451019</v>
       </c>
       <c r="H316" t="n">
         <v>3089</v>
@@ -9562,7 +9562,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963769435883</v>
+        <v>1.52963757514954</v>
       </c>
       <c r="H317" t="n">
         <v>1725</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817392349243</v>
+        <v>1.52817380428314</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9707,7 +9707,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.498166680336</v>
+        <v>1.49816644191742</v>
       </c>
       <c r="H322" t="n">
         <v>1750</v>
@@ -9794,7 +9794,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="n">
-        <v>1.49523901939392</v>
+        <v>1.49523913860321</v>
       </c>
       <c r="H325" t="n">
         <v>4358</v>
@@ -9823,7 +9823,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792028427124</v>
+        <v>1.48792016506195</v>
       </c>
       <c r="H326" t="n">
         <v>7683</v>
@@ -9852,7 +9852,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108697891235</v>
+        <v>1.47108709812164</v>
       </c>
       <c r="H327" t="n">
         <v>10631</v>
@@ -9997,7 +9997,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499286174774</v>
+        <v>1.48499274253845</v>
       </c>
       <c r="H332" t="n">
         <v>9406</v>
@@ -10055,7 +10055,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768837451935</v>
+        <v>1.53768849372864</v>
       </c>
       <c r="H334" t="n">
         <v>12975</v>
@@ -10084,7 +10084,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="n">
-        <v>1.58233344554901</v>
+        <v>1.58233368396759</v>
       </c>
       <c r="H335" t="n">
         <v>11207</v>
@@ -10113,7 +10113,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126373291016</v>
+        <v>1.63126385211945</v>
       </c>
       <c r="H336" t="n">
         <v>30984</v>
@@ -10142,7 +10142,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427472114563</v>
+        <v>1.63427484035492</v>
       </c>
       <c r="H337" t="n">
         <v>3259</v>
@@ -10171,7 +10171,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857769012451</v>
+        <v>1.64857733249664</v>
       </c>
       <c r="H338" t="n">
         <v>10071</v>
@@ -10200,7 +10200,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="n">
-        <v>1.63578033447266</v>
+        <v>1.63578045368195</v>
       </c>
       <c r="H339" t="n">
         <v>8432</v>
@@ -10229,7 +10229,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66664409637451</v>
+        <v>1.66664385795593</v>
       </c>
       <c r="H340" t="n">
         <v>4864</v>
@@ -10316,7 +10316,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902163028717</v>
+        <v>1.76902151107788</v>
       </c>
       <c r="H343" t="n">
         <v>13422</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816566944122</v>
+        <v>1.80816555023193</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429883956909</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10432,7 +10432,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485397338867</v>
+        <v>1.99485421180725</v>
       </c>
       <c r="H347" t="n">
         <v>48029</v>
@@ -10461,7 +10461,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="n">
-        <v>2.01367330551147</v>
+        <v>2.01367354393005</v>
       </c>
       <c r="H348" t="n">
         <v>26110</v>
@@ -10490,7 +10490,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345163345337</v>
+        <v>1.95345175266266</v>
       </c>
       <c r="H349" t="n">
         <v>31940</v>
@@ -10519,7 +10519,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="n">
-        <v>1.98205697536469</v>
+        <v>1.98205709457397</v>
       </c>
       <c r="H350" t="n">
         <v>15329</v>
@@ -10548,7 +10548,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.9301153421402</v>
+        <v>1.93011546134949</v>
       </c>
       <c r="H351" t="n">
         <v>6514</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429883956909</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376038074493</v>
+        <v>1.83376049995422</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10635,7 +10635,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.90301561355591</v>
+        <v>1.9030157327652</v>
       </c>
       <c r="H354" t="n">
         <v>11029</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452098846436</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10693,7 +10693,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.91204917430878</v>
+        <v>1.91204881668091</v>
       </c>
       <c r="H356" t="n">
         <v>4977</v>
@@ -10722,7 +10722,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.9353848695755</v>
+        <v>1.93538475036621</v>
       </c>
       <c r="H357" t="n">
         <v>14132</v>
@@ -10751,7 +10751,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.92258787155151</v>
+        <v>1.92258763313293</v>
       </c>
       <c r="H358" t="n">
         <v>3542</v>
@@ -10809,7 +10809,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118481636047</v>
+        <v>1.88118505477905</v>
       </c>
       <c r="H360" t="n">
         <v>6883</v>
@@ -10838,7 +10838,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="n">
-        <v>1.92860984802246</v>
+        <v>1.92860996723175</v>
       </c>
       <c r="H361" t="n">
         <v>5572</v>
@@ -10867,7 +10867,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.92183482646942</v>
+        <v>1.92183494567871</v>
       </c>
       <c r="H362" t="n">
         <v>4932</v>
@@ -10896,7 +10896,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.92559897899628</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H363" t="n">
         <v>5423</v>
@@ -10954,7 +10954,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9263516664505</v>
+        <v>1.92635154724121</v>
       </c>
       <c r="H365" t="n">
         <v>10408</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957664489746</v>
+        <v>1.91957652568817</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11070,7 +11070,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.92559897899628</v>
+        <v>1.9255987405777</v>
       </c>
       <c r="H369" t="n">
         <v>1846</v>
@@ -11099,7 +11099,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882371902466</v>
+        <v>1.91882383823395</v>
       </c>
       <c r="H370" t="n">
         <v>4343</v>
@@ -11128,7 +11128,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237376213074</v>
+        <v>1.93237364292145</v>
       </c>
       <c r="H371" t="n">
         <v>2941</v>
@@ -11157,7 +11157,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>1.94366562366486</v>
+        <v>1.94366538524628</v>
       </c>
       <c r="H372" t="n">
         <v>2905</v>
@@ -11186,7 +11186,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.92258787155151</v>
+        <v>1.92258763313293</v>
       </c>
       <c r="H373" t="n">
         <v>1590</v>
@@ -11215,7 +11215,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054344177246</v>
+        <v>1.91054308414459</v>
       </c>
       <c r="H374" t="n">
         <v>414</v>
@@ -11331,7 +11331,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473509788513</v>
+        <v>1.89473485946655</v>
       </c>
       <c r="H378" t="n">
         <v>803</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86010718345642</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052712440491</v>
+        <v>1.77052700519562</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762697219849</v>
+        <v>1.79762709140778</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11534,7 +11534,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741310119629</v>
+        <v>1.80741322040558</v>
       </c>
       <c r="H385" t="n">
         <v>3798</v>
@@ -11563,7 +11563,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074927330017</v>
+        <v>1.83074915409088</v>
       </c>
       <c r="H386" t="n">
         <v>3583</v>
@@ -11592,7 +11592,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H387" t="n">
         <v>1000</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11650,7 +11650,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>1.81042408943176</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H389" t="n">
         <v>98</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816566944122</v>
+        <v>1.80816555023193</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11708,7 +11708,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="n">
-        <v>1.8262323141098</v>
+        <v>1.82623243331909</v>
       </c>
       <c r="H391" t="n">
         <v>2650</v>
@@ -11737,7 +11737,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>1.81042408943176</v>
+        <v>1.81042420864105</v>
       </c>
       <c r="H392" t="n">
         <v>1413</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.83601832389832</v>
+        <v>1.83601868152618</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11795,7 +11795,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>1.83902966976166</v>
+        <v>1.83902990818024</v>
       </c>
       <c r="H394" t="n">
         <v>3433</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429883956909</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429883956909</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11882,7 +11882,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H397" t="n">
         <v>2269</v>
@@ -11911,7 +11911,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H398" t="n">
         <v>776</v>
@@ -11940,7 +11940,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>1.82171595096588</v>
+        <v>1.82171583175659</v>
       </c>
       <c r="H399" t="n">
         <v>788</v>
@@ -11969,7 +11969,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806299209595</v>
+        <v>1.84806287288666</v>
       </c>
       <c r="H400" t="n">
         <v>1454</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.8465576171875</v>
+        <v>1.84655737876892</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752393722534</v>
+        <v>1.83752417564392</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.8977462053299</v>
+        <v>1.89774596691132</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12085,7 +12085,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280162334442</v>
+        <v>1.91280174255371</v>
       </c>
       <c r="H404" t="n">
         <v>21296</v>
@@ -12114,7 +12114,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.97377622127533</v>
+        <v>1.9737765789032</v>
       </c>
       <c r="H405" t="n">
         <v>8569</v>
@@ -12143,7 +12143,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.97377622127533</v>
+        <v>1.9737765789032</v>
       </c>
       <c r="H406" t="n">
         <v>3339</v>
@@ -12172,7 +12172,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>1.97151827812195</v>
+        <v>1.97151815891266</v>
       </c>
       <c r="H407" t="n">
         <v>2092</v>
@@ -12201,7 +12201,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086802959442</v>
+        <v>1.93086814880371</v>
       </c>
       <c r="H408" t="n">
         <v>4037</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613743782043</v>
+        <v>1.93613767623901</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12259,7 +12259,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237376213074</v>
+        <v>1.93237364292145</v>
       </c>
       <c r="H410" t="n">
         <v>3461</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957664489746</v>
+        <v>1.91957652568817</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12346,7 +12346,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796019554138</v>
+        <v>1.88796007633209</v>
       </c>
       <c r="H413" t="n">
         <v>1727</v>
@@ -12404,7 +12404,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720738887787</v>
+        <v>1.88720726966858</v>
       </c>
       <c r="H415" t="n">
         <v>1165</v>
@@ -12433,7 +12433,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>1.89548766613007</v>
+        <v>1.89548778533936</v>
       </c>
       <c r="H416" t="n">
         <v>873</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452098846436</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.86010718345642</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12578,7 +12578,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860180854797</v>
       </c>
       <c r="H421" t="n">
         <v>1458</v>
@@ -12607,7 +12607,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H422" t="n">
         <v>5360</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.85634350776672</v>
+        <v>1.85634338855743</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H426" t="n">
         <v>1972</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.85634350776672</v>
+        <v>1.85634338855743</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12810,7 +12810,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215173244476</v>
+        <v>1.87215185165405</v>
       </c>
       <c r="H429" t="n">
         <v>140</v>
@@ -12839,7 +12839,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860204696655</v>
+        <v>1.85860180854797</v>
       </c>
       <c r="H430" t="n">
         <v>1130</v>
@@ -12868,7 +12868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H431" t="n">
         <v>1257</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.86010718345642</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12926,7 +12926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H433" t="n">
         <v>2572</v>
@@ -12955,7 +12955,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.87064647674561</v>
+        <v>1.87064611911774</v>
       </c>
       <c r="H434" t="n">
         <v>4633</v>
@@ -12984,7 +12984,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161291599274</v>
+        <v>1.86161279678345</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193762302399</v>
+        <v>1.88193798065186</v>
       </c>
       <c r="H436" t="n">
         <v>2642</v>
@@ -13042,7 +13042,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763513088226</v>
+        <v>1.86763501167297</v>
       </c>
       <c r="H437" t="n">
         <v>1511</v>
@@ -13071,7 +13071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688244342804</v>
       </c>
       <c r="H438" t="n">
         <v>969</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.8736572265625</v>
+        <v>1.87365746498108</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.86537706851959</v>
+        <v>1.8653769493103</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.86010718345642</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13216,7 +13216,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257971286774</v>
+        <v>1.85257947444916</v>
       </c>
       <c r="H443" t="n">
         <v>1174</v>
@@ -13245,7 +13245,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204089641571</v>
+        <v>1.84204077720642</v>
       </c>
       <c r="H444" t="n">
         <v>1977</v>
@@ -13303,7 +13303,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279370307922</v>
+        <v>1.84279334545135</v>
       </c>
       <c r="H446" t="n">
         <v>1136</v>
@@ -13332,7 +13332,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H447" t="n">
         <v>5011</v>
@@ -13361,7 +13361,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795179843903</v>
+        <v>1.81795191764832</v>
       </c>
       <c r="H448" t="n">
         <v>5592</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397401332855</v>
+        <v>1.82397413253784</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13419,7 +13419,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849073410034</v>
+        <v>1.82849085330963</v>
       </c>
       <c r="H450" t="n">
         <v>3382</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569397449493</v>
+        <v>1.81569385528564</v>
       </c>
       <c r="H451" t="n">
         <v>4388</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117677688599</v>
+        <v>1.81117689609528</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13593,7 +13593,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H456" t="n">
         <v>3211</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246840000153</v>
+        <v>1.82246851921082</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547986507416</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13767,7 +13767,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="n">
-        <v>1.83526563644409</v>
+        <v>1.83526575565338</v>
       </c>
       <c r="H462" t="n">
         <v>3800</v>
@@ -13796,7 +13796,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881567955017</v>
+        <v>1.84881579875946</v>
       </c>
       <c r="H463" t="n">
         <v>34293</v>
@@ -13825,7 +13825,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849901199341</v>
+        <v>1.89849889278412</v>
       </c>
       <c r="H464" t="n">
         <v>4953</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731798648834</v>
+        <v>1.91731834411621</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13941,7 +13941,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474301815033</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H468" t="n">
         <v>14648</v>
@@ -13970,7 +13970,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>1.94366562366486</v>
+        <v>1.94366538524628</v>
       </c>
       <c r="H469" t="n">
         <v>12171</v>
@@ -14086,7 +14086,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248483657837</v>
+        <v>1.96248459815979</v>
       </c>
       <c r="H473" t="n">
         <v>11988</v>
@@ -14144,7 +14144,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>2.04378461837769</v>
+        <v>2.04378437995911</v>
       </c>
       <c r="H475" t="n">
         <v>19009</v>
@@ -14260,7 +14260,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582077026367</v>
+        <v>1.98582065105438</v>
       </c>
       <c r="H479" t="n">
         <v>3201</v>
@@ -14318,7 +14318,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624863147736</v>
+        <v>1.96624851226807</v>
       </c>
       <c r="H481" t="n">
         <v>7605</v>
@@ -14347,7 +14347,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861812591553</v>
+        <v>1.99861788749695</v>
       </c>
       <c r="H482" t="n">
         <v>7953</v>
@@ -14405,7 +14405,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474301815033</v>
+        <v>1.96474325656891</v>
       </c>
       <c r="H484" t="n">
         <v>3107</v>
@@ -14463,7 +14463,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98280990123749</v>
+        <v>1.98280942440033</v>
       </c>
       <c r="H486" t="n">
         <v>699</v>
@@ -14492,7 +14492,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.97377622127533</v>
+        <v>1.9737765789032</v>
       </c>
       <c r="H487" t="n">
         <v>871</v>
@@ -14550,7 +14550,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H489" t="n">
         <v>11786</v>
@@ -14579,7 +14579,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H490" t="n">
         <v>4910</v>
@@ -14637,7 +14637,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>2.08142352104187</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H492" t="n">
         <v>5737</v>
@@ -14666,7 +14666,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.06260395050049</v>
+        <v>2.06260371208191</v>
       </c>
       <c r="H493" t="n">
         <v>9201</v>
@@ -14695,7 +14695,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="n">
-        <v>2.08217620849609</v>
+        <v>2.08217597007751</v>
       </c>
       <c r="H494" t="n">
         <v>11805</v>
@@ -14753,7 +14753,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>2.08142352104187</v>
+        <v>2.08142328262329</v>
       </c>
       <c r="H496" t="n">
         <v>1344</v>
@@ -14782,7 +14782,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765936851501</v>
+        <v>2.07765960693359</v>
       </c>
       <c r="H497" t="n">
         <v>3216</v>
@@ -14840,7 +14840,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>2.09045672416687</v>
+        <v>2.09045648574829</v>
       </c>
       <c r="H499" t="n">
         <v>6270</v>
@@ -14869,7 +14869,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.11153411865234</v>
+        <v>2.11153435707092</v>
       </c>
       <c r="H500" t="n">
         <v>1908</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024285316467</v>
+        <v>2.10024261474609</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -14985,7 +14985,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034541130066</v>
+        <v>2.06034564971924</v>
       </c>
       <c r="H504" t="n">
         <v>2924</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615375518799</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15188,7 +15188,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08518743515015</v>
+        <v>2.08518719673157</v>
       </c>
       <c r="H511" t="n">
         <v>1601</v>
@@ -15217,7 +15217,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185906410217</v>
+        <v>2.13185930252075</v>
       </c>
       <c r="H512" t="n">
         <v>18197</v>
@@ -15304,7 +15304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.1755199432373</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H515" t="n">
         <v>6715</v>
@@ -15362,7 +15362,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.1755199432373</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H517" t="n">
         <v>16053</v>
@@ -15478,7 +15478,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H521" t="n">
         <v>10697</v>
@@ -15507,7 +15507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31854724884033</v>
+        <v>2.31854748725891</v>
       </c>
       <c r="H522" t="n">
         <v>6269</v>
@@ -15536,7 +15536,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>2.31854724884033</v>
+        <v>2.31854748725891</v>
       </c>
       <c r="H523" t="n">
         <v>1601</v>
@@ -15623,7 +15623,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H526" t="n">
         <v>2705</v>
@@ -15797,7 +15797,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30349183082581</v>
+        <v>2.30349206924438</v>
       </c>
       <c r="H532" t="n">
         <v>3569</v>
@@ -15826,7 +15826,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596424102783</v>
+        <v>2.29596400260925</v>
       </c>
       <c r="H533" t="n">
         <v>4435</v>
@@ -15884,7 +15884,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="n">
-        <v>2.25832557678223</v>
+        <v>2.25832533836365</v>
       </c>
       <c r="H535" t="n">
         <v>3431</v>
@@ -15913,7 +15913,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="n">
-        <v>2.25832557678223</v>
+        <v>2.25832533836365</v>
       </c>
       <c r="H536" t="n">
         <v>5445</v>
@@ -15971,7 +15971,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810366630554</v>
+        <v>2.19810342788696</v>
       </c>
       <c r="H538" t="n">
         <v>2100</v>
@@ -16174,7 +16174,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="n">
-        <v>2.25832557678223</v>
+        <v>2.25832533836365</v>
       </c>
       <c r="H545" t="n">
         <v>2533</v>
@@ -16203,7 +16203,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="n">
-        <v>2.43899178504944</v>
+        <v>2.43899154663086</v>
       </c>
       <c r="H546" t="n">
         <v>30842</v>
@@ -16290,7 +16290,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190777778625</v>
+        <v>2.55190801620483</v>
       </c>
       <c r="H549" t="n">
         <v>41764</v>
@@ -16406,7 +16406,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168586730957</v>
       </c>
       <c r="H553" t="n">
         <v>5398</v>
@@ -16464,7 +16464,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>2.40135288238525</v>
+        <v>2.40135264396667</v>
       </c>
       <c r="H555" t="n">
         <v>12859</v>
@@ -16493,7 +16493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H556" t="n">
         <v>9076</v>
@@ -16522,7 +16522,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="n">
-        <v>2.43899178504944</v>
+        <v>2.43899154663086</v>
       </c>
       <c r="H557" t="n">
         <v>6923</v>
@@ -16551,7 +16551,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H558" t="n">
         <v>4749</v>
@@ -16609,7 +16609,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H560" t="n">
         <v>3851</v>
@@ -16667,7 +16667,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H562" t="n">
         <v>6597</v>
@@ -16725,7 +16725,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H564" t="n">
         <v>2298</v>
@@ -16754,7 +16754,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H565" t="n">
         <v>7437</v>
@@ -16812,7 +16812,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H567" t="n">
         <v>3892</v>
@@ -16841,7 +16841,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H568" t="n">
         <v>2129</v>
@@ -16870,7 +16870,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H569" t="n">
         <v>7088</v>
@@ -16899,7 +16899,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H570" t="n">
         <v>3764</v>
@@ -16928,7 +16928,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H571" t="n">
         <v>3605</v>
@@ -16957,7 +16957,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H572" t="n">
         <v>2095</v>
@@ -17015,7 +17015,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H574" t="n">
         <v>2337</v>
@@ -17044,7 +17044,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H575" t="n">
         <v>4786</v>
@@ -17073,7 +17073,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H576" t="n">
         <v>1561</v>
@@ -17102,7 +17102,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H577" t="n">
         <v>3502</v>
@@ -17131,7 +17131,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404672622681</v>
+        <v>2.45404696464539</v>
       </c>
       <c r="H578" t="n">
         <v>1479</v>
@@ -17160,7 +17160,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H579" t="n">
         <v>1694</v>
@@ -17189,7 +17189,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168586730957</v>
       </c>
       <c r="H580" t="n">
         <v>7145</v>
@@ -17218,7 +17218,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.44651913642883</v>
+        <v>2.44651937484741</v>
       </c>
       <c r="H581" t="n">
         <v>3145</v>
@@ -17247,7 +17247,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H582" t="n">
         <v>1436</v>
@@ -17276,7 +17276,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168586730957</v>
       </c>
       <c r="H583" t="n">
         <v>1838</v>
@@ -17334,7 +17334,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="n">
-        <v>2.47663068771362</v>
+        <v>2.47663044929504</v>
       </c>
       <c r="H585" t="n">
         <v>521</v>
@@ -17450,7 +17450,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H589" t="n">
         <v>8373</v>
@@ -17479,7 +17479,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H590" t="n">
         <v>1457</v>
@@ -17508,7 +17508,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H591" t="n">
         <v>1072</v>
@@ -17537,7 +17537,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363485336304</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H592" t="n">
         <v>1427</v>
@@ -17595,7 +17595,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604844093323</v>
       </c>
       <c r="H594" t="n">
         <v>2722</v>
@@ -17653,7 +17653,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G596" t="n">
-        <v>2.59139394760132</v>
+        <v>2.59139370918274</v>
       </c>
       <c r="H596" t="n">
         <v>14950</v>
@@ -17682,7 +17682,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363485336304</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H597" t="n">
         <v>5094</v>
@@ -17711,7 +17711,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H598" t="n">
         <v>3047</v>
@@ -17914,7 +17914,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604867935181</v>
+        <v>2.50604844093323</v>
       </c>
       <c r="H605" t="n">
         <v>1385</v>
@@ -17972,7 +17972,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846155166626</v>
       </c>
       <c r="H607" t="n">
         <v>6484</v>
@@ -18001,7 +18001,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H608" t="n">
         <v>12294</v>
@@ -18030,7 +18030,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H609" t="n">
         <v>3124</v>
@@ -18175,7 +18175,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H614" t="n">
         <v>7400</v>
@@ -18204,7 +18204,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H615" t="n">
         <v>6196</v>
@@ -18233,7 +18233,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.2189781665802</v>
+        <v>2.21897792816162</v>
       </c>
       <c r="H616" t="n">
         <v>2444</v>
@@ -18262,7 +18262,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>2.23449540138245</v>
+        <v>2.23449516296387</v>
       </c>
       <c r="H617" t="n">
         <v>4378</v>
@@ -18291,7 +18291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H618" t="n">
         <v>1075</v>
@@ -18436,7 +18436,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H623" t="n">
         <v>4311</v>
@@ -18465,7 +18465,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H624" t="n">
         <v>215</v>
@@ -18494,7 +18494,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H625" t="n">
         <v>1193</v>
@@ -18581,7 +18581,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H628" t="n">
         <v>125</v>
@@ -18610,7 +18610,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>2.23449540138245</v>
+        <v>2.23449516296387</v>
       </c>
       <c r="H629" t="n">
         <v>1246</v>
@@ -18639,7 +18639,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.2189781665802</v>
+        <v>2.21897792816162</v>
       </c>
       <c r="H630" t="n">
         <v>1237</v>
@@ -18668,7 +18668,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H631" t="n">
         <v>1652</v>
@@ -18697,7 +18697,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H632" t="n">
         <v>2259</v>
@@ -18755,7 +18755,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H634" t="n">
         <v>786</v>
@@ -18784,7 +18784,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H635" t="n">
         <v>2701</v>
@@ -18813,7 +18813,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H636" t="n">
         <v>1273</v>
@@ -18842,7 +18842,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H637" t="n">
         <v>1582</v>
@@ -18958,7 +18958,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H641" t="n">
         <v>2464</v>
@@ -19016,7 +19016,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H643" t="n">
         <v>2317</v>
@@ -19074,7 +19074,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H645" t="n">
         <v>4007</v>
@@ -19103,7 +19103,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H646" t="n">
         <v>7254</v>
@@ -19161,7 +19161,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H648" t="n">
         <v>3807</v>
@@ -19190,7 +19190,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H649" t="n">
         <v>1745</v>
@@ -19219,7 +19219,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.16466760635376</v>
+        <v>2.1646671295166</v>
       </c>
       <c r="H650" t="n">
         <v>2832</v>
@@ -19335,7 +19335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656434059143</v>
       </c>
       <c r="H654" t="n">
         <v>4303</v>
@@ -19422,7 +19422,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H657" t="n">
         <v>790</v>
@@ -19451,7 +19451,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H658" t="n">
         <v>1560</v>
@@ -19480,7 +19480,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23449540138245</v>
+        <v>2.23449516296387</v>
       </c>
       <c r="H659" t="n">
         <v>4624</v>
@@ -19509,7 +19509,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.18794322013855</v>
+        <v>2.18794345855713</v>
       </c>
       <c r="H660" t="n">
         <v>1057</v>
@@ -19538,7 +19538,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H661" t="n">
         <v>1158</v>
@@ -19567,7 +19567,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H662" t="n">
         <v>2066</v>
@@ -19625,7 +19625,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H664" t="n">
         <v>190</v>
@@ -19654,7 +19654,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H665" t="n">
         <v>392</v>
@@ -19683,7 +19683,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H666" t="n">
         <v>989</v>
@@ -19712,7 +19712,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H667" t="n">
         <v>232</v>
@@ -19741,7 +19741,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259795188904</v>
+        <v>2.10259819030762</v>
       </c>
       <c r="H668" t="n">
         <v>25</v>
@@ -19770,7 +19770,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H669" t="n">
         <v>1070</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H671" t="n">
         <v>3968</v>
@@ -19944,7 +19944,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>1.9707008600235</v>
+        <v>1.97070062160492</v>
       </c>
       <c r="H675" t="n">
         <v>420</v>
@@ -19973,7 +19973,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H676" t="n">
         <v>3545</v>
@@ -20002,7 +20002,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966579437256</v>
+        <v>1.93966615200043</v>
       </c>
       <c r="H677" t="n">
         <v>2534</v>
@@ -20060,7 +20060,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H679" t="n">
         <v>3984</v>
@@ -20089,7 +20089,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>1.85432064533234</v>
+        <v>1.85432076454163</v>
       </c>
       <c r="H680" t="n">
         <v>1873</v>
@@ -20118,7 +20118,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983788013458</v>
+        <v>1.86983799934387</v>
       </c>
       <c r="H681" t="n">
         <v>254</v>
@@ -20147,7 +20147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225158691406</v>
       </c>
       <c r="H682" t="n">
         <v>1859</v>
@@ -20205,7 +20205,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H684" t="n">
         <v>5886</v>
@@ -20234,7 +20234,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H685" t="n">
         <v>1968</v>
@@ -20292,7 +20292,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H687" t="n">
         <v>17503</v>
@@ -20350,7 +20350,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H689" t="n">
         <v>2525</v>
@@ -20437,7 +20437,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H692" t="n">
         <v>1912</v>
@@ -20698,7 +20698,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845935821533</v>
+        <v>1.97845923900604</v>
       </c>
       <c r="H701" t="n">
         <v>7483</v>
@@ -20785,7 +20785,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H704" t="n">
         <v>1</v>
@@ -20872,7 +20872,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294188499451</v>
       </c>
       <c r="H707" t="n">
         <v>4382</v>
@@ -20901,7 +20901,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845935821533</v>
+        <v>1.97845923900604</v>
       </c>
       <c r="H708" t="n">
         <v>6007</v>
@@ -20930,7 +20930,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H709" t="n">
         <v>2556</v>
@@ -20959,7 +20959,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H710" t="n">
         <v>965</v>
@@ -20988,7 +20988,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>1.92414855957031</v>
+        <v>1.9241486787796</v>
       </c>
       <c r="H711" t="n">
         <v>4086</v>
@@ -21075,7 +21075,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104491233826</v>
+        <v>1.83104467391968</v>
       </c>
       <c r="H714" t="n">
         <v>2033</v>
@@ -21104,7 +21104,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207938194275</v>
+        <v>1.86207926273346</v>
       </c>
       <c r="H715" t="n">
         <v>1620</v>
@@ -21162,7 +21162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225146770477</v>
+        <v>1.79225158691406</v>
       </c>
       <c r="H717" t="n">
         <v>747</v>
@@ -21191,7 +21191,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776846408844</v>
+        <v>1.80776870250702</v>
       </c>
       <c r="H718" t="n">
         <v>821</v>
@@ -21220,7 +21220,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.75345802307129</v>
+        <v>1.75345814228058</v>
       </c>
       <c r="H719" t="n">
         <v>3685</v>
@@ -21278,7 +21278,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569952487946</v>
+        <v>1.74569928646088</v>
       </c>
       <c r="H721" t="n">
         <v>2119</v>
@@ -21307,7 +21307,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="n">
-        <v>1.82328617572784</v>
+        <v>1.82328605651855</v>
       </c>
       <c r="H722" t="n">
         <v>1535</v>
@@ -21336,7 +21336,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="n">
-        <v>1.82328617572784</v>
+        <v>1.82328605651855</v>
       </c>
       <c r="H723" t="n">
         <v>8398</v>
@@ -21365,7 +21365,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H724" t="n">
         <v>2115</v>
@@ -21394,7 +21394,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311397075653</v>
+        <v>1.89311408996582</v>
       </c>
       <c r="H726" t="n">
         <v>6832</v>
@@ -21481,7 +21481,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.87759685516357</v>
+        <v>1.877596616745</v>
       </c>
       <c r="H728" t="n">
         <v>961</v>
@@ -21510,7 +21510,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966579437256</v>
+        <v>1.93966615200043</v>
       </c>
       <c r="H729" t="n">
         <v>4613</v>
@@ -21626,7 +21626,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H733" t="n">
         <v>5119</v>
@@ -21655,7 +21655,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>2.19570159912109</v>
+        <v>2.19570183753967</v>
       </c>
       <c r="H734" t="n">
         <v>12578</v>
@@ -21742,7 +21742,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H737" t="n">
         <v>2727</v>
@@ -21771,7 +21771,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H738" t="n">
         <v>169</v>
@@ -21858,7 +21858,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H741" t="n">
         <v>1711</v>
@@ -21916,7 +21916,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.16466760635376</v>
+        <v>2.1646671295166</v>
       </c>
       <c r="H743" t="n">
         <v>2565</v>
@@ -21974,7 +21974,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H745" t="n">
         <v>2434</v>
@@ -22003,7 +22003,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H746" t="n">
         <v>1264</v>
@@ -22061,7 +22061,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="n">
-        <v>2.13363265991211</v>
+        <v>2.13363242149353</v>
       </c>
       <c r="H748" t="n">
         <v>1576</v>
@@ -22090,7 +22090,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H749" t="n">
         <v>391</v>
@@ -22119,7 +22119,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H750" t="n">
         <v>1498</v>
@@ -22148,7 +22148,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H751" t="n">
         <v>290</v>
@@ -22177,7 +22177,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397683143616</v>
+        <v>1.99397671222687</v>
       </c>
       <c r="H752" t="n">
         <v>6924</v>
@@ -22206,7 +22206,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H753" t="n">
         <v>8109</v>
@@ -22235,7 +22235,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H754" t="n">
         <v>2611</v>
@@ -22264,7 +22264,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>2.07932209968567</v>
+        <v>2.07932186126709</v>
       </c>
       <c r="H755" t="n">
         <v>1058</v>
@@ -22438,7 +22438,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H761" t="n">
         <v>5897</v>
@@ -22496,7 +22496,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483933448792</v>
+        <v>2.09483909606934</v>
       </c>
       <c r="H763" t="n">
         <v>154</v>
@@ -22525,7 +22525,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="n">
-        <v>2.06380462646484</v>
+        <v>2.06380438804626</v>
       </c>
       <c r="H764" t="n">
         <v>350</v>
@@ -22670,7 +22670,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139151573181</v>
       </c>
       <c r="H769" t="n">
         <v>3390</v>
@@ -22757,7 +22757,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H772" t="n">
         <v>443</v>
@@ -22902,7 +22902,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H777" t="n">
         <v>329</v>
@@ -22931,7 +22931,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H778" t="n">
         <v>160</v>
@@ -22960,7 +22960,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>2.15690851211548</v>
+        <v>2.15690875053406</v>
       </c>
       <c r="H779" t="n">
         <v>3252</v>
@@ -23018,7 +23018,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.2034604549408</v>
+        <v>2.20346069335938</v>
       </c>
       <c r="H781" t="n">
         <v>1441</v>
@@ -23076,7 +23076,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H783" t="n">
         <v>1355</v>
@@ -23134,7 +23134,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26553010940552</v>
+        <v>2.26552987098694</v>
       </c>
       <c r="H785" t="n">
         <v>674</v>
@@ -23279,7 +23279,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H790" t="n">
         <v>6067</v>
@@ -23308,7 +23308,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656434059143</v>
       </c>
       <c r="H791" t="n">
         <v>238</v>
@@ -23337,7 +23337,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H792" t="n">
         <v>323</v>
@@ -23366,7 +23366,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656457901001</v>
+        <v>2.29656434059143</v>
       </c>
       <c r="H793" t="n">
         <v>206</v>
@@ -23395,7 +23395,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H794" t="n">
         <v>836</v>
@@ -23424,7 +23424,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H795" t="n">
         <v>1453</v>
@@ -23482,7 +23482,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H797" t="n">
         <v>1948</v>
@@ -23540,7 +23540,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432319641113</v>
+        <v>2.30432343482971</v>
       </c>
       <c r="H799" t="n">
         <v>553</v>
@@ -23569,7 +23569,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.32759928703308</v>
+        <v>2.3275990486145</v>
       </c>
       <c r="H800" t="n">
         <v>673</v>
@@ -23627,7 +23627,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H802" t="n">
         <v>276</v>
@@ -23656,7 +23656,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846155166626</v>
       </c>
       <c r="H803" t="n">
         <v>8524</v>
@@ -24004,7 +24004,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>2.42070341110229</v>
+        <v>2.42070317268372</v>
       </c>
       <c r="H815" t="n">
         <v>535</v>
@@ -24178,7 +24178,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="n">
-        <v>2.36639261245728</v>
+        <v>2.3663923740387</v>
       </c>
       <c r="H821" t="n">
         <v>1310</v>
@@ -24265,7 +24265,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.37415099143982</v>
+        <v>2.37415146827698</v>
       </c>
       <c r="H824" t="n">
         <v>915</v>
@@ -24497,7 +24497,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H832" t="n">
         <v>6312</v>
@@ -24526,7 +24526,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H833" t="n">
         <v>10097</v>
@@ -24555,7 +24555,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501397132874</v>
+        <v>2.47501373291016</v>
       </c>
       <c r="H834" t="n">
         <v>2763</v>
@@ -24642,7 +24642,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H837" t="n">
         <v>17949</v>
@@ -24816,7 +24816,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H843" t="n">
         <v>3263</v>
@@ -24845,7 +24845,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H844" t="n">
         <v>715</v>
@@ -24874,7 +24874,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H845" t="n">
         <v>800</v>
@@ -24903,7 +24903,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H846" t="n">
         <v>241</v>
@@ -24990,7 +24990,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H849" t="n">
         <v>1869</v>
@@ -25193,7 +25193,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H856" t="n">
         <v>3013</v>
@@ -25251,7 +25251,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807475090027</v>
       </c>
       <c r="H858" t="n">
         <v>6283</v>
@@ -25280,7 +25280,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H859" t="n">
         <v>1608</v>
@@ -25396,7 +25396,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H863" t="n">
         <v>11000</v>
@@ -25454,7 +25454,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H865" t="n">
         <v>4994</v>
@@ -25483,7 +25483,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H866" t="n">
         <v>6419</v>
@@ -25512,7 +25512,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H867" t="n">
         <v>13328</v>
@@ -25541,7 +25541,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H868" t="n">
         <v>3222</v>
@@ -25570,7 +25570,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H869" t="n">
         <v>2149</v>
@@ -25657,7 +25657,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H872" t="n">
         <v>854</v>
@@ -25715,7 +25715,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H874" t="n">
         <v>1167</v>
@@ -25744,7 +25744,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H875" t="n">
         <v>3142</v>
@@ -25802,7 +25802,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H877" t="n">
         <v>834</v>
@@ -25831,7 +25831,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H878" t="n">
         <v>1616</v>
@@ -25860,7 +25860,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H879" t="n">
         <v>4136</v>
@@ -25889,7 +25889,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H880" t="n">
         <v>3525</v>
@@ -25918,7 +25918,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H881" t="n">
         <v>2373</v>
@@ -25947,7 +25947,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H882" t="n">
         <v>5668</v>
@@ -25976,7 +25976,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H883" t="n">
         <v>3351</v>
@@ -26005,7 +26005,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H884" t="n">
         <v>1520</v>
@@ -26034,7 +26034,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H885" t="n">
         <v>538</v>
@@ -26063,7 +26063,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H886" t="n">
         <v>7315</v>
@@ -26092,7 +26092,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H887" t="n">
         <v>800</v>
@@ -26150,7 +26150,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H889" t="n">
         <v>1830</v>
@@ -26179,7 +26179,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H890" t="n">
         <v>1360</v>
@@ -26266,7 +26266,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H893" t="n">
         <v>110</v>
@@ -26324,7 +26324,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H895" t="n">
         <v>1271</v>
@@ -26498,7 +26498,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H901" t="n">
         <v>609</v>
@@ -26556,7 +26556,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H903" t="n">
         <v>350</v>
@@ -26585,7 +26585,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H904" t="n">
         <v>217</v>
@@ -26614,7 +26614,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H905" t="n">
         <v>1973</v>
@@ -26701,7 +26701,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H908" t="n">
         <v>2849</v>
@@ -26759,7 +26759,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H910" t="n">
         <v>1929</v>
@@ -26817,7 +26817,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H912" t="n">
         <v>600</v>
@@ -26875,7 +26875,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H914" t="n">
         <v>953</v>
@@ -26991,7 +26991,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H918" t="n">
         <v>1740</v>
@@ -27049,7 +27049,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H920" t="n">
         <v>1145</v>
@@ -27078,7 +27078,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H921" t="n">
         <v>26</v>
@@ -27136,7 +27136,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H923" t="n">
         <v>3737</v>
@@ -27165,7 +27165,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H924" t="n">
         <v>715</v>
@@ -27194,7 +27194,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H925" t="n">
         <v>1884</v>
@@ -27223,7 +27223,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H926" t="n">
         <v>550</v>
@@ -27310,7 +27310,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H929" t="n">
         <v>12745</v>
@@ -27368,7 +27368,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H931" t="n">
         <v>382</v>
@@ -27426,7 +27426,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H933" t="n">
         <v>570</v>
@@ -27832,7 +27832,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H947" t="n">
         <v>252</v>
@@ -27861,7 +27861,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H948" t="n">
         <v>60</v>
@@ -28006,7 +28006,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H953" t="n">
         <v>2198</v>
@@ -28064,7 +28064,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H955" t="n">
         <v>5035</v>
@@ -28180,7 +28180,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H959" t="n">
         <v>2779</v>
@@ -28296,7 +28296,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H963" t="n">
         <v>122</v>
@@ -28325,7 +28325,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253160476685</v>
+        <v>2.42253184318542</v>
       </c>
       <c r="H964" t="n">
         <v>5121</v>
@@ -28586,7 +28586,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H973" t="n">
         <v>1750</v>
@@ -28789,7 +28789,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>2.53634214401245</v>
+        <v>2.53634190559387</v>
       </c>
       <c r="H980" t="n">
         <v>239</v>
@@ -28818,7 +28818,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H981" t="n">
         <v>487</v>
@@ -28847,7 +28847,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H982" t="n">
         <v>1427</v>
@@ -28905,7 +28905,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H984" t="n">
         <v>3320</v>
@@ -28992,7 +28992,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H987" t="n">
         <v>13081</v>
@@ -29050,7 +29050,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H989" t="n">
         <v>3240</v>
@@ -29108,7 +29108,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H991" t="n">
         <v>1405</v>
@@ -29137,7 +29137,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511781692505</v>
+        <v>2.58511757850647</v>
       </c>
       <c r="H992" t="n">
         <v>1412</v>
@@ -29166,7 +29166,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H993" t="n">
         <v>1096</v>
@@ -29195,7 +29195,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.56072974205017</v>
+        <v>2.56072998046875</v>
       </c>
       <c r="H994" t="n">
         <v>3106</v>
@@ -29224,7 +29224,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H995" t="n">
         <v>1008</v>
@@ -29282,7 +29282,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.59324717521667</v>
+        <v>2.5932469367981</v>
       </c>
       <c r="H997" t="n">
         <v>2043</v>
@@ -29311,7 +29311,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>2.5444712638855</v>
+        <v>2.54447102546692</v>
       </c>
       <c r="H998" t="n">
         <v>2368</v>
@@ -29340,7 +29340,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H999" t="n">
         <v>2190</v>
@@ -29369,7 +29369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H1000" t="n">
         <v>2768</v>
@@ -29398,7 +29398,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1001" t="n">
         <v>6864</v>
@@ -29427,7 +29427,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H1002" t="n">
         <v>900</v>
@@ -29456,7 +29456,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1003" t="n">
         <v>101</v>
@@ -29572,7 +29572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382471084595</v>
+        <v>2.50382447242737</v>
       </c>
       <c r="H1007" t="n">
         <v>1267</v>
@@ -29659,7 +29659,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1010" t="n">
         <v>24</v>
@@ -29688,7 +29688,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1011" t="n">
         <v>1121</v>
@@ -29717,7 +29717,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1012" t="n">
         <v>21303</v>
@@ -29746,7 +29746,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1013" t="n">
         <v>1283</v>
@@ -29775,7 +29775,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1014" t="n">
         <v>2374</v>
@@ -29804,7 +29804,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1015" t="n">
         <v>284</v>
@@ -29833,7 +29833,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1016" t="n">
         <v>257</v>
@@ -29862,7 +29862,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130751609802</v>
+        <v>2.47130727767944</v>
       </c>
       <c r="H1017" t="n">
         <v>2120</v>
@@ -29949,7 +29949,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.47943687438965</v>
+        <v>2.47943663597107</v>
       </c>
       <c r="H1020" t="n">
         <v>2880</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1021" t="n">
         <v>1241</v>
@@ -30007,7 +30007,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1022" t="n">
         <v>825</v>
@@ -30123,7 +30123,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1026" t="n">
         <v>3715</v>
@@ -30384,7 +30384,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H1035" t="n">
         <v>4055</v>
@@ -30442,7 +30442,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936785697937</v>
+        <v>2.34936809539795</v>
       </c>
       <c r="H1037" t="n">
         <v>281</v>
@@ -30471,7 +30471,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1038" t="n">
         <v>2153</v>
@@ -30616,7 +30616,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1043" t="n">
         <v>734</v>
@@ -30645,7 +30645,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.29246282577515</v>
+        <v>2.29246306419373</v>
       </c>
       <c r="H1044" t="n">
         <v>1687</v>
@@ -30703,7 +30703,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1046" t="n">
         <v>202</v>
@@ -30761,7 +30761,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1048" t="n">
         <v>5485</v>
@@ -30790,7 +30790,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1049" t="n">
         <v>199</v>
@@ -30935,7 +30935,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.18678212165833</v>
+        <v>2.18678188323975</v>
       </c>
       <c r="H1054" t="n">
         <v>1553</v>
@@ -30964,7 +30964,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1055" t="n">
         <v>2197</v>
@@ -31167,7 +31167,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412689208984</v>
+        <v>1.89412701129913</v>
       </c>
       <c r="H1062" t="n">
         <v>1691</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1064" t="n">
         <v>931</v>
@@ -31254,7 +31254,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.6258602142334</v>
+        <v>1.62586009502411</v>
       </c>
       <c r="H1065" t="n">
         <v>2252</v>
@@ -31341,7 +31341,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205015182495</v>
       </c>
       <c r="H1068" t="n">
         <v>7444</v>
@@ -31370,7 +31370,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1069" t="n">
         <v>3426</v>
@@ -31399,7 +31399,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.55676102638245</v>
+        <v>1.55676114559174</v>
       </c>
       <c r="H1070" t="n">
         <v>1307</v>
@@ -31428,7 +31428,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.54863178730011</v>
+        <v>1.54863166809082</v>
       </c>
       <c r="H1071" t="n">
         <v>1513</v>
@@ -31457,7 +31457,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237330913544</v>
+        <v>1.53237318992615</v>
       </c>
       <c r="H1072" t="n">
         <v>3746</v>
@@ -31486,7 +31486,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1073" t="n">
         <v>1682</v>
@@ -31515,7 +31515,7 @@
         <v>19.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.58521378040314</v>
+        <v>1.58521366119385</v>
       </c>
       <c r="H1074" t="n">
         <v>4651</v>
@@ -31544,7 +31544,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1075" t="n">
         <v>5340</v>
@@ -31573,7 +31573,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1076" t="n">
         <v>10</v>
@@ -31602,7 +31602,7 @@
         <v>19.5</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.58521378040314</v>
+        <v>1.58521366119385</v>
       </c>
       <c r="H1077" t="n">
         <v>744</v>
@@ -31660,7 +31660,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.56082582473755</v>
+        <v>1.56082606315613</v>
       </c>
       <c r="H1079" t="n">
         <v>1845</v>
@@ -31718,7 +31718,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.56895506381989</v>
+        <v>1.5689549446106</v>
       </c>
       <c r="H1081" t="n">
         <v>3195</v>
@@ -31747,7 +31747,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.56895506381989</v>
+        <v>1.5689549446106</v>
       </c>
       <c r="H1082" t="n">
         <v>830</v>
@@ -31776,7 +31776,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1083" t="n">
         <v>2497</v>
@@ -31834,7 +31834,7 @@
         <v>19.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.58521378040314</v>
+        <v>1.58521366119385</v>
       </c>
       <c r="H1085" t="n">
         <v>5919</v>
@@ -32008,7 +32008,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.62179553508759</v>
+        <v>1.62179565429688</v>
       </c>
       <c r="H1091" t="n">
         <v>4180</v>
@@ -32066,7 +32066,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.58927822113037</v>
+        <v>1.58927810192108</v>
       </c>
       <c r="H1093" t="n">
         <v>1175</v>
@@ -32124,7 +32124,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1095" t="n">
         <v>2072</v>
@@ -32211,7 +32211,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1098" t="n">
         <v>2977</v>
@@ -32240,7 +32240,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.76405847072601</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1099" t="n">
         <v>3686</v>
@@ -32269,7 +32269,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.73154127597809</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1100" t="n">
         <v>668</v>
@@ -32327,7 +32327,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1102" t="n">
         <v>1150</v>
@@ -32501,7 +32501,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1108" t="n">
         <v>2147</v>
@@ -32530,7 +32530,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1109" t="n">
         <v>0</v>
@@ -32617,7 +32617,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1112" t="n">
         <v>194</v>
@@ -32704,7 +32704,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1115" t="n">
         <v>2809</v>
@@ -32762,7 +32762,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1117" t="n">
         <v>705</v>
@@ -32820,7 +32820,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1119" t="n">
         <v>653</v>
@@ -32849,7 +32849,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1120" t="n">
         <v>2501</v>
@@ -32878,7 +32878,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1121" t="n">
         <v>1115</v>
@@ -32907,7 +32907,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1122" t="n">
         <v>3180</v>
@@ -32936,7 +32936,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1123" t="n">
         <v>1674</v>
@@ -32965,7 +32965,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1124" t="n">
         <v>4336</v>
@@ -33023,7 +33023,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1126" t="n">
         <v>735</v>
@@ -33081,7 +33081,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1128" t="n">
         <v>2449</v>
@@ -33110,7 +33110,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1129" t="n">
         <v>1066</v>
@@ -33139,7 +33139,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1130" t="n">
         <v>474</v>
@@ -33168,7 +33168,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1131" t="n">
         <v>1560</v>
@@ -33197,7 +33197,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.82909286022186</v>
+        <v>1.82909274101257</v>
       </c>
       <c r="H1132" t="n">
         <v>3184</v>
@@ -33226,7 +33226,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.8047046661377</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1133" t="n">
         <v>100</v>
@@ -33284,7 +33284,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1135" t="n">
         <v>289</v>
@@ -33313,7 +33313,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.81283402442932</v>
+        <v>1.81283390522003</v>
       </c>
       <c r="H1136" t="n">
         <v>1910</v>
@@ -33371,7 +33371,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1138" t="n">
         <v>536</v>
@@ -33400,7 +33400,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1139" t="n">
         <v>2191</v>
@@ -33429,7 +33429,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.78031706809998</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1140" t="n">
         <v>87</v>
@@ -33458,7 +33458,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.8047046661377</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1141" t="n">
         <v>161</v>
@@ -33487,7 +33487,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.8047046661377</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1142" t="n">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1143" t="n">
         <v>1762</v>
@@ -33545,7 +33545,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.78844618797302</v>
+        <v>1.78844630718231</v>
       </c>
       <c r="H1144" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.81283402442932</v>
+        <v>1.81283390522003</v>
       </c>
       <c r="H1145" t="n">
         <v>480</v>
@@ -33603,7 +33603,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.8047046661377</v>
+        <v>1.80470502376556</v>
       </c>
       <c r="H1146" t="n">
         <v>30</v>
@@ -33661,7 +33661,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1148" t="n">
         <v>1910</v>
@@ -33690,7 +33690,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.76405847072601</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1149" t="n">
         <v>143</v>
@@ -33719,7 +33719,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1150" t="n">
         <v>1580</v>
@@ -33777,7 +33777,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.78031706809998</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1152" t="n">
         <v>7260</v>
@@ -33806,7 +33806,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.78031706809998</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1153" t="n">
         <v>4915</v>
@@ -33835,7 +33835,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.76405847072601</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1154" t="n">
         <v>50</v>
@@ -33864,7 +33864,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1155" t="n">
         <v>151</v>
@@ -33893,7 +33893,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.73154127597809</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1156" t="n">
         <v>1638</v>
@@ -33922,7 +33922,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.73154127597809</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1157" t="n">
         <v>452</v>
@@ -34096,7 +34096,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1163" t="n">
         <v>392</v>
@@ -34125,7 +34125,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.66650664806366</v>
+        <v>1.66650676727295</v>
       </c>
       <c r="H1164" t="n">
         <v>12</v>
@@ -34154,7 +34154,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1165" t="n">
         <v>675</v>
@@ -34328,7 +34328,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1171" t="n">
         <v>330</v>
@@ -34357,7 +34357,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.77218759059906</v>
+        <v>1.77218747138977</v>
       </c>
       <c r="H1172" t="n">
         <v>950</v>
@@ -34386,7 +34386,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1173" t="n">
         <v>886</v>
@@ -34415,7 +34415,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.73154127597809</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1174" t="n">
         <v>16</v>
@@ -34473,7 +34473,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.76405847072601</v>
+        <v>1.76405835151672</v>
       </c>
       <c r="H1176" t="n">
         <v>992</v>
@@ -34502,7 +34502,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1177" t="n">
         <v>402</v>
@@ -34531,7 +34531,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1178" t="n">
         <v>250</v>
@@ -34560,7 +34560,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.78031706809998</v>
+        <v>1.7803168296814</v>
       </c>
       <c r="H1179" t="n">
         <v>520</v>
@@ -34589,7 +34589,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1180" t="n">
         <v>289</v>
@@ -34618,7 +34618,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779975414276</v>
+        <v>1.74779963493347</v>
       </c>
       <c r="H1181" t="n">
         <v>15</v>
@@ -34647,7 +34647,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1182" t="n">
         <v>61</v>
@@ -34676,7 +34676,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.73154127597809</v>
+        <v>1.73154103755951</v>
       </c>
       <c r="H1183" t="n">
         <v>139</v>
@@ -34705,7 +34705,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.75592887401581</v>
+        <v>1.75592911243439</v>
       </c>
       <c r="H1184" t="n">
         <v>110</v>
@@ -34734,7 +34734,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1185" t="n">
         <v>3347</v>
@@ -34763,7 +34763,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.7071533203125</v>
+        <v>1.70715320110321</v>
       </c>
       <c r="H1186" t="n">
         <v>5</v>
@@ -34792,7 +34792,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.72341179847717</v>
+        <v>1.72341191768646</v>
       </c>
       <c r="H1187" t="n">
         <v>3434</v>
@@ -34850,7 +34850,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.68276536464691</v>
+        <v>1.6827654838562</v>
       </c>
       <c r="H1189" t="n">
         <v>2798</v>
@@ -34879,7 +34879,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.68276536464691</v>
+        <v>1.6827654838562</v>
       </c>
       <c r="H1190" t="n">
         <v>545</v>
@@ -34908,7 +34908,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.6258602142334</v>
+        <v>1.62586009502411</v>
       </c>
       <c r="H1191" t="n">
         <v>1130</v>
@@ -34937,7 +34937,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.6258602142334</v>
+        <v>1.62586009502411</v>
       </c>
       <c r="H1192" t="n">
         <v>3300</v>
@@ -35024,7 +35024,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.6014723777771</v>
+        <v>1.60147249698639</v>
       </c>
       <c r="H1195" t="n">
         <v>486</v>
@@ -35082,7 +35082,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1197" t="n">
         <v>6595</v>
@@ -35111,7 +35111,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.60960149765015</v>
+        <v>1.60960137844086</v>
       </c>
       <c r="H1198" t="n">
         <v>201</v>
@@ -35169,7 +35169,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.61366617679596</v>
+        <v>1.61366641521454</v>
       </c>
       <c r="H1200" t="n">
         <v>1704</v>
@@ -35256,7 +35256,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1203" t="n">
         <v>1145</v>
@@ -35314,7 +35314,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1205" t="n">
         <v>2215</v>
@@ -35372,7 +35372,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1207" t="n">
         <v>299</v>
@@ -35430,7 +35430,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.4957914352417</v>
+        <v>1.49579131603241</v>
       </c>
       <c r="H1209" t="n">
         <v>1093</v>
@@ -35459,7 +35459,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1210" t="n">
         <v>1502</v>
@@ -35488,7 +35488,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708442211151</v>
+        <v>1.57708418369293</v>
       </c>
       <c r="H1211" t="n">
         <v>302</v>
@@ -35575,7 +35575,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.48766195774078</v>
+        <v>1.48766207695007</v>
       </c>
       <c r="H1214" t="n">
         <v>540</v>
@@ -35604,7 +35604,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1215" t="n">
         <v>1216</v>
@@ -35691,7 +35691,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.41043365001678</v>
+        <v>1.41043376922607</v>
       </c>
       <c r="H1218" t="n">
         <v>1274</v>
@@ -35720,7 +35720,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.40636897087097</v>
+        <v>1.40636909008026</v>
       </c>
       <c r="H1219" t="n">
         <v>2254</v>
@@ -35749,7 +35749,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482160568237</v>
+        <v>1.43482148647308</v>
       </c>
       <c r="H1220" t="n">
         <v>925</v>
@@ -35807,7 +35807,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.4144983291626</v>
+        <v>1.41449844837189</v>
       </c>
       <c r="H1222" t="n">
         <v>2154</v>
@@ -35836,7 +35836,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.36572253704071</v>
+        <v>1.36572241783142</v>
       </c>
       <c r="H1223" t="n">
         <v>2886</v>
@@ -36010,7 +36010,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255890846252</v>
+        <v>1.29255878925323</v>
       </c>
       <c r="H1229" t="n">
         <v>989</v>
@@ -36039,7 +36039,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.3088173866272</v>
+        <v>1.30881750583649</v>
       </c>
       <c r="H1230" t="n">
         <v>1391</v>
@@ -36068,7 +36068,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.33727025985718</v>
+        <v>1.33727014064789</v>
       </c>
       <c r="H1231" t="n">
         <v>1538</v>
@@ -36126,7 +36126,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946393966675</v>
+        <v>1.34946405887604</v>
       </c>
       <c r="H1233" t="n">
         <v>466</v>
@@ -36184,7 +36184,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.35352849960327</v>
+        <v>1.35352861881256</v>
       </c>
       <c r="H1235" t="n">
         <v>9650</v>
@@ -36271,7 +36271,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.4144983291626</v>
+        <v>1.41449844837189</v>
       </c>
       <c r="H1238" t="n">
         <v>1249</v>
@@ -36300,7 +36300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.3860456943512</v>
+        <v>1.38604581356049</v>
       </c>
       <c r="H1239" t="n">
         <v>2206</v>
@@ -36358,7 +36358,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39011061191559</v>
+        <v>1.3901104927063</v>
       </c>
       <c r="H1241" t="n">
         <v>2655</v>
@@ -36561,7 +36561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.48766195774078</v>
+        <v>1.48766207695007</v>
       </c>
       <c r="H1248" t="n">
         <v>2886</v>
@@ -36619,7 +36619,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1250" t="n">
         <v>4696</v>
@@ -36648,7 +36648,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.56082582473755</v>
+        <v>1.56082606315613</v>
       </c>
       <c r="H1251" t="n">
         <v>2264</v>
@@ -36677,7 +36677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.55269646644592</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1252" t="n">
         <v>3478</v>
@@ -36764,7 +36764,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.49172687530518</v>
+        <v>1.49172675609589</v>
       </c>
       <c r="H1255" t="n">
         <v>3603</v>
@@ -36851,7 +36851,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1258" t="n">
         <v>2500</v>
@@ -36938,7 +36938,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237330913544</v>
+        <v>1.53237318992615</v>
       </c>
       <c r="H1261" t="n">
         <v>4222</v>
@@ -36967,7 +36967,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51204991340637</v>
+        <v>1.51205015182495</v>
       </c>
       <c r="H1262" t="n">
         <v>2986</v>
@@ -36996,7 +36996,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1263" t="n">
         <v>3075</v>
@@ -37054,7 +37054,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.52424395084381</v>
+        <v>1.5242440700531</v>
       </c>
       <c r="H1265" t="n">
         <v>1723</v>
@@ -37199,7 +37199,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.55269646644592</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1270" t="n">
         <v>19327</v>
@@ -37228,7 +37228,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.54050278663635</v>
+        <v>1.54050266742706</v>
       </c>
       <c r="H1271" t="n">
         <v>7329</v>
@@ -37257,7 +37257,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1272" t="n">
         <v>822</v>
@@ -37286,7 +37286,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.56895506381989</v>
+        <v>1.5689549446106</v>
       </c>
       <c r="H1273" t="n">
         <v>2790</v>
@@ -37315,7 +37315,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.55269646644592</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1274" t="n">
         <v>23428</v>
@@ -37344,7 +37344,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.56895506381989</v>
+        <v>1.5689549446106</v>
       </c>
       <c r="H1275" t="n">
         <v>5078</v>
@@ -37373,7 +37373,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1276" t="n">
         <v>3233</v>
@@ -37402,7 +37402,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.55269646644592</v>
+        <v>1.55269658565521</v>
       </c>
       <c r="H1277" t="n">
         <v>639</v>
@@ -37518,7 +37518,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643786907196</v>
+        <v>1.53643774986267</v>
       </c>
       <c r="H1281" t="n">
         <v>355</v>
@@ -37750,7 +37750,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.54050278663635</v>
+        <v>1.54050266742706</v>
       </c>
       <c r="H1289" t="n">
         <v>1527</v>
@@ -37779,7 +37779,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359739780426</v>
+        <v>1.48359751701355</v>
       </c>
       <c r="H1290" t="n">
         <v>593</v>
@@ -37866,7 +37866,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.86973941326141</v>
+        <v>1.86973929405212</v>
       </c>
       <c r="H1293" t="n">
         <v>71320</v>
@@ -37895,7 +37895,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.95103228092194</v>
+        <v>1.95103216171265</v>
       </c>
       <c r="H1294" t="n">
         <v>24305</v>
@@ -37924,7 +37924,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.0729718208313</v>
+        <v>2.07297158241272</v>
       </c>
       <c r="H1295" t="n">
         <v>21427</v>
@@ -37953,7 +37953,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1296" t="n">
         <v>31317</v>
@@ -38040,7 +38040,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1299" t="n">
         <v>11185</v>
@@ -38127,7 +38127,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1302" t="n">
         <v>4831</v>
@@ -38156,7 +38156,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H1303" t="n">
         <v>3636</v>
@@ -38185,7 +38185,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1304" t="n">
         <v>3101</v>
@@ -38214,7 +38214,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123873710632</v>
+        <v>2.34123849868774</v>
       </c>
       <c r="H1305" t="n">
         <v>1089</v>
@@ -38359,7 +38359,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807475090027</v>
       </c>
       <c r="H1310" t="n">
         <v>2703</v>
@@ -38388,7 +38388,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807522773743</v>
+        <v>2.26807475090027</v>
       </c>
       <c r="H1311" t="n">
         <v>801</v>
@@ -38562,7 +38562,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994563102722</v>
+        <v>2.25994539260864</v>
       </c>
       <c r="H1317" t="n">
         <v>1038</v>
@@ -38591,7 +38591,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994563102722</v>
+        <v>2.25994539260864</v>
       </c>
       <c r="H1318" t="n">
         <v>245</v>
@@ -38649,7 +38649,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.1786527633667</v>
+        <v>2.17865252494812</v>
       </c>
       <c r="H1320" t="n">
         <v>8330</v>
@@ -38794,7 +38794,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.0729718208313</v>
+        <v>2.07297158241272</v>
       </c>
       <c r="H1325" t="n">
         <v>1429</v>
@@ -38823,7 +38823,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671310424805</v>
+        <v>2.05671286582947</v>
       </c>
       <c r="H1326" t="n">
         <v>2194</v>
@@ -38939,7 +38939,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1330" t="n">
         <v>2995</v>
@@ -39084,7 +39084,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.21116971969604</v>
+        <v>2.21116995811462</v>
       </c>
       <c r="H1335" t="n">
         <v>2277</v>
@@ -39113,7 +39113,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.21116971969604</v>
+        <v>2.21116995811462</v>
       </c>
       <c r="H1336" t="n">
         <v>1420</v>
@@ -39142,7 +39142,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.23555779457092</v>
+        <v>2.23555755615234</v>
       </c>
       <c r="H1337" t="n">
         <v>4952</v>
@@ -39171,7 +39171,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.21116971969604</v>
+        <v>2.21116995811462</v>
       </c>
       <c r="H1338" t="n">
         <v>8557</v>
@@ -39316,7 +39316,7 @@
         <v>27</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1343" t="n">
         <v>1560</v>
@@ -39461,7 +39461,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1348" t="n">
         <v>260</v>
@@ -39490,7 +39490,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1349" t="n">
         <v>2010</v>
@@ -39577,7 +39577,7 @@
         <v>27</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1352" t="n">
         <v>626</v>
@@ -39664,7 +39664,7 @@
         <v>27</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1355" t="n">
         <v>15</v>
@@ -39809,7 +39809,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1360" t="n">
         <v>315</v>
@@ -39867,7 +39867,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1362" t="n">
         <v>1587</v>
@@ -40041,7 +40041,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1368" t="n">
         <v>2585</v>
@@ -40070,7 +40070,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1369" t="n">
         <v>3238</v>
@@ -40157,7 +40157,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1372" t="n">
         <v>4467</v>
@@ -40360,7 +40360,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1379" t="n">
         <v>4492</v>
@@ -40389,7 +40389,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1380" t="n">
         <v>3109</v>
@@ -40418,7 +40418,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1381" t="n">
         <v>14062</v>
@@ -40447,7 +40447,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1382" t="n">
         <v>4336</v>
@@ -40476,7 +40476,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1383" t="n">
         <v>30</v>
@@ -40592,7 +40592,7 @@
         <v>30</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1387" t="n">
         <v>3844</v>
@@ -40621,7 +40621,7 @@
         <v>30</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1388" t="n">
         <v>3485</v>
@@ -40650,7 +40650,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1389" t="n">
         <v>1513</v>
@@ -40679,7 +40679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274230003357</v>
+        <v>2.49274206161499</v>
       </c>
       <c r="H1390" t="n">
         <v>11</v>
@@ -40737,7 +40737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.39336347579956</v>
+        <v>2.39336371421814</v>
       </c>
       <c r="H1392" t="n">
         <v>2136</v>
@@ -40824,7 +40824,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1395" t="n">
         <v>3834</v>
@@ -40911,7 +40911,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.39336347579956</v>
+        <v>2.39336371421814</v>
       </c>
       <c r="H1398" t="n">
         <v>1418</v>
@@ -40969,7 +40969,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1400" t="n">
         <v>4528</v>
@@ -41027,7 +41027,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1402" t="n">
         <v>1523</v>
@@ -41056,7 +41056,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1403" t="n">
         <v>7033</v>
@@ -41085,7 +41085,7 @@
         <v>30</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1404" t="n">
         <v>1557</v>
@@ -41317,7 +41317,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1412" t="n">
         <v>1570</v>
@@ -41346,7 +41346,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1413" t="n">
         <v>722</v>
@@ -41404,7 +41404,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1415" t="n">
         <v>827</v>
@@ -41752,7 +41752,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1427" t="n">
         <v>706</v>
@@ -41781,7 +41781,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1428" t="n">
         <v>83</v>
@@ -41810,7 +41810,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1429" t="n">
         <v>110</v>
@@ -41839,7 +41839,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.38508224487305</v>
+        <v>2.38508200645447</v>
       </c>
       <c r="H1430" t="n">
         <v>52</v>
@@ -42071,7 +42071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1438" t="n">
         <v>325</v>
@@ -42129,7 +42129,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1440" t="n">
         <v>160</v>
@@ -42274,7 +42274,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1445" t="n">
         <v>1333</v>
@@ -42303,7 +42303,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1446" t="n">
         <v>2352</v>
@@ -43231,7 +43231,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.36851930618286</v>
+        <v>2.36851906776428</v>
       </c>
       <c r="H1478" t="n">
         <v>890</v>
@@ -43521,7 +43521,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1488" t="n">
         <v>110</v>
@@ -43637,7 +43637,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1492" t="n">
         <v>4229</v>
@@ -43695,7 +43695,7 @@
         <v>26</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1494" t="n">
         <v>4950</v>
@@ -43753,7 +43753,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1496" t="n">
         <v>5031</v>
@@ -43782,7 +43782,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1497" t="n">
         <v>556</v>
@@ -43811,7 +43811,7 @@
         <v>26</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1498" t="n">
         <v>4241</v>
@@ -43840,7 +43840,7 @@
         <v>26</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1499" t="n">
         <v>107</v>
@@ -43927,7 +43927,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835454940796</v>
+        <v>2.12835478782654</v>
       </c>
       <c r="H1502" t="n">
         <v>3129</v>
@@ -43956,7 +43956,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.08694672584534</v>
+        <v>2.08694696426392</v>
       </c>
       <c r="H1503" t="n">
         <v>684</v>
@@ -43985,7 +43985,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.10351014137268</v>
+        <v>2.1035099029541</v>
       </c>
       <c r="H1504" t="n">
         <v>610</v>
@@ -44043,7 +44043,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1506" t="n">
         <v>1917</v>
@@ -44072,7 +44072,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1507" t="n">
         <v>331</v>
@@ -44101,7 +44101,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.13663601875305</v>
+        <v>2.13663625717163</v>
       </c>
       <c r="H1508" t="n">
         <v>1055</v>
@@ -44130,7 +44130,7 @@
         <v>26</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1509" t="n">
         <v>617</v>
@@ -44217,7 +44217,7 @@
         <v>26</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1512" t="n">
         <v>1674</v>
@@ -44275,7 +44275,7 @@
         <v>26</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1514" t="n">
         <v>9003</v>
@@ -44304,7 +44304,7 @@
         <v>26</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1515" t="n">
         <v>561</v>
@@ -44333,7 +44333,7 @@
         <v>26</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.1531994342804</v>
+        <v>2.15319919586182</v>
       </c>
       <c r="H1516" t="n">
         <v>2644</v>
@@ -44565,7 +44565,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1524" t="n">
         <v>420</v>
@@ -44623,7 +44623,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1526" t="n">
         <v>311</v>
@@ -44652,7 +44652,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1527" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054830551147</v>
+        <v>2.31054854393005</v>
       </c>
       <c r="H1528" t="n">
         <v>137</v>
@@ -45000,7 +45000,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1539" t="n">
         <v>42</v>
@@ -45029,7 +45029,7 @@
         <v>27</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1540" t="n">
         <v>140</v>
@@ -45116,7 +45116,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.26085925102234</v>
+        <v>2.26085901260376</v>
       </c>
       <c r="H1543" t="n">
         <v>516</v>
@@ -45145,7 +45145,7 @@
         <v>27</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1544" t="n">
         <v>135</v>
@@ -45174,7 +45174,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.20288825035095</v>
+        <v>2.20288848876953</v>
       </c>
       <c r="H1545" t="n">
         <v>70</v>
@@ -45638,7 +45638,7 @@
         <v>27</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1561" t="n">
         <v>1549</v>
@@ -45667,7 +45667,7 @@
         <v>27</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.2360143661499</v>
+        <v>2.23601460456848</v>
       </c>
       <c r="H1562" t="n">
         <v>1015</v>
@@ -45870,7 +45870,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.40992665290833</v>
+        <v>2.4099268913269</v>
       </c>
       <c r="H1569" t="n">
         <v>420</v>
@@ -46044,7 +46044,7 @@
         <v>30</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.4844605922699</v>
+        <v>2.48446035385132</v>
       </c>
       <c r="H1575" t="n">
         <v>632</v>
@@ -46131,7 +46131,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930500030518</v>
+        <v>2.50930523872375</v>
       </c>
       <c r="H1578" t="n">
         <v>2055</v>
@@ -46189,7 +46189,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.71634340286255</v>
+        <v>2.71634364128113</v>
       </c>
       <c r="H1580" t="n">
         <v>8590</v>
@@ -46218,7 +46218,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978022575378</v>
+        <v>2.69978046417236</v>
       </c>
       <c r="H1581" t="n">
         <v>4224</v>
@@ -46247,7 +46247,7 @@
         <v>34</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.81572198867798</v>
+        <v>2.81572222709656</v>
       </c>
       <c r="H1582" t="n">
         <v>5135</v>
@@ -46363,7 +46363,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1586" t="n">
         <v>4777</v>
@@ -46392,7 +46392,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.24636197090149</v>
+        <v>3.24636220932007</v>
       </c>
       <c r="H1587" t="n">
         <v>14504</v>
@@ -46421,7 +46421,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.23808002471924</v>
+        <v>3.2380805015564</v>
       </c>
       <c r="H1588" t="n">
         <v>15352</v>
@@ -46479,7 +46479,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.23808002471924</v>
+        <v>3.2380805015564</v>
       </c>
       <c r="H1590" t="n">
         <v>7873</v>
@@ -46537,7 +46537,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1592" t="n">
         <v>19325</v>
@@ -46595,7 +46595,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.17182803153992</v>
+        <v>3.17182779312134</v>
       </c>
       <c r="H1594" t="n">
         <v>22091</v>
@@ -46624,7 +46624,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.17182803153992</v>
+        <v>3.17182779312134</v>
       </c>
       <c r="H1595" t="n">
         <v>58723</v>
@@ -46885,7 +46885,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1604" t="n">
         <v>3473</v>
@@ -46943,7 +46943,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1606" t="n">
         <v>701</v>
@@ -47001,7 +47001,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1608" t="n">
         <v>869</v>
@@ -47030,7 +47030,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1609" t="n">
         <v>201</v>
@@ -47088,7 +47088,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244944572449</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1611" t="n">
         <v>2250</v>
@@ -47233,7 +47233,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1616" t="n">
         <v>221</v>
@@ -47262,7 +47262,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464367866516</v>
       </c>
       <c r="H1617" t="n">
         <v>1595</v>
@@ -47291,7 +47291,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1618" t="n">
         <v>2357</v>
@@ -47407,7 +47407,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994522094727</v>
+        <v>2.93994498252869</v>
       </c>
       <c r="H1622" t="n">
         <v>2912</v>
@@ -47436,7 +47436,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1623" t="n">
         <v>4769</v>
@@ -47610,7 +47610,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1629" t="n">
         <v>1053</v>
@@ -47697,7 +47697,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1632" t="n">
         <v>112</v>
@@ -47784,7 +47784,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1635" t="n">
         <v>1882</v>
@@ -47842,7 +47842,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1637" t="n">
         <v>2785</v>
@@ -47871,7 +47871,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1638" t="n">
         <v>2270</v>
@@ -47900,7 +47900,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1639" t="n">
         <v>2725</v>
@@ -47958,7 +47958,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1641" t="n">
         <v>3746</v>
@@ -48016,7 +48016,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1643" t="n">
         <v>1105</v>
@@ -48045,7 +48045,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1644" t="n">
         <v>4061</v>
@@ -48074,7 +48074,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1645" t="n">
         <v>8289</v>
@@ -48103,7 +48103,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1646" t="n">
         <v>569</v>
@@ -48161,7 +48161,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1648" t="n">
         <v>13</v>
@@ -48190,7 +48190,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1649" t="n">
         <v>642</v>
@@ -48335,7 +48335,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526485443115</v>
+        <v>3.15526461601257</v>
       </c>
       <c r="H1654" t="n">
         <v>513</v>
@@ -48422,7 +48422,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1657" t="n">
         <v>692</v>
@@ -48451,7 +48451,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1658" t="n">
         <v>1340</v>
@@ -48538,7 +48538,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1661" t="n">
         <v>277</v>
@@ -48596,7 +48596,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1663" t="n">
         <v>3180</v>
@@ -48799,7 +48799,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1670" t="n">
         <v>184</v>
@@ -48944,7 +48944,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1675" t="n">
         <v>239</v>
@@ -48973,7 +48973,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1676" t="n">
         <v>460</v>
@@ -49031,7 +49031,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.03932356834412</v>
+        <v>3.03932332992554</v>
       </c>
       <c r="H1678" t="n">
         <v>1165</v>
@@ -49234,7 +49234,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.03932356834412</v>
+        <v>3.03932332992554</v>
       </c>
       <c r="H1685" t="n">
         <v>200</v>
@@ -49408,7 +49408,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1691" t="n">
         <v>198</v>
@@ -49814,7 +49814,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1705" t="n">
-        <v>3.03932356834412</v>
+        <v>3.03932332992554</v>
       </c>
       <c r="H1705" t="n">
         <v>170</v>
@@ -49872,7 +49872,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.03104162216187</v>
+        <v>3.03104186058044</v>
       </c>
       <c r="H1707" t="n">
         <v>30</v>
@@ -49901,7 +49901,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244944572449</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1708" t="n">
         <v>796</v>
@@ -49930,7 +49930,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1709" t="n">
         <v>546</v>
@@ -50365,7 +50365,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1724" t="n">
         <v>1000</v>
@@ -50394,7 +50394,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1725" t="n">
         <v>0</v>
@@ -50452,7 +50452,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1727" t="n">
         <v>91</v>
@@ -50481,7 +50481,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.04760503768921</v>
+        <v>3.04760479927063</v>
       </c>
       <c r="H1728" t="n">
         <v>3500</v>
@@ -50539,7 +50539,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.05588674545288</v>
+        <v>3.0558865070343</v>
       </c>
       <c r="H1730" t="n">
         <v>4694</v>
@@ -50568,7 +50568,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1731" t="n">
         <v>10</v>
@@ -50597,7 +50597,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1732" t="n">
         <v>150</v>
@@ -50713,7 +50713,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1736" t="n">
         <v>6368</v>
@@ -50771,7 +50771,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1738" t="n">
         <v>492</v>
@@ -50829,7 +50829,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1740" t="n">
         <v>4</v>
@@ -50945,7 +50945,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244944572449</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1744" t="n">
         <v>53786</v>
@@ -51003,7 +51003,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1746" t="n">
         <v>21294</v>
@@ -51032,7 +51032,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1747" t="n">
         <v>14353</v>
@@ -51061,7 +51061,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244944572449</v>
+        <v>3.07244920730591</v>
       </c>
       <c r="H1748" t="n">
         <v>4653</v>
@@ -51090,7 +51090,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1749" t="n">
         <v>20045</v>
@@ -51119,7 +51119,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1750" t="n">
         <v>29641</v>
@@ -51148,7 +51148,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1751" t="n">
         <v>15953</v>
@@ -51264,7 +51264,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.10557579994202</v>
+        <v>3.1055760383606</v>
       </c>
       <c r="H1755" t="n">
         <v>2128</v>
@@ -51409,7 +51409,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1760" t="n">
         <v>8943</v>
@@ -51467,7 +51467,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1762" t="n">
         <v>17040</v>
@@ -51525,7 +51525,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526485443115</v>
+        <v>3.15526461601257</v>
       </c>
       <c r="H1764" t="n">
         <v>6338</v>
@@ -51554,7 +51554,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.12213897705078</v>
+        <v>3.1221387386322</v>
       </c>
       <c r="H1765" t="n">
         <v>11888</v>
@@ -51583,7 +51583,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.13870215415955</v>
+        <v>3.13870191574097</v>
       </c>
       <c r="H1766" t="n">
         <v>9167</v>
@@ -51612,7 +51612,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.20495438575745</v>
+        <v>3.20495414733887</v>
       </c>
       <c r="H1767" t="n">
         <v>15127</v>
@@ -51670,7 +51670,7 @@
         <v>39.5</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.27120637893677</v>
+        <v>3.27120661735535</v>
       </c>
       <c r="H1769" t="n">
         <v>2890</v>
@@ -51699,7 +51699,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.254643201828</v>
+        <v>3.25464367866516</v>
       </c>
       <c r="H1770" t="n">
         <v>4370</v>
@@ -51786,7 +51786,7 @@
         <v>39.5</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.27120637893677</v>
+        <v>3.27120661735535</v>
       </c>
       <c r="H1773" t="n">
         <v>44802</v>
@@ -52047,7 +52047,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585054397583</v>
+        <v>5.01585006713867</v>
       </c>
       <c r="H1782" t="n">
         <v>29263</v>
@@ -52076,7 +52076,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.5828595161438</v>
+        <v>5.58285999298096</v>
       </c>
       <c r="H1783" t="n">
         <v>88580</v>
@@ -52105,7 +52105,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1784" t="n">
         <v>63372</v>
@@ -52250,7 +52250,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1789" t="n">
         <v>19527</v>
@@ -52366,7 +52366,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212291717529</v>
+        <v>5.21212244033813</v>
       </c>
       <c r="H1793" t="n">
         <v>17331</v>
@@ -52395,7 +52395,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669847488403</v>
+        <v>5.14669895172119</v>
       </c>
       <c r="H1794" t="n">
         <v>14779</v>
@@ -52540,7 +52540,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924369812012</v>
+        <v>5.53924322128296</v>
       </c>
       <c r="H1799" t="n">
         <v>13906</v>
@@ -52598,7 +52598,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1801" t="n">
         <v>9611</v>
@@ -52656,7 +52656,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1803" t="n">
         <v>17158</v>
@@ -52685,7 +52685,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020343780518</v>
+        <v>5.43020296096802</v>
       </c>
       <c r="H1804" t="n">
         <v>13501</v>
@@ -52714,7 +52714,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1805" t="n">
         <v>6792</v>
@@ -52743,7 +52743,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1806" t="n">
         <v>7235</v>
@@ -52830,7 +52830,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1809" t="n">
         <v>6507</v>
@@ -52859,7 +52859,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1810" t="n">
         <v>8854</v>
@@ -52917,7 +52917,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1812" t="n">
         <v>9617</v>
@@ -52975,7 +52975,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477899551392</v>
+        <v>5.36477947235107</v>
       </c>
       <c r="H1814" t="n">
         <v>872</v>
@@ -53004,7 +53004,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1815" t="n">
         <v>5517</v>
@@ -53033,7 +53033,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1816" t="n">
         <v>8058</v>
@@ -53062,7 +53062,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.3429708480835</v>
+        <v>5.34297132492065</v>
       </c>
       <c r="H1817" t="n">
         <v>10014</v>
@@ -53091,7 +53091,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658714294434</v>
+        <v>5.38658761978149</v>
       </c>
       <c r="H1818" t="n">
         <v>6825</v>
@@ -53236,7 +53236,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1823" t="n">
         <v>239358</v>
@@ -53294,7 +53294,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495798110962</v>
+        <v>6.93495845794678</v>
       </c>
       <c r="H1825" t="n">
         <v>187542</v>
@@ -53323,7 +53323,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1826" t="n">
         <v>81830</v>
@@ -53352,7 +53352,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868560791016</v>
+        <v>6.73868608474731</v>
       </c>
       <c r="H1827" t="n">
         <v>53720</v>
@@ -53497,7 +53497,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433319091797</v>
+        <v>6.32433271408081</v>
       </c>
       <c r="H1832" t="n">
         <v>51065</v>
@@ -53671,7 +53671,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964534759521</v>
+        <v>6.62964582443237</v>
       </c>
       <c r="H1838" t="n">
         <v>62153</v>
@@ -53700,7 +53700,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049423217773</v>
+        <v>6.76049375534058</v>
       </c>
       <c r="H1839" t="n">
         <v>45114</v>
@@ -53729,7 +53729,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.78230237960815</v>
+        <v>6.782301902771</v>
       </c>
       <c r="H1840" t="n">
         <v>29296</v>
@@ -53758,7 +53758,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1841" t="n">
         <v>16687</v>
@@ -53787,7 +53787,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591819763184</v>
+        <v>6.82591772079468</v>
       </c>
       <c r="H1842" t="n">
         <v>31740</v>
@@ -53816,7 +53816,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.02219104766846</v>
+        <v>7.0221905708313</v>
       </c>
       <c r="H1843" t="n">
         <v>31076</v>
@@ -53845,7 +53845,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1844" t="n">
         <v>50948</v>
@@ -53874,7 +53874,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399871826172</v>
+        <v>7.04399824142456</v>
       </c>
       <c r="H1845" t="n">
         <v>21268</v>
@@ -53932,7 +53932,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.0658073425293</v>
+        <v>7.06580686569214</v>
       </c>
       <c r="H1847" t="n">
         <v>32316</v>
@@ -53961,7 +53961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835208892822</v>
+        <v>7.45835161209106</v>
       </c>
       <c r="H1848" t="n">
         <v>130442</v>
@@ -53990,7 +53990,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1849" t="n">
         <v>125182</v>
@@ -54019,7 +54019,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377510070801</v>
+        <v>7.52377557754517</v>
       </c>
       <c r="H1850" t="n">
         <v>51748</v>
@@ -54135,7 +54135,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259365081787</v>
+        <v>8.11259269714355</v>
       </c>
       <c r="H1854" t="n">
         <v>76643</v>
@@ -80096,6 +80096,64 @@
         <v>100</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>45</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544644355774</v>
+        <v>1.24544656276703</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -485,7 +485,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H4" t="n">
         <v>158</v>
@@ -514,7 +514,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H5" t="n">
         <v>1168</v>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541845798492</v>
       </c>
       <c r="H6" t="n">
         <v>466</v>
@@ -572,7 +572,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22185325622559</v>
+        <v>1.22185301780701</v>
       </c>
       <c r="H7" t="n">
         <v>1052</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -630,7 +630,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H9" t="n">
         <v>8746</v>
@@ -659,7 +659,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327364444733</v>
+        <v>1.21327352523804</v>
       </c>
       <c r="H10" t="n">
         <v>4107</v>
@@ -688,7 +688,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683896541595</v>
+        <v>1.20683920383453</v>
       </c>
       <c r="H11" t="n">
         <v>9368</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.20111930370331</v>
+        <v>1.2011194229126</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -775,7 +775,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1668016910553</v>
+        <v>1.16680181026459</v>
       </c>
       <c r="H14" t="n">
         <v>2159</v>
@@ -804,7 +804,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.19468486309052</v>
+        <v>1.1946849822998</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688576698303</v>
+        <v>1.25688564777374</v>
       </c>
       <c r="H16" t="n">
         <v>6127</v>
@@ -891,7 +891,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H18" t="n">
         <v>605</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687659740448</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2147034406662</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1065,7 +1065,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541857719421</v>
+        <v>1.21541845798492</v>
       </c>
       <c r="H24" t="n">
         <v>132</v>
@@ -1123,7 +1123,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H26" t="n">
         <v>2636</v>
@@ -1181,7 +1181,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G28" t="n">
-        <v>1.210413813591</v>
+        <v>1.21041393280029</v>
       </c>
       <c r="H28" t="n">
         <v>118</v>
@@ -1210,7 +1210,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113823890686</v>
+        <v>1.22113811969757</v>
       </c>
       <c r="H29" t="n">
         <v>111</v>
@@ -1268,7 +1268,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H31" t="n">
         <v>39</v>
@@ -1355,7 +1355,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256815433502</v>
+        <v>1.22256803512573</v>
       </c>
       <c r="H34" t="n">
         <v>772</v>
@@ -1442,7 +1442,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546514034271</v>
       </c>
       <c r="H37" t="n">
         <v>11933</v>
@@ -1471,7 +1471,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903069972992</v>
+        <v>1.25903058052063</v>
       </c>
       <c r="H38" t="n">
         <v>6392</v>
@@ -1500,7 +1500,7 @@
         <v>17.75</v>
       </c>
       <c r="G39" t="n">
-        <v>1.26903986930847</v>
+        <v>1.26903998851776</v>
       </c>
       <c r="H39" t="n">
         <v>3180</v>
@@ -1529,7 +1529,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21684837341309</v>
+        <v>1.21684849262238</v>
       </c>
       <c r="H40" t="n">
         <v>6016</v>
@@ -1558,7 +1558,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828781604767</v>
+        <v>1.22828769683838</v>
       </c>
       <c r="H41" t="n">
         <v>573</v>
@@ -1587,7 +1587,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G42" t="n">
-        <v>1.22542786598206</v>
+        <v>1.22542774677277</v>
       </c>
       <c r="H42" t="n">
         <v>340</v>
@@ -1645,7 +1645,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H44" t="n">
         <v>139</v>
@@ -1703,7 +1703,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404451370239</v>
+        <v>1.27404463291168</v>
       </c>
       <c r="H46" t="n">
         <v>3010</v>
@@ -1732,7 +1732,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G47" t="n">
-        <v>1.26689517498016</v>
+        <v>1.26689505577087</v>
       </c>
       <c r="H47" t="n">
         <v>7764</v>
@@ -1761,7 +1761,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G48" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H48" t="n">
         <v>1421</v>
@@ -1819,7 +1819,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546514034271</v>
       </c>
       <c r="H50" t="n">
         <v>3624</v>
@@ -1964,7 +1964,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>1.265465259552</v>
+        <v>1.26546514034271</v>
       </c>
       <c r="H55" t="n">
         <v>584</v>
@@ -2022,7 +2022,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27261471748352</v>
+        <v>1.27261459827423</v>
       </c>
       <c r="H57" t="n">
         <v>62</v>
@@ -2080,7 +2080,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545585155487</v>
+        <v>1.25545597076416</v>
       </c>
       <c r="H59" t="n">
         <v>2269</v>
@@ -2167,7 +2167,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830627441406</v>
+        <v>1.24830603599548</v>
       </c>
       <c r="H62" t="n">
         <v>745</v>
@@ -2225,7 +2225,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>1.2490211725235</v>
+        <v>1.24902129173279</v>
       </c>
       <c r="H64" t="n">
         <v>523</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258673191071</v>
+        <v>1.24258649349213</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2312,7 +2312,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23686707019806</v>
+        <v>1.23686695098877</v>
       </c>
       <c r="H67" t="n">
         <v>70</v>
@@ -2370,7 +2370,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472237586975</v>
       </c>
       <c r="H69" t="n">
         <v>538</v>
@@ -2399,7 +2399,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472225666046</v>
+        <v>1.23472237586975</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400735855103</v>
+        <v>1.23400723934174</v>
       </c>
       <c r="H71" t="n">
         <v>6242</v>
@@ -2486,7 +2486,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H73" t="n">
         <v>1010</v>
@@ -2515,7 +2515,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H74" t="n">
         <v>1039</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225365161896</v>
+        <v>1.25225377082825</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2573,7 +2573,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H76" t="n">
         <v>2231</v>
@@ -2602,7 +2602,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H77" t="n">
         <v>1512</v>
@@ -2631,7 +2631,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835501194</v>
+        <v>1.26835513114929</v>
       </c>
       <c r="H78" t="n">
         <v>2507</v>
@@ -2660,7 +2660,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H79" t="n">
         <v>1551</v>
@@ -2689,7 +2689,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27860128879547</v>
+        <v>1.27860140800476</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27640581130981</v>
+        <v>1.27640569210052</v>
       </c>
       <c r="H81" t="n">
         <v>410</v>
@@ -2747,7 +2747,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27420997619629</v>
+        <v>1.27421009540558</v>
       </c>
       <c r="H82" t="n">
         <v>323</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -2950,7 +2950,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445625305176</v>
+        <v>1.28445649147034</v>
       </c>
       <c r="H89" t="n">
         <v>1506</v>
@@ -2979,7 +2979,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.280797123909</v>
+        <v>1.28079688549042</v>
       </c>
       <c r="H90" t="n">
         <v>217</v>
@@ -3095,7 +3095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347826957703</v>
+        <v>1.27347815036774</v>
       </c>
       <c r="H94" t="n">
         <v>370</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494215965271</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3182,7 +3182,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H97" t="n">
         <v>1320</v>
@@ -3211,7 +3211,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>1.28226089477539</v>
+        <v>1.2822607755661</v>
       </c>
       <c r="H98" t="n">
         <v>573</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811597824097</v>
+        <v>1.28811585903168</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299272060394</v>
+        <v>1.28299283981323</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G111" t="n">
-        <v>1.26176798343658</v>
+        <v>1.26176810264587</v>
       </c>
       <c r="H111" t="n">
         <v>594</v>
@@ -3646,7 +3646,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H113" t="n">
         <v>1458</v>
@@ -3704,7 +3704,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H115" t="n">
         <v>1050</v>
@@ -3733,7 +3733,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H116" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663772106171</v>
+        <v>1.22663760185242</v>
       </c>
       <c r="H117" t="n">
         <v>120</v>
@@ -3791,7 +3791,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687687397003</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687687397003</v>
+        <v>1.20687675476074</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760881900787</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -3936,7 +3936,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784785270691</v>
+        <v>1.18784773349762</v>
       </c>
       <c r="H123" t="n">
         <v>1361</v>
@@ -3994,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H125" t="n">
         <v>673</v>
@@ -4110,7 +4110,7 @@
         <v>16</v>
       </c>
       <c r="G129" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H129" t="n">
         <v>1649</v>
@@ -4168,7 +4168,7 @@
         <v>16.25</v>
       </c>
       <c r="G131" t="n">
-        <v>1.1893116235733</v>
+        <v>1.18931150436401</v>
       </c>
       <c r="H131" t="n">
         <v>1295</v>
@@ -4197,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="G132" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H132" t="n">
         <v>171</v>
@@ -4226,7 +4226,7 @@
         <v>16</v>
       </c>
       <c r="G133" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H133" t="n">
         <v>101</v>
@@ -4255,7 +4255,7 @@
         <v>16</v>
       </c>
       <c r="G134" t="n">
-        <v>1.17101442813873</v>
+        <v>1.17101454734802</v>
       </c>
       <c r="H134" t="n">
         <v>245</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760881900787</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4313,7 +4313,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H136" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224628925323</v>
+        <v>1.22224640846252</v>
       </c>
       <c r="H139" t="n">
         <v>451</v>
@@ -4487,7 +4487,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G142" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H142" t="n">
         <v>152</v>
@@ -4516,7 +4516,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G143" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H143" t="n">
         <v>116</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760881900787</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4690,7 +4690,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H149" t="n">
         <v>1154</v>
@@ -4719,7 +4719,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>1.2061448097229</v>
+        <v>1.20614469051361</v>
       </c>
       <c r="H150" t="n">
         <v>2847</v>
@@ -4893,7 +4893,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297835350037</v>
       </c>
       <c r="H156" t="n">
         <v>410</v>
@@ -4922,7 +4922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H157" t="n">
         <v>390</v>
@@ -4951,7 +4951,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>1.23249280452728</v>
+        <v>1.23249268531799</v>
       </c>
       <c r="H158" t="n">
         <v>2050</v>
@@ -4980,7 +4980,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883343696594</v>
+        <v>1.22883331775665</v>
       </c>
       <c r="H159" t="n">
         <v>486</v>
@@ -5009,7 +5009,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468840122223</v>
       </c>
       <c r="H160" t="n">
         <v>366</v>
@@ -5067,7 +5067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G162" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H162" t="n">
         <v>4104</v>
@@ -5096,7 +5096,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H163" t="n">
         <v>2568</v>
@@ -5125,7 +5125,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G164" t="n">
-        <v>1.28226089477539</v>
+        <v>1.2822607755661</v>
       </c>
       <c r="H164" t="n">
         <v>5537</v>
@@ -5183,7 +5183,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.3071448802948</v>
+        <v>1.30714499950409</v>
       </c>
       <c r="H166" t="n">
         <v>3048</v>
@@ -5241,7 +5241,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324624061584</v>
+        <v>1.32324647903442</v>
       </c>
       <c r="H168" t="n">
         <v>18315</v>
@@ -5270,7 +5270,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G169" t="n">
-        <v>1.31665945053101</v>
+        <v>1.31665933132172</v>
       </c>
       <c r="H169" t="n">
         <v>3060</v>
@@ -5299,7 +5299,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763767242432</v>
+        <v>1.32763755321503</v>
       </c>
       <c r="H170" t="n">
         <v>14161</v>
@@ -5328,7 +5328,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G171" t="n">
-        <v>1.30348539352417</v>
+        <v>1.30348551273346</v>
       </c>
       <c r="H171" t="n">
         <v>10698</v>
@@ -5386,7 +5386,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>1.3181232213974</v>
+        <v>1.31812334060669</v>
       </c>
       <c r="H173" t="n">
         <v>2430</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5473,7 +5473,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982602596283</v>
+        <v>1.29982614517212</v>
       </c>
       <c r="H176" t="n">
         <v>1808</v>
@@ -5502,7 +5502,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884792327881</v>
+        <v>1.28884780406952</v>
       </c>
       <c r="H177" t="n">
         <v>3982</v>
@@ -5531,7 +5531,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>1.29543483257294</v>
+        <v>1.29543471336365</v>
       </c>
       <c r="H178" t="n">
         <v>703</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5705,7 +5705,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055809020996</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055809020996</v>
+        <v>1.30055797100067</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763042926788</v>
+        <v>1.29763031005859</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250717163086</v>
+        <v>1.29250729084015</v>
       </c>
       <c r="H189" t="n">
         <v>625</v>
@@ -5966,7 +5966,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H193" t="n">
         <v>4252</v>
@@ -5995,7 +5995,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G194" t="n">
-        <v>1.26908695697784</v>
+        <v>1.26908683776855</v>
       </c>
       <c r="H194" t="n">
         <v>6154</v>
@@ -6053,7 +6053,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762306690216</v>
+        <v>1.26762318611145</v>
       </c>
       <c r="H196" t="n">
         <v>4114</v>
@@ -6082,7 +6082,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G197" t="n">
-        <v>1.25884068012238</v>
+        <v>1.25884056091309</v>
       </c>
       <c r="H197" t="n">
         <v>5843</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786221981049</v>
+        <v>1.2478621006012</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6169,7 +6169,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G200" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542770862579</v>
       </c>
       <c r="H200" t="n">
         <v>14244</v>
@@ -6227,7 +6227,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H202" t="n">
         <v>22671</v>
@@ -6256,7 +6256,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G203" t="n">
-        <v>1.25810885429382</v>
+        <v>1.25810873508453</v>
       </c>
       <c r="H203" t="n">
         <v>11122</v>
@@ -6343,7 +6343,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G206" t="n">
-        <v>1.24639868736267</v>
+        <v>1.24639856815338</v>
       </c>
       <c r="H206" t="n">
         <v>7757</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420273303986</v>
       </c>
       <c r="H208" t="n">
         <v>6264</v>
@@ -6430,7 +6430,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615217208862</v>
+        <v>1.23615193367004</v>
       </c>
       <c r="H209" t="n">
         <v>5810</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688399791718</v>
+        <v>1.23688387870789</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6488,7 +6488,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420285224915</v>
+        <v>1.24420273303986</v>
       </c>
       <c r="H211" t="n">
         <v>1424</v>
@@ -6546,7 +6546,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>1.23981153964996</v>
+        <v>1.23981165885925</v>
       </c>
       <c r="H213" t="n">
         <v>5199</v>
@@ -6604,7 +6604,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>1.2654275894165</v>
+        <v>1.26542770862579</v>
       </c>
       <c r="H215" t="n">
         <v>1220</v>
@@ -6633,7 +6633,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H216" t="n">
         <v>6370</v>
@@ -6662,7 +6662,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H217" t="n">
         <v>3330</v>
@@ -6691,7 +6691,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297811508179</v>
+        <v>1.22297835350037</v>
       </c>
       <c r="H218" t="n">
         <v>9836</v>
@@ -6749,7 +6749,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>1.23176085948944</v>
+        <v>1.23176074028015</v>
       </c>
       <c r="H220" t="n">
         <v>8086</v>
@@ -6778,7 +6778,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H221" t="n">
         <v>2500</v>
@@ -6807,7 +6807,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H222" t="n">
         <v>2781</v>
@@ -6836,7 +6836,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H223" t="n">
         <v>275</v>
@@ -6865,7 +6865,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H224" t="n">
         <v>2881</v>
@@ -6894,7 +6894,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H225" t="n">
         <v>13996</v>
@@ -6923,7 +6923,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H226" t="n">
         <v>2165</v>
@@ -6952,7 +6952,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H227" t="n">
         <v>1452</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126806735992</v>
+        <v>1.21126794815063</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7068,7 +7068,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322463035583</v>
+        <v>1.23322451114655</v>
       </c>
       <c r="H231" t="n">
         <v>434</v>
@@ -7126,7 +7126,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="n">
-        <v>1.19004344940186</v>
+        <v>1.19004356861115</v>
       </c>
       <c r="H233" t="n">
         <v>13873</v>
@@ -7155,7 +7155,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>1.18199276924133</v>
+        <v>1.18199265003204</v>
       </c>
       <c r="H234" t="n">
         <v>2528</v>
@@ -7184,7 +7184,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21419560909271</v>
+        <v>1.214195728302</v>
       </c>
       <c r="H235" t="n">
         <v>750</v>
@@ -7213,7 +7213,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>1.19297099113464</v>
+        <v>1.19297087192535</v>
       </c>
       <c r="H236" t="n">
         <v>8622</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663035869598</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760881900787</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760881900787</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7329,7 +7329,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="n">
-        <v>1.22005069255829</v>
+        <v>1.22005081176758</v>
       </c>
       <c r="H240" t="n">
         <v>740</v>
@@ -7358,7 +7358,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="n">
-        <v>1.21639144420624</v>
+        <v>1.21639132499695</v>
       </c>
       <c r="H241" t="n">
         <v>6606</v>
@@ -7387,7 +7387,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956502437592</v>
+        <v>1.22956514358521</v>
       </c>
       <c r="H242" t="n">
         <v>6732</v>
@@ -7474,7 +7474,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615941524506</v>
+        <v>1.26615917682648</v>
       </c>
       <c r="H245" t="n">
         <v>4030</v>
@@ -7532,7 +7532,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>1.28592014312744</v>
+        <v>1.28592026233673</v>
       </c>
       <c r="H247" t="n">
         <v>4452</v>
@@ -7619,7 +7619,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="n">
-        <v>1.29689860343933</v>
+        <v>1.29689848423004</v>
       </c>
       <c r="H250" t="n">
         <v>818</v>
@@ -7648,7 +7648,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>1.29689860343933</v>
+        <v>1.29689848423004</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.30568110942841</v>
+        <v>1.3056812286377</v>
       </c>
       <c r="H255" t="n">
         <v>2306</v>
@@ -7822,7 +7822,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007242202759</v>
+        <v>1.31007254123688</v>
       </c>
       <c r="H257" t="n">
         <v>7253</v>
@@ -7851,7 +7851,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544195652008</v>
+        <v>1.32544219493866</v>
       </c>
       <c r="H258" t="n">
         <v>4943</v>
@@ -7880,7 +7880,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081161022186</v>
+        <v>1.34081149101257</v>
       </c>
       <c r="H259" t="n">
         <v>24867</v>
@@ -7938,7 +7938,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422446250916</v>
       </c>
       <c r="H261" t="n">
         <v>6768</v>
@@ -7967,7 +7967,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>1.3320289850235</v>
+        <v>1.33202886581421</v>
       </c>
       <c r="H262" t="n">
         <v>1416</v>
@@ -8025,7 +8025,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H264" t="n">
         <v>396</v>
@@ -8054,7 +8054,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422470092773</v>
+        <v>1.33422446250916</v>
       </c>
       <c r="H265" t="n">
         <v>1429</v>
@@ -8083,7 +8083,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G266" t="n">
-        <v>1.31665945053101</v>
+        <v>1.31665933132172</v>
       </c>
       <c r="H266" t="n">
         <v>3165</v>
@@ -8199,7 +8199,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>1.32690560817719</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H270" t="n">
         <v>1643</v>
@@ -8228,7 +8228,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>1.3210506439209</v>
+        <v>1.32105052471161</v>
       </c>
       <c r="H271" t="n">
         <v>1933</v>
@@ -8315,7 +8315,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="n">
-        <v>1.36057257652283</v>
+        <v>1.36057245731354</v>
       </c>
       <c r="H274" t="n">
         <v>7391</v>
@@ -8344,7 +8344,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="n">
-        <v>1.32690560817719</v>
+        <v>1.32690572738647</v>
       </c>
       <c r="H275" t="n">
         <v>14713</v>
@@ -8402,7 +8402,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959423542023</v>
+        <v>1.34959411621094</v>
       </c>
       <c r="H277" t="n">
         <v>1064</v>
@@ -8460,7 +8460,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34373915195465</v>
+        <v>1.34373903274536</v>
       </c>
       <c r="H279" t="n">
         <v>886</v>
@@ -8489,7 +8489,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H280" t="n">
         <v>113</v>
@@ -8518,7 +8518,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>1.33934783935547</v>
+        <v>1.33934772014618</v>
       </c>
       <c r="H281" t="n">
         <v>3002</v>
@@ -8547,7 +8547,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>1.34520292282104</v>
+        <v>1.34520280361176</v>
       </c>
       <c r="H282" t="n">
         <v>3656</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910132408142</v>
+        <v>1.32910144329071</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8605,7 +8605,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349987983704</v>
+        <v>1.36349976062775</v>
       </c>
       <c r="H284" t="n">
         <v>4639</v>
@@ -8634,7 +8634,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>1.36789119243622</v>
+        <v>1.3678914308548</v>
       </c>
       <c r="H285" t="n">
         <v>3430</v>
@@ -8663,7 +8663,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667393684387</v>
+        <v>1.37667381763458</v>
       </c>
       <c r="H286" t="n">
         <v>5575</v>
@@ -8692,7 +8692,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="n">
-        <v>1.38252902030945</v>
+        <v>1.38252890110016</v>
       </c>
       <c r="H287" t="n">
         <v>4266</v>
@@ -8721,7 +8721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789867401123</v>
+        <v>1.39789855480194</v>
       </c>
       <c r="H288" t="n">
         <v>6393</v>
@@ -8750,7 +8750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.4125360250473</v>
+        <v>1.41253614425659</v>
       </c>
       <c r="H289" t="n">
         <v>1447</v>
@@ -8779,7 +8779,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668094158173</v>
+        <v>1.40668106079102</v>
       </c>
       <c r="H290" t="n">
         <v>14299</v>
@@ -8808,7 +8808,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.4081449508667</v>
+        <v>1.40814483165741</v>
       </c>
       <c r="H291" t="n">
         <v>7943</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302181243896</v>
+        <v>1.40302169322968</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -8895,7 +8895,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="n">
-        <v>1.39277529716492</v>
+        <v>1.39277541637421</v>
       </c>
       <c r="H294" t="n">
         <v>2571</v>
@@ -8924,7 +8924,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.36935484409332</v>
+        <v>1.36935496330261</v>
       </c>
       <c r="H295" t="n">
         <v>3982</v>
@@ -8953,7 +8953,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>1.37886965274811</v>
+        <v>1.37886953353882</v>
       </c>
       <c r="H296" t="n">
         <v>1185</v>
@@ -9011,7 +9011,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155792236328</v>
+        <v>1.40155780315399</v>
       </c>
       <c r="H298" t="n">
         <v>640</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.4762099981308</v>
+        <v>1.47621023654938</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9127,7 +9127,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H302" t="n">
         <v>4239</v>
@@ -9243,7 +9243,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864510536194</v>
+        <v>1.45864486694336</v>
       </c>
       <c r="H306" t="n">
         <v>3108</v>
@@ -9272,7 +9272,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="n">
-        <v>1.47913753986359</v>
+        <v>1.47913765907288</v>
       </c>
       <c r="H307" t="n">
         <v>4196</v>
@@ -9359,7 +9359,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="n">
-        <v>1.48792016506195</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H310" t="n">
         <v>3021</v>
@@ -9388,7 +9388,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H311" t="n">
         <v>124</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744209766388</v>
+        <v>1.52744197845459</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987684726715</v>
+        <v>1.50987672805786</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -9533,7 +9533,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>1.53256547451019</v>
+        <v>1.53256523609161</v>
       </c>
       <c r="H316" t="n">
         <v>3089</v>
@@ -9562,7 +9562,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963757514954</v>
+        <v>1.52963769435883</v>
       </c>
       <c r="H317" t="n">
         <v>1725</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817380428314</v>
+        <v>1.52817392349243</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9649,7 +9649,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51499998569489</v>
+        <v>1.51500010490417</v>
       </c>
       <c r="H320" t="n">
         <v>2425</v>
@@ -9707,7 +9707,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.49816644191742</v>
+        <v>1.49816656112671</v>
       </c>
       <c r="H322" t="n">
         <v>1750</v>
@@ -9765,7 +9765,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H324" t="n">
         <v>6036</v>
@@ -9823,7 +9823,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48792016506195</v>
+        <v>1.48792028427124</v>
       </c>
       <c r="H326" t="n">
         <v>7683</v>
@@ -9852,7 +9852,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108709812164</v>
+        <v>1.47108685970306</v>
       </c>
       <c r="H327" t="n">
         <v>10631</v>
@@ -9881,7 +9881,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="n">
-        <v>1.4842609167099</v>
+        <v>1.48426079750061</v>
       </c>
       <c r="H328" t="n">
         <v>6549</v>
@@ -9910,7 +9910,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206520080566</v>
+        <v>1.48206532001495</v>
       </c>
       <c r="H329" t="n">
         <v>3153</v>
@@ -9968,7 +9968,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>1.45498538017273</v>
+        <v>1.45498549938202</v>
       </c>
       <c r="H331" t="n">
         <v>6285</v>
@@ -10026,7 +10026,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="n">
-        <v>1.52085518836975</v>
+        <v>1.52085506916046</v>
       </c>
       <c r="H333" t="n">
         <v>14974</v>
@@ -10084,7 +10084,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="n">
-        <v>1.58233368396759</v>
+        <v>1.58233344554901</v>
       </c>
       <c r="H335" t="n">
         <v>11207</v>
@@ -10113,7 +10113,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126385211945</v>
+        <v>1.63126361370087</v>
       </c>
       <c r="H336" t="n">
         <v>30984</v>
@@ -10171,7 +10171,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857733249664</v>
+        <v>1.64857745170593</v>
       </c>
       <c r="H338" t="n">
         <v>10071</v>
@@ -10229,7 +10229,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="n">
-        <v>1.66664385795593</v>
+        <v>1.66664409637451</v>
       </c>
       <c r="H340" t="n">
         <v>4864</v>
@@ -10258,7 +10258,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288030147552</v>
+        <v>1.66288042068481</v>
       </c>
       <c r="H341" t="n">
         <v>8452</v>
@@ -10287,7 +10287,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.66137480735779</v>
+        <v>1.66137492656708</v>
       </c>
       <c r="H342" t="n">
         <v>1480</v>
@@ -10316,7 +10316,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902151107788</v>
+        <v>1.76902174949646</v>
       </c>
       <c r="H343" t="n">
         <v>13422</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816555023193</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429883956909</v>
+        <v>1.84429931640625</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10432,7 +10432,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485421180725</v>
+        <v>1.99485409259796</v>
       </c>
       <c r="H347" t="n">
         <v>48029</v>
@@ -10490,7 +10490,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>1.95345175266266</v>
+        <v>1.95345139503479</v>
       </c>
       <c r="H349" t="n">
         <v>31940</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429883956909</v>
+        <v>1.84429931640625</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452110767365</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10751,7 +10751,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.92258763313293</v>
+        <v>1.92258775234222</v>
       </c>
       <c r="H358" t="n">
         <v>3542</v>
@@ -10809,7 +10809,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118505477905</v>
+        <v>1.88118493556976</v>
       </c>
       <c r="H360" t="n">
         <v>6883</v>
@@ -10867,7 +10867,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.92183494567871</v>
+        <v>1.92183482646942</v>
       </c>
       <c r="H362" t="n">
         <v>4932</v>
@@ -10896,7 +10896,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559897899628</v>
       </c>
       <c r="H363" t="n">
         <v>5423</v>
@@ -10954,7 +10954,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.92635154724121</v>
+        <v>1.9263516664505</v>
       </c>
       <c r="H365" t="n">
         <v>10408</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11070,7 +11070,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.9255987405777</v>
+        <v>1.92559897899628</v>
       </c>
       <c r="H369" t="n">
         <v>1846</v>
@@ -11099,7 +11099,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882383823395</v>
+        <v>1.91882371902466</v>
       </c>
       <c r="H370" t="n">
         <v>4343</v>
@@ -11186,7 +11186,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.92258763313293</v>
+        <v>1.92258775234222</v>
       </c>
       <c r="H373" t="n">
         <v>1590</v>
@@ -11215,7 +11215,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054308414459</v>
+        <v>1.91054332256317</v>
       </c>
       <c r="H374" t="n">
         <v>414</v>
@@ -11244,7 +11244,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>1.89021849632263</v>
+        <v>1.89021825790405</v>
       </c>
       <c r="H375" t="n">
         <v>1836</v>
@@ -11302,7 +11302,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699339866638</v>
+        <v>1.89699327945709</v>
       </c>
       <c r="H377" t="n">
         <v>2654</v>
@@ -11331,7 +11331,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473485946655</v>
+        <v>1.89473497867584</v>
       </c>
       <c r="H378" t="n">
         <v>803</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762709140778</v>
+        <v>1.7976268529892</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11476,7 +11476,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826882362366</v>
+        <v>1.76826894283295</v>
       </c>
       <c r="H383" t="n">
         <v>2862</v>
@@ -11505,7 +11505,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="n">
-        <v>1.79461598396301</v>
+        <v>1.79461586475372</v>
       </c>
       <c r="H384" t="n">
         <v>2507</v>
@@ -11534,7 +11534,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="n">
-        <v>1.80741322040558</v>
+        <v>1.80741310119629</v>
       </c>
       <c r="H385" t="n">
         <v>3798</v>
@@ -11563,7 +11563,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074915409088</v>
+        <v>1.83074939250946</v>
       </c>
       <c r="H386" t="n">
         <v>3583</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816555023193</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.83601868152618</v>
+        <v>1.8360184431076</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11795,7 +11795,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>1.83902990818024</v>
+        <v>1.83902955055237</v>
       </c>
       <c r="H394" t="n">
         <v>3433</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429883956909</v>
+        <v>1.84429931640625</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429883956909</v>
+        <v>1.84429931640625</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11882,7 +11882,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H397" t="n">
         <v>2269</v>
@@ -11911,7 +11911,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H398" t="n">
         <v>776</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.84655737876892</v>
+        <v>1.84655749797821</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752417564392</v>
+        <v>1.83752393722534</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774596691132</v>
+        <v>1.89774608612061</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12114,7 +12114,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.9737765789032</v>
+        <v>1.97377622127533</v>
       </c>
       <c r="H405" t="n">
         <v>8569</v>
@@ -12143,7 +12143,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.9737765789032</v>
+        <v>1.97377622127533</v>
       </c>
       <c r="H406" t="n">
         <v>3339</v>
@@ -12201,7 +12201,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.93086814880371</v>
+        <v>1.930868268013</v>
       </c>
       <c r="H408" t="n">
         <v>4037</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613767623901</v>
+        <v>1.93613743782043</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957652568817</v>
+        <v>1.91957676410675</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12346,7 +12346,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="n">
-        <v>1.88796007633209</v>
+        <v>1.8879599571228</v>
       </c>
       <c r="H413" t="n">
         <v>1727</v>
@@ -12375,7 +12375,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="n">
-        <v>1.89021849632263</v>
+        <v>1.89021825790405</v>
       </c>
       <c r="H414" t="n">
         <v>818</v>
@@ -12404,7 +12404,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720726966858</v>
+        <v>1.88720738887787</v>
       </c>
       <c r="H415" t="n">
         <v>1165</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452098846436</v>
+        <v>1.90452110767365</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12578,7 +12578,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860180854797</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H421" t="n">
         <v>1458</v>
@@ -12694,7 +12694,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182690620422</v>
+        <v>1.85182702541351</v>
       </c>
       <c r="H425" t="n">
         <v>2952</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688244342804</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H426" t="n">
         <v>1972</v>
@@ -12781,7 +12781,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494908809662</v>
+        <v>1.88494884967804</v>
       </c>
       <c r="H428" t="n">
         <v>2953</v>
@@ -12810,7 +12810,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215185165405</v>
+        <v>1.87215209007263</v>
       </c>
       <c r="H429" t="n">
         <v>140</v>
@@ -12839,7 +12839,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860180854797</v>
+        <v>1.85860192775726</v>
       </c>
       <c r="H430" t="n">
         <v>1130</v>
@@ -12868,7 +12868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688244342804</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H431" t="n">
         <v>1257</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12926,7 +12926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688244342804</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H433" t="n">
         <v>2572</v>
@@ -12955,7 +12955,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.87064611911774</v>
+        <v>1.87064635753632</v>
       </c>
       <c r="H434" t="n">
         <v>4633</v>
@@ -12984,7 +12984,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161279678345</v>
+        <v>1.86161303520203</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193798065186</v>
+        <v>1.88193774223328</v>
       </c>
       <c r="H436" t="n">
         <v>2642</v>
@@ -13071,7 +13071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688244342804</v>
+        <v>1.86688208580017</v>
       </c>
       <c r="H438" t="n">
         <v>969</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.8653769493103</v>
+        <v>1.86537671089172</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.860107421875</v>
+        <v>1.86010730266571</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13187,7 +13187,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="n">
-        <v>1.84505200386047</v>
+        <v>1.84505188465118</v>
       </c>
       <c r="H442" t="n">
         <v>4195</v>
@@ -13216,7 +13216,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>1.85257947444916</v>
+        <v>1.85257971286774</v>
       </c>
       <c r="H443" t="n">
         <v>1174</v>
@@ -13274,7 +13274,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731030464172</v>
+        <v>1.84731066226959</v>
       </c>
       <c r="H445" t="n">
         <v>2208</v>
@@ -13303,7 +13303,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279334545135</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="n">
         <v>1136</v>
@@ -13361,7 +13361,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795191764832</v>
+        <v>1.81795179843903</v>
       </c>
       <c r="H448" t="n">
         <v>5592</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13419,7 +13419,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849085330963</v>
+        <v>1.82849061489105</v>
       </c>
       <c r="H450" t="n">
         <v>3382</v>
@@ -13477,7 +13477,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021033763885</v>
+        <v>1.82021045684814</v>
       </c>
       <c r="H452" t="n">
         <v>6137</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117689609528</v>
+        <v>1.81117701530457</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13535,7 +13535,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>1.81644630432129</v>
+        <v>1.81644642353058</v>
       </c>
       <c r="H454" t="n">
         <v>4767</v>
@@ -13564,7 +13564,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.81418800354004</v>
+        <v>1.81418812274933</v>
       </c>
       <c r="H455" t="n">
         <v>1684</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13651,7 +13651,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.8322548866272</v>
+        <v>1.83225464820862</v>
       </c>
       <c r="H458" t="n">
         <v>1829</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246851921082</v>
+        <v>1.82246828079224</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547986507416</v>
+        <v>1.82547950744629</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13854,7 +13854,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689036369324</v>
+        <v>1.93689024448395</v>
       </c>
       <c r="H465" t="n">
         <v>5512</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731834411621</v>
+        <v>1.91731810569763</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13912,7 +13912,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979855537415</v>
+        <v>1.97979831695557</v>
       </c>
       <c r="H467" t="n">
         <v>24938</v>
@@ -13941,7 +13941,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474313735962</v>
       </c>
       <c r="H468" t="n">
         <v>14648</v>
@@ -13999,7 +13999,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="n">
-        <v>1.94667661190033</v>
+        <v>1.94667649269104</v>
       </c>
       <c r="H470" t="n">
         <v>11729</v>
@@ -14028,7 +14028,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="n">
-        <v>1.97076547145844</v>
+        <v>1.97076535224915</v>
       </c>
       <c r="H471" t="n">
         <v>6065</v>
@@ -14057,7 +14057,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775412559509</v>
+        <v>1.96775448322296</v>
       </c>
       <c r="H472" t="n">
         <v>6595</v>
@@ -14086,7 +14086,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248459815979</v>
+        <v>1.96248483657837</v>
       </c>
       <c r="H473" t="n">
         <v>11988</v>
@@ -14202,7 +14202,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.98732650279999</v>
+        <v>1.9873263835907</v>
       </c>
       <c r="H477" t="n">
         <v>8901</v>
@@ -14231,7 +14231,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937057495117</v>
+        <v>1.99937069416046</v>
       </c>
       <c r="H478" t="n">
         <v>3901</v>
@@ -14260,7 +14260,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582065105438</v>
+        <v>1.98582077026367</v>
       </c>
       <c r="H479" t="n">
         <v>3201</v>
@@ -14289,7 +14289,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="n">
-        <v>1.99033761024475</v>
+        <v>1.99033749103546</v>
       </c>
       <c r="H480" t="n">
         <v>2850</v>
@@ -14318,7 +14318,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624851226807</v>
+        <v>1.96624875068665</v>
       </c>
       <c r="H481" t="n">
         <v>7605</v>
@@ -14347,7 +14347,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861788749695</v>
+        <v>1.99861812591553</v>
       </c>
       <c r="H482" t="n">
         <v>7953</v>
@@ -14405,7 +14405,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474325656891</v>
+        <v>1.96474313735962</v>
       </c>
       <c r="H484" t="n">
         <v>3107</v>
@@ -14463,7 +14463,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98280942440033</v>
+        <v>1.98281002044678</v>
       </c>
       <c r="H486" t="n">
         <v>699</v>
@@ -14492,7 +14492,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.9737765789032</v>
+        <v>1.97377622127533</v>
       </c>
       <c r="H487" t="n">
         <v>871</v>
@@ -14782,7 +14782,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765960693359</v>
+        <v>2.07765936851501</v>
       </c>
       <c r="H497" t="n">
         <v>3216</v>
@@ -14869,7 +14869,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.11153435707092</v>
+        <v>2.11153411865234</v>
       </c>
       <c r="H500" t="n">
         <v>1908</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024261474609</v>
+        <v>2.10024237632751</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -15014,7 +15014,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959296226501</v>
+        <v>2.05959272384644</v>
       </c>
       <c r="H505" t="n">
         <v>2166</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615399360657</v>
+        <v>2.07615375518799</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15217,7 +15217,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>2.13185930252075</v>
+        <v>2.13185906410217</v>
       </c>
       <c r="H512" t="n">
         <v>18197</v>
@@ -15304,7 +15304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17552018165588</v>
+        <v>2.1755199432373</v>
       </c>
       <c r="H515" t="n">
         <v>6715</v>
@@ -15362,7 +15362,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.17552018165588</v>
+        <v>2.1755199432373</v>
       </c>
       <c r="H517" t="n">
         <v>16053</v>
@@ -15420,7 +15420,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="n">
-        <v>2.22068667411804</v>
+        <v>2.22068691253662</v>
       </c>
       <c r="H519" t="n">
         <v>982</v>
@@ -15449,7 +15449,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H520" t="n">
         <v>13063</v>
@@ -15478,7 +15478,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H521" t="n">
         <v>10697</v>
@@ -15507,7 +15507,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="n">
-        <v>2.31854748725891</v>
+        <v>2.31854724884033</v>
       </c>
       <c r="H522" t="n">
         <v>6269</v>
@@ -15536,7 +15536,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>2.31854748725891</v>
+        <v>2.31854724884033</v>
       </c>
       <c r="H523" t="n">
         <v>1601</v>
@@ -15623,7 +15623,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H526" t="n">
         <v>2705</v>
@@ -15681,7 +15681,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H528" t="n">
         <v>6112</v>
@@ -15768,7 +15768,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>2.28090858459473</v>
+        <v>2.28090882301331</v>
       </c>
       <c r="H531" t="n">
         <v>1414</v>
@@ -15797,7 +15797,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30349206924438</v>
+        <v>2.30349183082581</v>
       </c>
       <c r="H532" t="n">
         <v>3569</v>
@@ -15826,7 +15826,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596400260925</v>
+        <v>2.29596447944641</v>
       </c>
       <c r="H533" t="n">
         <v>4435</v>
@@ -16058,7 +16058,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="n">
-        <v>2.18304800987244</v>
+        <v>2.18304777145386</v>
       </c>
       <c r="H541" t="n">
         <v>2730</v>
@@ -16232,7 +16232,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>2.38629722595215</v>
+        <v>2.38629698753357</v>
       </c>
       <c r="H547" t="n">
         <v>6727</v>
@@ -16319,7 +16319,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>2.5443799495697</v>
+        <v>2.54437971115112</v>
       </c>
       <c r="H550" t="n">
         <v>7288</v>
@@ -16348,7 +16348,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>2.61965751647949</v>
+        <v>2.61965727806091</v>
       </c>
       <c r="H551" t="n">
         <v>11195</v>
@@ -16406,7 +16406,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H553" t="n">
         <v>5398</v>
@@ -16435,7 +16435,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H554" t="n">
         <v>6023</v>
@@ -16464,7 +16464,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>2.40135264396667</v>
+        <v>2.40135288238525</v>
       </c>
       <c r="H555" t="n">
         <v>12859</v>
@@ -16493,7 +16493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H556" t="n">
         <v>9076</v>
@@ -16551,7 +16551,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H558" t="n">
         <v>4749</v>
@@ -16580,7 +16580,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H559" t="n">
         <v>4701</v>
@@ -16725,7 +16725,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H564" t="n">
         <v>2298</v>
@@ -16783,7 +16783,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="n">
-        <v>2.48415803909302</v>
+        <v>2.48415780067444</v>
       </c>
       <c r="H566" t="n">
         <v>3886</v>
@@ -16841,7 +16841,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H568" t="n">
         <v>2129</v>
@@ -16928,7 +16928,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H571" t="n">
         <v>3605</v>
@@ -17044,7 +17044,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146371841431</v>
+        <v>2.43146395683289</v>
       </c>
       <c r="H575" t="n">
         <v>4786</v>
@@ -17131,7 +17131,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>2.45404696464539</v>
+        <v>2.45404672622681</v>
       </c>
       <c r="H578" t="n">
         <v>1479</v>
@@ -17189,7 +17189,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H580" t="n">
         <v>7145</v>
@@ -17276,7 +17276,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>2.49168586730957</v>
+        <v>2.49168562889099</v>
       </c>
       <c r="H583" t="n">
         <v>1838</v>
@@ -17305,7 +17305,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="n">
-        <v>2.48415803909302</v>
+        <v>2.48415780067444</v>
       </c>
       <c r="H584" t="n">
         <v>1833</v>
@@ -17363,7 +17363,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910214424133</v>
+        <v>2.46910238265991</v>
       </c>
       <c r="H586" t="n">
         <v>3037</v>
@@ -17421,7 +17421,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>2.5293242931366</v>
+        <v>2.52932453155518</v>
       </c>
       <c r="H588" t="n">
         <v>10382</v>
@@ -17450,7 +17450,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H589" t="n">
         <v>8373</v>
@@ -17537,7 +17537,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.58363509178162</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H592" t="n">
         <v>1427</v>
@@ -17566,7 +17566,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56035923957825</v>
+        <v>2.56035900115967</v>
       </c>
       <c r="H593" t="n">
         <v>2134</v>
@@ -17595,7 +17595,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50604844093323</v>
+        <v>2.50604867935181</v>
       </c>
       <c r="H594" t="n">
         <v>2722</v>
@@ -17682,7 +17682,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.58363509178162</v>
+        <v>2.5836353302002</v>
       </c>
       <c r="H597" t="n">
         <v>5094</v>
@@ -17711,7 +17711,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587671279907</v>
+        <v>2.57587647438049</v>
       </c>
       <c r="H598" t="n">
         <v>3047</v>
@@ -17769,7 +17769,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484152793884</v>
+        <v>2.54484176635742</v>
       </c>
       <c r="H600" t="n">
         <v>1367</v>
@@ -17827,7 +17827,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H602" t="n">
         <v>16769</v>
@@ -17856,7 +17856,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>2.49828958511353</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H603" t="n">
         <v>729</v>
@@ -17885,7 +17885,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>2.49828958511353</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H604" t="n">
         <v>238</v>
@@ -17914,7 +17914,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>2.50604844093323</v>
+        <v>2.50604867935181</v>
       </c>
       <c r="H605" t="n">
         <v>1385</v>
@@ -17943,7 +17943,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="n">
-        <v>2.48277235031128</v>
+        <v>2.48277258872986</v>
       </c>
       <c r="H606" t="n">
         <v>109</v>
@@ -17972,7 +17972,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H607" t="n">
         <v>6484</v>
@@ -18001,7 +18001,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H608" t="n">
         <v>12294</v>
@@ -18117,7 +18117,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H612" t="n">
         <v>1071</v>
@@ -18175,7 +18175,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H614" t="n">
         <v>7400</v>
@@ -18291,7 +18291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25777101516724</v>
+        <v>2.25777125358582</v>
       </c>
       <c r="H618" t="n">
         <v>1075</v>
@@ -18407,7 +18407,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H622" t="n">
         <v>1065</v>
@@ -18436,7 +18436,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H623" t="n">
         <v>4311</v>
@@ -18465,7 +18465,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H624" t="n">
         <v>215</v>
@@ -18494,7 +18494,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H625" t="n">
         <v>1193</v>
@@ -18581,7 +18581,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H628" t="n">
         <v>125</v>
@@ -18697,7 +18697,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H632" t="n">
         <v>2259</v>
@@ -18726,7 +18726,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H633" t="n">
         <v>3975</v>
@@ -18755,7 +18755,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H634" t="n">
         <v>786</v>
@@ -18784,7 +18784,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H635" t="n">
         <v>2701</v>
@@ -18813,7 +18813,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H636" t="n">
         <v>1273</v>
@@ -18842,7 +18842,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H637" t="n">
         <v>1582</v>
@@ -18871,7 +18871,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H638" t="n">
         <v>413</v>
@@ -18900,7 +18900,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H639" t="n">
         <v>152</v>
@@ -18929,7 +18929,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H641" t="n">
         <v>2464</v>
@@ -19103,7 +19103,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156348228455</v>
+        <v>2.07156324386597</v>
       </c>
       <c r="H646" t="n">
         <v>7254</v>
@@ -19190,7 +19190,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H649" t="n">
         <v>1745</v>
@@ -19248,7 +19248,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H651" t="n">
         <v>1233</v>
@@ -19277,7 +19277,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14915013313293</v>
+        <v>2.14914989471436</v>
       </c>
       <c r="H652" t="n">
         <v>1217</v>
@@ -19335,7 +19335,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H654" t="n">
         <v>4303</v>
@@ -19451,7 +19451,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H658" t="n">
         <v>1560</v>
@@ -19509,7 +19509,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>2.18794345855713</v>
+        <v>2.18794322013855</v>
       </c>
       <c r="H660" t="n">
         <v>1057</v>
@@ -19538,7 +19538,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H661" t="n">
         <v>1158</v>
@@ -19567,7 +19567,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H662" t="n">
         <v>2066</v>
@@ -19596,7 +19596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H663" t="n">
         <v>44</v>
@@ -19625,7 +19625,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H664" t="n">
         <v>190</v>
@@ -19654,7 +19654,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H665" t="n">
         <v>392</v>
@@ -19683,7 +19683,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H666" t="n">
         <v>989</v>
@@ -19712,7 +19712,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H667" t="n">
         <v>232</v>
@@ -19741,7 +19741,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>2.10259819030762</v>
+        <v>2.10259795188904</v>
       </c>
       <c r="H668" t="n">
         <v>25</v>
@@ -19770,7 +19770,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H669" t="n">
         <v>1070</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H671" t="n">
         <v>3968</v>
@@ -19973,7 +19973,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.96294188499451</v>
+        <v>1.9629420042038</v>
       </c>
       <c r="H676" t="n">
         <v>3545</v>
@@ -20002,7 +20002,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>1.93966615200043</v>
+        <v>1.93966603279114</v>
       </c>
       <c r="H677" t="n">
         <v>2534</v>
@@ -20031,7 +20031,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>1.8853554725647</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H678" t="n">
         <v>5198</v>
@@ -20060,7 +20060,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H679" t="n">
         <v>3984</v>
@@ -20118,7 +20118,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.86983799934387</v>
+        <v>1.86983788013458</v>
       </c>
       <c r="H681" t="n">
         <v>254</v>
@@ -20147,7 +20147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225158691406</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H682" t="n">
         <v>1859</v>
@@ -20176,7 +20176,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880341053009</v>
       </c>
       <c r="H683" t="n">
         <v>3849</v>
@@ -20205,7 +20205,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>1.83104467391968</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H684" t="n">
         <v>5886</v>
@@ -20234,7 +20234,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207926273346</v>
+        <v>1.86207950115204</v>
       </c>
       <c r="H685" t="n">
         <v>1968</v>
@@ -20321,7 +20321,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H688" t="n">
         <v>6201</v>
@@ -20437,7 +20437,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H692" t="n">
         <v>1912</v>
@@ -20466,7 +20466,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H693" t="n">
         <v>2480</v>
@@ -20698,7 +20698,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H701" t="n">
         <v>7483</v>
@@ -20872,7 +20872,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.96294188499451</v>
+        <v>1.9629420042038</v>
       </c>
       <c r="H707" t="n">
         <v>4382</v>
@@ -20901,7 +20901,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="n">
-        <v>1.97845923900604</v>
+        <v>1.97845947742462</v>
       </c>
       <c r="H708" t="n">
         <v>6007</v>
@@ -21017,7 +21017,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>1.83880352973938</v>
+        <v>1.83880341053009</v>
       </c>
       <c r="H712" t="n">
         <v>2116</v>
@@ -21046,7 +21046,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>1.84656190872192</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H713" t="n">
         <v>609</v>
@@ -21075,7 +21075,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.83104467391968</v>
+        <v>1.83104491233826</v>
       </c>
       <c r="H714" t="n">
         <v>2033</v>
@@ -21104,7 +21104,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207926273346</v>
+        <v>1.86207950115204</v>
       </c>
       <c r="H715" t="n">
         <v>1620</v>
@@ -21133,7 +21133,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>1.84656190872192</v>
+        <v>1.84656202793121</v>
       </c>
       <c r="H716" t="n">
         <v>48</v>
@@ -21162,7 +21162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225158691406</v>
+        <v>1.79225134849548</v>
       </c>
       <c r="H717" t="n">
         <v>747</v>
@@ -21191,7 +21191,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776870250702</v>
+        <v>1.80776858329773</v>
       </c>
       <c r="H718" t="n">
         <v>821</v>
@@ -21220,7 +21220,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.75345814228058</v>
+        <v>1.753457903862</v>
       </c>
       <c r="H719" t="n">
         <v>3685</v>
@@ -21249,7 +21249,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673423290253</v>
+        <v>1.77673399448395</v>
       </c>
       <c r="H720" t="n">
         <v>6378</v>
@@ -21278,7 +21278,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="n">
-        <v>1.74569928646088</v>
+        <v>1.74569952487946</v>
       </c>
       <c r="H721" t="n">
         <v>2119</v>
@@ -21307,7 +21307,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328593730927</v>
       </c>
       <c r="H722" t="n">
         <v>1535</v>
@@ -21336,7 +21336,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="n">
-        <v>1.82328605651855</v>
+        <v>1.82328593730927</v>
       </c>
       <c r="H723" t="n">
         <v>8398</v>
@@ -21365,7 +21365,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H724" t="n">
         <v>2115</v>
@@ -21394,7 +21394,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.89311408996582</v>
+        <v>1.89311385154724</v>
       </c>
       <c r="H726" t="n">
         <v>6832</v>
@@ -21452,7 +21452,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.8853554725647</v>
+        <v>1.88535535335541</v>
       </c>
       <c r="H727" t="n">
         <v>1177</v>
@@ -21481,7 +21481,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.877596616745</v>
+        <v>1.87759685516357</v>
       </c>
       <c r="H728" t="n">
         <v>961</v>
@@ -21510,7 +21510,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.93966615200043</v>
+        <v>1.93966603279114</v>
       </c>
       <c r="H729" t="n">
         <v>4613</v>
@@ -21539,7 +21539,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>1.91639006137848</v>
+        <v>1.91639018058777</v>
       </c>
       <c r="H730" t="n">
         <v>2333</v>
@@ -21597,7 +21597,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H732" t="n">
         <v>19299</v>
@@ -21626,7 +21626,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H733" t="n">
         <v>5119</v>
@@ -21684,7 +21684,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H735" t="n">
         <v>3881</v>
@@ -21800,7 +21800,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H739" t="n">
         <v>2280</v>
@@ -21945,7 +21945,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H744" t="n">
         <v>6975</v>
@@ -21974,7 +21974,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H745" t="n">
         <v>2434</v>
@@ -22032,7 +22032,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>2.11811518669128</v>
+        <v>2.11811542510986</v>
       </c>
       <c r="H747" t="n">
         <v>149</v>
@@ -22061,7 +22061,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="n">
-        <v>2.13363242149353</v>
+        <v>2.13363265991211</v>
       </c>
       <c r="H748" t="n">
         <v>1576</v>
@@ -22090,7 +22090,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156348228455</v>
+        <v>2.07156324386597</v>
       </c>
       <c r="H749" t="n">
         <v>391</v>
@@ -22351,7 +22351,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H758" t="n">
         <v>645</v>
@@ -22409,7 +22409,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>2.0482873916626</v>
+        <v>2.04828715324402</v>
       </c>
       <c r="H760" t="n">
         <v>1417</v>
@@ -22438,7 +22438,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H761" t="n">
         <v>5897</v>
@@ -22496,7 +22496,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="n">
-        <v>2.09483909606934</v>
+        <v>2.09483933448792</v>
       </c>
       <c r="H763" t="n">
         <v>154</v>
@@ -22641,7 +22641,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>2.12587380409241</v>
+        <v>2.12587404251099</v>
       </c>
       <c r="H768" t="n">
         <v>3478</v>
@@ -22670,7 +22670,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>2.14139151573181</v>
+        <v>2.14139127731323</v>
       </c>
       <c r="H769" t="n">
         <v>3390</v>
@@ -22699,7 +22699,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H770" t="n">
         <v>1195</v>
@@ -22989,7 +22989,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="n">
-        <v>2.2112193107605</v>
+        <v>2.21121907234192</v>
       </c>
       <c r="H780" t="n">
         <v>7946</v>
@@ -23018,7 +23018,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.20346069335938</v>
+        <v>2.2034604549408</v>
       </c>
       <c r="H781" t="n">
         <v>1441</v>
@@ -23076,7 +23076,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>2.25777101516724</v>
+        <v>2.25777125358582</v>
       </c>
       <c r="H783" t="n">
         <v>1355</v>
@@ -23279,7 +23279,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H790" t="n">
         <v>6067</v>
@@ -23308,7 +23308,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H791" t="n">
         <v>238</v>
@@ -23337,7 +23337,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H792" t="n">
         <v>323</v>
@@ -23366,7 +23366,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>2.29656434059143</v>
+        <v>2.29656457901001</v>
       </c>
       <c r="H793" t="n">
         <v>206</v>
@@ -23395,7 +23395,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H794" t="n">
         <v>836</v>
@@ -23424,7 +23424,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H795" t="n">
         <v>1453</v>
@@ -23453,7 +23453,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.3353579044342</v>
+        <v>2.33535814285278</v>
       </c>
       <c r="H796" t="n">
         <v>1137</v>
@@ -23482,7 +23482,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H797" t="n">
         <v>1948</v>
@@ -23569,7 +23569,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="n">
-        <v>2.3275990486145</v>
+        <v>2.32759928703308</v>
       </c>
       <c r="H800" t="n">
         <v>673</v>
@@ -23598,7 +23598,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208181381226</v>
+        <v>2.31208157539368</v>
       </c>
       <c r="H801" t="n">
         <v>693</v>
@@ -23627,7 +23627,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984066963196</v>
+        <v>2.31984043121338</v>
       </c>
       <c r="H802" t="n">
         <v>276</v>
@@ -23656,7 +23656,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846155166626</v>
+        <v>2.42846179008484</v>
       </c>
       <c r="H803" t="n">
         <v>8524</v>
@@ -23685,7 +23685,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H804" t="n">
         <v>3185</v>
@@ -23714,7 +23714,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>2.3819100856781</v>
+        <v>2.38190984725952</v>
       </c>
       <c r="H805" t="n">
         <v>1473</v>
@@ -23743,7 +23743,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H806" t="n">
         <v>3492</v>
@@ -23801,7 +23801,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H808" t="n">
         <v>3206</v>
@@ -23830,7 +23830,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H809" t="n">
         <v>1118</v>
@@ -23859,7 +23859,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H810" t="n">
         <v>3272</v>
@@ -23888,7 +23888,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H811" t="n">
         <v>4135</v>
@@ -23917,7 +23917,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41294455528259</v>
+        <v>2.41294431686401</v>
       </c>
       <c r="H812" t="n">
         <v>1173</v>
@@ -23946,7 +23946,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H813" t="n">
         <v>222</v>
@@ -24033,7 +24033,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H816" t="n">
         <v>378</v>
@@ -24062,7 +24062,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H817" t="n">
         <v>604</v>
@@ -24120,7 +24120,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="n">
-        <v>2.40518593788147</v>
+        <v>2.40518617630005</v>
       </c>
       <c r="H819" t="n">
         <v>412</v>
@@ -24149,7 +24149,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H820" t="n">
         <v>2462</v>
@@ -24178,7 +24178,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="n">
-        <v>2.3663923740387</v>
+        <v>2.36639261245728</v>
       </c>
       <c r="H821" t="n">
         <v>1310</v>
@@ -24207,7 +24207,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311676025391</v>
+        <v>2.34311628341675</v>
       </c>
       <c r="H822" t="n">
         <v>940</v>
@@ -24265,7 +24265,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>2.37415146827698</v>
+        <v>2.3741512298584</v>
       </c>
       <c r="H824" t="n">
         <v>915</v>
@@ -24352,7 +24352,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966846466064</v>
+        <v>2.38966870307922</v>
       </c>
       <c r="H827" t="n">
         <v>622</v>
@@ -24497,7 +24497,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H832" t="n">
         <v>6312</v>
@@ -24526,7 +24526,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H833" t="n">
         <v>10097</v>
@@ -24555,7 +24555,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>2.47501373291016</v>
+        <v>2.47501397132874</v>
       </c>
       <c r="H834" t="n">
         <v>2763</v>
@@ -24584,7 +24584,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>2.49828958511353</v>
+        <v>2.4982898235321</v>
       </c>
       <c r="H835" t="n">
         <v>9123</v>
@@ -24613,7 +24613,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.5526008605957</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H836" t="n">
         <v>21589</v>
@@ -24816,7 +24816,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H843" t="n">
         <v>3263</v>
@@ -24845,7 +24845,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H844" t="n">
         <v>715</v>
@@ -24874,7 +24874,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H845" t="n">
         <v>800</v>
@@ -24903,7 +24903,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H846" t="n">
         <v>241</v>
@@ -24961,7 +24961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H848" t="n">
         <v>2347</v>
@@ -24990,7 +24990,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H849" t="n">
         <v>1869</v>
@@ -25048,7 +25048,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H851" t="n">
         <v>2444</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H852" t="n">
         <v>19648</v>
@@ -25106,7 +25106,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H853" t="n">
         <v>3476</v>
@@ -25164,7 +25164,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H855" t="n">
         <v>1424</v>
@@ -25193,7 +25193,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H856" t="n">
         <v>3013</v>
@@ -25251,7 +25251,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H858" t="n">
         <v>6283</v>
@@ -25280,7 +25280,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H859" t="n">
         <v>1608</v>
@@ -25367,7 +25367,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H862" t="n">
         <v>669</v>
@@ -25396,7 +25396,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H863" t="n">
         <v>11000</v>
@@ -25425,7 +25425,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H864" t="n">
         <v>462</v>
@@ -25454,7 +25454,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H865" t="n">
         <v>4994</v>
@@ -25483,7 +25483,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H866" t="n">
         <v>6419</v>
@@ -25512,7 +25512,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H867" t="n">
         <v>13328</v>
@@ -25541,7 +25541,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H868" t="n">
         <v>3222</v>
@@ -25570,7 +25570,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H869" t="n">
         <v>2149</v>
@@ -25657,7 +25657,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H872" t="n">
         <v>854</v>
@@ -25715,7 +25715,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H874" t="n">
         <v>1167</v>
@@ -25744,7 +25744,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H875" t="n">
         <v>3142</v>
@@ -25802,7 +25802,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H877" t="n">
         <v>834</v>
@@ -25831,7 +25831,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H878" t="n">
         <v>1616</v>
@@ -25860,7 +25860,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H879" t="n">
         <v>4136</v>
@@ -26063,7 +26063,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H886" t="n">
         <v>7315</v>
@@ -26150,7 +26150,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H889" t="n">
         <v>1830</v>
@@ -26324,7 +26324,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H895" t="n">
         <v>1271</v>
@@ -26498,7 +26498,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H901" t="n">
         <v>609</v>
@@ -26556,7 +26556,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H903" t="n">
         <v>350</v>
@@ -26585,7 +26585,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H904" t="n">
         <v>217</v>
@@ -26614,7 +26614,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H905" t="n">
         <v>1973</v>
@@ -26701,7 +26701,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H908" t="n">
         <v>2849</v>
@@ -26730,7 +26730,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H909" t="n">
         <v>1732</v>
@@ -26759,7 +26759,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H910" t="n">
         <v>1929</v>
@@ -26788,7 +26788,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>2.55260062217712</v>
+        <v>2.55260038375854</v>
       </c>
       <c r="H911" t="n">
         <v>241</v>
@@ -26817,7 +26817,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H912" t="n">
         <v>600</v>
@@ -26875,7 +26875,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H914" t="n">
         <v>953</v>
@@ -26933,7 +26933,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H916" t="n">
         <v>326</v>
@@ -26962,7 +26962,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="n">
-        <v>2.4144024848938</v>
+        <v>2.41440272331238</v>
       </c>
       <c r="H917" t="n">
         <v>2353</v>
@@ -26991,7 +26991,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H918" t="n">
         <v>1740</v>
@@ -27020,7 +27020,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H919" t="n">
         <v>897</v>
@@ -27049,7 +27049,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H920" t="n">
         <v>1145</v>
@@ -27136,7 +27136,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H923" t="n">
         <v>3737</v>
@@ -27165,7 +27165,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H924" t="n">
         <v>715</v>
@@ -27194,7 +27194,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H925" t="n">
         <v>1884</v>
@@ -27223,7 +27223,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H926" t="n">
         <v>550</v>
@@ -27368,7 +27368,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H931" t="n">
         <v>382</v>
@@ -27600,7 +27600,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>2.39001441001892</v>
+        <v>2.3900146484375</v>
       </c>
       <c r="H939" t="n">
         <v>2176</v>
@@ -27629,7 +27629,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H940" t="n">
         <v>650</v>
@@ -27832,7 +27832,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H947" t="n">
         <v>252</v>
@@ -27861,7 +27861,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H948" t="n">
         <v>60</v>
@@ -28006,7 +28006,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H953" t="n">
         <v>2198</v>
@@ -28064,7 +28064,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H955" t="n">
         <v>5035</v>
@@ -28180,7 +28180,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H959" t="n">
         <v>2779</v>
@@ -28296,7 +28296,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H963" t="n">
         <v>122</v>
@@ -28325,7 +28325,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="n">
-        <v>2.42253184318542</v>
+        <v>2.42253160476685</v>
       </c>
       <c r="H964" t="n">
         <v>5121</v>
@@ -28789,7 +28789,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>2.53634190559387</v>
+        <v>2.53634214401245</v>
       </c>
       <c r="H980" t="n">
         <v>239</v>
@@ -28847,7 +28847,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H982" t="n">
         <v>1427</v>
@@ -28905,7 +28905,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H984" t="n">
         <v>3320</v>
@@ -28992,7 +28992,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H987" t="n">
         <v>13081</v>
@@ -29050,7 +29050,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H989" t="n">
         <v>3240</v>
@@ -29108,7 +29108,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H991" t="n">
         <v>1405</v>
@@ -29166,7 +29166,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H993" t="n">
         <v>1096</v>
@@ -29195,7 +29195,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="n">
-        <v>2.56072998046875</v>
+        <v>2.56072974205017</v>
       </c>
       <c r="H994" t="n">
         <v>3106</v>
@@ -29340,7 +29340,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H999" t="n">
         <v>2190</v>
@@ -29369,7 +29369,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1000" t="n">
         <v>2768</v>
@@ -29398,7 +29398,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1001" t="n">
         <v>6864</v>
@@ -29427,7 +29427,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H1002" t="n">
         <v>900</v>
@@ -29456,7 +29456,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1003" t="n">
         <v>101</v>
@@ -29572,7 +29572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.50382447242737</v>
+        <v>2.50382471084595</v>
       </c>
       <c r="H1007" t="n">
         <v>1267</v>
@@ -29659,7 +29659,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1010" t="n">
         <v>24</v>
@@ -29688,7 +29688,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1011" t="n">
         <v>1121</v>
@@ -29717,7 +29717,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1012" t="n">
         <v>21303</v>
@@ -29746,7 +29746,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1013" t="n">
         <v>1283</v>
@@ -29775,7 +29775,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1014" t="n">
         <v>2374</v>
@@ -29833,7 +29833,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1016" t="n">
         <v>257</v>
@@ -29891,7 +29891,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1018" t="n">
         <v>5441</v>
@@ -29949,7 +29949,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.47943663597107</v>
+        <v>2.47943687438965</v>
       </c>
       <c r="H1020" t="n">
         <v>2880</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1021" t="n">
         <v>1241</v>
@@ -30007,7 +30007,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.48756623268127</v>
+        <v>2.4875659942627</v>
       </c>
       <c r="H1022" t="n">
         <v>825</v>
@@ -30123,7 +30123,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1026" t="n">
         <v>3715</v>
@@ -30152,7 +30152,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066096305847</v>
+        <v>2.43066120147705</v>
       </c>
       <c r="H1027" t="n">
         <v>4984</v>
@@ -30355,7 +30355,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H1034" t="n">
         <v>5053</v>
@@ -30413,7 +30413,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H1036" t="n">
         <v>167</v>
@@ -30471,7 +30471,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.29246306419373</v>
+        <v>2.29246282577515</v>
       </c>
       <c r="H1038" t="n">
         <v>2153</v>
@@ -30500,7 +30500,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1039" t="n">
         <v>2151</v>
@@ -30529,7 +30529,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.2843337059021</v>
+        <v>2.28433346748352</v>
       </c>
       <c r="H1040" t="n">
         <v>2028</v>
@@ -30558,7 +30558,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1041" t="n">
         <v>2270</v>
@@ -30587,7 +30587,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1042" t="n">
         <v>304</v>
@@ -30616,7 +30616,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.29246306419373</v>
+        <v>2.29246282577515</v>
       </c>
       <c r="H1043" t="n">
         <v>734</v>
@@ -30645,7 +30645,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.29246306419373</v>
+        <v>2.29246282577515</v>
       </c>
       <c r="H1044" t="n">
         <v>1687</v>
@@ -30674,7 +30674,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1045" t="n">
         <v>3499</v>
@@ -30703,7 +30703,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1046" t="n">
         <v>202</v>
@@ -30732,7 +30732,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H1047" t="n">
         <v>1727</v>
@@ -30761,7 +30761,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1048" t="n">
         <v>5485</v>
@@ -30790,7 +30790,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1049" t="n">
         <v>199</v>
@@ -30819,7 +30819,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1050" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H1050" t="n">
         <v>1224</v>
@@ -30848,7 +30848,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1051" t="n">
         <v>425</v>
@@ -30877,7 +30877,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1052" t="n">
         <v>1908</v>
@@ -30935,7 +30935,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.18678188323975</v>
+        <v>2.18678212165833</v>
       </c>
       <c r="H1054" t="n">
         <v>1553</v>
@@ -30964,7 +30964,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1055" t="n">
         <v>2197</v>
@@ -30993,7 +30993,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.12987685203552</v>
+        <v>2.1298770904541</v>
       </c>
       <c r="H1056" t="n">
         <v>1938</v>
@@ -31051,7 +31051,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548877716064</v>
+        <v>2.10548901557922</v>
       </c>
       <c r="H1058" t="n">
         <v>1769</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1064" t="n">
         <v>931</v>
@@ -31254,7 +31254,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1065" t="n">
         <v>2252</v>
@@ -31370,7 +31370,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1069" t="n">
         <v>3426</v>
@@ -31399,7 +31399,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.55676114559174</v>
+        <v>1.55676102638245</v>
       </c>
       <c r="H1070" t="n">
         <v>1307</v>
@@ -31428,7 +31428,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.54863166809082</v>
+        <v>1.54863178730011</v>
       </c>
       <c r="H1071" t="n">
         <v>1513</v>
@@ -31457,7 +31457,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237342834473</v>
       </c>
       <c r="H1072" t="n">
         <v>3746</v>
@@ -31486,7 +31486,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.49579131603241</v>
+        <v>1.4957914352417</v>
       </c>
       <c r="H1073" t="n">
         <v>1682</v>
@@ -31544,7 +31544,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1075" t="n">
         <v>5340</v>
@@ -31573,7 +31573,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1076" t="n">
         <v>10</v>
@@ -31631,7 +31631,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.5730197429657</v>
+        <v>1.57301986217499</v>
       </c>
       <c r="H1078" t="n">
         <v>1319</v>
@@ -31660,7 +31660,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.56082606315613</v>
+        <v>1.56082582473755</v>
       </c>
       <c r="H1079" t="n">
         <v>1845</v>
@@ -31689,7 +31689,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1080" t="n">
         <v>1096</v>
@@ -31718,7 +31718,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1081" t="n">
         <v>3195</v>
@@ -31747,7 +31747,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1082" t="n">
         <v>830</v>
@@ -31776,7 +31776,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1083" t="n">
         <v>2497</v>
@@ -31805,7 +31805,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1084" t="n">
         <v>8072</v>
@@ -31863,7 +31863,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63398957252502</v>
+        <v>1.63398969173431</v>
       </c>
       <c r="H1086" t="n">
         <v>6045</v>
@@ -31892,7 +31892,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1087" t="n">
         <v>6324</v>
@@ -31950,7 +31950,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1089" t="n">
         <v>2736</v>
@@ -32008,7 +32008,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.62179565429688</v>
+        <v>1.62179553508759</v>
       </c>
       <c r="H1091" t="n">
         <v>4180</v>
@@ -32037,7 +32037,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.63398957252502</v>
+        <v>1.63398969173431</v>
       </c>
       <c r="H1092" t="n">
         <v>531</v>
@@ -32066,7 +32066,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.58927810192108</v>
+        <v>1.58927822113037</v>
       </c>
       <c r="H1093" t="n">
         <v>1175</v>
@@ -32095,7 +32095,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.61773085594177</v>
+        <v>1.61773073673248</v>
       </c>
       <c r="H1094" t="n">
         <v>5830</v>
@@ -32124,7 +32124,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1095" t="n">
         <v>2072</v>
@@ -32153,7 +32153,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.63398957252502</v>
+        <v>1.63398969173431</v>
       </c>
       <c r="H1096" t="n">
         <v>1044</v>
@@ -32182,7 +32182,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1097" t="n">
         <v>2013</v>
@@ -32240,7 +32240,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1099" t="n">
         <v>3686</v>
@@ -32269,7 +32269,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1100" t="n">
         <v>668</v>
@@ -32298,7 +32298,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1101" t="n">
         <v>390</v>
@@ -32356,7 +32356,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1103" t="n">
         <v>1415</v>
@@ -32385,7 +32385,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1104" t="n">
         <v>934</v>
@@ -32414,7 +32414,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1105" t="n">
         <v>1244</v>
@@ -32443,7 +32443,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1106" t="n">
         <v>660</v>
@@ -32472,7 +32472,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1107" t="n">
         <v>749</v>
@@ -32501,7 +32501,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1108" t="n">
         <v>2147</v>
@@ -32530,7 +32530,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1109" t="n">
         <v>0</v>
@@ -32559,7 +32559,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1110" t="n">
         <v>1215</v>
@@ -32588,7 +32588,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1111" t="n">
         <v>125</v>
@@ -32617,7 +32617,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1112" t="n">
         <v>194</v>
@@ -32646,7 +32646,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.67463600635529</v>
+        <v>1.67463612556458</v>
       </c>
       <c r="H1113" t="n">
         <v>865</v>
@@ -32704,7 +32704,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1115" t="n">
         <v>2809</v>
@@ -32733,7 +32733,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1116" t="n">
         <v>2022</v>
@@ -32791,7 +32791,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1118" t="n">
         <v>546</v>
@@ -32849,7 +32849,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1120" t="n">
         <v>2501</v>
@@ -32878,7 +32878,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1121" t="n">
         <v>1115</v>
@@ -32936,7 +32936,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1123" t="n">
         <v>1674</v>
@@ -32965,7 +32965,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1124" t="n">
         <v>4336</v>
@@ -32994,7 +32994,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096326351166</v>
       </c>
       <c r="H1125" t="n">
         <v>10904</v>
@@ -33023,7 +33023,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1126" t="n">
         <v>735</v>
@@ -33081,7 +33081,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1128" t="n">
         <v>2449</v>
@@ -33110,7 +33110,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1129" t="n">
         <v>1066</v>
@@ -33139,7 +33139,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1130" t="n">
         <v>474</v>
@@ -33168,7 +33168,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1131" t="n">
         <v>1560</v>
@@ -33226,7 +33226,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1133" t="n">
         <v>100</v>
@@ -33255,7 +33255,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096338272095</v>
+        <v>1.82096326351166</v>
       </c>
       <c r="H1134" t="n">
         <v>1491</v>
@@ -33284,7 +33284,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1135" t="n">
         <v>289</v>
@@ -33313,7 +33313,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.81283390522003</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1136" t="n">
         <v>1910</v>
@@ -33342,7 +33342,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1137" t="n">
         <v>525</v>
@@ -33371,7 +33371,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1138" t="n">
         <v>536</v>
@@ -33400,7 +33400,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1139" t="n">
         <v>2191</v>
@@ -33429,7 +33429,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1140" t="n">
         <v>87</v>
@@ -33458,7 +33458,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1141" t="n">
         <v>161</v>
@@ -33487,7 +33487,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1142" t="n">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1143" t="n">
         <v>1762</v>
@@ -33545,7 +33545,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.78844630718231</v>
+        <v>1.78844618797302</v>
       </c>
       <c r="H1144" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.81283390522003</v>
+        <v>1.81283414363861</v>
       </c>
       <c r="H1145" t="n">
         <v>480</v>
@@ -33603,7 +33603,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470502376556</v>
+        <v>1.80470490455627</v>
       </c>
       <c r="H1146" t="n">
         <v>30</v>
@@ -33632,7 +33632,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.79657554626465</v>
+        <v>1.79657566547394</v>
       </c>
       <c r="H1147" t="n">
         <v>103</v>
@@ -33661,7 +33661,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1148" t="n">
         <v>1910</v>
@@ -33690,7 +33690,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1149" t="n">
         <v>143</v>
@@ -33748,7 +33748,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1151" t="n">
         <v>3317</v>
@@ -33777,7 +33777,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1152" t="n">
         <v>7260</v>
@@ -33806,7 +33806,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1153" t="n">
         <v>4915</v>
@@ -33835,7 +33835,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1154" t="n">
         <v>50</v>
@@ -33864,7 +33864,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1155" t="n">
         <v>151</v>
@@ -33893,7 +33893,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1156" t="n">
         <v>1638</v>
@@ -33922,7 +33922,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1157" t="n">
         <v>452</v>
@@ -33951,7 +33951,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1158" t="n">
         <v>1478</v>
@@ -33980,7 +33980,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1159" t="n">
         <v>1358</v>
@@ -34009,7 +34009,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1160" t="n">
         <v>405</v>
@@ -34038,7 +34038,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1161" t="n">
         <v>200</v>
@@ -34067,7 +34067,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1162" t="n">
         <v>185</v>
@@ -34096,7 +34096,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1163" t="n">
         <v>392</v>
@@ -34125,7 +34125,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.66650676727295</v>
+        <v>1.66650664806366</v>
       </c>
       <c r="H1164" t="n">
         <v>12</v>
@@ -34183,7 +34183,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1166" t="n">
         <v>1391</v>
@@ -34212,7 +34212,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089448451996</v>
+        <v>1.69089460372925</v>
       </c>
       <c r="H1167" t="n">
         <v>1114</v>
@@ -34241,7 +34241,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.69902396202087</v>
+        <v>1.69902384281158</v>
       </c>
       <c r="H1168" t="n">
         <v>182</v>
@@ -34270,7 +34270,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1169" t="n">
         <v>540</v>
@@ -34299,7 +34299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1170" t="n">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1171" t="n">
         <v>330</v>
@@ -34357,7 +34357,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.77218747138977</v>
+        <v>1.77218759059906</v>
       </c>
       <c r="H1172" t="n">
         <v>950</v>
@@ -34386,7 +34386,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1173" t="n">
         <v>886</v>
@@ -34415,7 +34415,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1174" t="n">
         <v>16</v>
@@ -34444,7 +34444,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.73967039585114</v>
+        <v>1.73967027664185</v>
       </c>
       <c r="H1175" t="n">
         <v>176</v>
@@ -34473,7 +34473,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.76405835151672</v>
+        <v>1.76405847072601</v>
       </c>
       <c r="H1176" t="n">
         <v>992</v>
@@ -34502,7 +34502,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1177" t="n">
         <v>402</v>
@@ -34531,7 +34531,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1178" t="n">
         <v>250</v>
@@ -34560,7 +34560,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.7803168296814</v>
+        <v>1.78031694889069</v>
       </c>
       <c r="H1179" t="n">
         <v>520</v>
@@ -34618,7 +34618,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779963493347</v>
+        <v>1.74779987335205</v>
       </c>
       <c r="H1181" t="n">
         <v>15</v>
@@ -34676,7 +34676,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.73154103755951</v>
+        <v>1.7315411567688</v>
       </c>
       <c r="H1183" t="n">
         <v>139</v>
@@ -34821,7 +34821,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.71528244018555</v>
+        <v>1.71528255939484</v>
       </c>
       <c r="H1188" t="n">
         <v>3060</v>
@@ -34850,7 +34850,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.6827654838562</v>
+        <v>1.68276536464691</v>
       </c>
       <c r="H1189" t="n">
         <v>2798</v>
@@ -34879,7 +34879,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.6827654838562</v>
+        <v>1.68276536464691</v>
       </c>
       <c r="H1190" t="n">
         <v>545</v>
@@ -34908,7 +34908,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1191" t="n">
         <v>1130</v>
@@ -34937,7 +34937,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.62586009502411</v>
+        <v>1.6258602142334</v>
       </c>
       <c r="H1192" t="n">
         <v>3300</v>
@@ -34966,7 +34966,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.61773085594177</v>
+        <v>1.61773073673248</v>
       </c>
       <c r="H1193" t="n">
         <v>105</v>
@@ -34995,7 +34995,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.63398957252502</v>
+        <v>1.63398969173431</v>
       </c>
       <c r="H1194" t="n">
         <v>630</v>
@@ -35024,7 +35024,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.60147249698639</v>
+        <v>1.6014723777771</v>
       </c>
       <c r="H1195" t="n">
         <v>486</v>
@@ -35082,7 +35082,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1197" t="n">
         <v>6595</v>
@@ -35111,7 +35111,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.60960137844086</v>
+        <v>1.60960149765015</v>
       </c>
       <c r="H1198" t="n">
         <v>201</v>
@@ -35169,7 +35169,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.61366641521454</v>
+        <v>1.61366629600525</v>
       </c>
       <c r="H1200" t="n">
         <v>1704</v>
@@ -35227,7 +35227,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58114922046661</v>
+        <v>1.58114910125732</v>
       </c>
       <c r="H1202" t="n">
         <v>782</v>
@@ -35256,7 +35256,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1203" t="n">
         <v>1145</v>
@@ -35314,7 +35314,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1205" t="n">
         <v>2215</v>
@@ -35372,7 +35372,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1207" t="n">
         <v>299</v>
@@ -35430,7 +35430,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.49579131603241</v>
+        <v>1.4957914352417</v>
       </c>
       <c r="H1209" t="n">
         <v>1093</v>
@@ -35488,7 +35488,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708418369293</v>
+        <v>1.57708430290222</v>
       </c>
       <c r="H1211" t="n">
         <v>302</v>
@@ -35604,7 +35604,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1215" t="n">
         <v>1216</v>
@@ -35720,7 +35720,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.40636909008026</v>
+        <v>1.40636897087097</v>
       </c>
       <c r="H1219" t="n">
         <v>2254</v>
@@ -35749,7 +35749,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.43482148647308</v>
+        <v>1.43482160568237</v>
       </c>
       <c r="H1220" t="n">
         <v>925</v>
@@ -35807,7 +35807,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.41449844837189</v>
+        <v>1.4144983291626</v>
       </c>
       <c r="H1222" t="n">
         <v>2154</v>
@@ -35836,7 +35836,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.36572241783142</v>
+        <v>1.36572253704071</v>
       </c>
       <c r="H1223" t="n">
         <v>2886</v>
@@ -35865,7 +35865,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.3332052230835</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1224" t="n">
         <v>2739</v>
@@ -35894,7 +35894,7 @@
         <v>17</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.38198125362396</v>
+        <v>1.38198113441467</v>
       </c>
       <c r="H1225" t="n">
         <v>2336</v>
@@ -35952,7 +35952,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.3332052230835</v>
+        <v>1.33320534229279</v>
       </c>
       <c r="H1227" t="n">
         <v>4118</v>
@@ -36271,7 +36271,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.41449844837189</v>
+        <v>1.4144983291626</v>
       </c>
       <c r="H1238" t="n">
         <v>1249</v>
@@ -36300,7 +36300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.38604581356049</v>
+        <v>1.3860456943512</v>
       </c>
       <c r="H1239" t="n">
         <v>2206</v>
@@ -36358,7 +36358,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.3901104927063</v>
+        <v>1.39011061191559</v>
       </c>
       <c r="H1241" t="n">
         <v>2655</v>
@@ -36503,7 +36503,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.4673388004303</v>
+        <v>1.46733868122101</v>
       </c>
       <c r="H1246" t="n">
         <v>4901</v>
@@ -36648,7 +36648,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.56082606315613</v>
+        <v>1.56082582473755</v>
       </c>
       <c r="H1251" t="n">
         <v>2264</v>
@@ -36764,7 +36764,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.49172675609589</v>
+        <v>1.49172687530518</v>
       </c>
       <c r="H1255" t="n">
         <v>3603</v>
@@ -36851,7 +36851,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1258" t="n">
         <v>2500</v>
@@ -36938,7 +36938,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237318992615</v>
+        <v>1.53237342834473</v>
       </c>
       <c r="H1261" t="n">
         <v>4222</v>
@@ -37054,7 +37054,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.5242440700531</v>
+        <v>1.52424395084381</v>
       </c>
       <c r="H1265" t="n">
         <v>1723</v>
@@ -37141,7 +37141,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.50798523426056</v>
+        <v>1.50798535346985</v>
       </c>
       <c r="H1268" t="n">
         <v>960</v>
@@ -37286,7 +37286,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1273" t="n">
         <v>2790</v>
@@ -37344,7 +37344,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.5689549446106</v>
+        <v>1.56895506381989</v>
       </c>
       <c r="H1275" t="n">
         <v>5078</v>
@@ -37779,7 +37779,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.48359751701355</v>
+        <v>1.48359739780426</v>
       </c>
       <c r="H1290" t="n">
         <v>593</v>
@@ -37924,7 +37924,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1295" t="n">
         <v>21427</v>
@@ -37953,7 +37953,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1296" t="n">
         <v>31317</v>
@@ -37982,7 +37982,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1297" t="n">
         <v>34162</v>
@@ -38040,7 +38040,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375593185425</v>
+        <v>2.37375617027283</v>
       </c>
       <c r="H1299" t="n">
         <v>11185</v>
@@ -38098,7 +38098,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.32498025894165</v>
+        <v>2.32498002052307</v>
       </c>
       <c r="H1301" t="n">
         <v>6160</v>
@@ -38127,7 +38127,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1302" t="n">
         <v>4831</v>
@@ -38156,7 +38156,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.357497215271</v>
+        <v>2.35749745368958</v>
       </c>
       <c r="H1303" t="n">
         <v>3636</v>
@@ -38185,7 +38185,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1304" t="n">
         <v>3101</v>
@@ -38214,7 +38214,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.34123849868774</v>
+        <v>2.34123873710632</v>
       </c>
       <c r="H1305" t="n">
         <v>1089</v>
@@ -38243,7 +38243,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.3331093788147</v>
+        <v>2.33310961723328</v>
       </c>
       <c r="H1306" t="n">
         <v>9266</v>
@@ -38272,7 +38272,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1307" t="n">
         <v>2734</v>
@@ -38301,7 +38301,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.30872130393982</v>
+        <v>2.3087215423584</v>
       </c>
       <c r="H1308" t="n">
         <v>12016</v>
@@ -38330,7 +38330,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1309" t="n">
         <v>5914</v>
@@ -38359,7 +38359,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1310" t="n">
         <v>2703</v>
@@ -38388,7 +38388,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.26807475090027</v>
+        <v>2.26807498931885</v>
       </c>
       <c r="H1311" t="n">
         <v>801</v>
@@ -38417,7 +38417,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1312" t="n">
         <v>2265</v>
@@ -38446,7 +38446,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.30059194564819</v>
+        <v>2.30059218406677</v>
       </c>
       <c r="H1313" t="n">
         <v>723</v>
@@ -38475,7 +38475,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1314" t="n">
         <v>802</v>
@@ -38504,7 +38504,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1315" t="n">
         <v>2691</v>
@@ -38533,7 +38533,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.27620434761047</v>
+        <v>2.27620410919189</v>
       </c>
       <c r="H1316" t="n">
         <v>902</v>
@@ -38562,7 +38562,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.25994539260864</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1317" t="n">
         <v>1038</v>
@@ -38591,7 +38591,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.25994539260864</v>
+        <v>2.25994563102722</v>
       </c>
       <c r="H1318" t="n">
         <v>245</v>
@@ -38620,7 +38620,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.24368715286255</v>
+        <v>2.24368691444397</v>
       </c>
       <c r="H1319" t="n">
         <v>910</v>
@@ -38649,7 +38649,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.17865252494812</v>
+        <v>2.1786527633667</v>
       </c>
       <c r="H1320" t="n">
         <v>8330</v>
@@ -38707,7 +38707,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.12987685203552</v>
+        <v>2.1298770904541</v>
       </c>
       <c r="H1322" t="n">
         <v>15712</v>
@@ -38794,7 +38794,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.07297158241272</v>
+        <v>2.0729718208313</v>
       </c>
       <c r="H1325" t="n">
         <v>1429</v>
@@ -38823,7 +38823,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671286582947</v>
+        <v>2.05671310424805</v>
       </c>
       <c r="H1326" t="n">
         <v>2194</v>
@@ -38939,7 +38939,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1330" t="n">
         <v>2995</v>
@@ -38997,7 +38997,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1332" t="n">
         <v>261</v>
@@ -39026,7 +39026,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800597190857</v>
+        <v>2.13800621032715</v>
       </c>
       <c r="H1333" t="n">
         <v>364</v>
@@ -39055,7 +39055,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.24368715286255</v>
+        <v>2.24368691444397</v>
       </c>
       <c r="H1334" t="n">
         <v>663</v>
@@ -39142,7 +39142,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.23555755615234</v>
+        <v>2.23555779457092</v>
       </c>
       <c r="H1337" t="n">
         <v>4952</v>
@@ -39316,7 +39316,7 @@
         <v>27</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1343" t="n">
         <v>1560</v>
@@ -39577,7 +39577,7 @@
         <v>27</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1352" t="n">
         <v>626</v>
@@ -39664,7 +39664,7 @@
         <v>27</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1355" t="n">
         <v>15</v>
@@ -40360,7 +40360,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1379" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1379" t="n">
         <v>4492</v>
@@ -40389,7 +40389,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1380" t="n">
         <v>3109</v>
@@ -40418,7 +40418,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1381" t="n">
         <v>14062</v>
@@ -40447,7 +40447,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1382" t="n">
         <v>4336</v>
@@ -40563,7 +40563,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1386" t="n">
         <v>12870</v>
@@ -40592,7 +40592,7 @@
         <v>30</v>
       </c>
       <c r="G1387" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1387" t="n">
         <v>3844</v>
@@ -40621,7 +40621,7 @@
         <v>30</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1388" t="n">
         <v>3485</v>
@@ -40650,7 +40650,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1389" t="n">
         <v>1513</v>
@@ -40679,7 +40679,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.49274206161499</v>
+        <v>2.49274230003357</v>
       </c>
       <c r="H1390" t="n">
         <v>11</v>
@@ -40708,7 +40708,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1391" t="n">
         <v>1103</v>
@@ -40737,7 +40737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1392" t="n">
         <v>2136</v>
@@ -40766,7 +40766,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1393" t="n">
         <v>3074</v>
@@ -40824,7 +40824,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1395" t="n">
         <v>3834</v>
@@ -40911,7 +40911,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.39336371421814</v>
+        <v>2.39336347579956</v>
       </c>
       <c r="H1398" t="n">
         <v>1418</v>
@@ -40940,7 +40940,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1399" t="n">
         <v>110</v>
@@ -41027,7 +41027,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1402" t="n">
         <v>1523</v>
@@ -41085,7 +41085,7 @@
         <v>30</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1404" t="n">
         <v>1557</v>
@@ -41259,7 +41259,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1410" t="n">
         <v>603</v>
@@ -41578,7 +41578,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1421" t="n">
         <v>2630</v>
@@ -41665,7 +41665,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1424" t="n">
         <v>784</v>
@@ -41694,7 +41694,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1425" t="n">
         <v>1447</v>
@@ -41926,7 +41926,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1433" t="n">
         <v>2277</v>
@@ -42071,7 +42071,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1438" t="n">
         <v>325</v>
@@ -42129,7 +42129,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1440" t="n">
         <v>160</v>
@@ -42245,7 +42245,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1444" t="n">
         <v>1866</v>
@@ -42274,7 +42274,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1445" t="n">
         <v>1333</v>
@@ -42303,7 +42303,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1446" t="n">
         <v>2352</v>
@@ -42564,7 +42564,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1455" t="n">
         <v>1776</v>
@@ -42941,7 +42941,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.32711148262024</v>
+        <v>2.32711124420166</v>
       </c>
       <c r="H1468" t="n">
         <v>141</v>
@@ -43144,7 +43144,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1475" t="n">
         <v>691</v>
@@ -43173,7 +43173,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.35195589065552</v>
+        <v>2.3519561290741</v>
       </c>
       <c r="H1476" t="n">
         <v>1400</v>
@@ -43202,7 +43202,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.37680077552795</v>
+        <v>2.37680053710938</v>
       </c>
       <c r="H1477" t="n">
         <v>169</v>
@@ -43231,7 +43231,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.36851906776428</v>
+        <v>2.36851930618286</v>
       </c>
       <c r="H1478" t="n">
         <v>890</v>
@@ -43521,7 +43521,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1488" t="n">
         <v>110</v>
@@ -43579,7 +43579,7 @@
         <v>27.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1490" t="n">
         <v>3333</v>
@@ -43869,7 +43869,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1500" t="n">
         <v>252</v>
@@ -43898,7 +43898,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -44565,7 +44565,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1524" t="n">
         <v>420</v>
@@ -44623,7 +44623,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1526" t="n">
         <v>311</v>
@@ -44652,7 +44652,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1527" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.31054854393005</v>
+        <v>2.31054830551147</v>
       </c>
       <c r="H1528" t="n">
         <v>137</v>
@@ -44739,7 +44739,7 @@
         <v>27.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1530" t="n">
         <v>242</v>
@@ -44826,7 +44826,7 @@
         <v>27.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1533" t="n">
         <v>200</v>
@@ -44855,7 +44855,7 @@
         <v>27.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1534" t="n">
         <v>0</v>
@@ -44884,7 +44884,7 @@
         <v>27.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1535" t="n">
         <v>300</v>
@@ -44913,7 +44913,7 @@
         <v>27.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1536" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>27</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1540" t="n">
         <v>140</v>
@@ -45087,7 +45087,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.18632531166077</v>
+        <v>2.18632507324219</v>
       </c>
       <c r="H1542" t="n">
         <v>511</v>
@@ -45116,7 +45116,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.26085901260376</v>
+        <v>2.26085925102234</v>
       </c>
       <c r="H1543" t="n">
         <v>516</v>
@@ -45145,7 +45145,7 @@
         <v>27</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1544" t="n">
         <v>135</v>
@@ -45464,7 +45464,7 @@
         <v>27.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1555" t="n">
         <v>107</v>
@@ -45493,7 +45493,7 @@
         <v>27.5</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1556" t="n">
         <v>639</v>
@@ -45551,7 +45551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.27742218971252</v>
+        <v>2.2774224281311</v>
       </c>
       <c r="H1558" t="n">
         <v>1582</v>
@@ -45638,7 +45638,7 @@
         <v>27</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1561" t="n">
         <v>1549</v>
@@ -45667,7 +45667,7 @@
         <v>27</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.23601460456848</v>
+        <v>2.2360143661499</v>
       </c>
       <c r="H1562" t="n">
         <v>1015</v>
@@ -45754,7 +45754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.418208360672</v>
+        <v>2.41820859909058</v>
       </c>
       <c r="H1565" t="n">
         <v>2831</v>
@@ -45899,7 +45899,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.4761791229248</v>
+        <v>2.47617888450623</v>
       </c>
       <c r="H1570" t="n">
         <v>3995</v>
@@ -45986,7 +45986,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.46789741516113</v>
+        <v>2.46789717674255</v>
       </c>
       <c r="H1573" t="n">
         <v>685</v>
@@ -46015,7 +46015,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102353096008</v>
+        <v>2.50102376937866</v>
       </c>
       <c r="H1574" t="n">
         <v>6269</v>
@@ -46044,7 +46044,7 @@
         <v>30</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.48446035385132</v>
+        <v>2.4844605922699</v>
       </c>
       <c r="H1575" t="n">
         <v>632</v>
@@ -46073,7 +46073,7 @@
         <v>30.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1576" t="n">
         <v>2316</v>
@@ -46102,7 +46102,7 @@
         <v>30.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.52586841583252</v>
+        <v>2.52586817741394</v>
       </c>
       <c r="H1577" t="n">
         <v>2195</v>
@@ -46189,7 +46189,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.71634364128113</v>
+        <v>2.71634340286255</v>
       </c>
       <c r="H1580" t="n">
         <v>8590</v>
@@ -46247,7 +46247,7 @@
         <v>34</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.81572222709656</v>
+        <v>2.81572198867798</v>
       </c>
       <c r="H1582" t="n">
         <v>5135</v>
@@ -46392,7 +46392,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.24636220932007</v>
+        <v>3.24636197090149</v>
       </c>
       <c r="H1587" t="n">
         <v>14504</v>
@@ -46421,7 +46421,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1588" t="n">
         <v>15352</v>
@@ -46479,7 +46479,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.2380805015564</v>
+        <v>3.23808002471924</v>
       </c>
       <c r="H1590" t="n">
         <v>7873</v>
@@ -46537,7 +46537,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1592" t="n">
         <v>19325</v>
@@ -46595,7 +46595,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1594" t="n">
         <v>22091</v>
@@ -46624,7 +46624,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.17182779312134</v>
+        <v>3.17182803153992</v>
       </c>
       <c r="H1595" t="n">
         <v>58723</v>
@@ -46653,7 +46653,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.21323561668396</v>
+        <v>3.21323585510254</v>
       </c>
       <c r="H1596" t="n">
         <v>2947</v>
@@ -46885,7 +46885,7 @@
         <v>37.5</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1604" t="n">
         <v>3473</v>
@@ -46943,7 +46943,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1606" t="n">
         <v>701</v>
@@ -46972,7 +46972,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1607" t="n">
         <v>5882</v>
@@ -47001,7 +47001,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1608" t="n">
         <v>869</v>
@@ -47030,7 +47030,7 @@
         <v>37.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1609" t="n">
         <v>201</v>
@@ -47088,7 +47088,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1611" t="n">
         <v>2250</v>
@@ -47117,7 +47117,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1612" t="n">
         <v>150</v>
@@ -47175,7 +47175,7 @@
         <v>37</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1614" t="n">
         <v>1853</v>
@@ -47204,7 +47204,7 @@
         <v>37</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1615" t="n">
         <v>1740</v>
@@ -47233,7 +47233,7 @@
         <v>37.5</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1616" t="n">
         <v>221</v>
@@ -47262,7 +47262,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1617" t="n">
         <v>1595</v>
@@ -47291,7 +47291,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1618" t="n">
         <v>2357</v>
@@ -47436,7 +47436,7 @@
         <v>37.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1623" t="n">
         <v>4769</v>
@@ -47552,7 +47552,7 @@
         <v>37</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1627" t="n">
         <v>500</v>
@@ -47726,7 +47726,7 @@
         <v>37</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1633" t="n">
         <v>593</v>
@@ -47784,7 +47784,7 @@
         <v>37.5</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1635" t="n">
         <v>1882</v>
@@ -47813,7 +47813,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1636" t="n">
         <v>365</v>
@@ -47842,7 +47842,7 @@
         <v>37.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1637" t="n">
         <v>2785</v>
@@ -47871,7 +47871,7 @@
         <v>37.5</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1638" t="n">
         <v>2270</v>
@@ -47900,7 +47900,7 @@
         <v>37.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1639" t="n">
         <v>2725</v>
@@ -48045,7 +48045,7 @@
         <v>37.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1644" t="n">
         <v>4061</v>
@@ -48074,7 +48074,7 @@
         <v>37.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1645" t="n">
         <v>8289</v>
@@ -48103,7 +48103,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1646" t="n">
         <v>569</v>
@@ -48161,7 +48161,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1648" t="n">
         <v>13</v>
@@ -48190,7 +48190,7 @@
         <v>37.5</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1649" t="n">
         <v>642</v>
@@ -48335,7 +48335,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1654" t="n">
         <v>513</v>
@@ -48422,7 +48422,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1657" t="n">
         <v>692</v>
@@ -48451,7 +48451,7 @@
         <v>37.5</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1658" t="n">
         <v>1340</v>
@@ -48480,7 +48480,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1659" t="n">
         <v>408</v>
@@ -48538,7 +48538,7 @@
         <v>37.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1661" t="n">
         <v>277</v>
@@ -48596,7 +48596,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1663" t="n">
         <v>3180</v>
@@ -48799,7 +48799,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1670" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1670" t="n">
         <v>184</v>
@@ -49060,7 +49060,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1679" t="n">
         <v>653</v>
@@ -49089,7 +49089,7 @@
         <v>37</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1680" t="n">
         <v>61</v>
@@ -49118,7 +49118,7 @@
         <v>37</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1681" t="n">
         <v>25</v>
@@ -49292,7 +49292,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1687" t="n">
         <v>76</v>
@@ -49321,7 +49321,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1688" t="n">
         <v>0</v>
@@ -49408,7 +49408,7 @@
         <v>37.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1691" t="n">
         <v>198</v>
@@ -49495,7 +49495,7 @@
         <v>37</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1694" t="n">
         <v>3210</v>
@@ -49524,7 +49524,7 @@
         <v>37</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1695" t="n">
         <v>46</v>
@@ -49553,7 +49553,7 @@
         <v>37</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1696" t="n">
         <v>3</v>
@@ -49727,7 +49727,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1702" t="n">
         <v>142</v>
@@ -49756,7 +49756,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1703" t="n">
         <v>0</v>
@@ -49785,7 +49785,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1704" t="n">
         <v>395</v>
@@ -49843,7 +49843,7 @@
         <v>37</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1706" t="n">
         <v>63</v>
@@ -49901,7 +49901,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1708" t="n">
         <v>796</v>
@@ -49959,7 +49959,7 @@
         <v>37</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1710" t="n">
         <v>2446</v>
@@ -49988,7 +49988,7 @@
         <v>37</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50249,7 +50249,7 @@
         <v>37</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1720" t="n">
         <v>1410</v>
@@ -50336,7 +50336,7 @@
         <v>37</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1723" t="n">
         <v>2800</v>
@@ -50510,7 +50510,7 @@
         <v>37</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1729" t="n">
         <v>7186</v>
@@ -50568,7 +50568,7 @@
         <v>37.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1731" t="n">
         <v>10</v>
@@ -50597,7 +50597,7 @@
         <v>37.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1732" t="n">
         <v>150</v>
@@ -50626,7 +50626,7 @@
         <v>37</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1733" t="n">
         <v>3284</v>
@@ -50655,7 +50655,7 @@
         <v>37</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1734" t="n">
         <v>886</v>
@@ -50684,7 +50684,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1735" t="n">
         <v>1334</v>
@@ -50713,7 +50713,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1736" t="n">
         <v>6368</v>
@@ -50742,7 +50742,7 @@
         <v>37</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1737" t="n">
         <v>860</v>
@@ -50771,7 +50771,7 @@
         <v>37.5</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1738" t="n">
         <v>492</v>
@@ -50800,7 +50800,7 @@
         <v>37</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.06416797637939</v>
+        <v>3.06416821479797</v>
       </c>
       <c r="H1739" t="n">
         <v>958</v>
@@ -50829,7 +50829,7 @@
         <v>37.5</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1740" t="n">
         <v>4</v>
@@ -50887,7 +50887,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1742" t="n">
         <v>1413</v>
@@ -50916,7 +50916,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1743" t="n">
         <v>71451</v>
@@ -50945,7 +50945,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1744" t="n">
         <v>53786</v>
@@ -50974,7 +50974,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1745" t="n">
         <v>4978</v>
@@ -51003,7 +51003,7 @@
         <v>37.5</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1746" t="n">
         <v>21294</v>
@@ -51032,7 +51032,7 @@
         <v>37.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1747" t="n">
         <v>14353</v>
@@ -51061,7 +51061,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244920730591</v>
+        <v>3.07244968414307</v>
       </c>
       <c r="H1748" t="n">
         <v>4653</v>
@@ -51090,7 +51090,7 @@
         <v>37.5</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1749" t="n">
         <v>20045</v>
@@ -51119,7 +51119,7 @@
         <v>37.5</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1750" t="n">
         <v>29641</v>
@@ -51148,7 +51148,7 @@
         <v>37.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1751" t="n">
         <v>15953</v>
@@ -51177,7 +51177,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.08901286125183</v>
+        <v>3.08901262283325</v>
       </c>
       <c r="H1752" t="n">
         <v>4145</v>
@@ -51264,7 +51264,7 @@
         <v>37.5</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.1055760383606</v>
+        <v>3.10557579994202</v>
       </c>
       <c r="H1755" t="n">
         <v>2128</v>
@@ -51409,7 +51409,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1760" t="n">
         <v>8943</v>
@@ -51467,7 +51467,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1762" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1762" t="n">
         <v>17040</v>
@@ -51496,7 +51496,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.11385703086853</v>
+        <v>3.11385726928711</v>
       </c>
       <c r="H1763" t="n">
         <v>11932</v>
@@ -51525,7 +51525,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.15526461601257</v>
+        <v>3.15526485443115</v>
       </c>
       <c r="H1764" t="n">
         <v>6338</v>
@@ -51554,7 +51554,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.1221387386322</v>
+        <v>3.12213897705078</v>
       </c>
       <c r="H1765" t="n">
         <v>11888</v>
@@ -51583,7 +51583,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.13870191574097</v>
+        <v>3.13870215415955</v>
       </c>
       <c r="H1766" t="n">
         <v>9167</v>
@@ -51612,7 +51612,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.20495414733887</v>
+        <v>3.20495438575745</v>
       </c>
       <c r="H1767" t="n">
         <v>15127</v>
@@ -51670,7 +51670,7 @@
         <v>39.5</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1769" t="n">
         <v>2890</v>
@@ -51699,7 +51699,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.25464367866516</v>
+        <v>3.254643201828</v>
       </c>
       <c r="H1770" t="n">
         <v>4370</v>
@@ -51786,7 +51786,7 @@
         <v>39.5</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.27120661735535</v>
+        <v>3.27120637893677</v>
       </c>
       <c r="H1773" t="n">
         <v>44802</v>
@@ -80154,6 +80154,35 @@
         <v>45</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>278</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544656276703</v>
+        <v>1.24544644355774</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -485,7 +485,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H4" t="n">
         <v>158</v>
@@ -572,7 +572,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22185301780701</v>
+        <v>1.2218531370163</v>
       </c>
       <c r="H7" t="n">
         <v>1052</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470367908478</v>
+        <v>1.21470355987549</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -630,7 +630,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615229129791</v>
       </c>
       <c r="H9" t="n">
         <v>8746</v>
@@ -659,7 +659,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G10" t="n">
-        <v>1.21327352523804</v>
+        <v>1.21327376365662</v>
       </c>
       <c r="H10" t="n">
         <v>4107</v>
@@ -688,7 +688,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683920383453</v>
+        <v>1.20683896541595</v>
       </c>
       <c r="H11" t="n">
         <v>9368</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2011194229126</v>
+        <v>1.20111930370331</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -804,7 +804,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1946849822998</v>
+        <v>1.19468486309052</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -833,7 +833,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25688564777374</v>
+        <v>1.25688576698303</v>
       </c>
       <c r="H16" t="n">
         <v>6127</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -891,7 +891,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G18" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615229129791</v>
       </c>
       <c r="H18" t="n">
         <v>605</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.24687659740448</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.24687659740448</v>
+        <v>1.2468763589859</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -1007,7 +1007,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475024223328</v>
+        <v>1.26475036144257</v>
       </c>
       <c r="H22" t="n">
         <v>1772</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470367908478</v>
+        <v>1.21470355987549</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1239,7 +1239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396996498108</v>
+        <v>1.19396984577179</v>
       </c>
       <c r="H30" t="n">
         <v>419</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685766220093</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1471,7 +1471,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25903058052063</v>
+        <v>1.25903069972992</v>
       </c>
       <c r="H38" t="n">
         <v>6392</v>
@@ -1529,7 +1529,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G40" t="n">
-        <v>1.21684849262238</v>
+        <v>1.21684837341309</v>
       </c>
       <c r="H40" t="n">
         <v>6016</v>
@@ -1558,7 +1558,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G41" t="n">
-        <v>1.22828769683838</v>
+        <v>1.22828757762909</v>
       </c>
       <c r="H41" t="n">
         <v>573</v>
@@ -1645,7 +1645,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330174922943</v>
+        <v>1.24330163002014</v>
       </c>
       <c r="H44" t="n">
         <v>139</v>
@@ -1703,7 +1703,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G46" t="n">
-        <v>1.27404463291168</v>
+        <v>1.27404451370239</v>
       </c>
       <c r="H46" t="n">
         <v>3010</v>
@@ -2080,7 +2080,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G59" t="n">
-        <v>1.25545597076416</v>
+        <v>1.25545573234558</v>
       </c>
       <c r="H59" t="n">
         <v>2269</v>
@@ -2167,7 +2167,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830603599548</v>
+        <v>1.24830615520477</v>
       </c>
       <c r="H62" t="n">
         <v>745</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045108795166</v>
+        <v>1.25045120716095</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685790061951</v>
+        <v>1.22685766220093</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2370,7 +2370,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G69" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H69" t="n">
         <v>538</v>
@@ -2399,7 +2399,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.23472237586975</v>
+        <v>1.23472225666046</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400723934174</v>
+        <v>1.23400735855103</v>
       </c>
       <c r="H71" t="n">
         <v>6242</v>
@@ -2486,7 +2486,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G73" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615229129791</v>
       </c>
       <c r="H73" t="n">
         <v>1010</v>
@@ -2515,7 +2515,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G74" t="n">
-        <v>1.23615205287933</v>
+        <v>1.23615229129791</v>
       </c>
       <c r="H74" t="n">
         <v>1039</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225377082825</v>
+        <v>1.25225365161896</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2602,7 +2602,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26835513114929</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H77" t="n">
         <v>1512</v>
@@ -2631,7 +2631,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G78" t="n">
-        <v>1.26835513114929</v>
+        <v>1.26835501194</v>
       </c>
       <c r="H78" t="n">
         <v>2507</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2805,7 +2805,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>1.26323187351227</v>
+        <v>1.26323199272156</v>
       </c>
       <c r="H84" t="n">
         <v>220</v>
@@ -2834,7 +2834,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G85" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H85" t="n">
         <v>149</v>
@@ -2863,7 +2863,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G86" t="n">
-        <v>1.26323187351227</v>
+        <v>1.26323199272156</v>
       </c>
       <c r="H86" t="n">
         <v>105</v>
@@ -2892,7 +2892,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G87" t="n">
-        <v>1.26689124107361</v>
+        <v>1.2668913602829</v>
       </c>
       <c r="H87" t="n">
         <v>1058</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -2950,7 +2950,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>1.28445649147034</v>
+        <v>1.28445637226105</v>
       </c>
       <c r="H89" t="n">
         <v>1506</v>
@@ -2979,7 +2979,7 @@
         <v>17.5</v>
       </c>
       <c r="G90" t="n">
-        <v>1.28079688549042</v>
+        <v>1.28079700469971</v>
       </c>
       <c r="H90" t="n">
         <v>217</v>
@@ -3095,7 +3095,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>1.27347815036774</v>
+        <v>1.27347826957703</v>
       </c>
       <c r="H94" t="n">
         <v>370</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494215965271</v>
+        <v>1.27494192123413</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3182,7 +3182,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H97" t="n">
         <v>1320</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28811585903168</v>
+        <v>1.28811597824097</v>
       </c>
       <c r="H99" t="n">
         <v>10</v>
@@ -3269,7 +3269,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>1.28738403320312</v>
+        <v>1.28738415241241</v>
       </c>
       <c r="H100" t="n">
         <v>70</v>
@@ -3356,7 +3356,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G103" t="n">
-        <v>1.28299283981323</v>
+        <v>1.28299272060394</v>
       </c>
       <c r="H103" t="n">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G108" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H108" t="n">
         <v>3785</v>
@@ -3530,7 +3530,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G109" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H109" t="n">
         <v>12</v>
@@ -3559,7 +3559,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G110" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H113" t="n">
         <v>1458</v>
@@ -3675,7 +3675,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H114" t="n">
         <v>1307</v>
@@ -3704,7 +3704,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H115" t="n">
         <v>1050</v>
@@ -3733,7 +3733,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H116" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663760185242</v>
+        <v>1.22663772106171</v>
       </c>
       <c r="H117" t="n">
         <v>120</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -3907,7 +3907,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>1.1783332824707</v>
+        <v>1.17833316326141</v>
       </c>
       <c r="H122" t="n">
         <v>4621</v>
@@ -3936,7 +3936,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18784773349762</v>
+        <v>1.18784785270691</v>
       </c>
       <c r="H123" t="n">
         <v>1361</v>
@@ -3965,7 +3965,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G124" t="n">
-        <v>1.16955077648163</v>
+        <v>1.16955053806305</v>
       </c>
       <c r="H124" t="n">
         <v>4411</v>
@@ -4168,7 +4168,7 @@
         <v>16.25</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18931150436401</v>
+        <v>1.1893116235733</v>
       </c>
       <c r="H131" t="n">
         <v>1295</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4313,7 +4313,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224628925323</v>
       </c>
       <c r="H136" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>1.22224640846252</v>
+        <v>1.22224628925323</v>
       </c>
       <c r="H139" t="n">
         <v>451</v>
@@ -4429,7 +4429,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H140" t="n">
         <v>730</v>
@@ -4458,7 +4458,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2434709072113</v>
+        <v>1.24347102642059</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>1.23834788799286</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H145" t="n">
         <v>265</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4632,7 +4632,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G147" t="n">
-        <v>1.23542022705078</v>
+        <v>1.23542010784149</v>
       </c>
       <c r="H147" t="n">
         <v>2025</v>
@@ -4661,7 +4661,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23834788799286</v>
+        <v>1.23834776878357</v>
       </c>
       <c r="H148" t="n">
         <v>20</v>
@@ -4748,7 +4748,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.2310289144516</v>
+        <v>1.23102879524231</v>
       </c>
       <c r="H151" t="n">
         <v>1211</v>
@@ -4777,7 +4777,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.2310289144516</v>
+        <v>1.23102879524231</v>
       </c>
       <c r="H152" t="n">
         <v>20</v>
@@ -4806,7 +4806,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>1.19736230373383</v>
+        <v>1.19736242294312</v>
       </c>
       <c r="H153" t="n">
         <v>1720</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.2171231508255</v>
+        <v>1.21712327003479</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -4893,7 +4893,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297835350037</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H156" t="n">
         <v>410</v>
@@ -4922,7 +4922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H157" t="n">
         <v>390</v>
@@ -4980,7 +4980,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883331775665</v>
+        <v>1.22883343696594</v>
       </c>
       <c r="H159" t="n">
         <v>486</v>
@@ -5009,7 +5009,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468840122223</v>
+        <v>1.23468852043152</v>
       </c>
       <c r="H160" t="n">
         <v>366</v>
@@ -5038,7 +5038,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H161" t="n">
         <v>10275</v>
@@ -5154,7 +5154,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G165" t="n">
-        <v>1.28518843650818</v>
+        <v>1.28518831729889</v>
       </c>
       <c r="H165" t="n">
         <v>430</v>
@@ -5183,7 +5183,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G166" t="n">
-        <v>1.30714499950409</v>
+        <v>1.3071448802948</v>
       </c>
       <c r="H166" t="n">
         <v>3048</v>
@@ -5212,7 +5212,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H167" t="n">
         <v>1738</v>
@@ -5241,7 +5241,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>1.32324647903442</v>
+        <v>1.32324624061584</v>
       </c>
       <c r="H168" t="n">
         <v>18315</v>
@@ -5270,7 +5270,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G169" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H169" t="n">
         <v>3060</v>
@@ -5415,7 +5415,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G174" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H174" t="n">
         <v>5572</v>
@@ -5444,7 +5444,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.30275356769562</v>
+        <v>1.30275344848633</v>
       </c>
       <c r="H175" t="n">
         <v>4841</v>
@@ -5473,7 +5473,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>1.29982614517212</v>
+        <v>1.29982602596283</v>
       </c>
       <c r="H176" t="n">
         <v>1808</v>
@@ -5502,7 +5502,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G177" t="n">
-        <v>1.28884780406952</v>
+        <v>1.28884792327881</v>
       </c>
       <c r="H177" t="n">
         <v>3982</v>
@@ -5560,7 +5560,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H179" t="n">
         <v>1599</v>
@@ -5589,7 +5589,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>1.30275356769562</v>
+        <v>1.30275344848633</v>
       </c>
       <c r="H180" t="n">
         <v>600</v>
@@ -5618,7 +5618,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>1.30275356769562</v>
+        <v>1.30275344848633</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>1.30275356769562</v>
+        <v>1.30275344848633</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>1.30275356769562</v>
+        <v>1.30275344848633</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G184" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H184" t="n">
         <v>2500</v>
@@ -5734,7 +5734,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G185" t="n">
-        <v>1.30055797100067</v>
+        <v>1.30055809020996</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>1.29836237430573</v>
+        <v>1.29836213588715</v>
       </c>
       <c r="H186" t="n">
         <v>4389</v>
@@ -5821,7 +5821,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>1.29763031005859</v>
+        <v>1.29763042926788</v>
       </c>
       <c r="H188" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G189" t="n">
-        <v>1.29250729084015</v>
+        <v>1.29250717163086</v>
       </c>
       <c r="H189" t="n">
         <v>625</v>
@@ -5879,7 +5879,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G190" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H190" t="n">
         <v>135</v>
@@ -5908,7 +5908,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G191" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H191" t="n">
         <v>80</v>
@@ -5937,7 +5937,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G192" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H192" t="n">
         <v>81</v>
@@ -5966,7 +5966,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568099021912</v>
       </c>
       <c r="H193" t="n">
         <v>4252</v>
@@ -6053,7 +6053,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26762318611145</v>
+        <v>1.26762306690216</v>
       </c>
       <c r="H196" t="n">
         <v>4114</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.2478621006012</v>
+        <v>1.24786233901978</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6227,7 +6227,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H202" t="n">
         <v>22671</v>
@@ -6285,7 +6285,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H204" t="n">
         <v>3493</v>
@@ -6314,7 +6314,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H205" t="n">
         <v>7291</v>
@@ -6372,7 +6372,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H207" t="n">
         <v>6005</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="G208" t="n">
-        <v>1.24420273303986</v>
+        <v>1.24420285224915</v>
       </c>
       <c r="H208" t="n">
         <v>6264</v>
@@ -6430,7 +6430,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="n">
-        <v>1.23615193367004</v>
+        <v>1.23615205287933</v>
       </c>
       <c r="H209" t="n">
         <v>5810</v>
@@ -6459,7 +6459,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="n">
-        <v>1.23688387870789</v>
+        <v>1.23688399791718</v>
       </c>
       <c r="H210" t="n">
         <v>6361</v>
@@ -6488,7 +6488,7 @@
         <v>17</v>
       </c>
       <c r="G211" t="n">
-        <v>1.24420273303986</v>
+        <v>1.24420285224915</v>
       </c>
       <c r="H211" t="n">
         <v>1424</v>
@@ -6517,7 +6517,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="n">
-        <v>1.24200713634491</v>
+        <v>1.2420072555542</v>
       </c>
       <c r="H212" t="n">
         <v>21105</v>
@@ -6575,7 +6575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005805492401</v>
+        <v>1.25005793571472</v>
       </c>
       <c r="H214" t="n">
         <v>3399</v>
@@ -6633,7 +6633,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H216" t="n">
         <v>6370</v>
@@ -6662,7 +6662,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H217" t="n">
         <v>3330</v>
@@ -6691,7 +6691,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297835350037</v>
+        <v>1.22297823429108</v>
       </c>
       <c r="H218" t="n">
         <v>9836</v>
@@ -6720,7 +6720,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>1.24054348468781</v>
+        <v>1.24054360389709</v>
       </c>
       <c r="H219" t="n">
         <v>20</v>
@@ -6778,7 +6778,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H221" t="n">
         <v>2500</v>
@@ -6807,7 +6807,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H222" t="n">
         <v>2781</v>
@@ -6836,7 +6836,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127531051636</v>
+        <v>1.24127519130707</v>
       </c>
       <c r="H223" t="n">
         <v>275</v>
@@ -6865,7 +6865,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H224" t="n">
         <v>2881</v>
@@ -6894,7 +6894,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H225" t="n">
         <v>13996</v>
@@ -6923,7 +6923,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H226" t="n">
         <v>2165</v>
@@ -6952,7 +6952,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H227" t="n">
         <v>1452</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126794815063</v>
+        <v>1.21126818656921</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7068,7 +7068,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>1.23322451114655</v>
+        <v>1.23322463035583</v>
       </c>
       <c r="H231" t="n">
         <v>434</v>
@@ -7097,7 +7097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492755413055</v>
+        <v>1.21492743492126</v>
       </c>
       <c r="H232" t="n">
         <v>842</v>
@@ -7155,7 +7155,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>1.18199265003204</v>
+        <v>1.18199276924133</v>
       </c>
       <c r="H234" t="n">
         <v>2528</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663035869598</v>
+        <v>1.19663047790527</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760869979858</v>
+        <v>1.20760858058929</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7387,7 +7387,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>1.22956514358521</v>
+        <v>1.22956502437592</v>
       </c>
       <c r="H242" t="n">
         <v>6732</v>
@@ -7445,7 +7445,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G244" t="n">
-        <v>1.27128279209137</v>
+        <v>1.27128267288208</v>
       </c>
       <c r="H244" t="n">
         <v>6714</v>
@@ -7474,7 +7474,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G245" t="n">
-        <v>1.26615917682648</v>
+        <v>1.26615929603577</v>
       </c>
       <c r="H245" t="n">
         <v>4030</v>
@@ -7503,7 +7503,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786946296692</v>
+        <v>1.27786934375763</v>
       </c>
       <c r="H246" t="n">
         <v>2816</v>
@@ -7561,7 +7561,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="n">
-        <v>1.2947028875351</v>
+        <v>1.29470300674438</v>
       </c>
       <c r="H248" t="n">
         <v>6791</v>
@@ -7590,7 +7590,7 @@
         <v>17.75</v>
       </c>
       <c r="G249" t="n">
-        <v>1.29909408092499</v>
+        <v>1.29909420013428</v>
       </c>
       <c r="H249" t="n">
         <v>2175</v>
@@ -7706,7 +7706,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G253" t="n">
-        <v>1.28738403320312</v>
+        <v>1.28738415241241</v>
       </c>
       <c r="H253" t="n">
         <v>1178</v>
@@ -7735,7 +7735,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="n">
-        <v>1.2947028875351</v>
+        <v>1.29470300674438</v>
       </c>
       <c r="H254" t="n">
         <v>310</v>
@@ -7764,7 +7764,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G255" t="n">
-        <v>1.3056812286377</v>
+        <v>1.30568099021912</v>
       </c>
       <c r="H255" t="n">
         <v>2306</v>
@@ -7793,7 +7793,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G256" t="n">
-        <v>1.30128991603851</v>
+        <v>1.30128979682922</v>
       </c>
       <c r="H256" t="n">
         <v>1826</v>
@@ -7822,7 +7822,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>1.31007254123688</v>
+        <v>1.31007242202759</v>
       </c>
       <c r="H257" t="n">
         <v>7253</v>
@@ -7851,7 +7851,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="n">
-        <v>1.32544219493866</v>
+        <v>1.32544195652008</v>
       </c>
       <c r="H258" t="n">
         <v>4943</v>
@@ -7938,7 +7938,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="n">
-        <v>1.33422446250916</v>
+        <v>1.33422458171844</v>
       </c>
       <c r="H261" t="n">
         <v>6768</v>
@@ -7996,7 +7996,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="n">
-        <v>1.33861589431763</v>
+        <v>1.33861601352692</v>
       </c>
       <c r="H263" t="n">
         <v>3514</v>
@@ -8054,7 +8054,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="n">
-        <v>1.33422446250916</v>
+        <v>1.33422458171844</v>
       </c>
       <c r="H265" t="n">
         <v>1429</v>
@@ -8083,7 +8083,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G266" t="n">
-        <v>1.31665933132172</v>
+        <v>1.31665945053101</v>
       </c>
       <c r="H266" t="n">
         <v>3165</v>
@@ -8112,7 +8112,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.34666657447815</v>
+        <v>1.34666669368744</v>
       </c>
       <c r="H267" t="n">
         <v>4055</v>
@@ -8170,7 +8170,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34007978439331</v>
+        <v>1.3400799036026</v>
       </c>
       <c r="H269" t="n">
         <v>383</v>
@@ -8228,7 +8228,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32105052471161</v>
+        <v>1.3210506439209</v>
       </c>
       <c r="H271" t="n">
         <v>1933</v>
@@ -8286,7 +8286,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130440235138</v>
+        <v>1.36130428314209</v>
       </c>
       <c r="H273" t="n">
         <v>6282</v>
@@ -8402,7 +8402,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="n">
-        <v>1.34959411621094</v>
+        <v>1.34959423542023</v>
       </c>
       <c r="H277" t="n">
         <v>1064</v>
@@ -8460,7 +8460,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>1.34373903274536</v>
+        <v>1.34373927116394</v>
       </c>
       <c r="H279" t="n">
         <v>886</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910144329071</v>
+        <v>1.32910132408142</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8605,7 +8605,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36349976062775</v>
+        <v>1.36350011825562</v>
       </c>
       <c r="H284" t="n">
         <v>4639</v>
@@ -8663,7 +8663,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="n">
-        <v>1.37667381763458</v>
+        <v>1.37667393684387</v>
       </c>
       <c r="H286" t="n">
         <v>5575</v>
@@ -8750,7 +8750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>1.41253614425659</v>
+        <v>1.4125360250473</v>
       </c>
       <c r="H289" t="n">
         <v>1447</v>
@@ -8779,7 +8779,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="n">
-        <v>1.40668106079102</v>
+        <v>1.40668094158173</v>
       </c>
       <c r="H290" t="n">
         <v>14299</v>
@@ -8808,7 +8808,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.40814483165741</v>
+        <v>1.4081449508667</v>
       </c>
       <c r="H291" t="n">
         <v>7943</v>
@@ -8837,7 +8837,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="n">
-        <v>1.40887677669525</v>
+        <v>1.40887665748596</v>
       </c>
       <c r="H292" t="n">
         <v>5253</v>
@@ -8866,7 +8866,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.40302169322968</v>
+        <v>1.40302181243896</v>
       </c>
       <c r="H293" t="n">
         <v>550</v>
@@ -8895,7 +8895,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="n">
-        <v>1.39277541637421</v>
+        <v>1.3927755355835</v>
       </c>
       <c r="H294" t="n">
         <v>2571</v>
@@ -8924,7 +8924,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.36935496330261</v>
+        <v>1.3693550825119</v>
       </c>
       <c r="H295" t="n">
         <v>3982</v>
@@ -9011,7 +9011,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>1.40155780315399</v>
+        <v>1.40155792236328</v>
       </c>
       <c r="H298" t="n">
         <v>640</v>
@@ -9040,7 +9040,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H299" t="n">
         <v>23394</v>
@@ -9069,7 +9069,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="n">
-        <v>1.49304342269897</v>
+        <v>1.49304354190826</v>
       </c>
       <c r="H300" t="n">
         <v>14396</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621023654938</v>
+        <v>1.47621035575867</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9127,7 +9127,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="n">
-        <v>1.48206532001495</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H302" t="n">
         <v>4239</v>
@@ -9156,7 +9156,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="n">
-        <v>1.49157953262329</v>
+        <v>1.49157965183258</v>
       </c>
       <c r="H303" t="n">
         <v>5662</v>
@@ -9214,7 +9214,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742761135101</v>
+        <v>1.46742749214172</v>
       </c>
       <c r="H305" t="n">
         <v>2232</v>
@@ -9243,7 +9243,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="n">
-        <v>1.45864486694336</v>
+        <v>1.45864498615265</v>
       </c>
       <c r="H306" t="n">
         <v>3108</v>
@@ -9388,7 +9388,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="n">
-        <v>1.48206532001495</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H311" t="n">
         <v>124</v>
@@ -9446,7 +9446,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744221687317</v>
       </c>
       <c r="H313" t="n">
         <v>5175</v>
@@ -9475,7 +9475,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="n">
-        <v>1.52744197845459</v>
+        <v>1.52744221687317</v>
       </c>
       <c r="H314" t="n">
         <v>8473</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987672805786</v>
+        <v>1.50987684726715</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -9562,7 +9562,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>1.52963769435883</v>
+        <v>1.52963757514954</v>
       </c>
       <c r="H317" t="n">
         <v>1725</v>
@@ -9620,7 +9620,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52817392349243</v>
+        <v>1.52817380428314</v>
       </c>
       <c r="H319" t="n">
         <v>4073</v>
@@ -9649,7 +9649,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>1.51500010490417</v>
+        <v>1.51499998569489</v>
       </c>
       <c r="H320" t="n">
         <v>2425</v>
@@ -9678,7 +9678,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="n">
-        <v>1.4996303319931</v>
+        <v>1.49963057041168</v>
       </c>
       <c r="H321" t="n">
         <v>5351</v>
@@ -9707,7 +9707,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>1.49816656112671</v>
+        <v>1.498166680336</v>
       </c>
       <c r="H322" t="n">
         <v>1750</v>
@@ -9736,7 +9736,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>1.485724568367</v>
+        <v>1.48572444915771</v>
       </c>
       <c r="H323" t="n">
         <v>2881</v>
@@ -9765,7 +9765,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48206532001495</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H324" t="n">
         <v>6036</v>
@@ -9852,7 +9852,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47108685970306</v>
+        <v>1.47108697891235</v>
       </c>
       <c r="H327" t="n">
         <v>10631</v>
@@ -9910,7 +9910,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="n">
-        <v>1.48206532001495</v>
+        <v>1.48206520080566</v>
       </c>
       <c r="H329" t="n">
         <v>3153</v>
@@ -9939,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="n">
-        <v>1.46376800537109</v>
+        <v>1.46376812458038</v>
       </c>
       <c r="H330" t="n">
         <v>9218</v>
@@ -9997,7 +9997,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="n">
-        <v>1.48499274253845</v>
+        <v>1.48499286174774</v>
       </c>
       <c r="H332" t="n">
         <v>9406</v>
@@ -10055,7 +10055,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768849372864</v>
+        <v>1.53768837451935</v>
       </c>
       <c r="H334" t="n">
         <v>12975</v>
@@ -10113,7 +10113,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>1.63126361370087</v>
+        <v>1.63126349449158</v>
       </c>
       <c r="H336" t="n">
         <v>30984</v>
@@ -10142,7 +10142,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="n">
-        <v>1.63427484035492</v>
+        <v>1.63427472114563</v>
       </c>
       <c r="H337" t="n">
         <v>3259</v>
@@ -10171,7 +10171,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>1.64857745170593</v>
+        <v>1.64857757091522</v>
       </c>
       <c r="H338" t="n">
         <v>10071</v>
@@ -10287,7 +10287,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="n">
-        <v>1.66137492656708</v>
+        <v>1.66137480735779</v>
       </c>
       <c r="H342" t="n">
         <v>1480</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816578865051</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429931640625</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10403,7 +10403,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="n">
-        <v>1.9165655374527</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H346" t="n">
         <v>37449</v>
@@ -10432,7 +10432,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="n">
-        <v>1.99485409259796</v>
+        <v>1.99485397338867</v>
       </c>
       <c r="H347" t="n">
         <v>48029</v>
@@ -10548,7 +10548,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="n">
-        <v>1.93011546134949</v>
+        <v>1.93011558055878</v>
       </c>
       <c r="H351" t="n">
         <v>6514</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429931640625</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376049995422</v>
+        <v>1.83376014232635</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10664,7 +10664,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452086925507</v>
       </c>
       <c r="H355" t="n">
         <v>6898</v>
@@ -10693,7 +10693,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>1.91204881668091</v>
+        <v>1.91204905509949</v>
       </c>
       <c r="H356" t="n">
         <v>4977</v>
@@ -10722,7 +10722,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538475036621</v>
+        <v>1.93538498878479</v>
       </c>
       <c r="H357" t="n">
         <v>14132</v>
@@ -10751,7 +10751,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="n">
-        <v>1.92258775234222</v>
+        <v>1.92258763313293</v>
       </c>
       <c r="H358" t="n">
         <v>3542</v>
@@ -10809,7 +10809,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>1.88118493556976</v>
+        <v>1.88118481636047</v>
       </c>
       <c r="H360" t="n">
         <v>6883</v>
@@ -10867,7 +10867,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="n">
-        <v>1.92183482646942</v>
+        <v>1.92183494567871</v>
       </c>
       <c r="H362" t="n">
         <v>4932</v>
@@ -10896,7 +10896,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>1.92559897899628</v>
+        <v>1.92559885978699</v>
       </c>
       <c r="H363" t="n">
         <v>5423</v>
@@ -10925,7 +10925,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>1.94065427780151</v>
+        <v>1.9406543970108</v>
       </c>
       <c r="H364" t="n">
         <v>4029</v>
@@ -10954,7 +10954,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9263516664505</v>
+        <v>1.92635154724121</v>
       </c>
       <c r="H365" t="n">
         <v>10408</v>
@@ -10983,7 +10983,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>1.9165655374527</v>
+        <v>1.91656541824341</v>
       </c>
       <c r="H366" t="n">
         <v>5653</v>
@@ -11012,7 +11012,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="n">
-        <v>1.90376842021942</v>
+        <v>1.90376853942871</v>
       </c>
       <c r="H367" t="n">
         <v>5873</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957676410675</v>
+        <v>1.91957640647888</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11070,7 +11070,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="n">
-        <v>1.92559897899628</v>
+        <v>1.92559885978699</v>
       </c>
       <c r="H369" t="n">
         <v>1846</v>
@@ -11099,7 +11099,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="n">
-        <v>1.91882371902466</v>
+        <v>1.91882383823395</v>
       </c>
       <c r="H370" t="n">
         <v>4343</v>
@@ -11128,7 +11128,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237376213074</v>
       </c>
       <c r="H371" t="n">
         <v>2941</v>
@@ -11157,7 +11157,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>1.94366538524628</v>
+        <v>1.94366526603699</v>
       </c>
       <c r="H372" t="n">
         <v>2905</v>
@@ -11186,7 +11186,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="n">
-        <v>1.92258775234222</v>
+        <v>1.92258763313293</v>
       </c>
       <c r="H373" t="n">
         <v>1590</v>
@@ -11244,7 +11244,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>1.89021825790405</v>
+        <v>1.89021837711334</v>
       </c>
       <c r="H375" t="n">
         <v>1836</v>
@@ -11273,7 +11273,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753221511841</v>
+        <v>1.90753185749054</v>
       </c>
       <c r="H376" t="n">
         <v>4843</v>
@@ -11331,7 +11331,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="n">
-        <v>1.89473497867584</v>
+        <v>1.89473509788513</v>
       </c>
       <c r="H378" t="n">
         <v>803</v>
@@ -11360,7 +11360,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742114067078</v>
+        <v>1.87742137908936</v>
       </c>
       <c r="H379" t="n">
         <v>4228</v>
@@ -11389,7 +11389,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86010730266571</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H380" t="n">
         <v>957</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052700519562</v>
+        <v>1.77052712440491</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.7976268529892</v>
+        <v>1.79762673377991</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11476,7 +11476,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="n">
-        <v>1.76826894283295</v>
+        <v>1.76826858520508</v>
       </c>
       <c r="H383" t="n">
         <v>2862</v>
@@ -11563,7 +11563,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>1.83074939250946</v>
+        <v>1.83074927330017</v>
       </c>
       <c r="H386" t="n">
         <v>3583</v>
@@ -11592,7 +11592,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881556034088</v>
       </c>
       <c r="H387" t="n">
         <v>1000</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547974586487</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11650,7 +11650,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>1.81042420864105</v>
+        <v>1.81042408943176</v>
       </c>
       <c r="H389" t="n">
         <v>98</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.8081659078598</v>
+        <v>1.80816578865051</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11737,7 +11737,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>1.81042420864105</v>
+        <v>1.81042408943176</v>
       </c>
       <c r="H392" t="n">
         <v>1413</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.8360184431076</v>
+        <v>1.83601856231689</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429931640625</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429931640625</v>
+        <v>1.84429907798767</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11969,7 +11969,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806287288666</v>
+        <v>1.84806299209595</v>
       </c>
       <c r="H400" t="n">
         <v>1454</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.84655749797821</v>
+        <v>1.8465576171875</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752393722534</v>
+        <v>1.83752405643463</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774608612061</v>
+        <v>1.89774632453918</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12085,7 +12085,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>1.91280174255371</v>
+        <v>1.91280162334442</v>
       </c>
       <c r="H404" t="n">
         <v>21296</v>
@@ -12114,7 +12114,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H405" t="n">
         <v>8569</v>
@@ -12143,7 +12143,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H406" t="n">
         <v>3339</v>
@@ -12172,7 +12172,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>1.97151815891266</v>
+        <v>1.97151803970337</v>
       </c>
       <c r="H407" t="n">
         <v>2092</v>
@@ -12201,7 +12201,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="n">
-        <v>1.930868268013</v>
+        <v>1.93086814880371</v>
       </c>
       <c r="H408" t="n">
         <v>4037</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613743782043</v>
+        <v>1.93613755702972</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12259,7 +12259,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="n">
-        <v>1.93237364292145</v>
+        <v>1.93237376213074</v>
       </c>
       <c r="H410" t="n">
         <v>3461</v>
@@ -12288,7 +12288,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>1.9210821390152</v>
+        <v>1.92108225822449</v>
       </c>
       <c r="H411" t="n">
         <v>931</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957676410675</v>
+        <v>1.91957640647888</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12375,7 +12375,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="n">
-        <v>1.89021825790405</v>
+        <v>1.89021837711334</v>
       </c>
       <c r="H414" t="n">
         <v>818</v>
@@ -12404,7 +12404,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="n">
-        <v>1.88720738887787</v>
+        <v>1.88720726966858</v>
       </c>
       <c r="H415" t="n">
         <v>1165</v>
@@ -12433,7 +12433,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="n">
-        <v>1.89548778533936</v>
+        <v>1.89548754692078</v>
       </c>
       <c r="H416" t="n">
         <v>873</v>
@@ -12462,7 +12462,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.90452110767365</v>
+        <v>1.90452086925507</v>
       </c>
       <c r="H417" t="n">
         <v>770</v>
@@ -12520,7 +12520,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="n">
-        <v>1.869140625</v>
+        <v>1.86914050579071</v>
       </c>
       <c r="H419" t="n">
         <v>2296</v>
@@ -12549,7 +12549,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>1.86010730266571</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H420" t="n">
         <v>1208</v>
@@ -12607,7 +12607,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881556034088</v>
       </c>
       <c r="H422" t="n">
         <v>5360</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.85634338855743</v>
+        <v>1.85634362697601</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12694,7 +12694,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.85182702541351</v>
+        <v>1.85182678699493</v>
       </c>
       <c r="H425" t="n">
         <v>2952</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688208580017</v>
+        <v>1.86688232421875</v>
       </c>
       <c r="H426" t="n">
         <v>1972</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.85634338855743</v>
+        <v>1.85634362697601</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12781,7 +12781,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88494884967804</v>
+        <v>1.88494873046875</v>
       </c>
       <c r="H428" t="n">
         <v>2953</v>
@@ -12810,7 +12810,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="n">
-        <v>1.87215209007263</v>
+        <v>1.87215197086334</v>
       </c>
       <c r="H429" t="n">
         <v>140</v>
@@ -12868,7 +12868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688208580017</v>
+        <v>1.86688232421875</v>
       </c>
       <c r="H431" t="n">
         <v>1257</v>
@@ -12897,7 +12897,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="n">
-        <v>1.86010730266571</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H432" t="n">
         <v>3720</v>
@@ -12926,7 +12926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688208580017</v>
+        <v>1.86688232421875</v>
       </c>
       <c r="H433" t="n">
         <v>2572</v>
@@ -13013,7 +13013,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193774223328</v>
+        <v>1.88193762302399</v>
       </c>
       <c r="H436" t="n">
         <v>2642</v>
@@ -13071,7 +13071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688208580017</v>
+        <v>1.86688232421875</v>
       </c>
       <c r="H438" t="n">
         <v>969</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365746498108</v>
+        <v>1.87365734577179</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13129,7 +13129,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="n">
-        <v>1.86537671089172</v>
+        <v>1.8653769493103</v>
       </c>
       <c r="H440" t="n">
         <v>2630</v>
@@ -13158,7 +13158,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.86010730266571</v>
+        <v>1.860107421875</v>
       </c>
       <c r="H441" t="n">
         <v>702</v>
@@ -13187,7 +13187,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="n">
-        <v>1.84505188465118</v>
+        <v>1.84505200386047</v>
       </c>
       <c r="H442" t="n">
         <v>4195</v>
@@ -13274,7 +13274,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="n">
-        <v>1.84731066226959</v>
+        <v>1.84731030464172</v>
       </c>
       <c r="H445" t="n">
         <v>2208</v>
@@ -13303,7 +13303,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279358386993</v>
+        <v>1.84279370307922</v>
       </c>
       <c r="H446" t="n">
         <v>1136</v>
@@ -13332,7 +13332,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881556034088</v>
       </c>
       <c r="H447" t="n">
         <v>5011</v>
@@ -13361,7 +13361,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>1.81795179843903</v>
+        <v>1.8179520368576</v>
       </c>
       <c r="H448" t="n">
         <v>5592</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397401332855</v>
+        <v>1.82397413253784</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13419,7 +13419,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="n">
-        <v>1.82849061489105</v>
+        <v>1.82849073410034</v>
       </c>
       <c r="H450" t="n">
         <v>3382</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>1.81569385528564</v>
+        <v>1.81569397449493</v>
       </c>
       <c r="H451" t="n">
         <v>4388</v>
@@ -13477,7 +13477,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="n">
-        <v>1.82021045684814</v>
+        <v>1.82021033763885</v>
       </c>
       <c r="H452" t="n">
         <v>6137</v>
@@ -13506,7 +13506,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="n">
-        <v>1.81117701530457</v>
+        <v>1.81117677688599</v>
       </c>
       <c r="H453" t="n">
         <v>5132</v>
@@ -13564,7 +13564,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="n">
-        <v>1.81418812274933</v>
+        <v>1.81418788433075</v>
       </c>
       <c r="H455" t="n">
         <v>1684</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547974586487</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13680,7 +13680,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="n">
-        <v>1.82246828079224</v>
+        <v>1.82246851921082</v>
       </c>
       <c r="H459" t="n">
         <v>4906</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547950744629</v>
+        <v>1.82547974586487</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13796,7 +13796,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881579875946</v>
+        <v>1.84881556034088</v>
       </c>
       <c r="H463" t="n">
         <v>34293</v>
@@ -13825,7 +13825,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849889278412</v>
+        <v>1.89849877357483</v>
       </c>
       <c r="H464" t="n">
         <v>4953</v>
@@ -13883,7 +13883,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91731810569763</v>
+        <v>1.91731822490692</v>
       </c>
       <c r="H466" t="n">
         <v>7056</v>
@@ -13912,7 +13912,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>1.97979831695557</v>
+        <v>1.97979843616486</v>
       </c>
       <c r="H467" t="n">
         <v>24938</v>
@@ -13970,7 +13970,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="n">
-        <v>1.94366538524628</v>
+        <v>1.94366526603699</v>
       </c>
       <c r="H469" t="n">
         <v>12171</v>
@@ -14057,7 +14057,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775448322296</v>
+        <v>1.96775424480438</v>
       </c>
       <c r="H472" t="n">
         <v>6595</v>
@@ -14086,7 +14086,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="n">
-        <v>1.96248483657837</v>
+        <v>1.96248459815979</v>
       </c>
       <c r="H473" t="n">
         <v>11988</v>
@@ -14144,7 +14144,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>2.04378437995911</v>
+        <v>2.04378461837769</v>
       </c>
       <c r="H475" t="n">
         <v>19009</v>
@@ -14202,7 +14202,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>1.9873263835907</v>
+        <v>1.98732650279999</v>
       </c>
       <c r="H477" t="n">
         <v>8901</v>
@@ -14231,7 +14231,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="n">
-        <v>1.99937069416046</v>
+        <v>1.99937057495117</v>
       </c>
       <c r="H478" t="n">
         <v>3901</v>
@@ -14260,7 +14260,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582077026367</v>
+        <v>1.98582065105438</v>
       </c>
       <c r="H479" t="n">
         <v>3201</v>
@@ -14347,7 +14347,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="n">
-        <v>1.99861812591553</v>
+        <v>1.99861800670624</v>
       </c>
       <c r="H482" t="n">
         <v>7953</v>
@@ -14376,7 +14376,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549594402313</v>
+        <v>1.96549582481384</v>
       </c>
       <c r="H483" t="n">
         <v>212</v>
@@ -14463,7 +14463,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="n">
-        <v>1.98281002044678</v>
+        <v>1.9828097820282</v>
       </c>
       <c r="H486" t="n">
         <v>699</v>
@@ -14492,7 +14492,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="n">
-        <v>1.97377622127533</v>
+        <v>1.97377645969391</v>
       </c>
       <c r="H487" t="n">
         <v>871</v>
@@ -14550,7 +14550,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>2.06260371208191</v>
+        <v>2.06260395050049</v>
       </c>
       <c r="H489" t="n">
         <v>11786</v>
@@ -14579,7 +14579,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="n">
-        <v>2.06260371208191</v>
+        <v>2.06260395050049</v>
       </c>
       <c r="H490" t="n">
         <v>4910</v>
@@ -14608,7 +14608,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540106773376</v>
+        <v>2.07540082931519</v>
       </c>
       <c r="H491" t="n">
         <v>2166</v>
@@ -14666,7 +14666,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="n">
-        <v>2.06260371208191</v>
+        <v>2.06260395050049</v>
       </c>
       <c r="H493" t="n">
         <v>9201</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024237632751</v>
+        <v>2.10024285316467</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -14985,7 +14985,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>2.06034564971924</v>
+        <v>2.06034541130066</v>
       </c>
       <c r="H504" t="n">
         <v>2924</v>
@@ -15014,7 +15014,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>2.05959272384644</v>
+        <v>2.05959296226501</v>
       </c>
       <c r="H505" t="n">
         <v>2166</v>
@@ -15072,7 +15072,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540106773376</v>
+        <v>2.07540082931519</v>
       </c>
       <c r="H507" t="n">
         <v>1590</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615375518799</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15188,7 +15188,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>2.08518719673157</v>
+        <v>2.08518743515015</v>
       </c>
       <c r="H511" t="n">
         <v>1601</v>
@@ -15246,7 +15246,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057536125183</v>
       </c>
       <c r="H513" t="n">
         <v>13248</v>
@@ -15304,7 +15304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.1755199432373</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H515" t="n">
         <v>6715</v>
@@ -15362,7 +15362,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.1755199432373</v>
+        <v>2.17552018165588</v>
       </c>
       <c r="H517" t="n">
         <v>16053</v>
@@ -15391,7 +15391,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H518" t="n">
         <v>3359</v>
@@ -15420,7 +15420,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="n">
-        <v>2.22068691253662</v>
+        <v>2.22068667411804</v>
       </c>
       <c r="H519" t="n">
         <v>982</v>
@@ -15449,7 +15449,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="n">
-        <v>2.31101965904236</v>
+        <v>2.31101989746094</v>
       </c>
       <c r="H520" t="n">
         <v>13063</v>
@@ -15478,7 +15478,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H521" t="n">
         <v>10697</v>
@@ -15594,7 +15594,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="n">
-        <v>2.37124156951904</v>
+        <v>2.37124180793762</v>
       </c>
       <c r="H525" t="n">
         <v>3481</v>
@@ -15623,7 +15623,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H526" t="n">
         <v>2705</v>
@@ -15652,7 +15652,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G527" t="n">
-        <v>2.32607507705688</v>
+        <v>2.32607483863831</v>
       </c>
       <c r="H527" t="n">
         <v>3389</v>
@@ -15681,7 +15681,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.31101965904236</v>
+        <v>2.31101989746094</v>
       </c>
       <c r="H528" t="n">
         <v>6112</v>
@@ -15768,7 +15768,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>2.28090882301331</v>
+        <v>2.28090858459473</v>
       </c>
       <c r="H531" t="n">
         <v>1414</v>
@@ -15826,7 +15826,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596447944641</v>
+        <v>2.29596400260925</v>
       </c>
       <c r="H533" t="n">
         <v>4435</v>
@@ -15942,7 +15942,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057536125183</v>
       </c>
       <c r="H537" t="n">
         <v>6576</v>
@@ -15971,7 +15971,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="n">
-        <v>2.19810342788696</v>
+        <v>2.19810366630554</v>
       </c>
       <c r="H538" t="n">
         <v>2100</v>
@@ -16029,7 +16029,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057536125183</v>
       </c>
       <c r="H540" t="n">
         <v>5940</v>
@@ -16087,7 +16087,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="n">
-        <v>2.20563125610352</v>
+        <v>2.20563101768494</v>
       </c>
       <c r="H542" t="n">
         <v>3615</v>
@@ -16116,7 +16116,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057559967041</v>
+        <v>2.19057536125183</v>
       </c>
       <c r="H543" t="n">
         <v>161</v>
@@ -16232,7 +16232,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>2.38629698753357</v>
+        <v>2.38629746437073</v>
       </c>
       <c r="H547" t="n">
         <v>6727</v>
@@ -16261,7 +16261,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="n">
-        <v>2.37124156951904</v>
+        <v>2.37124180793762</v>
       </c>
       <c r="H548" t="n">
         <v>2154</v>
@@ -16290,7 +16290,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="n">
-        <v>2.55190801620483</v>
+        <v>2.55190777778625</v>
       </c>
       <c r="H549" t="n">
         <v>41764</v>
@@ -16319,7 +16319,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="n">
-        <v>2.54437971115112</v>
+        <v>2.5443799495697</v>
       </c>
       <c r="H550" t="n">
         <v>7288</v>
@@ -16348,7 +16348,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>2.61965727806091</v>
+        <v>2.61965751647949</v>
       </c>
       <c r="H551" t="n">
         <v>11195</v>
@@ -16406,7 +16406,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168539047241</v>
       </c>
       <c r="H553" t="n">
         <v>5398</v>
@@ -16435,7 +16435,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H554" t="n">
         <v>6023</v>
@@ -16493,7 +16493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.36371421813965</v>
+        <v>2.36371397972107</v>
       </c>
       <c r="H556" t="n">
         <v>9076</v>
@@ -16551,7 +16551,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H558" t="n">
         <v>4749</v>
@@ -16580,7 +16580,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H559" t="n">
         <v>4701</v>
@@ -16696,7 +16696,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="n">
-        <v>2.40888047218323</v>
+        <v>2.40888023376465</v>
       </c>
       <c r="H563" t="n">
         <v>3721</v>
@@ -16725,7 +16725,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H564" t="n">
         <v>2298</v>
@@ -16783,7 +16783,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="n">
-        <v>2.48415780067444</v>
+        <v>2.48415803909302</v>
       </c>
       <c r="H566" t="n">
         <v>3886</v>
@@ -16928,7 +16928,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H571" t="n">
         <v>3605</v>
@@ -17044,7 +17044,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43146395683289</v>
+        <v>2.43146371841431</v>
       </c>
       <c r="H575" t="n">
         <v>4786</v>
@@ -17189,7 +17189,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168539047241</v>
       </c>
       <c r="H580" t="n">
         <v>7145</v>
@@ -17276,7 +17276,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="n">
-        <v>2.49168562889099</v>
+        <v>2.49168539047241</v>
       </c>
       <c r="H583" t="n">
         <v>1838</v>
@@ -17305,7 +17305,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="n">
-        <v>2.48415780067444</v>
+        <v>2.48415803909302</v>
       </c>
       <c r="H584" t="n">
         <v>1833</v>
@@ -17363,7 +17363,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>2.46910238265991</v>
+        <v>2.46910214424133</v>
       </c>
       <c r="H586" t="n">
         <v>3037</v>
@@ -17450,7 +17450,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H589" t="n">
         <v>8373</v>
@@ -17537,7 +17537,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>2.5836353302002</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H592" t="n">
         <v>1427</v>
@@ -17682,7 +17682,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>2.5836353302002</v>
+        <v>2.58363509178162</v>
       </c>
       <c r="H597" t="n">
         <v>5094</v>
@@ -17711,7 +17711,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.57587647438049</v>
+        <v>2.57587671279907</v>
       </c>
       <c r="H598" t="n">
         <v>3047</v>
@@ -17740,7 +17740,7 @@
         <v>32.5</v>
       </c>
       <c r="G599" t="n">
-        <v>2.52156591415405</v>
+        <v>2.52156567573547</v>
       </c>
       <c r="H599" t="n">
         <v>8906</v>
@@ -17769,7 +17769,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.54484176635742</v>
+        <v>2.54484152793884</v>
       </c>
       <c r="H600" t="n">
         <v>1367</v>
@@ -17827,7 +17827,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="n">
-        <v>2.48277258872986</v>
+        <v>2.48277235031128</v>
       </c>
       <c r="H602" t="n">
         <v>16769</v>
@@ -17943,7 +17943,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="n">
-        <v>2.48277258872986</v>
+        <v>2.48277235031128</v>
       </c>
       <c r="H606" t="n">
         <v>109</v>
@@ -17972,7 +17972,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846155166626</v>
       </c>
       <c r="H607" t="n">
         <v>6484</v>
@@ -18030,7 +18030,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>2.30432343482971</v>
+        <v>2.30432319641113</v>
       </c>
       <c r="H609" t="n">
         <v>3124</v>
@@ -18117,7 +18117,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>2.31208157539368</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H612" t="n">
         <v>1071</v>
@@ -18146,7 +18146,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H613" t="n">
         <v>5750</v>
@@ -18233,7 +18233,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H616" t="n">
         <v>2444</v>
@@ -18291,7 +18291,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H618" t="n">
         <v>1075</v>
@@ -18407,7 +18407,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="n">
-        <v>2.11811542510986</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H622" t="n">
         <v>1065</v>
@@ -18639,7 +18639,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="n">
-        <v>2.21897792816162</v>
+        <v>2.2189781665802</v>
       </c>
       <c r="H630" t="n">
         <v>1237</v>
@@ -18900,7 +18900,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.11811542510986</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H639" t="n">
         <v>152</v>
@@ -18929,7 +18929,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.11811542510986</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H646" t="n">
         <v>7254</v>
@@ -19190,7 +19190,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H649" t="n">
         <v>1745</v>
@@ -19248,7 +19248,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H651" t="n">
         <v>1233</v>
@@ -19277,7 +19277,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>2.14914989471436</v>
+        <v>2.14915013313293</v>
       </c>
       <c r="H652" t="n">
         <v>1217</v>
@@ -19364,7 +19364,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H655" t="n">
         <v>3734</v>
@@ -19393,7 +19393,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H656" t="n">
         <v>2106</v>
@@ -19538,7 +19538,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H661" t="n">
         <v>1158</v>
@@ -19567,7 +19567,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H662" t="n">
         <v>2066</v>
@@ -19654,7 +19654,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H665" t="n">
         <v>392</v>
@@ -19683,7 +19683,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H666" t="n">
         <v>989</v>
@@ -19712,7 +19712,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H667" t="n">
         <v>232</v>
@@ -19799,7 +19799,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H670" t="n">
         <v>10470</v>
@@ -19857,7 +19857,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H672" t="n">
         <v>8845</v>
@@ -19944,7 +19944,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>1.97070062160492</v>
+        <v>1.97070074081421</v>
       </c>
       <c r="H675" t="n">
         <v>420</v>
@@ -19973,7 +19973,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294176578522</v>
       </c>
       <c r="H676" t="n">
         <v>3545</v>
@@ -20060,7 +20060,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>1.87759685516357</v>
+        <v>1.87759697437286</v>
       </c>
       <c r="H679" t="n">
         <v>3984</v>
@@ -20147,7 +20147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="n">
-        <v>1.79225134849548</v>
+        <v>1.79225146770477</v>
       </c>
       <c r="H682" t="n">
         <v>1859</v>
@@ -20234,7 +20234,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>1.86207950115204</v>
+        <v>1.86207938194275</v>
       </c>
       <c r="H685" t="n">
         <v>1968</v>
@@ -20292,7 +20292,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H687" t="n">
         <v>17503</v>
@@ -20379,7 +20379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H690" t="n">
         <v>725</v>
@@ -20408,7 +20408,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H693" t="n">
         <v>2480</v>
@@ -20495,7 +20495,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H694" t="n">
         <v>80</v>
@@ -20524,7 +20524,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H695" t="n">
         <v>2142</v>
@@ -20553,7 +20553,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H696" t="n">
         <v>2090</v>
@@ -20611,7 +20611,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H698" t="n">
         <v>1482</v>
@@ -20640,7 +20640,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H699" t="n">
         <v>4797</v>
@@ -20669,7 +20669,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H700" t="n">
         <v>2148</v>
@@ -20756,7 +20756,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H703" t="n">
         <v>3410</v>
@@ -20785,7 +20785,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="n">
-        <v>1.99397671222687</v>
+        <v>1.99397659301758</v>
       </c>
       <c r="H704" t="n">
         <v>1</v>
@@ -20814,7 +20814,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="n">
-        <v>2.01725268363953</v>
+        <v>2.01725292205811</v>
       </c>
       <c r="H705" t="n">
         <v>2758</v>
@@ -20843,7 +20843,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="n">
-        <v>2.0017352104187</v>
+        <v>2.00173544883728</v>
       </c>
       <c r="H706" t="n">
         <v>1168</v>
@@ -20872,7 +20872,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="n">
-        <v>1.9629420042038</v>
+        <v>1.96294176578522</v>
       </c>
       <c r="H707" t="n">
         <v>4382</v>
@@ -20930,7 +20930,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99397671222687</v>
+        <v>1.99397659301758</v>
       </c>
       <c r="H709" t="n">
         <v>2556</v>
@@ -20959,7 +20959,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>1.9241486787796</v>
+        <v>1.92414855957031</v>
       </c>
       <c r="H710" t="n">
         <v>965</v>
@@ -20988,7 +20988,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>1.9241486787796</v>
+        <v>1.92414855957031</v>
       </c>
       <c r="H711" t="n">
         <v>4086</v>
@@ -21046,7 +21046,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>1.84656202793121</v>
+        <v>1.84656190872192</v>
       </c>
       <c r="H713" t="n">
         <v>609</v>
@@ -21104,7 +21104,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="n">
-        <v>1.86207950115204</v>
+        <v>1.86207938194275</v>
       </c>
       <c r="H715" t="n">
         <v>1620</v>
@@ -21133,7 +21133,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>1.84656202793121</v>
+        <v>1.84656190872192</v>
       </c>
       <c r="H716" t="n">
         <v>48</v>
@@ -21162,7 +21162,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225134849548</v>
+        <v>1.79225146770477</v>
       </c>
       <c r="H717" t="n">
         <v>747</v>
@@ -21191,7 +21191,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80776858329773</v>
+        <v>1.80776846408844</v>
       </c>
       <c r="H718" t="n">
         <v>821</v>
@@ -21220,7 +21220,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>1.753457903862</v>
+        <v>1.75345802307129</v>
       </c>
       <c r="H719" t="n">
         <v>3685</v>
@@ -21249,7 +21249,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="n">
-        <v>1.77673399448395</v>
+        <v>1.77673411369324</v>
       </c>
       <c r="H720" t="n">
         <v>6378</v>
@@ -21307,7 +21307,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="n">
-        <v>1.82328593730927</v>
+        <v>1.82328605651855</v>
       </c>
       <c r="H722" t="n">
         <v>1535</v>
@@ -21336,7 +21336,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="n">
-        <v>1.82328593730927</v>
+        <v>1.82328605651855</v>
       </c>
       <c r="H723" t="n">
         <v>8398</v>
@@ -21365,7 +21365,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87759685516357</v>
+        <v>1.87759697437286</v>
       </c>
       <c r="H724" t="n">
         <v>2115</v>
@@ -21394,7 +21394,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.87759685516357</v>
+        <v>1.87759697437286</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.87759685516357</v>
+        <v>1.87759697437286</v>
       </c>
       <c r="H728" t="n">
         <v>961</v>
@@ -21597,7 +21597,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="n">
-        <v>2.21121907234192</v>
+        <v>2.2112193107605</v>
       </c>
       <c r="H732" t="n">
         <v>19299</v>
@@ -21742,7 +21742,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H737" t="n">
         <v>2727</v>
@@ -21858,7 +21858,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H741" t="n">
         <v>1711</v>
@@ -22032,7 +22032,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>2.11811542510986</v>
+        <v>2.11811518669128</v>
       </c>
       <c r="H747" t="n">
         <v>149</v>
@@ -22090,7 +22090,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07156324386597</v>
+        <v>2.07156348228455</v>
       </c>
       <c r="H749" t="n">
         <v>391</v>
@@ -22177,7 +22177,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99397671222687</v>
+        <v>1.99397659301758</v>
       </c>
       <c r="H752" t="n">
         <v>6924</v>
@@ -22293,7 +22293,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>2.03276991844177</v>
+        <v>2.03277015686035</v>
       </c>
       <c r="H756" t="n">
         <v>1439</v>
@@ -22351,7 +22351,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H758" t="n">
         <v>645</v>
@@ -22409,7 +22409,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>2.04828715324402</v>
+        <v>2.0482873916626</v>
       </c>
       <c r="H760" t="n">
         <v>1417</v>
@@ -22670,7 +22670,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="n">
-        <v>2.14139127731323</v>
+        <v>2.14139103889465</v>
       </c>
       <c r="H769" t="n">
         <v>3390</v>
@@ -22699,7 +22699,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="n">
-        <v>2.21121907234192</v>
+        <v>2.2112193107605</v>
       </c>
       <c r="H770" t="n">
         <v>1195</v>
@@ -22757,7 +22757,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H772" t="n">
         <v>443</v>
@@ -22902,7 +22902,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H777" t="n">
         <v>329</v>
@@ -22931,7 +22931,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H778" t="n">
         <v>160</v>
@@ -22960,7 +22960,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>2.15690875053406</v>
+        <v>2.15690851211548</v>
       </c>
       <c r="H779" t="n">
         <v>3252</v>
@@ -22989,7 +22989,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="n">
-        <v>2.21121907234192</v>
+        <v>2.2112193107605</v>
       </c>
       <c r="H780" t="n">
         <v>7946</v>
@@ -23047,7 +23047,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H782" t="n">
         <v>15901</v>
@@ -23076,7 +23076,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>2.25777125358582</v>
+        <v>2.25777101516724</v>
       </c>
       <c r="H783" t="n">
         <v>1355</v>
@@ -23134,7 +23134,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="n">
-        <v>2.26552987098694</v>
+        <v>2.26553010940552</v>
       </c>
       <c r="H785" t="n">
         <v>674</v>
@@ -23163,7 +23163,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>2.22673654556274</v>
+        <v>2.22673678398132</v>
       </c>
       <c r="H786" t="n">
         <v>7919</v>
@@ -23250,7 +23250,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087490081787</v>
       </c>
       <c r="H789" t="n">
         <v>9758</v>
@@ -23279,7 +23279,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H790" t="n">
         <v>6067</v>
@@ -23337,7 +23337,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H792" t="n">
         <v>323</v>
@@ -23395,7 +23395,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H794" t="n">
         <v>836</v>
@@ -23424,7 +23424,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H795" t="n">
         <v>1453</v>
@@ -23482,7 +23482,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H797" t="n">
         <v>1948</v>
@@ -23511,7 +23511,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H798" t="n">
         <v>381</v>
@@ -23540,7 +23540,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="n">
-        <v>2.30432343482971</v>
+        <v>2.30432319641113</v>
       </c>
       <c r="H799" t="n">
         <v>553</v>
@@ -23598,7 +23598,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.31208157539368</v>
+        <v>2.31208181381226</v>
       </c>
       <c r="H801" t="n">
         <v>693</v>
@@ -23627,7 +23627,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="n">
-        <v>2.31984043121338</v>
+        <v>2.31984066963196</v>
       </c>
       <c r="H802" t="n">
         <v>276</v>
@@ -23656,7 +23656,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>2.42846179008484</v>
+        <v>2.42846155166626</v>
       </c>
       <c r="H803" t="n">
         <v>8524</v>
@@ -23685,7 +23685,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H804" t="n">
         <v>3185</v>
@@ -23743,7 +23743,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>2.38966870307922</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H806" t="n">
         <v>3492</v>
@@ -23801,7 +23801,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H808" t="n">
         <v>3206</v>
@@ -23830,7 +23830,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H809" t="n">
         <v>1118</v>
@@ -23859,7 +23859,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H810" t="n">
         <v>3272</v>
@@ -23888,7 +23888,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H811" t="n">
         <v>4135</v>
@@ -23917,7 +23917,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41294431686401</v>
+        <v>2.41294455528259</v>
       </c>
       <c r="H812" t="n">
         <v>1173</v>
@@ -23946,7 +23946,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="n">
-        <v>2.38966870307922</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H813" t="n">
         <v>222</v>
@@ -24004,7 +24004,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>2.42070317268372</v>
+        <v>2.42070341110229</v>
       </c>
       <c r="H815" t="n">
         <v>535</v>
@@ -24033,7 +24033,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>2.38966870307922</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H816" t="n">
         <v>378</v>
@@ -24062,7 +24062,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H817" t="n">
         <v>604</v>
@@ -24120,7 +24120,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="n">
-        <v>2.40518617630005</v>
+        <v>2.40518593788147</v>
       </c>
       <c r="H819" t="n">
         <v>412</v>
@@ -24149,7 +24149,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="n">
-        <v>2.38966870307922</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H820" t="n">
         <v>2462</v>
@@ -24207,7 +24207,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.34311628341675</v>
+        <v>2.34311652183533</v>
       </c>
       <c r="H822" t="n">
         <v>940</v>
@@ -24236,7 +24236,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.35087513923645</v>
+        <v>2.35087490081787</v>
       </c>
       <c r="H823" t="n">
         <v>367</v>
@@ -24294,7 +24294,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H825" t="n">
         <v>186</v>
@@ -24323,7 +24323,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="n">
-        <v>2.35863375663757</v>
+        <v>2.35863399505615</v>
       </c>
       <c r="H826" t="n">
         <v>1041</v>
@@ -24352,7 +24352,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>2.38966870307922</v>
+        <v>2.38966846466064</v>
       </c>
       <c r="H827" t="n">
         <v>622</v>
@@ -24410,7 +24410,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H829" t="n">
         <v>12604</v>
@@ -24439,7 +24439,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H830" t="n">
         <v>1806</v>
@@ -24468,7 +24468,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>2.45173788070679</v>
+        <v>2.45173764228821</v>
       </c>
       <c r="H831" t="n">
         <v>6065</v>
@@ -24613,7 +24613,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="n">
-        <v>2.55260062217712</v>
+        <v>2.5526008605957</v>
       </c>
       <c r="H836" t="n">
         <v>21589</v>
@@ -24671,7 +24671,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H838" t="n">
         <v>12949</v>
@@ -24700,7 +24700,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H839" t="n">
         <v>9697</v>
@@ -24729,7 +24729,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H840" t="n">
         <v>2792</v>
@@ -24787,7 +24787,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H842" t="n">
         <v>1676</v>
@@ -24845,7 +24845,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H844" t="n">
         <v>715</v>
@@ -24961,7 +24961,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H848" t="n">
         <v>2347</v>
@@ -25048,7 +25048,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>2.3900146484375</v>
+        <v>2.39001441001892</v>
       </c>
       <c r="H851" t="n">
         <v>2444</v>
@@ -25077,7 +25077,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.28433346748352</v>
+        <v>2.2843337059021</v>
       </c>
       <c r="H852" t="n">
         <v>19648</v>
@@ -25396,7 +25396,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H863" t="n">
         <v>11000</v>
@@ -25425,7 +25425,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>2.32498002052307</v>
+        <v>2.32498025894165</v>
       </c>
       <c r="H864" t="n">
         <v>462</v>
@@ -25454,7 +25454,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H865" t="n">
         <v>4994</v>
@@ -25512,7 +25512,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H867" t="n">
         <v>13328</v>
@@ -25541,7 +25541,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H868" t="n">
         <v>3222</v>
@@ -25570,7 +25570,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H869" t="n">
         <v>2149</v>
@@ -25657,7 +25657,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H872" t="n">
         <v>854</v>
@@ -25686,7 +25686,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>2.4631781578064</v>
+        <v>2.46317791938782</v>
       </c>
       <c r="H873" t="n">
         <v>8240</v>
@@ -25744,7 +25744,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H875" t="n">
         <v>3142</v>
@@ -25889,7 +25889,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H880" t="n">
         <v>3525</v>
@@ -25918,7 +25918,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H881" t="n">
         <v>2373</v>
@@ -25947,7 +25947,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H882" t="n">
         <v>5668</v>
@@ -26034,7 +26034,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H885" t="n">
         <v>538</v>
@@ -26092,7 +26092,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H887" t="n">
         <v>800</v>
@@ -26179,7 +26179,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H890" t="n">
         <v>1360</v>
@@ -26266,7 +26266,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H893" t="n">
         <v>110</v>
@@ -26411,7 +26411,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H898" t="n">
         <v>2539</v>
@@ -26440,7 +26440,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H899" t="n">
         <v>483</v>
@@ -26469,7 +26469,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -26527,7 +26527,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H902" t="n">
         <v>587</v>
@@ -26643,7 +26643,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H906" t="n">
         <v>2576</v>
@@ -26672,7 +26672,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H907" t="n">
         <v>1983</v>
@@ -26730,7 +26730,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>2.55260038375854</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H909" t="n">
         <v>1732</v>
@@ -26788,7 +26788,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="n">
-        <v>2.55260038375854</v>
+        <v>2.55260062217712</v>
       </c>
       <c r="H911" t="n">
         <v>241</v>
@@ -26846,7 +26846,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H913" t="n">
         <v>1085</v>
@@ -26933,7 +26933,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H916" t="n">
         <v>326</v>
@@ -26962,7 +26962,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="n">
-        <v>2.41440272331238</v>
+        <v>2.4144024848938</v>
       </c>
       <c r="H917" t="n">
         <v>2353</v>
@@ -26991,7 +26991,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H918" t="n">
         <v>1740</v>
@@ -27049,7 +27049,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H920" t="n">
         <v>1145</v>
@@ -27078,7 +27078,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H921" t="n">
         <v>26</v>
@@ -27107,7 +27107,7 @@
         <v>29.5</v>
       </c>
       <c r="G922" t="n">
-        <v>2.39814376831055</v>
+        <v>2.39814400672913</v>
       </c>
       <c r="H922" t="n">
         <v>2663</v>
@@ -27136,7 +27136,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H923" t="n">
         <v>3737</v>
@@ -27194,7 +27194,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H925" t="n">
         <v>1884</v>
@@ -27223,7 +27223,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H926" t="n">
         <v>550</v>
@@ -27310,7 +27310,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H929" t="n">
         <v>12745</v>
@@ -27339,7 +27339,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H930" t="n">
         <v>855</v>
@@ -27397,7 +27397,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>2.4631781578064</v>
+        <v>2.46317791938782</v>
       </c>
       <c r="H932" t="n">
         <v>3008</v>
@@ -27426,7 +27426,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H933" t="n">
         <v>570</v>
@@ -27542,7 +27542,7 @@
         <v>29.5</v>
       </c>
       <c r="G937" t="n">
-        <v>2.39814376831055</v>
+        <v>2.39814400672913</v>
       </c>
       <c r="H937" t="n">
         <v>7290</v>
@@ -27571,7 +27571,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="n">
-        <v>2.39814376831055</v>
+        <v>2.39814400672913</v>
       </c>
       <c r="H938" t="n">
         <v>874</v>
@@ -27600,7 +27600,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>2.3900146484375</v>
+        <v>2.39001441001892</v>
       </c>
       <c r="H939" t="n">
         <v>2176</v>
@@ -27629,7 +27629,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H940" t="n">
         <v>650</v>
@@ -27658,7 +27658,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H941" t="n">
         <v>2257</v>
@@ -27687,7 +27687,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H942" t="n">
         <v>1218</v>
@@ -28122,7 +28122,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>2.4631781578064</v>
+        <v>2.46317791938782</v>
       </c>
       <c r="H957" t="n">
         <v>1773</v>
@@ -28586,7 +28586,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H973" t="n">
         <v>1750</v>
@@ -28615,7 +28615,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H974" t="n">
         <v>2339</v>
@@ -28644,7 +28644,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>2.4631781578064</v>
+        <v>2.46317791938782</v>
       </c>
       <c r="H975" t="n">
         <v>1700</v>
@@ -28731,7 +28731,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H978" t="n">
         <v>1913</v>
@@ -28760,7 +28760,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H979" t="n">
         <v>295</v>
@@ -28876,7 +28876,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H983" t="n">
         <v>562</v>
@@ -28934,7 +28934,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H985" t="n">
         <v>1181</v>
@@ -28963,7 +28963,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H986" t="n">
         <v>1030</v>
@@ -29137,7 +29137,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>2.58511757850647</v>
+        <v>2.58511781692505</v>
       </c>
       <c r="H992" t="n">
         <v>1412</v>
@@ -29282,7 +29282,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.5932469367981</v>
+        <v>2.59324717521667</v>
       </c>
       <c r="H997" t="n">
         <v>2043</v>
@@ -29398,7 +29398,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1001" t="n">
         <v>6864</v>
@@ -29456,7 +29456,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1003" t="n">
         <v>101</v>
@@ -29485,7 +29485,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1004" t="n">
         <v>50</v>
@@ -29514,7 +29514,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1005" t="n">
         <v>605</v>
@@ -29543,7 +29543,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.5200834274292</v>
+        <v>2.52008366584778</v>
       </c>
       <c r="H1006" t="n">
         <v>585</v>
@@ -29659,7 +29659,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1010" t="n">
         <v>24</v>
@@ -29688,7 +29688,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1011" t="n">
         <v>1121</v>
@@ -29717,7 +29717,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1012" t="n">
         <v>21303</v>
@@ -29804,7 +29804,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1015" t="n">
         <v>284</v>
@@ -29862,7 +29862,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.47130727767944</v>
+        <v>2.47130751609802</v>
       </c>
       <c r="H1017" t="n">
         <v>2120</v>
@@ -29891,7 +29891,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H1018" t="n">
         <v>5441</v>
@@ -29978,7 +29978,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1021" t="n">
         <v>1241</v>
@@ -30007,7 +30007,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.4875659942627</v>
+        <v>2.48756623268127</v>
       </c>
       <c r="H1022" t="n">
         <v>825</v>
@@ -30036,7 +30036,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.4956955909729</v>
+        <v>2.49569535255432</v>
       </c>
       <c r="H1023" t="n">
         <v>1133</v>
@@ -30065,7 +30065,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1024" t="n">
         <v>15330</v>
@@ -30094,7 +30094,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1025" t="n">
         <v>1646</v>
@@ -30123,7 +30123,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1026" t="n">
         <v>3715</v>
@@ -30152,7 +30152,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.43066120147705</v>
+        <v>2.43066096305847</v>
       </c>
       <c r="H1027" t="n">
         <v>4984</v>
@@ -30181,7 +30181,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1028" t="n">
         <v>637</v>
@@ -30210,7 +30210,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30297,7 +30297,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.45504903793335</v>
+        <v>2.45504879951477</v>
       </c>
       <c r="H1032" t="n">
         <v>515</v>
@@ -30384,7 +30384,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H1035" t="n">
         <v>4055</v>
@@ -30442,7 +30442,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.34936809539795</v>
+        <v>2.34936785697937</v>
       </c>
       <c r="H1037" t="n">
         <v>281</v>
@@ -30500,7 +30500,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.32498002052307</v>
+        <v>2.32498025894165</v>
       </c>
       <c r="H1039" t="n">
         <v>2151</v>
@@ -30529,7 +30529,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>2.28433346748352</v>
+        <v>2.2843337059021</v>
       </c>
       <c r="H1040" t="n">
         <v>2028</v>
@@ -30587,7 +30587,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.3087215423584</v>
+        <v>2.30872130393982</v>
       </c>
       <c r="H1042" t="n">
         <v>304</v>
@@ -30761,7 +30761,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1048" t="n">
         <v>5485</v>
@@ -30848,7 +30848,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>2.32498002052307</v>
+        <v>2.32498025894165</v>
       </c>
       <c r="H1051" t="n">
         <v>425</v>
@@ -30906,7 +30906,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361861228943</v>
       </c>
       <c r="H1053" t="n">
         <v>6320</v>
@@ -31051,7 +31051,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.10548901557922</v>
+        <v>2.10548877716064</v>
       </c>
       <c r="H1058" t="n">
         <v>1769</v>
@@ -31138,7 +31138,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.048583984375</v>
+        <v>2.04858374595642</v>
       </c>
       <c r="H1061" t="n">
         <v>1381</v>
@@ -31167,7 +31167,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.89412701129913</v>
+        <v>1.89412689208984</v>
       </c>
       <c r="H1062" t="n">
         <v>1691</v>
@@ -31341,7 +31341,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.51205015182495</v>
+        <v>1.51205003261566</v>
       </c>
       <c r="H1068" t="n">
         <v>7444</v>
@@ -31399,7 +31399,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.55676102638245</v>
+        <v>1.55676114559174</v>
       </c>
       <c r="H1070" t="n">
         <v>1307</v>
@@ -31457,7 +31457,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.53237342834473</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1072" t="n">
         <v>3746</v>
@@ -31718,7 +31718,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.56895506381989</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1081" t="n">
         <v>3195</v>
@@ -31747,7 +31747,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.56895506381989</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1082" t="n">
         <v>830</v>
@@ -31863,7 +31863,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.63398969173431</v>
+        <v>1.63398945331573</v>
       </c>
       <c r="H1086" t="n">
         <v>6045</v>
@@ -31892,7 +31892,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089448451996</v>
       </c>
       <c r="H1087" t="n">
         <v>6324</v>
@@ -32008,7 +32008,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.62179553508759</v>
+        <v>1.62179565429688</v>
       </c>
       <c r="H1091" t="n">
         <v>4180</v>
@@ -32037,7 +32037,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.63398969173431</v>
+        <v>1.63398945331573</v>
       </c>
       <c r="H1092" t="n">
         <v>531</v>
@@ -32095,7 +32095,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.61773073673248</v>
+        <v>1.61773085594177</v>
       </c>
       <c r="H1094" t="n">
         <v>5830</v>
@@ -32153,7 +32153,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.63398969173431</v>
+        <v>1.63398945331573</v>
       </c>
       <c r="H1096" t="n">
         <v>1044</v>
@@ -32182,7 +32182,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.67463612556458</v>
+        <v>1.674635887146</v>
       </c>
       <c r="H1097" t="n">
         <v>2013</v>
@@ -32211,7 +32211,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1098" t="n">
         <v>2977</v>
@@ -32240,7 +32240,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.76405847072601</v>
+        <v>1.7640585899353</v>
       </c>
       <c r="H1099" t="n">
         <v>3686</v>
@@ -32327,7 +32327,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1102" t="n">
         <v>1150</v>
@@ -32356,7 +32356,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089448451996</v>
       </c>
       <c r="H1103" t="n">
         <v>1415</v>
@@ -32414,7 +32414,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.67463612556458</v>
+        <v>1.674635887146</v>
       </c>
       <c r="H1105" t="n">
         <v>1244</v>
@@ -32443,7 +32443,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.67463612556458</v>
+        <v>1.674635887146</v>
       </c>
       <c r="H1106" t="n">
         <v>660</v>
@@ -32472,7 +32472,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.67463612556458</v>
+        <v>1.674635887146</v>
       </c>
       <c r="H1107" t="n">
         <v>749</v>
@@ -32559,7 +32559,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1110" t="n">
         <v>1215</v>
@@ -32588,7 +32588,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089448451996</v>
       </c>
       <c r="H1111" t="n">
         <v>125</v>
@@ -32646,7 +32646,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.67463612556458</v>
+        <v>1.674635887146</v>
       </c>
       <c r="H1113" t="n">
         <v>865</v>
@@ -32733,7 +32733,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1116" t="n">
         <v>2022</v>
@@ -32762,7 +32762,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1117" t="n">
         <v>705</v>
@@ -32791,7 +32791,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1118" t="n">
         <v>546</v>
@@ -32820,7 +32820,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1119" t="n">
         <v>653</v>
@@ -32849,7 +32849,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1120" t="n">
         <v>2501</v>
@@ -32878,7 +32878,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1121" t="n">
         <v>1115</v>
@@ -32907,7 +32907,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.75592911243439</v>
+        <v>1.7559289932251</v>
       </c>
       <c r="H1122" t="n">
         <v>3180</v>
@@ -32994,7 +32994,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.82096326351166</v>
+        <v>1.82096338272095</v>
       </c>
       <c r="H1125" t="n">
         <v>10904</v>
@@ -33052,7 +33052,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.87786865234375</v>
+        <v>1.87786853313446</v>
       </c>
       <c r="H1127" t="n">
         <v>3120</v>
@@ -33081,7 +33081,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1128" t="n">
         <v>2449</v>
@@ -33226,7 +33226,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.80470490455627</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1133" t="n">
         <v>100</v>
@@ -33255,7 +33255,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.82096326351166</v>
+        <v>1.82096338272095</v>
       </c>
       <c r="H1134" t="n">
         <v>1491</v>
@@ -33313,7 +33313,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.81283414363861</v>
+        <v>1.8128342628479</v>
       </c>
       <c r="H1136" t="n">
         <v>1910</v>
@@ -33342,7 +33342,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.79657566547394</v>
+        <v>1.79657554626465</v>
       </c>
       <c r="H1137" t="n">
         <v>525</v>
@@ -33458,7 +33458,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.80470490455627</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1141" t="n">
         <v>161</v>
@@ -33487,7 +33487,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.80470490455627</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1142" t="n">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.81283414363861</v>
+        <v>1.8128342628479</v>
       </c>
       <c r="H1145" t="n">
         <v>480</v>
@@ -33603,7 +33603,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.80470490455627</v>
+        <v>1.80470478534698</v>
       </c>
       <c r="H1146" t="n">
         <v>30</v>
@@ -33632,7 +33632,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.79657566547394</v>
+        <v>1.79657554626465</v>
       </c>
       <c r="H1147" t="n">
         <v>103</v>
@@ -33661,7 +33661,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1148" t="n">
         <v>1910</v>
@@ -33690,7 +33690,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.76405847072601</v>
+        <v>1.7640585899353</v>
       </c>
       <c r="H1149" t="n">
         <v>143</v>
@@ -33748,7 +33748,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1151" t="n">
         <v>3317</v>
@@ -33835,7 +33835,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.76405847072601</v>
+        <v>1.7640585899353</v>
       </c>
       <c r="H1154" t="n">
         <v>50</v>
@@ -33951,7 +33951,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.73967027664185</v>
+        <v>1.73967039585114</v>
       </c>
       <c r="H1158" t="n">
         <v>1478</v>
@@ -33980,7 +33980,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089448451996</v>
       </c>
       <c r="H1159" t="n">
         <v>1358</v>
@@ -34009,7 +34009,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1160" t="n">
         <v>405</v>
@@ -34038,7 +34038,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1161" t="n">
         <v>200</v>
@@ -34067,7 +34067,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1162" t="n">
         <v>185</v>
@@ -34154,7 +34154,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1165" t="n">
         <v>675</v>
@@ -34183,7 +34183,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.73967027664185</v>
+        <v>1.73967039585114</v>
       </c>
       <c r="H1166" t="n">
         <v>1391</v>
@@ -34212,7 +34212,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.69089460372925</v>
+        <v>1.69089448451996</v>
       </c>
       <c r="H1167" t="n">
         <v>1114</v>
@@ -34241,7 +34241,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.69902384281158</v>
+        <v>1.69902396202087</v>
       </c>
       <c r="H1168" t="n">
         <v>182</v>
@@ -34328,7 +34328,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1171" t="n">
         <v>330</v>
@@ -34386,7 +34386,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1173" t="n">
         <v>886</v>
@@ -34444,7 +34444,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.73967027664185</v>
+        <v>1.73967039585114</v>
       </c>
       <c r="H1175" t="n">
         <v>176</v>
@@ -34473,7 +34473,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.76405847072601</v>
+        <v>1.7640585899353</v>
       </c>
       <c r="H1176" t="n">
         <v>992</v>
@@ -34502,7 +34502,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1177" t="n">
         <v>402</v>
@@ -34531,7 +34531,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1178" t="n">
         <v>250</v>
@@ -34589,7 +34589,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.75592911243439</v>
+        <v>1.7559289932251</v>
       </c>
       <c r="H1180" t="n">
         <v>289</v>
@@ -34618,7 +34618,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.74779987335205</v>
+        <v>1.74779975414276</v>
       </c>
       <c r="H1181" t="n">
         <v>15</v>
@@ -34705,7 +34705,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.75592911243439</v>
+        <v>1.7559289932251</v>
       </c>
       <c r="H1184" t="n">
         <v>110</v>
@@ -34734,7 +34734,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1185" t="n">
         <v>3347</v>
@@ -34763,7 +34763,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.70715320110321</v>
+        <v>1.7071533203125</v>
       </c>
       <c r="H1186" t="n">
         <v>5</v>
@@ -34966,7 +34966,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.61773073673248</v>
+        <v>1.61773085594177</v>
       </c>
       <c r="H1193" t="n">
         <v>105</v>
@@ -34995,7 +34995,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.63398969173431</v>
+        <v>1.63398945331573</v>
       </c>
       <c r="H1194" t="n">
         <v>630</v>
@@ -35256,7 +35256,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.57708430290222</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1203" t="n">
         <v>1145</v>
@@ -35314,7 +35314,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.57708430290222</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1205" t="n">
         <v>2215</v>
@@ -35372,7 +35372,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.57708430290222</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1207" t="n">
         <v>299</v>
@@ -35459,7 +35459,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1210" t="n">
         <v>1502</v>
@@ -35488,7 +35488,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.57708430290222</v>
+        <v>1.57708442211151</v>
       </c>
       <c r="H1211" t="n">
         <v>302</v>
@@ -35575,7 +35575,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1214" t="n">
         <v>540</v>
@@ -35633,7 +35633,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.43075704574585</v>
+        <v>1.43075692653656</v>
       </c>
       <c r="H1216" t="n">
         <v>2095</v>
@@ -35923,7 +35923,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.35759329795837</v>
+        <v>1.35759317874908</v>
       </c>
       <c r="H1226" t="n">
         <v>100</v>
@@ -36010,7 +36010,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.29255878925323</v>
+        <v>1.29255890846252</v>
       </c>
       <c r="H1229" t="n">
         <v>989</v>
@@ -36126,7 +36126,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.34946405887604</v>
+        <v>1.34946393966675</v>
       </c>
       <c r="H1233" t="n">
         <v>466</v>
@@ -36155,7 +36155,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.37385189533234</v>
+        <v>1.37385177612305</v>
       </c>
       <c r="H1234" t="n">
         <v>1911</v>
@@ -36358,7 +36358,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39011061191559</v>
+        <v>1.3901104927063</v>
       </c>
       <c r="H1241" t="n">
         <v>2655</v>
@@ -36561,7 +36561,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.48766207695007</v>
+        <v>1.48766195774078</v>
       </c>
       <c r="H1248" t="n">
         <v>2886</v>
@@ -36619,7 +36619,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1250" t="n">
         <v>4696</v>
@@ -36764,7 +36764,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.49172687530518</v>
+        <v>1.49172675609589</v>
       </c>
       <c r="H1255" t="n">
         <v>3603</v>
@@ -36938,7 +36938,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.53237342834473</v>
+        <v>1.53237330913544</v>
       </c>
       <c r="H1261" t="n">
         <v>4222</v>
@@ -36967,7 +36967,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.51205015182495</v>
+        <v>1.51205003261566</v>
       </c>
       <c r="H1262" t="n">
         <v>2986</v>
@@ -36996,7 +36996,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1263" t="n">
         <v>3075</v>
@@ -37141,7 +37141,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.50798535346985</v>
+        <v>1.50798523426056</v>
       </c>
       <c r="H1268" t="n">
         <v>960</v>
@@ -37257,7 +37257,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1272" t="n">
         <v>822</v>
@@ -37286,7 +37286,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.56895506381989</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1273" t="n">
         <v>2790</v>
@@ -37344,7 +37344,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.56895506381989</v>
+        <v>1.56895518302917</v>
       </c>
       <c r="H1275" t="n">
         <v>5078</v>
@@ -37373,7 +37373,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1276" t="n">
         <v>3233</v>
@@ -37518,7 +37518,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.53643774986267</v>
+        <v>1.53643786907196</v>
       </c>
       <c r="H1281" t="n">
         <v>355</v>
@@ -37982,7 +37982,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.32498002052307</v>
+        <v>2.32498025894165</v>
       </c>
       <c r="H1297" t="n">
         <v>34162</v>
@@ -38040,7 +38040,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.37375617027283</v>
+        <v>2.37375593185425</v>
       </c>
       <c r="H1299" t="n">
         <v>11185</v>
@@ -38098,7 +38098,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.32498002052307</v>
+        <v>2.32498025894165</v>
       </c>
       <c r="H1301" t="n">
         <v>6160</v>
@@ -38156,7 +38156,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.35749745368958</v>
+        <v>2.357497215271</v>
       </c>
       <c r="H1303" t="n">
         <v>3636</v>
@@ -38272,7 +38272,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.3087215423584</v>
+        <v>2.30872130393982</v>
       </c>
       <c r="H1307" t="n">
         <v>2734</v>
@@ -38301,7 +38301,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.3087215423584</v>
+        <v>2.30872130393982</v>
       </c>
       <c r="H1308" t="n">
         <v>12016</v>
@@ -38736,7 +38736,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361861228943</v>
       </c>
       <c r="H1323" t="n">
         <v>547</v>
@@ -38823,7 +38823,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.05671310424805</v>
+        <v>2.05671286582947</v>
       </c>
       <c r="H1326" t="n">
         <v>2194</v>
@@ -38910,7 +38910,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.11361837387085</v>
+        <v>2.11361861228943</v>
       </c>
       <c r="H1329" t="n">
         <v>574</v>
@@ -38997,7 +38997,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1332" t="n">
         <v>261</v>
@@ -39026,7 +39026,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.13800621032715</v>
+        <v>2.13800597190857</v>
       </c>
       <c r="H1333" t="n">
         <v>364</v>
@@ -39084,7 +39084,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.21116995811462</v>
+        <v>2.21116971969604</v>
       </c>
       <c r="H1335" t="n">
         <v>2277</v>
@@ -39113,7 +39113,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.21116995811462</v>
+        <v>2.21116971969604</v>
       </c>
       <c r="H1336" t="n">
         <v>1420</v>
@@ -39171,7 +39171,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.21116995811462</v>
+        <v>2.21116971969604</v>
       </c>
       <c r="H1338" t="n">
         <v>8557</v>
@@ -39461,7 +39461,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1348" t="n">
         <v>260</v>
@@ -39490,7 +39490,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1349" t="n">
         <v>2010</v>
@@ -39809,7 +39809,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1360" t="n">
         <v>315</v>
@@ -39867,7 +39867,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1362" t="n">
         <v>1587</v>
@@ -40041,7 +40041,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1368" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1368" t="n">
         <v>2585</v>
@@ -40070,7 +40070,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1369" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1369" t="n">
         <v>3238</v>
@@ -40157,7 +40157,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1372" t="n">
         <v>4467</v>
@@ -40476,7 +40476,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1383" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1383" t="n">
         <v>30</v>
@@ -40563,7 +40563,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>2.47617888450623</v>
+        <v>2.4761791229248</v>
       </c>
       <c r="H1386" t="n">
         <v>12870</v>
@@ -40708,7 +40708,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.41820859909058</v>
+        <v>2.418208360672</v>
       </c>
       <c r="H1391" t="n">
         <v>1103</v>
@@ -40766,7 +40766,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1393" t="n">
         <v>3074</v>
@@ -40940,7 +40940,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1399" t="n">
         <v>110</v>
@@ -40969,7 +40969,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1400" t="n">
         <v>4528</v>
@@ -41056,7 +41056,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1403" t="n">
         <v>7033</v>
@@ -41259,7 +41259,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1410" t="n">
         <v>603</v>
@@ -41317,7 +41317,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1412" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1412" t="n">
         <v>1570</v>
@@ -41346,7 +41346,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1413" t="n">
         <v>722</v>
@@ -41404,7 +41404,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1415" t="n">
         <v>827</v>
@@ -41578,7 +41578,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.41820859909058</v>
+        <v>2.418208360672</v>
       </c>
       <c r="H1421" t="n">
         <v>2630</v>
@@ -41665,7 +41665,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1424" t="n">
         <v>784</v>
@@ -41694,7 +41694,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1425" t="n">
         <v>1447</v>
@@ -41752,7 +41752,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1427" t="n">
         <v>706</v>
@@ -41781,7 +41781,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1428" t="n">
         <v>83</v>
@@ -41810,7 +41810,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1429" t="n">
         <v>110</v>
@@ -41839,7 +41839,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.38508200645447</v>
+        <v>2.38508224487305</v>
       </c>
       <c r="H1430" t="n">
         <v>52</v>
@@ -41926,7 +41926,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.32711124420166</v>
+        <v>2.32711148262024</v>
       </c>
       <c r="H1433" t="n">
         <v>2277</v>
@@ -42245,7 +42245,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.3519561290741</v>
+        <v>2.35195589065552</v>
       </c>
       <c r="H1444" t="n">
         <v>1866</v>
@@ -42564,7 +42564,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.32711124420166</v>
+        <v>2.32711148262024</v>
       </c>
       <c r="H1455" t="n">
         <v>1776</v>
@@ -42941,7 +42941,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.32711124420166</v>
+        <v>2.32711148262024</v>
       </c>
       <c r="H1468" t="n">
         <v>141</v>
@@ -43144,7 +43144,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.3519561290741</v>
+        <v>2.35195589065552</v>
       </c>
       <c r="H1475" t="n">
         <v>691</v>
@@ -43173,7 +43173,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1476" t="n">
-        <v>2.3519561290741</v>
+        <v>2.35195589065552</v>
       </c>
       <c r="H1476" t="n">
         <v>1400</v>
@@ -43202,7 +43202,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.37680053710938</v>
+        <v>2.37680077552795</v>
       </c>
       <c r="H1477" t="n">
         <v>169</v>
@@ -43579,7 +43579,7 @@
         <v>27.5</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1490" t="n">
         <v>3333</v>
@@ -43637,7 +43637,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1492" t="n">
         <v>4229</v>
@@ -43695,7 +43695,7 @@
         <v>26</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1494" t="n">
         <v>4950</v>
@@ -43753,7 +43753,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.12835478782654</v>
+        <v>2.12835454940796</v>
       </c>
       <c r="H1496" t="n">
         <v>5031</v>
@@ -43782,7 +43782,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.13663625717163</v>
+        <v>2.13663601875305</v>
       </c>
       <c r="H1497" t="n">
         <v>556</v>
@@ -43811,7 +43811,7 @@
         <v>26</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1498" t="n">
         <v>4241</v>
@@ -43840,7 +43840,7 @@
         <v>26</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1499" t="n">
         <v>107</v>
@@ -43869,7 +43869,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.18632507324219</v>
+        <v>2.18632531166077</v>
       </c>
       <c r="H1500" t="n">
         <v>252</v>
@@ -43898,7 +43898,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.18632507324219</v>
+        <v>2.18632531166077</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -43927,7 +43927,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.12835478782654</v>
+        <v>2.12835454940796</v>
       </c>
       <c r="H1502" t="n">
         <v>3129</v>
@@ -43956,7 +43956,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.08694696426392</v>
+        <v>2.08694672584534</v>
       </c>
       <c r="H1503" t="n">
         <v>684</v>
@@ -43985,7 +43985,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.1035099029541</v>
+        <v>2.10351014137268</v>
       </c>
       <c r="H1504" t="n">
         <v>610</v>
@@ -44043,7 +44043,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.13663625717163</v>
+        <v>2.13663601875305</v>
       </c>
       <c r="H1506" t="n">
         <v>1917</v>
@@ -44072,7 +44072,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.13663625717163</v>
+        <v>2.13663601875305</v>
       </c>
       <c r="H1507" t="n">
         <v>331</v>
@@ -44101,7 +44101,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.13663625717163</v>
+        <v>2.13663601875305</v>
       </c>
       <c r="H1508" t="n">
         <v>1055</v>
@@ -44130,7 +44130,7 @@
         <v>26</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1509" t="n">
         <v>617</v>
@@ -44217,7 +44217,7 @@
         <v>26</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1512" t="n">
         <v>1674</v>
@@ -44275,7 +44275,7 @@
         <v>26</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1514" t="n">
         <v>9003</v>
@@ -44304,7 +44304,7 @@
         <v>26</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1515" t="n">
         <v>561</v>
@@ -44333,7 +44333,7 @@
         <v>26</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.15319919586182</v>
+        <v>2.1531994342804</v>
       </c>
       <c r="H1516" t="n">
         <v>2644</v>
@@ -44739,7 +44739,7 @@
         <v>27.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1530" t="n">
         <v>242</v>
@@ -44826,7 +44826,7 @@
         <v>27.5</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1533" t="n">
         <v>200</v>
@@ -44855,7 +44855,7 @@
         <v>27.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1534" t="n">
         <v>0</v>
@@ -44884,7 +44884,7 @@
         <v>27.5</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1535" t="n">
         <v>300</v>
@@ -44913,7 +44913,7 @@
         <v>27.5</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1536" t="n">
         <v>0</v>
@@ -45000,7 +45000,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1539" t="n">
         <v>42</v>
@@ -45087,7 +45087,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.18632507324219</v>
+        <v>2.18632531166077</v>
       </c>
       <c r="H1542" t="n">
         <v>511</v>
@@ -45174,7 +45174,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.20288848876953</v>
+        <v>2.20288825035095</v>
       </c>
       <c r="H1545" t="n">
         <v>70</v>
@@ -45464,7 +45464,7 @@
         <v>27.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1555" t="n">
         <v>107</v>
@@ -45493,7 +45493,7 @@
         <v>27.5</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1556" t="n">
         <v>639</v>
@@ -45551,7 +45551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.2774224281311</v>
+        <v>2.27742218971252</v>
       </c>
       <c r="H1558" t="n">
         <v>1582</v>
@@ -45754,7 +45754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.41820859909058</v>
+        <v>2.418208360672</v>
       </c>
       <c r="H1565" t="n">
         <v>2831</v>
@@ -45870,7 +45870,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.4099268913269</v>
+        <v>2.40992665290833</v>
       </c>
       <c r="H1569" t="n">
         <v>420</v>
@@ -45899,7 +45899,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.47617888450623</v>
+        <v>2.4761791229248</v>
       </c>
       <c r="H1570" t="n">
         <v>3995</v>
@@ -45986,7 +45986,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.46789717674255</v>
+        <v>2.46789741516113</v>
       </c>
       <c r="H1573" t="n">
         <v>685</v>
@@ -46015,7 +46015,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.50102376937866</v>
+        <v>2.50102353096008</v>
       </c>
       <c r="H1574" t="n">
         <v>6269</v>
@@ -46073,7 +46073,7 @@
         <v>30.5</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.52586817741394</v>
+        <v>2.52586841583252</v>
       </c>
       <c r="H1576" t="n">
         <v>2316</v>
@@ -46102,7 +46102,7 @@
         <v>30.5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.52586817741394</v>
+        <v>2.52586841583252</v>
       </c>
       <c r="H1577" t="n">
         <v>2195</v>
@@ -46131,7 +46131,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.50930523872375</v>
+        <v>2.50930500030518</v>
       </c>
       <c r="H1578" t="n">
         <v>2055</v>
@@ -46218,7 +46218,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.69978046417236</v>
+        <v>2.69978022575378</v>
       </c>
       <c r="H1581" t="n">
         <v>4224</v>
@@ -46363,7 +46363,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.03104186058044</v>
+        <v>3.03104162216187</v>
       </c>
       <c r="H1586" t="n">
         <v>4777</v>
@@ -46653,7 +46653,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.21323585510254</v>
+        <v>3.21323561668396</v>
       </c>
       <c r="H1596" t="n">
         <v>2947</v>
@@ -46972,7 +46972,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1607" t="n">
         <v>5882</v>
@@ -47088,7 +47088,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244944572449</v>
       </c>
       <c r="H1611" t="n">
         <v>2250</v>
@@ -47117,7 +47117,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1612" t="n">
         <v>150</v>
@@ -47175,7 +47175,7 @@
         <v>37</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1614" t="n">
         <v>1853</v>
@@ -47204,7 +47204,7 @@
         <v>37</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1615" t="n">
         <v>1740</v>
@@ -47407,7 +47407,7 @@
         <v>35.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.93994498252869</v>
+        <v>2.93994522094727</v>
       </c>
       <c r="H1622" t="n">
         <v>2912</v>
@@ -47552,7 +47552,7 @@
         <v>37</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1627" t="n">
         <v>500</v>
@@ -47610,7 +47610,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.04760479927063</v>
+        <v>3.04760503768921</v>
       </c>
       <c r="H1629" t="n">
         <v>1053</v>
@@ -47697,7 +47697,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.03104186058044</v>
+        <v>3.03104162216187</v>
       </c>
       <c r="H1632" t="n">
         <v>112</v>
@@ -47726,7 +47726,7 @@
         <v>37</v>
       </c>
       <c r="G1633" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1633" t="n">
         <v>593</v>
@@ -47813,7 +47813,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1636" t="n">
         <v>365</v>
@@ -47958,7 +47958,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1641" t="n">
         <v>3746</v>
@@ -48016,7 +48016,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1643" t="n">
         <v>1105</v>
@@ -48480,7 +48480,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1659" t="n">
         <v>408</v>
@@ -48944,7 +48944,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.03104186058044</v>
+        <v>3.03104162216187</v>
       </c>
       <c r="H1675" t="n">
         <v>239</v>
@@ -48973,7 +48973,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1676" t="n">
         <v>460</v>
@@ -49031,7 +49031,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.03932332992554</v>
+        <v>3.03932356834412</v>
       </c>
       <c r="H1678" t="n">
         <v>1165</v>
@@ -49060,7 +49060,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1679" t="n">
         <v>653</v>
@@ -49089,7 +49089,7 @@
         <v>37</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1680" t="n">
         <v>61</v>
@@ -49118,7 +49118,7 @@
         <v>37</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1681" t="n">
         <v>25</v>
@@ -49234,7 +49234,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.03932332992554</v>
+        <v>3.03932356834412</v>
       </c>
       <c r="H1685" t="n">
         <v>200</v>
@@ -49292,7 +49292,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1687" t="n">
         <v>76</v>
@@ -49321,7 +49321,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1688" t="n">
         <v>0</v>
@@ -49495,7 +49495,7 @@
         <v>37</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1694" t="n">
         <v>3210</v>
@@ -49524,7 +49524,7 @@
         <v>37</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1695" t="n">
         <v>46</v>
@@ -49553,7 +49553,7 @@
         <v>37</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1696" t="n">
         <v>3</v>
@@ -49727,7 +49727,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1702" t="n">
         <v>142</v>
@@ -49756,7 +49756,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1703" t="n">
         <v>0</v>
@@ -49785,7 +49785,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1704" t="n">
         <v>395</v>
@@ -49814,7 +49814,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1705" t="n">
-        <v>3.03932332992554</v>
+        <v>3.03932356834412</v>
       </c>
       <c r="H1705" t="n">
         <v>170</v>
@@ -49843,7 +49843,7 @@
         <v>37</v>
       </c>
       <c r="G1706" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1706" t="n">
         <v>63</v>
@@ -49872,7 +49872,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.03104186058044</v>
+        <v>3.03104162216187</v>
       </c>
       <c r="H1707" t="n">
         <v>30</v>
@@ -49901,7 +49901,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1708" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244944572449</v>
       </c>
       <c r="H1708" t="n">
         <v>796</v>
@@ -49930,7 +49930,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.04760479927063</v>
+        <v>3.04760503768921</v>
       </c>
       <c r="H1709" t="n">
         <v>546</v>
@@ -49959,7 +49959,7 @@
         <v>37</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1710" t="n">
         <v>2446</v>
@@ -49988,7 +49988,7 @@
         <v>37</v>
       </c>
       <c r="G1711" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1711" t="n">
         <v>0</v>
@@ -50249,7 +50249,7 @@
         <v>37</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1720" t="n">
         <v>1410</v>
@@ -50336,7 +50336,7 @@
         <v>37</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1723" t="n">
         <v>2800</v>
@@ -50365,7 +50365,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1724" t="n">
         <v>1000</v>
@@ -50394,7 +50394,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1725" t="n">
         <v>0</v>
@@ -50452,7 +50452,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.04760479927063</v>
+        <v>3.04760503768921</v>
       </c>
       <c r="H1727" t="n">
         <v>91</v>
@@ -50481,7 +50481,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.04760479927063</v>
+        <v>3.04760503768921</v>
       </c>
       <c r="H1728" t="n">
         <v>3500</v>
@@ -50510,7 +50510,7 @@
         <v>37</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1729" t="n">
         <v>7186</v>
@@ -50539,7 +50539,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.0558865070343</v>
+        <v>3.05588674545288</v>
       </c>
       <c r="H1730" t="n">
         <v>4694</v>
@@ -50626,7 +50626,7 @@
         <v>37</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1733" t="n">
         <v>3284</v>
@@ -50655,7 +50655,7 @@
         <v>37</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1734" t="n">
         <v>886</v>
@@ -50684,7 +50684,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1735" t="n">
         <v>1334</v>
@@ -50742,7 +50742,7 @@
         <v>37</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1737" t="n">
         <v>860</v>
@@ -50800,7 +50800,7 @@
         <v>37</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.06416821479797</v>
+        <v>3.06416797637939</v>
       </c>
       <c r="H1739" t="n">
         <v>958</v>
@@ -50887,7 +50887,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1742" t="n">
         <v>1413</v>
@@ -50916,7 +50916,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1743" t="n">
         <v>71451</v>
@@ -50945,7 +50945,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1744" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244944572449</v>
       </c>
       <c r="H1744" t="n">
         <v>53786</v>
@@ -50974,7 +50974,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1745" t="n">
         <v>4978</v>
@@ -51061,7 +51061,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1748" t="n">
-        <v>3.07244968414307</v>
+        <v>3.07244944572449</v>
       </c>
       <c r="H1748" t="n">
         <v>4653</v>
@@ -51177,7 +51177,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.08901262283325</v>
+        <v>3.08901286125183</v>
       </c>
       <c r="H1752" t="n">
         <v>4145</v>
@@ -51496,7 +51496,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1763" t="n">
-        <v>3.11385726928711</v>
+        <v>3.11385703086853</v>
       </c>
       <c r="H1763" t="n">
         <v>11932</v>
@@ -52047,7 +52047,7 @@
         <v>11.5</v>
       </c>
       <c r="G1782" t="n">
-        <v>5.01585006713867</v>
+        <v>5.01585054397583</v>
       </c>
       <c r="H1782" t="n">
         <v>29263</v>
@@ -52076,7 +52076,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1783" t="n">
-        <v>5.58285999298096</v>
+        <v>5.5828595161438</v>
       </c>
       <c r="H1783" t="n">
         <v>88580</v>
@@ -52105,7 +52105,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1784" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1784" t="n">
         <v>63372</v>
@@ -52250,7 +52250,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1789" t="n">
-        <v>5.14669895172119</v>
+        <v>5.14669847488403</v>
       </c>
       <c r="H1789" t="n">
         <v>19527</v>
@@ -52366,7 +52366,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1793" t="n">
-        <v>5.21212244033813</v>
+        <v>5.21212291717529</v>
       </c>
       <c r="H1793" t="n">
         <v>17331</v>
@@ -52395,7 +52395,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.14669895172119</v>
+        <v>5.14669847488403</v>
       </c>
       <c r="H1794" t="n">
         <v>14779</v>
@@ -52540,7 +52540,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1799" t="n">
-        <v>5.53924322128296</v>
+        <v>5.53924369812012</v>
       </c>
       <c r="H1799" t="n">
         <v>13906</v>
@@ -52598,7 +52598,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1801" t="n">
         <v>9611</v>
@@ -52656,7 +52656,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1803" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1803" t="n">
         <v>17158</v>
@@ -52685,7 +52685,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>5.43020296096802</v>
+        <v>5.43020343780518</v>
       </c>
       <c r="H1804" t="n">
         <v>13501</v>
@@ -52714,7 +52714,7 @@
         <v>12.25</v>
       </c>
       <c r="G1805" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1805" t="n">
         <v>6792</v>
@@ -52743,7 +52743,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1806" t="n">
         <v>7235</v>
@@ -52830,7 +52830,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1809" t="n">
         <v>6507</v>
@@ -52859,7 +52859,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1810" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1810" t="n">
         <v>8854</v>
@@ -52917,7 +52917,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1812" t="n">
         <v>9617</v>
@@ -52975,7 +52975,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1814" t="n">
-        <v>5.36477947235107</v>
+        <v>5.36477899551392</v>
       </c>
       <c r="H1814" t="n">
         <v>872</v>
@@ -53004,7 +53004,7 @@
         <v>12.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1815" t="n">
         <v>5517</v>
@@ -53033,7 +53033,7 @@
         <v>12.25</v>
       </c>
       <c r="G1816" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1816" t="n">
         <v>8058</v>
@@ -53062,7 +53062,7 @@
         <v>12.25</v>
       </c>
       <c r="G1817" t="n">
-        <v>5.34297132492065</v>
+        <v>5.3429708480835</v>
       </c>
       <c r="H1817" t="n">
         <v>10014</v>
@@ -53091,7 +53091,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1818" t="n">
-        <v>5.38658761978149</v>
+        <v>5.38658714294434</v>
       </c>
       <c r="H1818" t="n">
         <v>6825</v>
@@ -53236,7 +53236,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1823" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1823" t="n">
         <v>239358</v>
@@ -53294,7 +53294,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>6.93495845794678</v>
+        <v>6.93495798110962</v>
       </c>
       <c r="H1825" t="n">
         <v>187542</v>
@@ -53323,7 +53323,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1826" t="n">
-        <v>6.782301902771</v>
+        <v>6.78230237960815</v>
       </c>
       <c r="H1826" t="n">
         <v>81830</v>
@@ -53352,7 +53352,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>6.73868608474731</v>
+        <v>6.73868560791016</v>
       </c>
       <c r="H1827" t="n">
         <v>53720</v>
@@ -53497,7 +53497,7 @@
         <v>14.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>6.32433271408081</v>
+        <v>6.32433319091797</v>
       </c>
       <c r="H1832" t="n">
         <v>51065</v>
@@ -53671,7 +53671,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="n">
-        <v>6.62964582443237</v>
+        <v>6.62964534759521</v>
       </c>
       <c r="H1838" t="n">
         <v>62153</v>
@@ -53700,7 +53700,7 @@
         <v>15.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>6.76049375534058</v>
+        <v>6.76049423217773</v>
       </c>
       <c r="H1839" t="n">
         <v>45114</v>
@@ -53729,7 +53729,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1840" t="n">
-        <v>6.782301902771</v>
+        <v>6.78230237960815</v>
       </c>
       <c r="H1840" t="n">
         <v>29296</v>
@@ -53758,7 +53758,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1841" t="n">
         <v>16687</v>
@@ -53787,7 +53787,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1842" t="n">
-        <v>6.82591772079468</v>
+        <v>6.82591819763184</v>
       </c>
       <c r="H1842" t="n">
         <v>31740</v>
@@ -53816,7 +53816,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.0221905708313</v>
+        <v>7.02219104766846</v>
       </c>
       <c r="H1843" t="n">
         <v>31076</v>
@@ -53845,7 +53845,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.06580686569214</v>
+        <v>7.0658073425293</v>
       </c>
       <c r="H1844" t="n">
         <v>50948</v>
@@ -53874,7 +53874,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.04399824142456</v>
+        <v>7.04399871826172</v>
       </c>
       <c r="H1845" t="n">
         <v>21268</v>
@@ -53932,7 +53932,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.06580686569214</v>
+        <v>7.0658073425293</v>
       </c>
       <c r="H1847" t="n">
         <v>32316</v>
@@ -53961,7 +53961,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.45835161209106</v>
+        <v>7.45835208892822</v>
       </c>
       <c r="H1848" t="n">
         <v>130442</v>
@@ -53990,7 +53990,7 @@
         <v>17.25</v>
       </c>
       <c r="G1849" t="n">
-        <v>7.52377557754517</v>
+        <v>7.52377510070801</v>
       </c>
       <c r="H1849" t="n">
         <v>125182</v>
@@ -54019,7 +54019,7 @@
         <v>17.25</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.52377557754517</v>
+        <v>7.52377510070801</v>
       </c>
       <c r="H1850" t="n">
         <v>51748</v>
@@ -54135,7 +54135,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>8.11259269714355</v>
+        <v>8.11259365081787</v>
       </c>
       <c r="H1854" t="n">
         <v>76643</v>
@@ -80183,6 +80183,35 @@
         <v>278</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>3995</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24544644355774</v>
+        <v>1.24544656276703</v>
       </c>
       <c r="H3" t="n">
         <v>625</v>
@@ -485,7 +485,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H4" t="n">
         <v>158</v>
@@ -514,7 +514,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H5" t="n">
         <v>1168</v>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H6" t="n">
         <v>466</v>
@@ -572,7 +572,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2218531370163</v>
+        <v>1.22185301780701</v>
       </c>
       <c r="H7" t="n">
         <v>1052</v>
@@ -601,7 +601,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H8" t="n">
         <v>1518</v>
@@ -688,7 +688,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>1.20683896541595</v>
+        <v>1.20683884620667</v>
       </c>
       <c r="H11" t="n">
         <v>9368</v>
@@ -717,7 +717,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G12" t="n">
-        <v>1.20111930370331</v>
+        <v>1.2011194229126</v>
       </c>
       <c r="H12" t="n">
         <v>76</v>
@@ -746,7 +746,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G13" t="n">
-        <v>1.20040464401245</v>
+        <v>1.20040452480316</v>
       </c>
       <c r="H13" t="n">
         <v>1439</v>
@@ -862,7 +862,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H17" t="n">
         <v>7168</v>
@@ -920,7 +920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687647819519</v>
       </c>
       <c r="H19" t="n">
         <v>5142</v>
@@ -949,7 +949,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2468763589859</v>
+        <v>1.24687647819519</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -1007,7 +1007,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G22" t="n">
-        <v>1.26475036144257</v>
+        <v>1.26475024223328</v>
       </c>
       <c r="H22" t="n">
         <v>1772</v>
@@ -1036,7 +1036,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21470355987549</v>
+        <v>1.21470367908478</v>
       </c>
       <c r="H23" t="n">
         <v>1866</v>
@@ -1065,7 +1065,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21541845798492</v>
+        <v>1.21541857719421</v>
       </c>
       <c r="H24" t="n">
         <v>132</v>
@@ -1094,7 +1094,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2354371547699</v>
+        <v>1.23543727397919</v>
       </c>
       <c r="H25" t="n">
         <v>505</v>
@@ -1152,7 +1152,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>1.20040464401245</v>
+        <v>1.20040452480316</v>
       </c>
       <c r="H27" t="n">
         <v>4499</v>
@@ -1210,7 +1210,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G29" t="n">
-        <v>1.22113811969757</v>
+        <v>1.22113800048828</v>
       </c>
       <c r="H29" t="n">
         <v>111</v>
@@ -1239,7 +1239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G30" t="n">
-        <v>1.19396984577179</v>
+        <v>1.19396996498108</v>
       </c>
       <c r="H30" t="n">
         <v>419</v>
@@ -1268,7 +1268,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H31" t="n">
         <v>39</v>
@@ -1297,7 +1297,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22685766220093</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H32" t="n">
         <v>554</v>
@@ -1355,7 +1355,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22256803512573</v>
+        <v>1.22256815433502</v>
       </c>
       <c r="H34" t="n">
         <v>772</v>
@@ -1645,7 +1645,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>1.24330163002014</v>
+        <v>1.24330174922943</v>
       </c>
       <c r="H44" t="n">
         <v>139</v>
@@ -1877,7 +1877,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G52" t="n">
-        <v>1.27904915809631</v>
+        <v>1.27904939651489</v>
       </c>
       <c r="H52" t="n">
         <v>663</v>
@@ -2167,7 +2167,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G62" t="n">
-        <v>1.24830615520477</v>
+        <v>1.24830627441406</v>
       </c>
       <c r="H62" t="n">
         <v>745</v>
@@ -2254,7 +2254,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G65" t="n">
-        <v>1.25045120716095</v>
+        <v>1.25045132637024</v>
       </c>
       <c r="H65" t="n">
         <v>90</v>
@@ -2283,7 +2283,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24258649349213</v>
+        <v>1.24258661270142</v>
       </c>
       <c r="H66" t="n">
         <v>1317</v>
@@ -2341,7 +2341,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G68" t="n">
-        <v>1.22685766220093</v>
+        <v>1.22685778141022</v>
       </c>
       <c r="H68" t="n">
         <v>2044</v>
@@ -2428,7 +2428,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>1.23400735855103</v>
+        <v>1.23400747776031</v>
       </c>
       <c r="H71" t="n">
         <v>6242</v>
@@ -2457,7 +2457,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G72" t="n">
-        <v>1.2354371547699</v>
+        <v>1.23543727397919</v>
       </c>
       <c r="H72" t="n">
         <v>795</v>
@@ -2544,7 +2544,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25225365161896</v>
+        <v>1.25225353240967</v>
       </c>
       <c r="H75" t="n">
         <v>1086</v>
@@ -2718,7 +2718,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27640569210052</v>
+        <v>1.27640581130981</v>
       </c>
       <c r="H81" t="n">
         <v>410</v>
@@ -2747,7 +2747,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>1.27421009540558</v>
+        <v>1.27421021461487</v>
       </c>
       <c r="H82" t="n">
         <v>323</v>
@@ -2776,7 +2776,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H83" t="n">
         <v>2589</v>
@@ -2921,7 +2921,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G88" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H88" t="n">
         <v>702</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>1.27494192123413</v>
+        <v>1.27494204044342</v>
       </c>
       <c r="H95" t="n">
         <v>3561</v>
@@ -3646,7 +3646,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H113" t="n">
         <v>1458</v>
@@ -3675,7 +3675,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>1.24347102642059</v>
+        <v>1.24347114562988</v>
       </c>
       <c r="H114" t="n">
         <v>1307</v>
@@ -3733,7 +3733,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G116" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468863964081</v>
       </c>
       <c r="H116" t="n">
         <v>761</v>
@@ -3762,7 +3762,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G117" t="n">
-        <v>1.22663772106171</v>
+        <v>1.22663760185242</v>
       </c>
       <c r="H117" t="n">
         <v>120</v>
@@ -3791,7 +3791,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G118" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H118" t="n">
         <v>150</v>
@@ -3820,7 +3820,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G119" t="n">
-        <v>1.20687675476074</v>
+        <v>1.20687687397003</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>16.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H120" t="n">
         <v>445</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H135" t="n">
         <v>1260</v>
@@ -4429,7 +4429,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G140" t="n">
-        <v>1.24347102642059</v>
+        <v>1.24347114562988</v>
       </c>
       <c r="H140" t="n">
         <v>730</v>
@@ -4458,7 +4458,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G141" t="n">
-        <v>1.24347102642059</v>
+        <v>1.24347114562988</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H146" t="n">
         <v>249</v>
@@ -4748,7 +4748,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G151" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H151" t="n">
         <v>1211</v>
@@ -4777,7 +4777,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G152" t="n">
-        <v>1.23102879524231</v>
+        <v>1.2310289144516</v>
       </c>
       <c r="H152" t="n">
         <v>20</v>
@@ -4835,7 +4835,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G154" t="n">
-        <v>1.21712327003479</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H154" t="n">
         <v>767</v>
@@ -4864,7 +4864,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G155" t="n">
-        <v>1.21712327003479</v>
+        <v>1.2171231508255</v>
       </c>
       <c r="H155" t="n">
         <v>10</v>
@@ -4893,7 +4893,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G156" t="n">
-        <v>1.22297823429108</v>
+        <v>1.22297811508179</v>
       </c>
       <c r="H156" t="n">
         <v>410</v>
@@ -4980,7 +4980,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G159" t="n">
-        <v>1.22883343696594</v>
+        <v>1.22883331775665</v>
       </c>
       <c r="H159" t="n">
         <v>486</v>
@@ -5009,7 +5009,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G160" t="n">
-        <v>1.23468852043152</v>
+        <v>1.23468863964081</v>
       </c>
       <c r="H160" t="n">
         <v>366</v>
@@ -5299,7 +5299,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>1.32763755321503</v>
+        <v>1.32763743400574</v>
       </c>
       <c r="H170" t="n">
         <v>14161</v>
@@ -5792,7 +5792,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G187" t="n">
-        <v>1.29323923587799</v>
+        <v>1.2932391166687</v>
       </c>
       <c r="H187" t="n">
         <v>4615</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24786233901978</v>
+        <v>1.24786221981049</v>
       </c>
       <c r="H198" t="n">
         <v>11212</v>
@@ -6198,7 +6198,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G201" t="n">
-        <v>1.28006517887115</v>
+        <v>1.28006529808044</v>
       </c>
       <c r="H201" t="n">
         <v>19504</v>
@@ -6285,7 +6285,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G204" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005781650543</v>
       </c>
       <c r="H204" t="n">
         <v>3493</v>
@@ -6575,7 +6575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>1.25005793571472</v>
+        <v>1.25005781650543</v>
       </c>
       <c r="H214" t="n">
         <v>3399</v>
@@ -6691,7 +6691,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G218" t="n">
-        <v>1.22297823429108</v>
+        <v>1.22297811508179</v>
       </c>
       <c r="H218" t="n">
         <v>9836</v>
@@ -6807,7 +6807,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G222" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H222" t="n">
         <v>2781</v>
@@ -6836,7 +6836,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G223" t="n">
-        <v>1.24127519130707</v>
+        <v>1.24127531051636</v>
       </c>
       <c r="H223" t="n">
         <v>275</v>
@@ -7010,7 +7010,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="n">
-        <v>1.21126818656921</v>
+        <v>1.21126806735992</v>
       </c>
       <c r="H229" t="n">
         <v>2474</v>
@@ -7097,7 +7097,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>1.21492743492126</v>
+        <v>1.21492731571198</v>
       </c>
       <c r="H232" t="n">
         <v>842</v>
@@ -7155,7 +7155,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>1.18199276924133</v>
+        <v>1.18199265003204</v>
       </c>
       <c r="H234" t="n">
         <v>2528</v>
@@ -7184,7 +7184,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="n">
-        <v>1.214195728302</v>
+        <v>1.21419560909271</v>
       </c>
       <c r="H235" t="n">
         <v>750</v>
@@ -7242,7 +7242,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>1.19663047790527</v>
+        <v>1.19663059711456</v>
       </c>
       <c r="H237" t="n">
         <v>29484</v>
@@ -7271,7 +7271,7 @@
         <v>16.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H238" t="n">
         <v>3574</v>
@@ -7300,7 +7300,7 @@
         <v>16.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.20760858058929</v>
+        <v>1.20760869979858</v>
       </c>
       <c r="H239" t="n">
         <v>3705</v>
@@ -7503,7 +7503,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="n">
-        <v>1.27786934375763</v>
+        <v>1.27786946296692</v>
       </c>
       <c r="H246" t="n">
         <v>2816</v>
@@ -7561,7 +7561,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="n">
-        <v>1.29470300674438</v>
+        <v>1.2947028875351</v>
       </c>
       <c r="H248" t="n">
         <v>6791</v>
@@ -7677,7 +7677,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>1.29323923587799</v>
+        <v>1.2932391166687</v>
       </c>
       <c r="H252" t="n">
         <v>321</v>
@@ -7735,7 +7735,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="n">
-        <v>1.29470300674438</v>
+        <v>1.2947028875351</v>
       </c>
       <c r="H254" t="n">
         <v>310</v>
@@ -7880,7 +7880,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="n">
-        <v>1.34081149101257</v>
+        <v>1.34081161022186</v>
       </c>
       <c r="H259" t="n">
         <v>24867</v>
@@ -8141,7 +8141,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>1.34227526187897</v>
+        <v>1.34227538108826</v>
       </c>
       <c r="H268" t="n">
         <v>2370</v>
@@ -8170,7 +8170,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="n">
-        <v>1.3400799036026</v>
+        <v>1.34007978439331</v>
       </c>
       <c r="H269" t="n">
         <v>383</v>
@@ -8286,7 +8286,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>1.36130428314209</v>
+        <v>1.3613041639328</v>
       </c>
       <c r="H273" t="n">
         <v>6282</v>
@@ -8576,7 +8576,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32910132408142</v>
+        <v>1.32910120487213</v>
       </c>
       <c r="H283" t="n">
         <v>6127</v>
@@ -8605,7 +8605,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>1.36350011825562</v>
+        <v>1.36349999904633</v>
       </c>
       <c r="H284" t="n">
         <v>4639</v>
@@ -8721,7 +8721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>1.39789855480194</v>
+        <v>1.39789843559265</v>
       </c>
       <c r="H288" t="n">
         <v>6393</v>
@@ -8808,7 +8808,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="n">
-        <v>1.4081449508667</v>
+        <v>1.40814483165741</v>
       </c>
       <c r="H291" t="n">
         <v>7943</v>
@@ -8924,7 +8924,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="n">
-        <v>1.3693550825119</v>
+        <v>1.36935496330261</v>
       </c>
       <c r="H295" t="n">
         <v>3982</v>
@@ -8982,7 +8982,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="n">
-        <v>1.38911581039429</v>
+        <v>1.38911592960358</v>
       </c>
       <c r="H297" t="n">
         <v>1150</v>
@@ -9098,7 +9098,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="n">
-        <v>1.47621035575867</v>
+        <v>1.47621023654938</v>
       </c>
       <c r="H301" t="n">
         <v>13926</v>
@@ -9185,7 +9185,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50328993797302</v>
+        <v>1.50329005718231</v>
       </c>
       <c r="H304" t="n">
         <v>18505</v>
@@ -9214,7 +9214,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>1.46742749214172</v>
+        <v>1.46742761135101</v>
       </c>
       <c r="H305" t="n">
         <v>2232</v>
@@ -9504,7 +9504,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="n">
-        <v>1.50987684726715</v>
+        <v>1.50987672805786</v>
       </c>
       <c r="H315" t="n">
         <v>6169</v>
@@ -10055,7 +10055,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="n">
-        <v>1.53768837451935</v>
+        <v>1.53768849372864</v>
       </c>
       <c r="H334" t="n">
         <v>12975</v>
@@ -10084,7 +10084,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="n">
-        <v>1.58233344554901</v>
+        <v>1.58233332633972</v>
       </c>
       <c r="H335" t="n">
         <v>11207</v>
@@ -10258,7 +10258,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>1.66288042068481</v>
+        <v>1.66288030147552</v>
       </c>
       <c r="H341" t="n">
         <v>8452</v>
@@ -10316,7 +10316,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76902174949646</v>
+        <v>1.76902163028717</v>
       </c>
       <c r="H343" t="n">
         <v>13422</v>
@@ -10345,7 +10345,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80816578865051</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H344" t="n">
         <v>14565</v>
@@ -10374,7 +10374,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429919719696</v>
       </c>
       <c r="H345" t="n">
         <v>14954</v>
@@ -10461,7 +10461,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="n">
-        <v>2.01367354393005</v>
+        <v>2.01367378234863</v>
       </c>
       <c r="H348" t="n">
         <v>26110</v>
@@ -10577,7 +10577,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429919719696</v>
       </c>
       <c r="H352" t="n">
         <v>22668</v>
@@ -10606,7 +10606,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>1.83376014232635</v>
+        <v>1.83376026153564</v>
       </c>
       <c r="H353" t="n">
         <v>22283</v>
@@ -10635,7 +10635,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="n">
-        <v>1.9030157327652</v>
+        <v>1.90301549434662</v>
       </c>
       <c r="H354" t="n">
         <v>11029</v>
@@ -10722,7 +10722,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93538498878479</v>
+        <v>1.93538475036621</v>
       </c>
       <c r="H357" t="n">
         <v>14132</v>
@@ -10925,7 +10925,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="n">
-        <v>1.9406543970108</v>
+        <v>1.94065415859222</v>
       </c>
       <c r="H364" t="n">
         <v>4029</v>
@@ -11041,7 +11041,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H368" t="n">
         <v>3607</v>
@@ -11215,7 +11215,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="n">
-        <v>1.91054332256317</v>
+        <v>1.91054356098175</v>
       </c>
       <c r="H374" t="n">
         <v>414</v>
@@ -11244,7 +11244,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="n">
-        <v>1.89021837711334</v>
+        <v>1.89021861553192</v>
       </c>
       <c r="H375" t="n">
         <v>1836</v>
@@ -11273,7 +11273,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="n">
-        <v>1.90753185749054</v>
+        <v>1.90753209590912</v>
       </c>
       <c r="H376" t="n">
         <v>4843</v>
@@ -11302,7 +11302,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="n">
-        <v>1.89699327945709</v>
+        <v>1.8969931602478</v>
       </c>
       <c r="H377" t="n">
         <v>2654</v>
@@ -11360,7 +11360,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="n">
-        <v>1.87742137908936</v>
+        <v>1.87742125988007</v>
       </c>
       <c r="H379" t="n">
         <v>4228</v>
@@ -11418,7 +11418,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="n">
-        <v>1.77052712440491</v>
+        <v>1.7705272436142</v>
       </c>
       <c r="H381" t="n">
         <v>13997</v>
@@ -11447,7 +11447,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="n">
-        <v>1.79762673377991</v>
+        <v>1.7976268529892</v>
       </c>
       <c r="H382" t="n">
         <v>3396</v>
@@ -11592,7 +11592,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H387" t="n">
         <v>1000</v>
@@ -11621,7 +11621,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H388" t="n">
         <v>200</v>
@@ -11679,7 +11679,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="n">
-        <v>1.80816578865051</v>
+        <v>1.8081659078598</v>
       </c>
       <c r="H390" t="n">
         <v>13605</v>
@@ -11766,7 +11766,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="n">
-        <v>1.83601856231689</v>
+        <v>1.8360184431076</v>
       </c>
       <c r="H393" t="n">
         <v>330</v>
@@ -11824,7 +11824,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429919719696</v>
       </c>
       <c r="H395" t="n">
         <v>3526</v>
@@ -11853,7 +11853,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="n">
-        <v>1.84429907798767</v>
+        <v>1.84429919719696</v>
       </c>
       <c r="H396" t="n">
         <v>359</v>
@@ -11940,7 +11940,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>1.82171583175659</v>
+        <v>1.82171595096588</v>
       </c>
       <c r="H399" t="n">
         <v>788</v>
@@ -11969,7 +11969,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="n">
-        <v>1.84806299209595</v>
+        <v>1.84806287288666</v>
       </c>
       <c r="H400" t="n">
         <v>1454</v>
@@ -11998,7 +11998,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="n">
-        <v>1.8465576171875</v>
+        <v>1.84655749797821</v>
       </c>
       <c r="H401" t="n">
         <v>3479</v>
@@ -12027,7 +12027,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.83752405643463</v>
+        <v>1.83752393722534</v>
       </c>
       <c r="H402" t="n">
         <v>2341</v>
@@ -12056,7 +12056,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>1.89774632453918</v>
+        <v>1.89774608612061</v>
       </c>
       <c r="H403" t="n">
         <v>20408</v>
@@ -12230,7 +12230,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="n">
-        <v>1.93613755702972</v>
+        <v>1.93613767623901</v>
       </c>
       <c r="H409" t="n">
         <v>3552</v>
@@ -12317,7 +12317,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="n">
-        <v>1.91957640647888</v>
+        <v>1.91957664489746</v>
       </c>
       <c r="H412" t="n">
         <v>2967</v>
@@ -12375,7 +12375,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="n">
-        <v>1.89021837711334</v>
+        <v>1.89021861553192</v>
       </c>
       <c r="H414" t="n">
         <v>818</v>
@@ -12520,7 +12520,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="n">
-        <v>1.86914050579071</v>
+        <v>1.869140625</v>
       </c>
       <c r="H419" t="n">
         <v>2296</v>
@@ -12578,7 +12578,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="n">
-        <v>1.85860192775726</v>
+        <v>1.85860180854797</v>
       </c>
       <c r="H421" t="n">
         <v>1458</v>
@@ -12607,7 +12607,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H422" t="n">
         <v>5360</v>
@@ -12636,7 +12636,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="n">
-        <v>1.85634362697601</v>
+        <v>1.85634350776672</v>
       </c>
       <c r="H423" t="n">
         <v>1890</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H426" t="n">
         <v>1972</v>
@@ -12752,7 +12752,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="n">
-        <v>1.85634362697601</v>
+        <v>1.85634350776672</v>
       </c>
       <c r="H427" t="n">
         <v>5286</v>
@@ -12839,7 +12839,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>1.85860192775726</v>
+        <v>1.85860180854797</v>
       </c>
       <c r="H430" t="n">
         <v>1130</v>
@@ -12868,7 +12868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H431" t="n">
         <v>1257</v>
@@ -12926,7 +12926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H433" t="n">
         <v>2572</v>
@@ -12984,7 +12984,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="n">
-        <v>1.86161303520203</v>
+        <v>1.86161291599274</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="n">
-        <v>1.88193762302399</v>
+        <v>1.88193786144257</v>
       </c>
       <c r="H436" t="n">
         <v>2642</v>
@@ -13042,7 +13042,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="n">
-        <v>1.86763501167297</v>
+        <v>1.86763513088226</v>
       </c>
       <c r="H437" t="n">
         <v>1511</v>
@@ -13071,7 +13071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="n">
-        <v>1.86688232421875</v>
+        <v>1.86688220500946</v>
       </c>
       <c r="H438" t="n">
         <v>969</v>
@@ -13100,7 +13100,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="n">
-        <v>1.87365734577179</v>
+        <v>1.8736572265625</v>
       </c>
       <c r="H439" t="n">
         <v>5904</v>
@@ -13245,7 +13245,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="n">
-        <v>1.84204077720642</v>
+        <v>1.84204089641571</v>
       </c>
       <c r="H444" t="n">
         <v>1977</v>
@@ -13303,7 +13303,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="n">
-        <v>1.84279370307922</v>
+        <v>1.84279358386993</v>
       </c>
       <c r="H446" t="n">
         <v>1136</v>
@@ -13332,7 +13332,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H447" t="n">
         <v>5011</v>
@@ -13390,7 +13390,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>1.82397413253784</v>
+        <v>1.82397401332855</v>
       </c>
       <c r="H449" t="n">
         <v>24784</v>
@@ -13622,7 +13622,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H457" t="n">
         <v>3947</v>
@@ -13651,7 +13651,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83225464820862</v>
+        <v>1.8322548866272</v>
       </c>
       <c r="H458" t="n">
         <v>1829</v>
@@ -13709,7 +13709,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="n">
-        <v>1.82547974586487</v>
+        <v>1.82547962665558</v>
       </c>
       <c r="H460" t="n">
         <v>3803</v>
@@ -13738,7 +13738,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="n">
-        <v>1.8503212928772</v>
+        <v>1.85032141208649</v>
       </c>
       <c r="H461" t="n">
         <v>11043</v>
@@ -13796,7 +13796,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="n">
-        <v>1.84881556034088</v>
+        <v>1.84881567955017</v>
       </c>
       <c r="H463" t="n">
         <v>34293</v>
@@ -13825,7 +13825,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="n">
-        <v>1.89849877357483</v>
+        <v>1.89849901199341</v>
       </c>
       <c r="H464" t="n">
         <v>4953</v>
@@ -13854,7 +13854,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="n">
-        <v>1.93689024448395</v>
+        <v>1.93689048290253</v>
       </c>
       <c r="H465" t="n">
         <v>5512</v>
@@ -13941,7 +13941,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>1.96474313735962</v>
+        <v>1.96474289894104</v>
       </c>
       <c r="H468" t="n">
         <v>14648</v>
@@ -14057,7 +14057,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="n">
-        <v>1.96775424480438</v>
+        <v>1.96775448322296</v>
       </c>
       <c r="H472" t="n">
         <v>6595</v>
@@ -14115,7 +14115,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="n">
-        <v>2.10325384140015</v>
+        <v>2.10325407981873</v>
       </c>
       <c r="H474" t="n">
         <v>27423</v>
@@ -14260,7 +14260,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>1.98582065105438</v>
+        <v>1.98582088947296</v>
       </c>
       <c r="H479" t="n">
         <v>3201</v>
@@ -14289,7 +14289,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="n">
-        <v>1.99033749103546</v>
+        <v>1.99033737182617</v>
       </c>
       <c r="H480" t="n">
         <v>2850</v>
@@ -14318,7 +14318,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="n">
-        <v>1.96624875068665</v>
+        <v>1.96624898910522</v>
       </c>
       <c r="H481" t="n">
         <v>7605</v>
@@ -14376,7 +14376,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="n">
-        <v>1.96549582481384</v>
+        <v>1.96549606323242</v>
       </c>
       <c r="H483" t="n">
         <v>212</v>
@@ -14405,7 +14405,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>1.96474313735962</v>
+        <v>1.96474289894104</v>
       </c>
       <c r="H484" t="n">
         <v>3107</v>
@@ -14434,7 +14434,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="n">
-        <v>1.97603464126587</v>
+        <v>1.97603487968445</v>
       </c>
       <c r="H485" t="n">
         <v>2600</v>
@@ -14608,7 +14608,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="n">
-        <v>2.07540082931519</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H491" t="n">
         <v>2166</v>
@@ -14782,7 +14782,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.07765936851501</v>
+        <v>2.07765913009644</v>
       </c>
       <c r="H497" t="n">
         <v>3216</v>
@@ -14898,7 +14898,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>2.10024285316467</v>
+        <v>2.10024261474609</v>
       </c>
       <c r="H501" t="n">
         <v>4665</v>
@@ -15072,7 +15072,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="n">
-        <v>2.07540082931519</v>
+        <v>2.07540106773376</v>
       </c>
       <c r="H507" t="n">
         <v>1590</v>
@@ -15101,7 +15101,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="n">
-        <v>2.07615399360657</v>
+        <v>2.07615375518799</v>
       </c>
       <c r="H508" t="n">
         <v>8225</v>
@@ -15246,7 +15246,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H513" t="n">
         <v>13248</v>
@@ -15275,7 +15275,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H514" t="n">
         <v>7527</v>
@@ -15304,7 +15304,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17552018165588</v>
+        <v>2.1755199432373</v>
       </c>
       <c r="H515" t="n">
         <v>6715</v>
@@ -15333,7 +15333,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>2.16799235343933</v>
+        <v>2.16799259185791</v>
       </c>
       <c r="H516" t="n">
         <v>4995</v>
@@ -15362,7 +15362,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>2.17552018165588</v>
+        <v>2.1755199432373</v>
       </c>
       <c r="H517" t="n">
         <v>16053</v>
@@ -15449,7 +15449,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H520" t="n">
         <v>13063</v>
@@ -15478,7 +15478,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H521" t="n">
         <v>10697</v>
@@ -15565,7 +15565,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="n">
-        <v>2.33360314369202</v>
+        <v>2.3336033821106</v>
       </c>
       <c r="H524" t="n">
         <v>4155</v>
@@ -15623,7 +15623,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H526" t="n">
         <v>2705</v>
@@ -15681,7 +15681,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.31101989746094</v>
+        <v>2.31101965904236</v>
       </c>
       <c r="H528" t="n">
         <v>6112</v>
@@ -15739,7 +15739,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>2.2658531665802</v>
+        <v>2.26585340499878</v>
       </c>
       <c r="H530" t="n">
         <v>7075</v>
@@ -15797,7 +15797,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30349183082581</v>
+        <v>2.30349206924438</v>
       </c>
       <c r="H532" t="n">
         <v>3569</v>
@@ -15826,7 +15826,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="n">
-        <v>2.29596400260925</v>
+        <v>2.29596424102783</v>
       </c>
       <c r="H533" t="n">
         <v>4435</v>
@@ -15884,7 +15884,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H535" t="n">
         <v>3431</v>
@@ -15913,7 +15913,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H536" t="n">
         <v>5445</v>
@@ -15942,7 +15942,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H537" t="n">
         <v>6576</v>
@@ -16000,7 +16000,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H539" t="n">
         <v>1456</v>
@@ -16029,7 +16029,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H540" t="n">
         <v>5940</v>
@@ -16116,7 +16116,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>2.19057536125183</v>
+        <v>2.19057559967041</v>
       </c>
       <c r="H543" t="n">
         <v>161</v>
@@ -16145,7 +16145,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.21315884590149</v>
+        <v>2.21315860748291</v>
       </c>
       <c r="H544" t="n">
         <v>815</v>
@@ -16174,7 +16174,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="n">
-        <v>2.25832533836365</v>
+        <v>2.25832557678223</v>
       </c>
       <c r="H545" t="n">
         <v>2533</v>
@@ -16232,7 +16232,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>2.38629746437073</v>
+        <v>2.38629722595215</v>
       </c>
       <c r="H547" t="n">
         <v>6727</v>
@@ -16464,7 +16464,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>2.40135288238525</v>
+        <v>2.40135312080383</v>
       </c>
       <c r="H555" t="n">
         <v>12859</v>
@@ -16493,7 +16493,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.36371397972107</v>
+        <v>2.36371421813965</v>
       </c>
       <c r="H556" t="n">
         <v>9076</v>
@@ -17392,7 +17392,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.50674104690552</v>
+        <v>2.5067412853241</v>
       </c>
       <c r="H587" t="n">
         <v>11895</v>
@@ -80212,6 +80212,35 @@
         <v>3995</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>360</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
